--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122607160</v>
+        <v>122607048</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485961</v>
+        <v>485855</v>
       </c>
       <c r="R2" t="n">
-        <v>6790453</v>
+        <v>6790443</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122608630</v>
+        <v>122607141</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485504</v>
+        <v>485906</v>
       </c>
       <c r="R3" t="n">
-        <v>6790441</v>
+        <v>6790433</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,19 +892,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609017</v>
+        <v>122608158</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -935,14 +940,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486064</v>
+        <v>486281</v>
       </c>
       <c r="R4" t="n">
-        <v>6790364</v>
+        <v>6790441</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122606235</v>
+        <v>122607665</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1047,17 +1057,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485615</v>
+        <v>486035</v>
       </c>
       <c r="R5" t="n">
-        <v>6790353</v>
+        <v>6790401</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,19 +1121,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122608938</v>
+        <v>122606108</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1159,14 +1169,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486253</v>
+        <v>485649</v>
       </c>
       <c r="R6" t="n">
-        <v>6790356</v>
+        <v>6790375</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1198,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122607823</v>
+        <v>122606176</v>
       </c>
       <c r="B7" t="n">
-        <v>56593</v>
+        <v>78682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486144</v>
+        <v>485613</v>
       </c>
       <c r="R7" t="n">
-        <v>6790420</v>
+        <v>6790370</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1315,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122607613</v>
+        <v>122608967</v>
       </c>
       <c r="B8" t="n">
-        <v>78392</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1427,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122607948</v>
+        <v>122608832</v>
       </c>
       <c r="B9" t="n">
         <v>78393</v>
@@ -1539,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,7 +1581,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122606105</v>
+        <v>122607713</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1612,17 +1617,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485662</v>
+        <v>486156</v>
       </c>
       <c r="R10" t="n">
-        <v>6790357</v>
+        <v>6790429</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,19 +1681,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122608781</v>
+        <v>122606708</v>
       </c>
       <c r="B11" t="n">
         <v>78656</v>
@@ -1728,13 +1733,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486035</v>
+        <v>485568</v>
       </c>
       <c r="R11" t="n">
-        <v>6790401</v>
+        <v>6790397</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1763,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,7 +1805,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122606653</v>
+        <v>122606394</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1836,14 +1841,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485568</v>
+        <v>485411</v>
       </c>
       <c r="R12" t="n">
-        <v>6790397</v>
+        <v>6790441</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,12 +1905,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2024,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606339</v>
+        <v>122608926</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>78392</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,34 +2045,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485528</v>
+        <v>486252</v>
       </c>
       <c r="R14" t="n">
-        <v>6790365</v>
+        <v>6790351</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2099,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,7 +2141,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122607518</v>
+        <v>122606139</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2172,17 +2177,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486071</v>
+        <v>485662</v>
       </c>
       <c r="R15" t="n">
-        <v>6790384</v>
+        <v>6790357</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2211,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,22 +2241,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122607953</v>
+        <v>122607815</v>
       </c>
       <c r="B16" t="n">
-        <v>8441</v>
+        <v>56593</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,37 +2269,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486214</v>
+        <v>486035</v>
       </c>
       <c r="R16" t="n">
-        <v>6790429</v>
+        <v>6790401</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2323,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,19 +2353,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122606145</v>
+        <v>122606669</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2400,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485616</v>
+        <v>485407</v>
       </c>
       <c r="R17" t="n">
-        <v>6790356</v>
+        <v>6790437</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2435,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,7 +2477,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122606271</v>
+        <v>122608938</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2508,14 +2513,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485553</v>
+        <v>486253</v>
       </c>
       <c r="R18" t="n">
-        <v>6790369</v>
+        <v>6790356</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2547,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122607815</v>
+        <v>122607613</v>
       </c>
       <c r="B19" t="n">
-        <v>56593</v>
+        <v>78392</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,41 +2601,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486035</v>
+        <v>485504</v>
       </c>
       <c r="R19" t="n">
-        <v>6790401</v>
+        <v>6790441</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2659,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2674,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,19 +2689,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122606787</v>
+        <v>122607518</v>
       </c>
       <c r="B20" t="n">
         <v>78656</v>
@@ -2732,17 +2737,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>485706</v>
+        <v>486071</v>
       </c>
       <c r="R20" t="n">
-        <v>6790427</v>
+        <v>6790384</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2771,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2796,19 +2801,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122606955</v>
+        <v>122606977</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -2848,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>485759</v>
+        <v>485766</v>
       </c>
       <c r="R21" t="n">
-        <v>6790467</v>
+        <v>6790457</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2883,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2898,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2920,7 +2930,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122607713</v>
+        <v>122606204</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -2960,13 +2970,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486156</v>
+        <v>485615</v>
       </c>
       <c r="R22" t="n">
-        <v>6790429</v>
+        <v>6790353</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2995,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3005,7 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,19 +3030,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122607995</v>
+        <v>122606452</v>
       </c>
       <c r="B23" t="n">
         <v>78656</v>
@@ -3072,10 +3082,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486213</v>
+        <v>485428</v>
       </c>
       <c r="R23" t="n">
-        <v>6790435</v>
+        <v>6790393</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3107,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3117,7 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3144,10 +3154,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122607141</v>
+        <v>122605767</v>
       </c>
       <c r="B24" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3156,46 +3166,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>485906</v>
+        <v>485706</v>
       </c>
       <c r="R24" t="n">
-        <v>6790433</v>
+        <v>6790427</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3224,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3239,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3249,19 +3254,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122607974</v>
+        <v>122606651</v>
       </c>
       <c r="B25" t="n">
         <v>78656</v>
@@ -3301,10 +3306,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486212</v>
+        <v>485432</v>
       </c>
       <c r="R25" t="n">
-        <v>6790432</v>
+        <v>6790417</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3336,7 +3341,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3351,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,7 +3378,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122606286</v>
+        <v>122608061</v>
       </c>
       <c r="B26" t="n">
         <v>78656</v>
@@ -3413,10 +3418,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>485541</v>
+        <v>486229</v>
       </c>
       <c r="R26" t="n">
-        <v>6790372</v>
+        <v>6790440</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3448,7 +3453,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,12 +3463,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På 3 tallar på stammen</t>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3490,7 +3495,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122606417</v>
+        <v>122608844</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -3526,17 +3531,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>485407</v>
+        <v>486338</v>
       </c>
       <c r="R27" t="n">
-        <v>6790439</v>
+        <v>6790352</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3565,7 +3570,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3575,7 +3580,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3590,22 +3600,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122608856</v>
+        <v>122607915</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3614,38 +3624,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486343</v>
+        <v>486193</v>
       </c>
       <c r="R28" t="n">
-        <v>6790373</v>
+        <v>6790410</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3677,7 +3687,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3687,7 +3697,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,10 +3724,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122608926</v>
+        <v>122608856</v>
       </c>
       <c r="B29" t="n">
-        <v>78392</v>
+        <v>8441</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3726,25 +3736,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3754,10 +3764,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486252</v>
+        <v>486343</v>
       </c>
       <c r="R29" t="n">
-        <v>6790351</v>
+        <v>6790373</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3789,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3799,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3826,10 +3836,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122606108</v>
+        <v>122607224</v>
       </c>
       <c r="B30" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3838,38 +3848,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>485649</v>
+        <v>485981</v>
       </c>
       <c r="R30" t="n">
-        <v>6790375</v>
+        <v>6790453</v>
       </c>
       <c r="S30" t="n">
         <v>9</v>
@@ -3901,7 +3916,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3911,7 +3926,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3938,7 +3953,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122606651</v>
+        <v>122607160</v>
       </c>
       <c r="B31" t="n">
         <v>78656</v>
@@ -3978,10 +3993,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>485432</v>
+        <v>485961</v>
       </c>
       <c r="R31" t="n">
-        <v>6790417</v>
+        <v>6790453</v>
       </c>
       <c r="S31" t="n">
         <v>9</v>
@@ -4013,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4023,7 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4050,10 +4065,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122608110</v>
+        <v>122607446</v>
       </c>
       <c r="B32" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4062,38 +4077,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486270</v>
+        <v>486045</v>
       </c>
       <c r="R32" t="n">
-        <v>6790427</v>
+        <v>6790383</v>
       </c>
       <c r="S32" t="n">
         <v>9</v>
@@ -4125,7 +4145,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4135,7 +4155,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4162,10 +4182,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122607495</v>
+        <v>122607596</v>
       </c>
       <c r="B33" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4174,38 +4194,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486056</v>
+        <v>486109</v>
       </c>
       <c r="R33" t="n">
-        <v>6790394</v>
+        <v>6790384</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -4237,7 +4262,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4247,7 +4272,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4274,10 +4299,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122606394</v>
+        <v>122607953</v>
       </c>
       <c r="B34" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4286,25 +4311,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4314,13 +4339,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485411</v>
+        <v>486214</v>
       </c>
       <c r="R34" t="n">
-        <v>6790441</v>
+        <v>6790429</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4349,7 +4374,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4359,7 +4384,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4374,22 +4399,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122606176</v>
+        <v>122606208</v>
       </c>
       <c r="B35" t="n">
-        <v>78682</v>
+        <v>8441</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4402,21 +4427,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6434</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4451,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485613</v>
+        <v>485592</v>
       </c>
       <c r="R35" t="n">
-        <v>6790370</v>
+        <v>6790353</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
@@ -4461,7 +4486,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4471,7 +4496,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4498,7 +4523,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122607107</v>
+        <v>122606955</v>
       </c>
       <c r="B36" t="n">
         <v>78656</v>
@@ -4538,10 +4563,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485855</v>
+        <v>485759</v>
       </c>
       <c r="R36" t="n">
-        <v>6790443</v>
+        <v>6790467</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -4573,7 +4598,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4583,7 +4608,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4610,10 +4635,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122607224</v>
+        <v>122606417</v>
       </c>
       <c r="B37" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4622,46 +4647,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>485981</v>
+        <v>485407</v>
       </c>
       <c r="R37" t="n">
-        <v>6790453</v>
+        <v>6790439</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4690,7 +4710,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4700,7 +4720,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4715,19 +4735,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122608651</v>
+        <v>122606677</v>
       </c>
       <c r="B38" t="n">
         <v>78656</v>
@@ -4763,14 +4783,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486380</v>
+        <v>485490</v>
       </c>
       <c r="R38" t="n">
-        <v>6790321</v>
+        <v>6790430</v>
       </c>
       <c r="S38" t="n">
         <v>9</v>
@@ -4802,7 +4822,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4812,12 +4832,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4844,10 +4859,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122607915</v>
+        <v>122607118</v>
       </c>
       <c r="B39" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4856,38 +4871,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486193</v>
+        <v>485884</v>
       </c>
       <c r="R39" t="n">
-        <v>6790410</v>
+        <v>6790450</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
@@ -4919,7 +4939,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4929,7 +4949,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4956,10 +4976,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122607596</v>
+        <v>122609017</v>
       </c>
       <c r="B40" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4968,43 +4988,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486109</v>
+        <v>486064</v>
       </c>
       <c r="R40" t="n">
-        <v>6790384</v>
+        <v>6790364</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -5036,7 +5051,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5046,7 +5061,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5073,10 +5088,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122607688</v>
+        <v>122607995</v>
       </c>
       <c r="B41" t="n">
-        <v>90859</v>
+        <v>78656</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5089,38 +5104,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486156</v>
+        <v>486213</v>
       </c>
       <c r="R41" t="n">
-        <v>6790429</v>
+        <v>6790435</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5152,7 +5163,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5162,7 +5173,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5189,7 +5200,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122608990</v>
+        <v>122607495</v>
       </c>
       <c r="B42" t="n">
         <v>78656</v>
@@ -5225,14 +5236,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486070</v>
+        <v>486056</v>
       </c>
       <c r="R42" t="n">
-        <v>6790363</v>
+        <v>6790394</v>
       </c>
       <c r="S42" t="n">
         <v>9</v>
@@ -5264,7 +5275,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5274,7 +5285,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5301,7 +5312,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122606154</v>
+        <v>122606339</v>
       </c>
       <c r="B43" t="n">
         <v>78656</v>
@@ -5341,13 +5352,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>485616</v>
+        <v>485528</v>
       </c>
       <c r="R43" t="n">
-        <v>6790354</v>
+        <v>6790365</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5376,7 +5387,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5386,7 +5397,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5401,22 +5412,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122606208</v>
+        <v>122606286</v>
       </c>
       <c r="B44" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5425,25 +5436,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5453,10 +5464,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>485592</v>
+        <v>485541</v>
       </c>
       <c r="R44" t="n">
-        <v>6790353</v>
+        <v>6790372</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -5488,7 +5499,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5498,7 +5509,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På 3 tallar på stammen</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5525,7 +5541,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122606669</v>
+        <v>122606230</v>
       </c>
       <c r="B45" t="n">
         <v>78656</v>
@@ -5565,13 +5581,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>485407</v>
+        <v>485561</v>
       </c>
       <c r="R45" t="n">
-        <v>6790437</v>
+        <v>6790367</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5600,7 +5616,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5610,7 +5626,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5625,22 +5641,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122608902</v>
+        <v>122606154</v>
       </c>
       <c r="B46" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5653,37 +5669,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486280</v>
+        <v>485616</v>
       </c>
       <c r="R46" t="n">
-        <v>6790345</v>
+        <v>6790354</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5712,7 +5728,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5722,7 +5738,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5737,19 +5753,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122608844</v>
+        <v>122606271</v>
       </c>
       <c r="B47" t="n">
         <v>78656</v>
@@ -5785,14 +5801,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486338</v>
+        <v>485553</v>
       </c>
       <c r="R47" t="n">
-        <v>6790352</v>
+        <v>6790369</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5824,7 +5840,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5834,12 +5850,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5866,10 +5877,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122606807</v>
+        <v>122608902</v>
       </c>
       <c r="B48" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5882,34 +5893,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>485749</v>
+        <v>486280</v>
       </c>
       <c r="R48" t="n">
-        <v>6790424</v>
+        <v>6790345</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5941,7 +5952,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5951,7 +5962,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5978,7 +5989,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122607254</v>
+        <v>122606145</v>
       </c>
       <c r="B49" t="n">
         <v>78656</v>
@@ -6018,13 +6029,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486016</v>
+        <v>485616</v>
       </c>
       <c r="R49" t="n">
-        <v>6790443</v>
+        <v>6790356</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6053,7 +6064,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6063,7 +6074,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6078,19 +6089,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122608061</v>
+        <v>122607974</v>
       </c>
       <c r="B50" t="n">
         <v>78656</v>
@@ -6130,10 +6141,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486229</v>
+        <v>486212</v>
       </c>
       <c r="R50" t="n">
-        <v>6790440</v>
+        <v>6790432</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -6165,7 +6176,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6175,12 +6186,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6207,7 +6213,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122606452</v>
+        <v>122608990</v>
       </c>
       <c r="B51" t="n">
         <v>78656</v>
@@ -6243,14 +6249,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>485428</v>
+        <v>486070</v>
       </c>
       <c r="R51" t="n">
-        <v>6790393</v>
+        <v>6790363</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -6282,7 +6288,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6292,7 +6298,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6319,10 +6325,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122607118</v>
+        <v>122606131</v>
       </c>
       <c r="B52" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6331,43 +6337,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>485884</v>
+        <v>485629</v>
       </c>
       <c r="R52" t="n">
-        <v>6790450</v>
+        <v>6790369</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6399,7 +6400,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6409,7 +6410,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6436,7 +6437,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122606677</v>
+        <v>122608651</v>
       </c>
       <c r="B53" t="n">
         <v>78656</v>
@@ -6472,14 +6473,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>485490</v>
+        <v>486380</v>
       </c>
       <c r="R53" t="n">
-        <v>6790430</v>
+        <v>6790321</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6511,7 +6512,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6521,7 +6522,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6548,7 +6554,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122606230</v>
+        <v>122608110</v>
       </c>
       <c r="B54" t="n">
         <v>78656</v>
@@ -6584,14 +6590,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>485561</v>
+        <v>486270</v>
       </c>
       <c r="R54" t="n">
-        <v>6790367</v>
+        <v>6790427</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6623,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6633,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6660,10 +6666,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122607446</v>
+        <v>122606807</v>
       </c>
       <c r="B55" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6672,43 +6678,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486045</v>
+        <v>485749</v>
       </c>
       <c r="R55" t="n">
-        <v>6790383</v>
+        <v>6790424</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6740,7 +6741,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6750,7 +6751,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6777,7 +6778,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122608158</v>
+        <v>122607254</v>
       </c>
       <c r="B56" t="n">
         <v>78656</v>
@@ -6813,14 +6814,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486281</v>
+        <v>486016</v>
       </c>
       <c r="R56" t="n">
-        <v>6790441</v>
+        <v>6790443</v>
       </c>
       <c r="S56" t="n">
         <v>9</v>
@@ -6852,7 +6853,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6862,12 +6863,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6894,10 +6890,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122606977</v>
+        <v>122607823</v>
       </c>
       <c r="B57" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6906,38 +6902,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>485766</v>
+        <v>486144</v>
       </c>
       <c r="R57" t="n">
-        <v>6790457</v>
+        <v>6790420</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -6969,7 +6970,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6979,12 +6980,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7011,7 +7007,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122606131</v>
+        <v>122606143</v>
       </c>
       <c r="B58" t="n">
         <v>78656</v>
@@ -7051,10 +7047,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485629</v>
+        <v>485681</v>
       </c>
       <c r="R58" t="n">
-        <v>6790369</v>
+        <v>6790440</v>
       </c>
       <c r="S58" t="n">
         <v>9</v>
@@ -7086,7 +7082,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7096,7 +7092,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7111,15 +7107,1977 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>122607077</v>
+      </c>
+      <c r="B59" t="n">
+        <v>56593</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Jäskänget, Jäskänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>485772</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6790421</v>
+      </c>
+      <c r="S59" t="n">
+        <v>8</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>122606756</v>
+      </c>
+      <c r="B60" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Jäskänget, Jäskänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>485504</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6790441</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>122606642</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Jäskänget, Jäskänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>485586</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6790395</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>122608928</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79274</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lindflot, Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>486063</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6790348</v>
+      </c>
+      <c r="S62" t="n">
+        <v>9</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>122609008</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lindflot, Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>486063</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6790348</v>
+      </c>
+      <c r="S63" t="n">
+        <v>8</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>122607688</v>
+      </c>
+      <c r="B64" t="n">
+        <v>90859</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Jäskänget, Jäskänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>486156</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6790429</v>
+      </c>
+      <c r="S64" t="n">
+        <v>9</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
           <t>Bo karlstens</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
+      <c r="AX64" t="inlineStr">
         <is>
           <t>Bo karlstens</t>
         </is>
       </c>
-      <c r="AY58" t="inlineStr"/>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>122607467</v>
+      </c>
+      <c r="B65" t="n">
+        <v>56593</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Jäskänget, Jäskänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>485504</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6790441</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>122606247</v>
+      </c>
+      <c r="B66" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Jäskänget, Jäskänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>485626</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6790401</v>
+      </c>
+      <c r="S66" t="n">
+        <v>9</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>122608724</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lindflot, Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>486211</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6790317</v>
+      </c>
+      <c r="S67" t="n">
+        <v>8</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>122609064</v>
+      </c>
+      <c r="B68" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lindflot, Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>486063</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6790348</v>
+      </c>
+      <c r="S68" t="n">
+        <v>8</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>122607719</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Jäskänget, Jäskänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>486157</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6790397</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>122608142</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lindflot, Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>486240</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6790382</v>
+      </c>
+      <c r="S70" t="n">
+        <v>9</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>122607445</v>
+      </c>
+      <c r="B71" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Jäskänget, Jäskänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>486082</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6790427</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>122608903</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78393</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lindflot, Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>486211</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6790317</v>
+      </c>
+      <c r="S72" t="n">
+        <v>8</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>122607038</v>
+      </c>
+      <c r="B73" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Jäskänget, Jäskänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>485772</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6790421</v>
+      </c>
+      <c r="S73" t="n">
+        <v>9</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>122606760</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57399</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Jäskänget, Jäskänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>485504</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6790441</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>122607273</v>
+      </c>
+      <c r="B75" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Jäskänget, Jäskänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>485932</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6790416</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6890,10 +6890,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122607823</v>
+        <v>122606143</v>
       </c>
       <c r="B57" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6902,43 +6902,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486144</v>
+        <v>485681</v>
       </c>
       <c r="R57" t="n">
-        <v>6790420</v>
+        <v>6790440</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -6970,7 +6965,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6980,7 +6975,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6995,22 +6990,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122606143</v>
+        <v>122607077</v>
       </c>
       <c r="B58" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7019,41 +7014,49 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485681</v>
+        <v>485772</v>
       </c>
       <c r="R58" t="n">
-        <v>6790440</v>
+        <v>6790421</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7082,7 +7085,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7092,7 +7095,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7119,10 +7122,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122607077</v>
+        <v>122606756</v>
       </c>
       <c r="B59" t="n">
-        <v>56593</v>
+        <v>8441</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7135,29 +7138,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7167,13 +7171,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>485772</v>
+        <v>485504</v>
       </c>
       <c r="R59" t="n">
-        <v>6790421</v>
+        <v>6790441</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7202,7 +7206,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7212,7 +7216,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7221,28 +7225,29 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122606756</v>
+        <v>122606642</v>
       </c>
       <c r="B60" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7251,47 +7256,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>485504</v>
+        <v>485586</v>
       </c>
       <c r="R60" t="n">
-        <v>6790441</v>
+        <v>6790395</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7323,7 +7319,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7333,7 +7329,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7342,29 +7338,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122606642</v>
+        <v>122608928</v>
       </c>
       <c r="B61" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7377,37 +7372,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>485586</v>
+        <v>486063</v>
       </c>
       <c r="R61" t="n">
-        <v>6790395</v>
+        <v>6790348</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7436,7 +7431,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7446,7 +7441,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7473,10 +7468,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122608928</v>
+        <v>122609008</v>
       </c>
       <c r="B62" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7489,21 +7484,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7519,7 +7514,7 @@
         <v>6790348</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7548,7 +7543,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7558,7 +7553,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7585,10 +7580,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122609008</v>
+        <v>122607688</v>
       </c>
       <c r="B63" t="n">
-        <v>78656</v>
+        <v>90859</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7601,37 +7596,41 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486063</v>
+        <v>486156</v>
       </c>
       <c r="R63" t="n">
-        <v>6790348</v>
+        <v>6790429</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7660,7 +7659,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7670,7 +7669,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7685,22 +7684,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122607688</v>
+        <v>122607467</v>
       </c>
       <c r="B64" t="n">
-        <v>90859</v>
+        <v>56593</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7709,45 +7708,49 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486156</v>
+        <v>485504</v>
       </c>
       <c r="R64" t="n">
-        <v>6790429</v>
+        <v>6790441</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7776,7 +7779,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7786,7 +7789,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7801,22 +7804,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122607467</v>
+        <v>122606247</v>
       </c>
       <c r="B65" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7825,49 +7828,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>485504</v>
+        <v>485626</v>
       </c>
       <c r="R65" t="n">
-        <v>6790441</v>
+        <v>6790401</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7896,7 +7891,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7906,7 +7901,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7921,19 +7916,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122606247</v>
+        <v>122608724</v>
       </c>
       <c r="B66" t="n">
         <v>78656</v>
@@ -7969,17 +7964,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>485626</v>
+        <v>486211</v>
       </c>
       <c r="R66" t="n">
-        <v>6790401</v>
+        <v>6790317</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8008,7 +8003,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8018,7 +8013,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8045,10 +8040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122608724</v>
+        <v>122609064</v>
       </c>
       <c r="B67" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8057,38 +8052,47 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486211</v>
+        <v>486063</v>
       </c>
       <c r="R67" t="n">
-        <v>6790317</v>
+        <v>6790348</v>
       </c>
       <c r="S67" t="n">
         <v>8</v>
@@ -8120,7 +8124,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8130,7 +8134,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8139,6 +8143,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8157,10 +8162,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122609064</v>
+        <v>122607719</v>
       </c>
       <c r="B68" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8169,50 +8174,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486063</v>
+        <v>486157</v>
       </c>
       <c r="R68" t="n">
-        <v>6790348</v>
+        <v>6790397</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8241,7 +8237,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8251,7 +8247,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8260,7 +8256,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8279,7 +8274,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122607719</v>
+        <v>122608142</v>
       </c>
       <c r="B69" t="n">
         <v>78656</v>
@@ -8315,17 +8310,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486157</v>
+        <v>486240</v>
       </c>
       <c r="R69" t="n">
-        <v>6790397</v>
+        <v>6790382</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8354,7 +8349,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8364,7 +8359,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8391,7 +8386,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122608142</v>
+        <v>122607445</v>
       </c>
       <c r="B70" t="n">
         <v>78656</v>
@@ -8427,17 +8422,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486240</v>
+        <v>486082</v>
       </c>
       <c r="R70" t="n">
-        <v>6790382</v>
+        <v>6790427</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8466,7 +8461,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8476,7 +8471,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8503,10 +8498,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122607445</v>
+        <v>122608903</v>
       </c>
       <c r="B71" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8519,37 +8514,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486082</v>
+        <v>486211</v>
       </c>
       <c r="R71" t="n">
-        <v>6790427</v>
+        <v>6790317</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8578,7 +8573,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8588,7 +8583,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8615,10 +8610,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122608903</v>
+        <v>122607038</v>
       </c>
       <c r="B72" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8631,37 +8626,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486211</v>
+        <v>485772</v>
       </c>
       <c r="R72" t="n">
-        <v>6790317</v>
+        <v>6790421</v>
       </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8690,7 +8685,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8700,7 +8695,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8727,10 +8722,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122607038</v>
+        <v>122606760</v>
       </c>
       <c r="B73" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8743,37 +8738,45 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>485772</v>
+        <v>485504</v>
       </c>
       <c r="R73" t="n">
-        <v>6790421</v>
+        <v>6790441</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8802,7 +8805,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8812,7 +8815,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8827,22 +8830,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122606760</v>
+        <v>122607273</v>
       </c>
       <c r="B74" t="n">
-        <v>57399</v>
+        <v>8441</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8851,33 +8854,34 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -8887,10 +8891,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>485504</v>
+        <v>485932</v>
       </c>
       <c r="R74" t="n">
-        <v>6790441</v>
+        <v>6790416</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8922,7 +8926,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8932,7 +8936,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8941,143 +8945,22 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>122607273</v>
-      </c>
-      <c r="B75" t="n">
-        <v>8441</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>485932</v>
-      </c>
-      <c r="R75" t="n">
-        <v>6790416</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF75" t="inlineStr"/>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Lisa Olson</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Lisa Olson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122607048</v>
+        <v>122607254</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485855</v>
+        <v>486016</v>
       </c>
       <c r="R2" t="n">
         <v>6790443</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122607141</v>
+        <v>122607995</v>
       </c>
       <c r="B3" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485906</v>
+        <v>486213</v>
       </c>
       <c r="R3" t="n">
-        <v>6790433</v>
+        <v>6790435</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122608158</v>
+        <v>122607048</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -940,14 +935,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486281</v>
+        <v>485855</v>
       </c>
       <c r="R4" t="n">
-        <v>6790441</v>
+        <v>6790443</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122607665</v>
+        <v>122607108</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1057,17 +1047,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486035</v>
+        <v>485504</v>
       </c>
       <c r="R5" t="n">
-        <v>6790401</v>
+        <v>6790441</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,19 +1111,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122606108</v>
+        <v>122608651</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1169,14 +1159,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485649</v>
+        <v>486380</v>
       </c>
       <c r="R6" t="n">
-        <v>6790375</v>
+        <v>6790321</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1208,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1208,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122606176</v>
+        <v>122608694</v>
       </c>
       <c r="B7" t="n">
-        <v>78682</v>
+        <v>56593</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,37 +1256,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485613</v>
+        <v>486035</v>
       </c>
       <c r="R7" t="n">
-        <v>6790370</v>
+        <v>6790401</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,19 +1340,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122608967</v>
+        <v>122606105</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1393,17 +1388,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485504</v>
+        <v>485662</v>
       </c>
       <c r="R8" t="n">
-        <v>6790441</v>
+        <v>6790357</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,22 +1452,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122608832</v>
+        <v>122606417</v>
       </c>
       <c r="B9" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485504</v>
+        <v>485407</v>
       </c>
       <c r="R9" t="n">
-        <v>6790441</v>
+        <v>6790439</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1576,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122607713</v>
+        <v>122607160</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1621,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486156</v>
+        <v>485961</v>
       </c>
       <c r="R10" t="n">
-        <v>6790429</v>
+        <v>6790453</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1656,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,7 +1688,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122606708</v>
+        <v>122606787</v>
       </c>
       <c r="B11" t="n">
         <v>78656</v>
@@ -1733,13 +1728,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485568</v>
+        <v>485706</v>
       </c>
       <c r="R11" t="n">
-        <v>6790397</v>
+        <v>6790427</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,7 +1800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122606394</v>
+        <v>122607518</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1845,13 +1840,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485411</v>
+        <v>486071</v>
       </c>
       <c r="R12" t="n">
-        <v>6790441</v>
+        <v>6790384</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1880,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,19 +1900,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122606919</v>
+        <v>122606154</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1957,13 +1952,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485753</v>
+        <v>485616</v>
       </c>
       <c r="R13" t="n">
-        <v>6790423</v>
+        <v>6790354</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1992,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,22 +2012,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122608926</v>
+        <v>122607596</v>
       </c>
       <c r="B14" t="n">
-        <v>78392</v>
+        <v>56593</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2041,38 +2036,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486252</v>
+        <v>486109</v>
       </c>
       <c r="R14" t="n">
-        <v>6790351</v>
+        <v>6790384</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,7 +2141,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122606139</v>
+        <v>122608844</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2177,17 +2177,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485662</v>
+        <v>486338</v>
       </c>
       <c r="R15" t="n">
-        <v>6790357</v>
+        <v>6790352</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2226,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,22 +2246,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122607815</v>
+        <v>122606176</v>
       </c>
       <c r="B16" t="n">
-        <v>56593</v>
+        <v>78682</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,37 +2274,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486035</v>
+        <v>485613</v>
       </c>
       <c r="R16" t="n">
-        <v>6790401</v>
+        <v>6790370</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2328,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2353,19 +2358,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122606669</v>
+        <v>122608792</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2401,17 +2406,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485407</v>
+        <v>486035</v>
       </c>
       <c r="R17" t="n">
-        <v>6790437</v>
+        <v>6790401</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2440,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2455,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,12 +2470,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2589,10 +2594,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122607613</v>
+        <v>122606442</v>
       </c>
       <c r="B19" t="n">
-        <v>78392</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2605,21 +2610,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2629,10 +2634,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>485504</v>
+        <v>485407</v>
       </c>
       <c r="R19" t="n">
-        <v>6790441</v>
+        <v>6790437</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2664,7 +2669,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2679,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,7 +2706,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122607518</v>
+        <v>122608061</v>
       </c>
       <c r="B20" t="n">
         <v>78656</v>
@@ -2741,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486071</v>
+        <v>486229</v>
       </c>
       <c r="R20" t="n">
-        <v>6790384</v>
+        <v>6790440</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2776,7 +2781,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2791,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,10 +2823,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122606977</v>
+        <v>122607118</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2825,38 +2835,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>485766</v>
+        <v>485884</v>
       </c>
       <c r="R21" t="n">
-        <v>6790457</v>
+        <v>6790450</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2888,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,12 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122606204</v>
+        <v>122608926</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>78392</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2946,37 +2956,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>485615</v>
+        <v>486252</v>
       </c>
       <c r="R22" t="n">
-        <v>6790353</v>
+        <v>6790351</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3005,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,19 +3040,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122606452</v>
+        <v>122606394</v>
       </c>
       <c r="B23" t="n">
         <v>78656</v>
@@ -3082,13 +3092,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>485428</v>
+        <v>485411</v>
       </c>
       <c r="R23" t="n">
-        <v>6790393</v>
+        <v>6790441</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3117,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3137,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3142,19 +3152,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122605767</v>
+        <v>122608990</v>
       </c>
       <c r="B24" t="n">
         <v>78656</v>
@@ -3190,17 +3200,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>485706</v>
+        <v>486070</v>
       </c>
       <c r="R24" t="n">
-        <v>6790427</v>
+        <v>6790363</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3229,7 +3239,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,7 +3249,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3254,19 +3264,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122606651</v>
+        <v>122606919</v>
       </c>
       <c r="B25" t="n">
         <v>78656</v>
@@ -3306,10 +3316,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>485432</v>
+        <v>485753</v>
       </c>
       <c r="R25" t="n">
-        <v>6790417</v>
+        <v>6790423</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3341,7 +3351,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3351,7 +3361,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3378,10 +3388,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122608061</v>
+        <v>122607141</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3390,38 +3400,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486229</v>
+        <v>485906</v>
       </c>
       <c r="R26" t="n">
-        <v>6790440</v>
+        <v>6790433</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3453,7 +3468,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3463,12 +3478,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3495,10 +3505,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122608844</v>
+        <v>122607224</v>
       </c>
       <c r="B27" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3507,38 +3517,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486338</v>
+        <v>485981</v>
       </c>
       <c r="R27" t="n">
-        <v>6790352</v>
+        <v>6790453</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3570,7 +3585,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3580,12 +3595,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3612,10 +3622,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122607915</v>
+        <v>122607948</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3628,21 +3638,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3652,13 +3662,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486193</v>
+        <v>485504</v>
       </c>
       <c r="R28" t="n">
-        <v>6790410</v>
+        <v>6790441</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3687,7 +3697,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3697,7 +3707,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3712,19 +3722,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122608856</v>
+        <v>122606208</v>
       </c>
       <c r="B29" t="n">
         <v>8441</v>
@@ -3760,14 +3770,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486343</v>
+        <v>485592</v>
       </c>
       <c r="R29" t="n">
-        <v>6790373</v>
+        <v>6790353</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3799,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3819,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3836,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122607224</v>
+        <v>122607953</v>
       </c>
       <c r="B30" t="n">
-        <v>56593</v>
+        <v>8441</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3852,39 +3862,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>485981</v>
+        <v>486214</v>
       </c>
       <c r="R30" t="n">
-        <v>6790453</v>
+        <v>6790429</v>
       </c>
       <c r="S30" t="n">
         <v>9</v>
@@ -3916,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3926,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3953,7 +3958,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122607160</v>
+        <v>122606977</v>
       </c>
       <c r="B31" t="n">
         <v>78656</v>
@@ -3993,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>485961</v>
+        <v>485766</v>
       </c>
       <c r="R31" t="n">
-        <v>6790453</v>
+        <v>6790457</v>
       </c>
       <c r="S31" t="n">
         <v>9</v>
@@ -4028,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4043,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,10 +4075,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122607446</v>
+        <v>122606145</v>
       </c>
       <c r="B32" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4077,46 +4087,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486045</v>
+        <v>485616</v>
       </c>
       <c r="R32" t="n">
-        <v>6790383</v>
+        <v>6790356</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4145,7 +4150,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4155,7 +4160,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4170,22 +4175,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122607596</v>
+        <v>122606452</v>
       </c>
       <c r="B33" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4194,43 +4199,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486109</v>
+        <v>485428</v>
       </c>
       <c r="R33" t="n">
-        <v>6790384</v>
+        <v>6790393</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4299,10 +4299,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122607953</v>
+        <v>122606339</v>
       </c>
       <c r="B34" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4311,25 +4311,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4339,10 +4339,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486214</v>
+        <v>485528</v>
       </c>
       <c r="R34" t="n">
-        <v>6790429</v>
+        <v>6790365</v>
       </c>
       <c r="S34" t="n">
         <v>9</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4411,10 +4411,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122606208</v>
+        <v>122609017</v>
       </c>
       <c r="B35" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4423,38 +4423,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485592</v>
+        <v>486064</v>
       </c>
       <c r="R35" t="n">
-        <v>6790353</v>
+        <v>6790364</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4523,10 +4523,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122606955</v>
+        <v>122607446</v>
       </c>
       <c r="B36" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4535,38 +4535,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485759</v>
+        <v>486045</v>
       </c>
       <c r="R36" t="n">
-        <v>6790467</v>
+        <v>6790383</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -4598,7 +4603,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4608,7 +4613,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4635,10 +4640,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122606417</v>
+        <v>122607613</v>
       </c>
       <c r="B37" t="n">
-        <v>78656</v>
+        <v>78392</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4651,21 +4656,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4675,10 +4680,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>485407</v>
+        <v>485504</v>
       </c>
       <c r="R37" t="n">
-        <v>6790439</v>
+        <v>6790441</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4710,7 +4715,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4720,7 +4725,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,7 +4752,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122606677</v>
+        <v>122606108</v>
       </c>
       <c r="B38" t="n">
         <v>78656</v>
@@ -4787,10 +4792,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>485490</v>
+        <v>485649</v>
       </c>
       <c r="R38" t="n">
-        <v>6790430</v>
+        <v>6790375</v>
       </c>
       <c r="S38" t="n">
         <v>9</v>
@@ -4822,7 +4827,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4832,7 +4837,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4859,10 +4864,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122607118</v>
+        <v>122607713</v>
       </c>
       <c r="B39" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4871,43 +4876,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>485884</v>
+        <v>486156</v>
       </c>
       <c r="R39" t="n">
-        <v>6790450</v>
+        <v>6790429</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4976,7 +4976,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122609017</v>
+        <v>122608158</v>
       </c>
       <c r="B40" t="n">
         <v>78656</v>
@@ -5012,14 +5012,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486064</v>
+        <v>486281</v>
       </c>
       <c r="R40" t="n">
-        <v>6790364</v>
+        <v>6790441</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5061,7 +5061,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5088,7 +5093,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122607995</v>
+        <v>122606271</v>
       </c>
       <c r="B41" t="n">
         <v>78656</v>
@@ -5128,10 +5133,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486213</v>
+        <v>485553</v>
       </c>
       <c r="R41" t="n">
-        <v>6790435</v>
+        <v>6790369</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5163,7 +5168,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5173,7 +5178,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5200,7 +5205,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122607495</v>
+        <v>122606653</v>
       </c>
       <c r="B42" t="n">
         <v>78656</v>
@@ -5236,17 +5241,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486056</v>
+        <v>485568</v>
       </c>
       <c r="R42" t="n">
-        <v>6790394</v>
+        <v>6790397</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5275,7 +5280,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5285,7 +5290,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5300,22 +5305,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122606339</v>
+        <v>122608856</v>
       </c>
       <c r="B43" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5324,38 +5329,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>485528</v>
+        <v>486343</v>
       </c>
       <c r="R43" t="n">
-        <v>6790365</v>
+        <v>6790373</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5387,7 +5392,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5397,7 +5402,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5424,7 +5429,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122606286</v>
+        <v>122606204</v>
       </c>
       <c r="B44" t="n">
         <v>78656</v>
@@ -5464,13 +5469,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>485541</v>
+        <v>485615</v>
       </c>
       <c r="R44" t="n">
-        <v>6790372</v>
+        <v>6790353</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5499,7 +5504,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5509,12 +5514,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På 3 tallar på stammen</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5529,19 +5529,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122606230</v>
+        <v>122607915</v>
       </c>
       <c r="B45" t="n">
         <v>78656</v>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>485561</v>
+        <v>486193</v>
       </c>
       <c r="R45" t="n">
-        <v>6790367</v>
+        <v>6790410</v>
       </c>
       <c r="S45" t="n">
         <v>9</v>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5653,7 +5653,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122606154</v>
+        <v>122606131</v>
       </c>
       <c r="B46" t="n">
         <v>78656</v>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>485616</v>
+        <v>485629</v>
       </c>
       <c r="R46" t="n">
-        <v>6790354</v>
+        <v>6790369</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5753,19 +5753,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122606271</v>
+        <v>122608110</v>
       </c>
       <c r="B47" t="n">
         <v>78656</v>
@@ -5801,14 +5801,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>485553</v>
+        <v>486270</v>
       </c>
       <c r="R47" t="n">
-        <v>6790369</v>
+        <v>6790427</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5877,10 +5877,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122608902</v>
+        <v>122606955</v>
       </c>
       <c r="B48" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5893,34 +5893,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486280</v>
+        <v>485759</v>
       </c>
       <c r="R48" t="n">
-        <v>6790345</v>
+        <v>6790467</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5989,7 +5989,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122606145</v>
+        <v>122607495</v>
       </c>
       <c r="B49" t="n">
         <v>78656</v>
@@ -6029,13 +6029,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>485616</v>
+        <v>486056</v>
       </c>
       <c r="R49" t="n">
-        <v>6790356</v>
+        <v>6790394</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6089,19 +6089,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122607974</v>
+        <v>122606651</v>
       </c>
       <c r="B50" t="n">
         <v>78656</v>
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486212</v>
+        <v>485432</v>
       </c>
       <c r="R50" t="n">
-        <v>6790432</v>
+        <v>6790417</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6213,7 +6213,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122608990</v>
+        <v>122606286</v>
       </c>
       <c r="B51" t="n">
         <v>78656</v>
@@ -6249,14 +6249,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486070</v>
+        <v>485541</v>
       </c>
       <c r="R51" t="n">
-        <v>6790363</v>
+        <v>6790372</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6298,7 +6298,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På 3 tallar på stammen</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6325,7 +6330,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122606131</v>
+        <v>122606230</v>
       </c>
       <c r="B52" t="n">
         <v>78656</v>
@@ -6365,10 +6370,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>485629</v>
+        <v>485561</v>
       </c>
       <c r="R52" t="n">
-        <v>6790369</v>
+        <v>6790367</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6400,7 +6405,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6410,7 +6415,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6437,7 +6442,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122608651</v>
+        <v>122606677</v>
       </c>
       <c r="B53" t="n">
         <v>78656</v>
@@ -6473,14 +6478,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486380</v>
+        <v>485490</v>
       </c>
       <c r="R53" t="n">
-        <v>6790321</v>
+        <v>6790430</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6512,7 +6517,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6522,12 +6527,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6554,7 +6554,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122608110</v>
+        <v>122606807</v>
       </c>
       <c r="B54" t="n">
         <v>78656</v>
@@ -6590,14 +6590,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486270</v>
+        <v>485749</v>
       </c>
       <c r="R54" t="n">
-        <v>6790427</v>
+        <v>6790424</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6666,10 +6666,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122606807</v>
+        <v>122608902</v>
       </c>
       <c r="B55" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6682,34 +6682,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>485749</v>
+        <v>486280</v>
       </c>
       <c r="R55" t="n">
-        <v>6790424</v>
+        <v>6790345</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6778,7 +6778,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122607254</v>
+        <v>122607974</v>
       </c>
       <c r="B56" t="n">
         <v>78656</v>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486016</v>
+        <v>486212</v>
       </c>
       <c r="R56" t="n">
-        <v>6790443</v>
+        <v>6790432</v>
       </c>
       <c r="S56" t="n">
         <v>9</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6890,10 +6890,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122606143</v>
+        <v>122607077</v>
       </c>
       <c r="B57" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6902,41 +6902,49 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>485681</v>
+        <v>485772</v>
       </c>
       <c r="R57" t="n">
-        <v>6790440</v>
+        <v>6790421</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6965,7 +6973,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6975,7 +6983,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7002,10 +7010,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122607077</v>
+        <v>122607216</v>
       </c>
       <c r="B58" t="n">
-        <v>56593</v>
+        <v>8441</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7018,29 +7026,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7050,13 +7059,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485772</v>
+        <v>485504</v>
       </c>
       <c r="R58" t="n">
-        <v>6790421</v>
+        <v>6790441</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7085,7 +7094,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7095,7 +7104,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7104,28 +7113,29 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122606756</v>
+        <v>122608928</v>
       </c>
       <c r="B59" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7134,50 +7144,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>485504</v>
+        <v>486063</v>
       </c>
       <c r="R59" t="n">
-        <v>6790441</v>
+        <v>6790348</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7206,7 +7207,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7216,7 +7217,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7225,26 +7226,25 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122606642</v>
+        <v>122607719</v>
       </c>
       <c r="B60" t="n">
         <v>78656</v>
@@ -7284,13 +7284,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>485586</v>
+        <v>486157</v>
       </c>
       <c r="R60" t="n">
-        <v>6790395</v>
+        <v>6790397</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7356,10 +7356,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122608928</v>
+        <v>122606642</v>
       </c>
       <c r="B61" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7372,37 +7372,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486063</v>
+        <v>485586</v>
       </c>
       <c r="R61" t="n">
-        <v>6790348</v>
+        <v>6790395</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7468,7 +7468,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122609008</v>
+        <v>122607038</v>
       </c>
       <c r="B62" t="n">
         <v>78656</v>
@@ -7504,17 +7504,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486063</v>
+        <v>485772</v>
       </c>
       <c r="R62" t="n">
-        <v>6790348</v>
+        <v>6790421</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7580,10 +7580,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122607688</v>
+        <v>122607467</v>
       </c>
       <c r="B63" t="n">
-        <v>90859</v>
+        <v>56593</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7592,45 +7592,49 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486156</v>
+        <v>485504</v>
       </c>
       <c r="R63" t="n">
-        <v>6790429</v>
+        <v>6790441</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7659,7 +7663,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7669,7 +7673,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7684,22 +7688,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122607467</v>
+        <v>122609008</v>
       </c>
       <c r="B64" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7708,49 +7712,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>485504</v>
+        <v>486063</v>
       </c>
       <c r="R64" t="n">
-        <v>6790441</v>
+        <v>6790348</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7779,7 +7775,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7789,7 +7785,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7804,19 +7800,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122606247</v>
+        <v>122607445</v>
       </c>
       <c r="B65" t="n">
         <v>78656</v>
@@ -7856,13 +7852,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>485626</v>
+        <v>486082</v>
       </c>
       <c r="R65" t="n">
-        <v>6790401</v>
+        <v>6790427</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7891,7 +7887,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7901,7 +7897,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7928,10 +7924,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122608724</v>
+        <v>122606760</v>
       </c>
       <c r="B66" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7944,37 +7940,45 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486211</v>
+        <v>485504</v>
       </c>
       <c r="R66" t="n">
-        <v>6790317</v>
+        <v>6790441</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8003,7 +8007,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8013,7 +8017,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8028,22 +8032,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122609064</v>
+        <v>122606247</v>
       </c>
       <c r="B67" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8052,50 +8056,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486063</v>
+        <v>485626</v>
       </c>
       <c r="R67" t="n">
-        <v>6790348</v>
+        <v>6790401</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8124,7 +8119,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8134,7 +8129,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8143,7 +8138,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8162,10 +8156,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122607719</v>
+        <v>122607273</v>
       </c>
       <c r="B68" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8174,41 +8168,50 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486157</v>
+        <v>485932</v>
       </c>
       <c r="R68" t="n">
-        <v>6790397</v>
+        <v>6790416</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8237,7 +8240,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8247,7 +8250,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8256,6 +8259,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8274,10 +8278,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122608142</v>
+        <v>122609064</v>
       </c>
       <c r="B69" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8286,41 +8290,50 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486240</v>
+        <v>486063</v>
       </c>
       <c r="R69" t="n">
-        <v>6790382</v>
+        <v>6790348</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8349,7 +8362,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8359,7 +8372,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8368,6 +8381,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8386,7 +8400,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122607445</v>
+        <v>122608142</v>
       </c>
       <c r="B70" t="n">
         <v>78656</v>
@@ -8422,17 +8436,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486082</v>
+        <v>486240</v>
       </c>
       <c r="R70" t="n">
-        <v>6790427</v>
+        <v>6790382</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8461,7 +8475,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8471,7 +8485,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8498,10 +8512,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122608903</v>
+        <v>122607688</v>
       </c>
       <c r="B71" t="n">
-        <v>78393</v>
+        <v>90853</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8514,37 +8528,41 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486211</v>
+        <v>486156</v>
       </c>
       <c r="R71" t="n">
-        <v>6790317</v>
+        <v>6790429</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8573,7 +8591,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8583,7 +8601,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8598,19 +8616,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122607038</v>
+        <v>122608724</v>
       </c>
       <c r="B72" t="n">
         <v>78656</v>
@@ -8646,17 +8664,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>485772</v>
+        <v>486211</v>
       </c>
       <c r="R72" t="n">
-        <v>6790421</v>
+        <v>6790317</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8685,7 +8703,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8695,7 +8713,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8722,10 +8740,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122606760</v>
+        <v>122608903</v>
       </c>
       <c r="B73" t="n">
-        <v>57399</v>
+        <v>78393</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8738,45 +8756,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>485504</v>
+        <v>486211</v>
       </c>
       <c r="R73" t="n">
-        <v>6790441</v>
+        <v>6790317</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8805,7 +8815,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8815,7 +8825,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8830,22 +8840,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122607273</v>
+        <v>122606143</v>
       </c>
       <c r="B74" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8854,50 +8864,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>485932</v>
+        <v>485681</v>
       </c>
       <c r="R74" t="n">
-        <v>6790416</v>
+        <v>6790440</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8926,7 +8927,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8936,7 +8937,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8945,7 +8946,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122607254</v>
+        <v>122607027</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486016</v>
+        <v>485504</v>
       </c>
       <c r="R2" t="n">
-        <v>6790443</v>
+        <v>6790441</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122607995</v>
+        <v>122606946</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -823,17 +823,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486213</v>
+        <v>485706</v>
       </c>
       <c r="R3" t="n">
-        <v>6790435</v>
+        <v>6790427</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,19 +887,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122607048</v>
+        <v>122606452</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485855</v>
+        <v>485428</v>
       </c>
       <c r="R4" t="n">
-        <v>6790443</v>
+        <v>6790393</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122607108</v>
+        <v>122606193</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1047,17 +1047,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485504</v>
+        <v>485662</v>
       </c>
       <c r="R5" t="n">
-        <v>6790441</v>
+        <v>6790357</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,19 +1111,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122608651</v>
+        <v>122606131</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1159,14 +1159,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486380</v>
+        <v>485629</v>
       </c>
       <c r="R6" t="n">
-        <v>6790321</v>
+        <v>6790369</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,12 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122608694</v>
+        <v>122606919</v>
       </c>
       <c r="B7" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,41 +1247,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486035</v>
+        <v>485753</v>
       </c>
       <c r="R7" t="n">
-        <v>6790401</v>
+        <v>6790423</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,19 +1335,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122606105</v>
+        <v>122607495</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1388,17 +1383,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485662</v>
+        <v>486056</v>
       </c>
       <c r="R8" t="n">
-        <v>6790357</v>
+        <v>6790394</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,19 +1447,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122606417</v>
+        <v>122606108</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1504,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485407</v>
+        <v>485649</v>
       </c>
       <c r="R9" t="n">
-        <v>6790439</v>
+        <v>6790375</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,19 +1559,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122607160</v>
+        <v>122608651</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1612,14 +1607,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485961</v>
+        <v>486380</v>
       </c>
       <c r="R10" t="n">
-        <v>6790453</v>
+        <v>6790321</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1651,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1656,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,7 +1688,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122606787</v>
+        <v>122606154</v>
       </c>
       <c r="B11" t="n">
         <v>78656</v>
@@ -1724,17 +1724,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485706</v>
+        <v>485616</v>
       </c>
       <c r="R11" t="n">
-        <v>6790427</v>
+        <v>6790354</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,22 +1788,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122607518</v>
+        <v>122607118</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,38 +1812,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486071</v>
+        <v>485884</v>
       </c>
       <c r="R12" t="n">
-        <v>6790384</v>
+        <v>6790450</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1875,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122606154</v>
+        <v>122608926</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>78392</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,37 +1933,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485616</v>
+        <v>486252</v>
       </c>
       <c r="R13" t="n">
-        <v>6790354</v>
+        <v>6790351</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1987,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,22 +2017,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122607596</v>
+        <v>122608828</v>
       </c>
       <c r="B14" t="n">
-        <v>56593</v>
+        <v>78392</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,46 +2041,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486109</v>
+        <v>485504</v>
       </c>
       <c r="R14" t="n">
-        <v>6790384</v>
+        <v>6790441</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,22 +2129,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122608844</v>
+        <v>122606208</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2153,38 +2153,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486338</v>
+        <v>485592</v>
       </c>
       <c r="R15" t="n">
-        <v>6790352</v>
+        <v>6790353</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,12 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122606176</v>
+        <v>122607995</v>
       </c>
       <c r="B16" t="n">
-        <v>78682</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2270,25 +2265,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485613</v>
+        <v>486213</v>
       </c>
       <c r="R16" t="n">
-        <v>6790370</v>
+        <v>6790435</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2333,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,7 +2365,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122608792</v>
+        <v>122608938</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2406,17 +2401,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486035</v>
+        <v>486253</v>
       </c>
       <c r="R17" t="n">
-        <v>6790401</v>
+        <v>6790356</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2445,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,22 +2465,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122608938</v>
+        <v>122606176</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>78682</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2494,38 +2489,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486253</v>
+        <v>485613</v>
       </c>
       <c r="R18" t="n">
-        <v>6790356</v>
+        <v>6790370</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2557,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2567,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,7 +2589,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122606442</v>
+        <v>122607518</v>
       </c>
       <c r="B19" t="n">
         <v>78656</v>
@@ -2634,13 +2629,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>485407</v>
+        <v>486071</v>
       </c>
       <c r="R19" t="n">
-        <v>6790437</v>
+        <v>6790384</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2669,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2679,7 +2674,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,19 +2689,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122608061</v>
+        <v>122606977</v>
       </c>
       <c r="B20" t="n">
         <v>78656</v>
@@ -2746,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486229</v>
+        <v>485766</v>
       </c>
       <c r="R20" t="n">
-        <v>6790440</v>
+        <v>6790457</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2781,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,12 +2786,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På 5 tallar</t>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,10 +2818,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122607118</v>
+        <v>122607616</v>
       </c>
       <c r="B21" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2835,46 +2830,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>485884</v>
+        <v>486035</v>
       </c>
       <c r="R21" t="n">
-        <v>6790450</v>
+        <v>6790401</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2903,7 +2893,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2903,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,22 +2918,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122608926</v>
+        <v>122606442</v>
       </c>
       <c r="B22" t="n">
-        <v>78392</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2956,37 +2946,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486252</v>
+        <v>485407</v>
       </c>
       <c r="R22" t="n">
-        <v>6790351</v>
+        <v>6790437</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3015,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,19 +3030,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122606394</v>
+        <v>122608158</v>
       </c>
       <c r="B23" t="n">
         <v>78656</v>
@@ -3088,17 +3078,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>485411</v>
+        <v>486281</v>
       </c>
       <c r="R23" t="n">
         <v>6790441</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3127,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3137,7 +3127,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,22 +3147,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122608990</v>
+        <v>122608856</v>
       </c>
       <c r="B24" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3176,25 +3171,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3204,10 +3199,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486070</v>
+        <v>486343</v>
       </c>
       <c r="R24" t="n">
-        <v>6790363</v>
+        <v>6790373</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3239,7 +3234,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3249,7 +3244,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,7 +3271,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122606919</v>
+        <v>122606708</v>
       </c>
       <c r="B25" t="n">
         <v>78656</v>
@@ -3312,17 +3307,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>485753</v>
+        <v>485568</v>
       </c>
       <c r="R25" t="n">
-        <v>6790423</v>
+        <v>6790397</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3351,7 +3346,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3361,7 +3356,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3376,22 +3371,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122607141</v>
+        <v>122608844</v>
       </c>
       <c r="B26" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3400,43 +3395,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>485906</v>
+        <v>486338</v>
       </c>
       <c r="R26" t="n">
-        <v>6790433</v>
+        <v>6790352</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3468,7 +3458,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3478,7 +3468,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3505,10 +3500,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122607224</v>
+        <v>122606408</v>
       </c>
       <c r="B27" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3517,46 +3512,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>485981</v>
+        <v>485407</v>
       </c>
       <c r="R27" t="n">
-        <v>6790453</v>
+        <v>6790439</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3585,7 +3575,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3595,7 +3585,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3610,22 +3600,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122607948</v>
+        <v>122606204</v>
       </c>
       <c r="B28" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3638,21 +3628,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3662,10 +3652,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>485504</v>
+        <v>485615</v>
       </c>
       <c r="R28" t="n">
-        <v>6790441</v>
+        <v>6790353</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3697,7 +3687,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3707,7 +3697,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3734,10 +3724,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122606208</v>
+        <v>122606286</v>
       </c>
       <c r="B29" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3746,25 +3736,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3774,10 +3764,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>485592</v>
+        <v>485541</v>
       </c>
       <c r="R29" t="n">
-        <v>6790353</v>
+        <v>6790372</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3809,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3819,7 +3809,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På 3 tallar på stammen</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3846,10 +3841,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122607953</v>
+        <v>122606271</v>
       </c>
       <c r="B30" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3858,25 +3853,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3886,10 +3881,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486214</v>
+        <v>485553</v>
       </c>
       <c r="R30" t="n">
-        <v>6790429</v>
+        <v>6790369</v>
       </c>
       <c r="S30" t="n">
         <v>9</v>
@@ -3921,7 +3916,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3926,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3958,7 +3953,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122606977</v>
+        <v>122608990</v>
       </c>
       <c r="B31" t="n">
         <v>78656</v>
@@ -3994,14 +3989,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>485766</v>
+        <v>486070</v>
       </c>
       <c r="R31" t="n">
-        <v>6790457</v>
+        <v>6790363</v>
       </c>
       <c r="S31" t="n">
         <v>9</v>
@@ -4033,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,12 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4075,7 +4065,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122606145</v>
+        <v>122606955</v>
       </c>
       <c r="B32" t="n">
         <v>78656</v>
@@ -4115,13 +4105,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>485616</v>
+        <v>485759</v>
       </c>
       <c r="R32" t="n">
-        <v>6790356</v>
+        <v>6790467</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4150,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4160,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4175,22 +4165,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122606452</v>
+        <v>122607558</v>
       </c>
       <c r="B33" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4199,41 +4189,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>485428</v>
+        <v>486035</v>
       </c>
       <c r="R33" t="n">
-        <v>6790393</v>
+        <v>6790401</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4262,7 +4252,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4272,7 +4262,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4287,22 +4277,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122606339</v>
+        <v>122608902</v>
       </c>
       <c r="B34" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4315,34 +4305,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485528</v>
+        <v>486280</v>
       </c>
       <c r="R34" t="n">
-        <v>6790365</v>
+        <v>6790345</v>
       </c>
       <c r="S34" t="n">
         <v>9</v>
@@ -4374,7 +4364,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4384,7 +4374,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4411,10 +4401,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122609017</v>
+        <v>122607224</v>
       </c>
       <c r="B35" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4423,38 +4413,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486064</v>
+        <v>485981</v>
       </c>
       <c r="R35" t="n">
-        <v>6790364</v>
+        <v>6790453</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
@@ -4486,7 +4481,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4496,7 +4491,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4523,10 +4518,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122607446</v>
+        <v>122607948</v>
       </c>
       <c r="B36" t="n">
-        <v>56593</v>
+        <v>78393</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4535,46 +4530,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486045</v>
+        <v>485504</v>
       </c>
       <c r="R36" t="n">
-        <v>6790383</v>
+        <v>6790441</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4603,7 +4593,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4613,7 +4603,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4628,22 +4618,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122607613</v>
+        <v>122606145</v>
       </c>
       <c r="B37" t="n">
-        <v>78392</v>
+        <v>78656</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4656,21 +4646,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4680,10 +4670,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>485504</v>
+        <v>485616</v>
       </c>
       <c r="R37" t="n">
-        <v>6790441</v>
+        <v>6790356</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4715,7 +4705,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4725,7 +4715,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4752,7 +4742,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122606108</v>
+        <v>122606394</v>
       </c>
       <c r="B38" t="n">
         <v>78656</v>
@@ -4792,13 +4782,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>485649</v>
+        <v>485411</v>
       </c>
       <c r="R38" t="n">
-        <v>6790375</v>
+        <v>6790441</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4827,7 +4817,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4837,7 +4827,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4852,19 +4842,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122607713</v>
+        <v>122606677</v>
       </c>
       <c r="B39" t="n">
         <v>78656</v>
@@ -4904,10 +4894,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486156</v>
+        <v>485490</v>
       </c>
       <c r="R39" t="n">
-        <v>6790429</v>
+        <v>6790430</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
@@ -4939,7 +4929,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4949,7 +4939,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4976,7 +4966,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122608158</v>
+        <v>122608110</v>
       </c>
       <c r="B40" t="n">
         <v>78656</v>
@@ -5016,10 +5006,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486281</v>
+        <v>486270</v>
       </c>
       <c r="R40" t="n">
-        <v>6790441</v>
+        <v>6790427</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -5051,7 +5041,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5061,12 +5051,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5093,10 +5078,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122606271</v>
+        <v>122607953</v>
       </c>
       <c r="B41" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5105,25 +5090,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5133,10 +5118,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>485553</v>
+        <v>486214</v>
       </c>
       <c r="R41" t="n">
-        <v>6790369</v>
+        <v>6790429</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5168,7 +5153,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5178,7 +5163,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5205,7 +5190,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122606653</v>
+        <v>122607974</v>
       </c>
       <c r="B42" t="n">
         <v>78656</v>
@@ -5241,17 +5226,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>485568</v>
+        <v>486212</v>
       </c>
       <c r="R42" t="n">
-        <v>6790397</v>
+        <v>6790432</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5280,7 +5265,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5290,7 +5275,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5305,22 +5290,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122608856</v>
+        <v>122606339</v>
       </c>
       <c r="B43" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5329,38 +5314,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486343</v>
+        <v>485528</v>
       </c>
       <c r="R43" t="n">
-        <v>6790373</v>
+        <v>6790365</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5392,7 +5377,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5402,7 +5387,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5429,7 +5414,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122606204</v>
+        <v>122607915</v>
       </c>
       <c r="B44" t="n">
         <v>78656</v>
@@ -5469,13 +5454,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>485615</v>
+        <v>486193</v>
       </c>
       <c r="R44" t="n">
-        <v>6790353</v>
+        <v>6790410</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5504,7 +5489,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5514,7 +5499,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5529,19 +5514,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122607915</v>
+        <v>122608061</v>
       </c>
       <c r="B45" t="n">
         <v>78656</v>
@@ -5581,10 +5566,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486193</v>
+        <v>486229</v>
       </c>
       <c r="R45" t="n">
-        <v>6790410</v>
+        <v>6790440</v>
       </c>
       <c r="S45" t="n">
         <v>9</v>
@@ -5616,7 +5601,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5626,7 +5611,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5653,7 +5643,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122606131</v>
+        <v>122609017</v>
       </c>
       <c r="B46" t="n">
         <v>78656</v>
@@ -5689,14 +5679,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>485629</v>
+        <v>486064</v>
       </c>
       <c r="R46" t="n">
-        <v>6790369</v>
+        <v>6790364</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5728,7 +5718,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5738,7 +5728,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5765,7 +5755,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122608110</v>
+        <v>122607048</v>
       </c>
       <c r="B47" t="n">
         <v>78656</v>
@@ -5801,14 +5791,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486270</v>
+        <v>485855</v>
       </c>
       <c r="R47" t="n">
-        <v>6790427</v>
+        <v>6790443</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5840,7 +5830,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5850,7 +5840,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5877,10 +5867,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122606955</v>
+        <v>122607141</v>
       </c>
       <c r="B48" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5889,38 +5879,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>485759</v>
+        <v>485906</v>
       </c>
       <c r="R48" t="n">
-        <v>6790467</v>
+        <v>6790433</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5952,7 +5947,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5962,7 +5957,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5989,10 +5984,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122607495</v>
+        <v>122607596</v>
       </c>
       <c r="B49" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6001,38 +5996,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486056</v>
+        <v>486109</v>
       </c>
       <c r="R49" t="n">
-        <v>6790394</v>
+        <v>6790384</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6213,7 +6213,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122606286</v>
+        <v>122606230</v>
       </c>
       <c r="B51" t="n">
         <v>78656</v>
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>485541</v>
+        <v>485561</v>
       </c>
       <c r="R51" t="n">
-        <v>6790372</v>
+        <v>6790367</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6298,12 +6298,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På 3 tallar på stammen</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6330,7 +6325,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122606230</v>
+        <v>122607713</v>
       </c>
       <c r="B52" t="n">
         <v>78656</v>
@@ -6370,10 +6365,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>485561</v>
+        <v>486156</v>
       </c>
       <c r="R52" t="n">
-        <v>6790367</v>
+        <v>6790429</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6405,7 +6400,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6415,7 +6410,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6442,7 +6437,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122606677</v>
+        <v>122607254</v>
       </c>
       <c r="B53" t="n">
         <v>78656</v>
@@ -6482,10 +6477,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>485490</v>
+        <v>486016</v>
       </c>
       <c r="R53" t="n">
-        <v>6790430</v>
+        <v>6790443</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6517,7 +6512,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6527,7 +6522,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6554,7 +6549,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122606807</v>
+        <v>122607160</v>
       </c>
       <c r="B54" t="n">
         <v>78656</v>
@@ -6594,10 +6589,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>485749</v>
+        <v>485961</v>
       </c>
       <c r="R54" t="n">
-        <v>6790424</v>
+        <v>6790453</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6629,7 +6624,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6634,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6666,10 +6661,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122608902</v>
+        <v>122606807</v>
       </c>
       <c r="B55" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6682,34 +6677,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486280</v>
+        <v>485749</v>
       </c>
       <c r="R55" t="n">
-        <v>6790345</v>
+        <v>6790424</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6741,7 +6736,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6751,7 +6746,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6778,10 +6773,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122607974</v>
+        <v>122607446</v>
       </c>
       <c r="B56" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6790,38 +6785,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486212</v>
+        <v>486045</v>
       </c>
       <c r="R56" t="n">
-        <v>6790432</v>
+        <v>6790383</v>
       </c>
       <c r="S56" t="n">
         <v>9</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6890,10 +6890,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122607077</v>
+        <v>122606642</v>
       </c>
       <c r="B57" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6902,49 +6902,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>485772</v>
+        <v>485586</v>
       </c>
       <c r="R57" t="n">
-        <v>6790421</v>
+        <v>6790395</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6973,7 +6965,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6983,7 +6975,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7010,10 +7002,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122607216</v>
+        <v>122608903</v>
       </c>
       <c r="B58" t="n">
-        <v>8441</v>
+        <v>78393</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7022,50 +7014,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485504</v>
+        <v>486211</v>
       </c>
       <c r="R58" t="n">
-        <v>6790441</v>
+        <v>6790317</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7094,7 +7077,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7104,7 +7087,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7113,29 +7096,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122608928</v>
+        <v>122607077</v>
       </c>
       <c r="B59" t="n">
-        <v>79274</v>
+        <v>56593</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7144,41 +7126,49 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486063</v>
+        <v>485772</v>
       </c>
       <c r="R59" t="n">
-        <v>6790348</v>
+        <v>6790421</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7207,7 +7197,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7217,7 +7207,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7244,7 +7234,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122607719</v>
+        <v>122606247</v>
       </c>
       <c r="B60" t="n">
         <v>78656</v>
@@ -7284,13 +7274,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486157</v>
+        <v>485626</v>
       </c>
       <c r="R60" t="n">
-        <v>6790397</v>
+        <v>6790401</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7319,7 +7309,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7329,7 +7319,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7356,10 +7346,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122606642</v>
+        <v>122608928</v>
       </c>
       <c r="B61" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7372,37 +7362,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>485586</v>
+        <v>486063</v>
       </c>
       <c r="R61" t="n">
-        <v>6790395</v>
+        <v>6790348</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7431,7 +7421,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7441,7 +7431,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7468,10 +7458,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122607038</v>
+        <v>122607547</v>
       </c>
       <c r="B62" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7480,41 +7470,49 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>485772</v>
+        <v>485504</v>
       </c>
       <c r="R62" t="n">
-        <v>6790421</v>
+        <v>6790441</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7543,7 +7541,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7553,7 +7551,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7568,22 +7566,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122607467</v>
+        <v>122607038</v>
       </c>
       <c r="B63" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7592,49 +7590,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>485504</v>
+        <v>485772</v>
       </c>
       <c r="R63" t="n">
-        <v>6790441</v>
+        <v>6790421</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7663,7 +7653,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7673,7 +7663,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7688,22 +7678,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122609008</v>
+        <v>122609064</v>
       </c>
       <c r="B64" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7712,28 +7702,37 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Lindflot, Lindflot, Dlr</t>
@@ -7775,7 +7774,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7785,7 +7784,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7794,6 +7793,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7812,7 +7812,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122607445</v>
+        <v>122606143</v>
       </c>
       <c r="B65" t="n">
         <v>78656</v>
@@ -7852,13 +7852,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486082</v>
+        <v>485681</v>
       </c>
       <c r="R65" t="n">
-        <v>6790427</v>
+        <v>6790440</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7924,10 +7924,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122606760</v>
+        <v>122609008</v>
       </c>
       <c r="B66" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7940,45 +7940,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>485504</v>
+        <v>486063</v>
       </c>
       <c r="R66" t="n">
-        <v>6790441</v>
+        <v>6790348</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8007,7 +7999,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8017,7 +8009,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8032,19 +8024,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122606247</v>
+        <v>122607719</v>
       </c>
       <c r="B67" t="n">
         <v>78656</v>
@@ -8084,13 +8076,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>485626</v>
+        <v>486157</v>
       </c>
       <c r="R67" t="n">
-        <v>6790401</v>
+        <v>6790397</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8119,7 +8111,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8129,7 +8121,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8156,10 +8148,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122607273</v>
+        <v>122608142</v>
       </c>
       <c r="B68" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8168,50 +8160,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>485932</v>
+        <v>486240</v>
       </c>
       <c r="R68" t="n">
-        <v>6790416</v>
+        <v>6790382</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8240,7 +8223,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8250,7 +8233,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8259,7 +8242,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8278,7 +8260,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122609064</v>
+        <v>122607216</v>
       </c>
       <c r="B69" t="n">
         <v>8441</v>
@@ -8323,17 +8305,17 @@
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486063</v>
+        <v>485504</v>
       </c>
       <c r="R69" t="n">
-        <v>6790348</v>
+        <v>6790441</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8362,7 +8344,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8372,7 +8354,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8388,19 +8370,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122608142</v>
+        <v>122608724</v>
       </c>
       <c r="B70" t="n">
         <v>78656</v>
@@ -8440,13 +8422,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486240</v>
+        <v>486211</v>
       </c>
       <c r="R70" t="n">
-        <v>6790382</v>
+        <v>6790317</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8475,7 +8457,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8485,7 +8467,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8512,10 +8494,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122607688</v>
+        <v>122607445</v>
       </c>
       <c r="B71" t="n">
-        <v>90853</v>
+        <v>78656</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8528,41 +8510,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486156</v>
+        <v>486082</v>
       </c>
       <c r="R71" t="n">
-        <v>6790429</v>
+        <v>6790427</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8591,7 +8569,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8601,7 +8579,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8616,22 +8594,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122608724</v>
+        <v>122606760</v>
       </c>
       <c r="B72" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8644,37 +8622,45 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486211</v>
+        <v>485504</v>
       </c>
       <c r="R72" t="n">
-        <v>6790317</v>
+        <v>6790441</v>
       </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8703,7 +8689,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8713,7 +8699,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8728,22 +8714,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122608903</v>
+        <v>122607688</v>
       </c>
       <c r="B73" t="n">
-        <v>78393</v>
+        <v>90853</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8756,37 +8742,41 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486211</v>
+        <v>486156</v>
       </c>
       <c r="R73" t="n">
-        <v>6790317</v>
+        <v>6790429</v>
       </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8815,7 +8805,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8825,7 +8815,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8840,22 +8830,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122606143</v>
+        <v>122607273</v>
       </c>
       <c r="B74" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8864,41 +8854,50 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>485681</v>
+        <v>485932</v>
       </c>
       <c r="R74" t="n">
-        <v>6790440</v>
+        <v>6790416</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8927,7 +8926,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8937,7 +8936,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8946,6 +8945,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122607027</v>
+        <v>122606669</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485504</v>
+        <v>485407</v>
       </c>
       <c r="R2" t="n">
-        <v>6790441</v>
+        <v>6790437</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122606946</v>
+        <v>122606394</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,17 +823,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485706</v>
+        <v>485411</v>
       </c>
       <c r="R3" t="n">
-        <v>6790427</v>
+        <v>6790441</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122606452</v>
+        <v>122607558</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>56594</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,41 +911,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485428</v>
+        <v>486035</v>
       </c>
       <c r="R4" t="n">
-        <v>6790393</v>
+        <v>6790401</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122606193</v>
+        <v>122607224</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>56594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,41 +1023,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485662</v>
+        <v>485981</v>
       </c>
       <c r="R5" t="n">
-        <v>6790357</v>
+        <v>6790453</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122606131</v>
+        <v>122606651</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485629</v>
+        <v>485432</v>
       </c>
       <c r="R6" t="n">
-        <v>6790369</v>
+        <v>6790417</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122606919</v>
+        <v>122608705</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,13 +1280,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485753</v>
+        <v>485504</v>
       </c>
       <c r="R7" t="n">
-        <v>6790423</v>
+        <v>6790441</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,22 +1340,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122607495</v>
+        <v>122608832</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>78394</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486056</v>
+        <v>485504</v>
       </c>
       <c r="R8" t="n">
-        <v>6790394</v>
+        <v>6790441</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,22 +1452,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122606108</v>
+        <v>122606955</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485649</v>
+        <v>485759</v>
       </c>
       <c r="R9" t="n">
-        <v>6790375</v>
+        <v>6790467</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1534,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122608651</v>
+        <v>122606286</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,14 +1612,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486380</v>
+        <v>485541</v>
       </c>
       <c r="R10" t="n">
-        <v>6790321</v>
+        <v>6790372</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1646,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,12 +1661,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På 3 tallar</t>
+          <t>På 3 tallar på stammen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122606154</v>
+        <v>122608158</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,17 +1729,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485616</v>
+        <v>486281</v>
       </c>
       <c r="R11" t="n">
-        <v>6790354</v>
+        <v>6790441</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1763,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1778,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,22 +1798,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122607118</v>
+        <v>122607048</v>
       </c>
       <c r="B12" t="n">
-        <v>56593</v>
+        <v>78657</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,43 +1822,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485884</v>
+        <v>485855</v>
       </c>
       <c r="R12" t="n">
-        <v>6790450</v>
+        <v>6790443</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1880,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122608926</v>
+        <v>122606452</v>
       </c>
       <c r="B13" t="n">
-        <v>78392</v>
+        <v>78657</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,34 +1938,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486252</v>
+        <v>485428</v>
       </c>
       <c r="R13" t="n">
-        <v>6790351</v>
+        <v>6790393</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -1992,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122608828</v>
+        <v>122606946</v>
       </c>
       <c r="B14" t="n">
-        <v>78392</v>
+        <v>78657</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,37 +2050,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485504</v>
+        <v>485706</v>
       </c>
       <c r="R14" t="n">
-        <v>6790441</v>
+        <v>6790427</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2104,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,22 +2134,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122606208</v>
+        <v>122607446</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>56594</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,34 +2162,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485592</v>
+        <v>486045</v>
       </c>
       <c r="R15" t="n">
-        <v>6790353</v>
+        <v>6790383</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2216,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122607995</v>
+        <v>122607495</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,10 +2303,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486213</v>
+        <v>486056</v>
       </c>
       <c r="R16" t="n">
-        <v>6790435</v>
+        <v>6790394</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2328,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2375,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122608938</v>
+        <v>122606139</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,17 +2411,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486253</v>
+        <v>485662</v>
       </c>
       <c r="R17" t="n">
-        <v>6790356</v>
+        <v>6790357</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2440,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,22 +2475,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122606176</v>
+        <v>122608892</v>
       </c>
       <c r="B18" t="n">
-        <v>78682</v>
+        <v>78657</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2489,41 +2499,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485613</v>
+        <v>486035</v>
       </c>
       <c r="R18" t="n">
-        <v>6790370</v>
+        <v>6790401</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2552,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2572,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,22 +2587,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122607518</v>
+        <v>122607713</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2629,10 +2639,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486071</v>
+        <v>486156</v>
       </c>
       <c r="R19" t="n">
-        <v>6790384</v>
+        <v>6790429</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2664,7 +2674,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2684,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,10 +2711,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122606977</v>
+        <v>122607941</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2717,21 +2727,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,13 +2751,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>485766</v>
+        <v>485504</v>
       </c>
       <c r="R20" t="n">
-        <v>6790457</v>
+        <v>6790441</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2776,7 +2786,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,12 +2796,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2806,22 +2811,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122607616</v>
+        <v>122607160</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2854,17 +2859,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486035</v>
+        <v>485961</v>
       </c>
       <c r="R21" t="n">
-        <v>6790401</v>
+        <v>6790453</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2893,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2903,7 +2908,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2918,22 +2923,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122606442</v>
+        <v>122606145</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2970,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>485407</v>
+        <v>485616</v>
       </c>
       <c r="R22" t="n">
-        <v>6790437</v>
+        <v>6790356</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122608158</v>
+        <v>122606653</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3078,17 +3083,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486281</v>
+        <v>485568</v>
       </c>
       <c r="R23" t="n">
-        <v>6790441</v>
+        <v>6790397</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3117,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,12 +3132,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3147,22 +3147,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122608856</v>
+        <v>122606204</v>
       </c>
       <c r="B24" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3171,41 +3171,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486343</v>
+        <v>485615</v>
       </c>
       <c r="R24" t="n">
-        <v>6790373</v>
+        <v>6790353</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,22 +3259,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122606708</v>
+        <v>122608844</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3307,17 +3307,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>485568</v>
+        <v>486338</v>
       </c>
       <c r="R25" t="n">
-        <v>6790397</v>
+        <v>6790352</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3356,7 +3356,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3371,22 +3376,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122608844</v>
+        <v>122606977</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3419,14 +3424,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486338</v>
+        <v>485766</v>
       </c>
       <c r="R26" t="n">
-        <v>6790352</v>
+        <v>6790457</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3458,7 +3463,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3468,12 +3473,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På 5 tallar</t>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3500,10 +3505,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122606408</v>
+        <v>122607974</v>
       </c>
       <c r="B27" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3540,13 +3545,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>485407</v>
+        <v>486212</v>
       </c>
       <c r="R27" t="n">
-        <v>6790439</v>
+        <v>6790432</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3575,7 +3580,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3585,7 +3590,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3600,22 +3605,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122606204</v>
+        <v>122607141</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>56594</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3624,41 +3629,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>485615</v>
+        <v>485906</v>
       </c>
       <c r="R28" t="n">
-        <v>6790353</v>
+        <v>6790433</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3687,7 +3697,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3697,7 +3707,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3712,22 +3722,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122606286</v>
+        <v>122607254</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3764,10 +3774,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>485541</v>
+        <v>486016</v>
       </c>
       <c r="R29" t="n">
-        <v>6790372</v>
+        <v>6790443</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3799,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,12 +3819,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På 3 tallar på stammen</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3841,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122606271</v>
+        <v>122606408</v>
       </c>
       <c r="B30" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3881,13 +3886,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>485553</v>
+        <v>485407</v>
       </c>
       <c r="R30" t="n">
-        <v>6790369</v>
+        <v>6790439</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3916,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3926,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3941,22 +3946,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122608990</v>
+        <v>122606339</v>
       </c>
       <c r="B31" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3989,14 +3994,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486070</v>
+        <v>485528</v>
       </c>
       <c r="R31" t="n">
-        <v>6790363</v>
+        <v>6790365</v>
       </c>
       <c r="S31" t="n">
         <v>9</v>
@@ -4028,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,10 +4070,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122606955</v>
+        <v>122606919</v>
       </c>
       <c r="B32" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4105,10 +4110,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>485759</v>
+        <v>485753</v>
       </c>
       <c r="R32" t="n">
-        <v>6790467</v>
+        <v>6790423</v>
       </c>
       <c r="S32" t="n">
         <v>9</v>
@@ -4140,7 +4145,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4155,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4177,10 +4182,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122607558</v>
+        <v>122607118</v>
       </c>
       <c r="B33" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4211,19 +4216,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486035</v>
+        <v>485884</v>
       </c>
       <c r="R33" t="n">
-        <v>6790401</v>
+        <v>6790450</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4252,7 +4262,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4262,7 +4272,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4277,22 +4287,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122608902</v>
+        <v>122608061</v>
       </c>
       <c r="B34" t="n">
-        <v>78393</v>
+        <v>78657</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4305,34 +4315,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486280</v>
+        <v>486229</v>
       </c>
       <c r="R34" t="n">
-        <v>6790345</v>
+        <v>6790440</v>
       </c>
       <c r="S34" t="n">
         <v>9</v>
@@ -4364,7 +4374,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4374,7 +4384,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4401,10 +4416,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122607224</v>
+        <v>122606176</v>
       </c>
       <c r="B35" t="n">
-        <v>56593</v>
+        <v>78683</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4417,39 +4432,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485981</v>
+        <v>485613</v>
       </c>
       <c r="R35" t="n">
-        <v>6790453</v>
+        <v>6790370</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
@@ -4481,7 +4491,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4491,7 +4501,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,10 +4528,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122607948</v>
+        <v>122608110</v>
       </c>
       <c r="B36" t="n">
-        <v>78393</v>
+        <v>78657</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4534,37 +4544,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485504</v>
+        <v>486270</v>
       </c>
       <c r="R36" t="n">
-        <v>6790441</v>
+        <v>6790427</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4593,7 +4603,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4603,7 +4613,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4618,22 +4628,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122606145</v>
+        <v>122606271</v>
       </c>
       <c r="B37" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4670,13 +4680,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>485616</v>
+        <v>485553</v>
       </c>
       <c r="R37" t="n">
-        <v>6790356</v>
+        <v>6790369</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4705,7 +4715,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4715,7 +4725,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4730,22 +4740,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122606394</v>
+        <v>122606131</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4782,13 +4792,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>485411</v>
+        <v>485629</v>
       </c>
       <c r="R38" t="n">
-        <v>6790441</v>
+        <v>6790369</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4817,7 +4827,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4827,7 +4837,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4842,22 +4852,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122606677</v>
+        <v>122608902</v>
       </c>
       <c r="B39" t="n">
-        <v>78656</v>
+        <v>78394</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4870,34 +4880,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>485490</v>
+        <v>486280</v>
       </c>
       <c r="R39" t="n">
-        <v>6790430</v>
+        <v>6790345</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
@@ -4929,7 +4939,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4939,7 +4949,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4966,10 +4976,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122608110</v>
+        <v>122606208</v>
       </c>
       <c r="B40" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4978,38 +4988,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486270</v>
+        <v>485592</v>
       </c>
       <c r="R40" t="n">
-        <v>6790427</v>
+        <v>6790353</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -5041,7 +5051,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5051,7 +5061,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5078,10 +5088,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122607953</v>
+        <v>122608938</v>
       </c>
       <c r="B41" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5090,38 +5100,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486214</v>
+        <v>486253</v>
       </c>
       <c r="R41" t="n">
-        <v>6790429</v>
+        <v>6790356</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5153,7 +5163,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5163,7 +5173,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5190,10 +5200,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122607974</v>
+        <v>122608651</v>
       </c>
       <c r="B42" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5226,14 +5236,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486212</v>
+        <v>486380</v>
       </c>
       <c r="R42" t="n">
-        <v>6790432</v>
+        <v>6790321</v>
       </c>
       <c r="S42" t="n">
         <v>9</v>
@@ -5265,7 +5275,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5275,7 +5285,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5302,10 +5317,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122606339</v>
+        <v>122609017</v>
       </c>
       <c r="B43" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5338,14 +5353,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>485528</v>
+        <v>486064</v>
       </c>
       <c r="R43" t="n">
-        <v>6790365</v>
+        <v>6790364</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5377,7 +5392,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5387,7 +5402,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5414,10 +5429,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122607915</v>
+        <v>122608926</v>
       </c>
       <c r="B44" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5430,34 +5445,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486193</v>
+        <v>486252</v>
       </c>
       <c r="R44" t="n">
-        <v>6790410</v>
+        <v>6790351</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -5489,7 +5504,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5499,7 +5514,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5526,10 +5541,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122608061</v>
+        <v>122607596</v>
       </c>
       <c r="B45" t="n">
-        <v>78656</v>
+        <v>56594</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5538,38 +5553,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486229</v>
+        <v>486109</v>
       </c>
       <c r="R45" t="n">
-        <v>6790440</v>
+        <v>6790384</v>
       </c>
       <c r="S45" t="n">
         <v>9</v>
@@ -5601,7 +5621,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5611,12 +5631,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5643,10 +5658,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122609017</v>
+        <v>122606677</v>
       </c>
       <c r="B46" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5679,14 +5694,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486064</v>
+        <v>485490</v>
       </c>
       <c r="R46" t="n">
-        <v>6790364</v>
+        <v>6790430</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5718,7 +5733,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5728,7 +5743,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5755,10 +5770,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122607048</v>
+        <v>122606154</v>
       </c>
       <c r="B47" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5795,13 +5810,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>485855</v>
+        <v>485616</v>
       </c>
       <c r="R47" t="n">
-        <v>6790443</v>
+        <v>6790354</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5830,7 +5845,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5840,7 +5855,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5855,22 +5870,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122607141</v>
+        <v>122607915</v>
       </c>
       <c r="B48" t="n">
-        <v>56593</v>
+        <v>78657</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5879,43 +5894,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>485906</v>
+        <v>486193</v>
       </c>
       <c r="R48" t="n">
-        <v>6790433</v>
+        <v>6790410</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5947,7 +5957,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5957,7 +5967,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5984,10 +5994,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122607596</v>
+        <v>122606807</v>
       </c>
       <c r="B49" t="n">
-        <v>56593</v>
+        <v>78657</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5996,43 +6006,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486109</v>
+        <v>485749</v>
       </c>
       <c r="R49" t="n">
-        <v>6790384</v>
+        <v>6790424</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -6064,7 +6069,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6074,7 +6079,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6101,10 +6106,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122606651</v>
+        <v>122608856</v>
       </c>
       <c r="B50" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6113,38 +6118,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>485432</v>
+        <v>486343</v>
       </c>
       <c r="R50" t="n">
-        <v>6790417</v>
+        <v>6790373</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -6176,7 +6181,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6186,7 +6191,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6213,10 +6218,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122606230</v>
+        <v>122608990</v>
       </c>
       <c r="B51" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6249,14 +6254,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>485561</v>
+        <v>486070</v>
       </c>
       <c r="R51" t="n">
-        <v>6790367</v>
+        <v>6790363</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -6288,7 +6293,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6298,7 +6303,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6325,10 +6330,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122607713</v>
+        <v>122607995</v>
       </c>
       <c r="B52" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6365,10 +6370,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486156</v>
+        <v>486213</v>
       </c>
       <c r="R52" t="n">
-        <v>6790429</v>
+        <v>6790435</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6400,7 +6405,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6410,7 +6415,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6437,10 +6442,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122607254</v>
+        <v>122606108</v>
       </c>
       <c r="B53" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6477,10 +6482,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486016</v>
+        <v>485649</v>
       </c>
       <c r="R53" t="n">
-        <v>6790443</v>
+        <v>6790375</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6512,7 +6517,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6522,7 +6527,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6549,10 +6554,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122607160</v>
+        <v>122607518</v>
       </c>
       <c r="B54" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6589,10 +6594,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>485961</v>
+        <v>486071</v>
       </c>
       <c r="R54" t="n">
-        <v>6790453</v>
+        <v>6790384</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6624,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6634,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6661,10 +6666,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122606807</v>
+        <v>122606230</v>
       </c>
       <c r="B55" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6701,10 +6706,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>485749</v>
+        <v>485561</v>
       </c>
       <c r="R55" t="n">
-        <v>6790424</v>
+        <v>6790367</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6736,7 +6741,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6746,7 +6751,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6773,10 +6778,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122607446</v>
+        <v>122607953</v>
       </c>
       <c r="B56" t="n">
-        <v>56593</v>
+        <v>8441</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6789,39 +6794,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486045</v>
+        <v>486214</v>
       </c>
       <c r="R56" t="n">
-        <v>6790383</v>
+        <v>6790429</v>
       </c>
       <c r="S56" t="n">
         <v>9</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6890,10 +6890,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122606642</v>
+        <v>122606760</v>
       </c>
       <c r="B57" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6906,34 +6906,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>485586</v>
+        <v>485504</v>
       </c>
       <c r="R57" t="n">
-        <v>6790395</v>
+        <v>6790441</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6965,7 +6973,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6975,7 +6983,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6990,22 +6998,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122608903</v>
+        <v>122608713</v>
       </c>
       <c r="B58" t="n">
-        <v>78393</v>
+        <v>56594</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7014,41 +7022,49 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486211</v>
+        <v>485504</v>
       </c>
       <c r="R58" t="n">
-        <v>6790317</v>
+        <v>6790441</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7077,7 +7093,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7087,7 +7103,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7102,22 +7118,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122607077</v>
+        <v>122607719</v>
       </c>
       <c r="B59" t="n">
-        <v>56593</v>
+        <v>78657</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7126,49 +7142,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>485772</v>
+        <v>486157</v>
       </c>
       <c r="R59" t="n">
-        <v>6790421</v>
+        <v>6790397</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7197,7 +7205,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7207,7 +7215,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7234,10 +7242,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122606247</v>
+        <v>122608903</v>
       </c>
       <c r="B60" t="n">
-        <v>78656</v>
+        <v>78394</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7250,37 +7258,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>485626</v>
+        <v>486211</v>
       </c>
       <c r="R60" t="n">
-        <v>6790401</v>
+        <v>6790317</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7309,7 +7317,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7319,7 +7327,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7349,7 +7357,7 @@
         <v>122608928</v>
       </c>
       <c r="B61" t="n">
-        <v>79274</v>
+        <v>79275</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7458,10 +7466,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122607547</v>
+        <v>122606247</v>
       </c>
       <c r="B62" t="n">
-        <v>56593</v>
+        <v>78657</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7470,49 +7478,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>485504</v>
+        <v>485626</v>
       </c>
       <c r="R62" t="n">
-        <v>6790441</v>
+        <v>6790401</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7566,22 +7566,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122607038</v>
+        <v>122609008</v>
       </c>
       <c r="B63" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7614,17 +7614,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>485772</v>
+        <v>486063</v>
       </c>
       <c r="R63" t="n">
-        <v>6790421</v>
+        <v>6790348</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7690,10 +7690,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122609064</v>
+        <v>122608724</v>
       </c>
       <c r="B64" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7702,47 +7702,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486063</v>
+        <v>486211</v>
       </c>
       <c r="R64" t="n">
-        <v>6790348</v>
+        <v>6790317</v>
       </c>
       <c r="S64" t="n">
         <v>8</v>
@@ -7774,7 +7765,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7784,7 +7775,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7793,7 +7784,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7815,7 +7805,7 @@
         <v>122606143</v>
       </c>
       <c r="B65" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7924,10 +7914,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122609008</v>
+        <v>122606642</v>
       </c>
       <c r="B66" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7960,17 +7950,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486063</v>
+        <v>485586</v>
       </c>
       <c r="R66" t="n">
-        <v>6790348</v>
+        <v>6790395</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7999,7 +7989,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8009,7 +7999,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8036,10 +8026,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122607719</v>
+        <v>122607445</v>
       </c>
       <c r="B67" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8076,13 +8066,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486157</v>
+        <v>486082</v>
       </c>
       <c r="R67" t="n">
-        <v>6790397</v>
+        <v>6790427</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8111,7 +8101,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8121,7 +8111,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8148,10 +8138,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122608142</v>
+        <v>122609064</v>
       </c>
       <c r="B68" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8160,41 +8150,50 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486240</v>
+        <v>486063</v>
       </c>
       <c r="R68" t="n">
-        <v>6790382</v>
+        <v>6790348</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8223,7 +8222,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8233,7 +8232,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8242,6 +8241,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8260,10 +8260,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122607216</v>
+        <v>122607038</v>
       </c>
       <c r="B69" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8272,50 +8272,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>485504</v>
+        <v>485772</v>
       </c>
       <c r="R69" t="n">
-        <v>6790441</v>
+        <v>6790421</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8344,7 +8335,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8354,7 +8345,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8363,29 +8354,28 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122608724</v>
+        <v>122608142</v>
       </c>
       <c r="B70" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8422,13 +8412,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486211</v>
+        <v>486240</v>
       </c>
       <c r="R70" t="n">
-        <v>6790317</v>
+        <v>6790382</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8457,7 +8447,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8467,7 +8457,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8494,10 +8484,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122607445</v>
+        <v>122607273</v>
       </c>
       <c r="B71" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8506,38 +8496,47 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486082</v>
+        <v>485932</v>
       </c>
       <c r="R71" t="n">
-        <v>6790427</v>
+        <v>6790416</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8569,7 +8568,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8579,7 +8578,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8588,6 +8587,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8606,10 +8606,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122606760</v>
+        <v>122607688</v>
       </c>
       <c r="B72" t="n">
-        <v>57399</v>
+        <v>90854</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8622,45 +8622,41 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>485504</v>
+        <v>486156</v>
       </c>
       <c r="R72" t="n">
-        <v>6790441</v>
+        <v>6790429</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8689,7 +8685,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8699,7 +8695,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8714,22 +8710,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122607688</v>
+        <v>122606756</v>
       </c>
       <c r="B73" t="n">
-        <v>90853</v>
+        <v>8441</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8738,45 +8734,50 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486156</v>
+        <v>485504</v>
       </c>
       <c r="R73" t="n">
-        <v>6790429</v>
+        <v>6790441</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8805,7 +8806,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8815,7 +8816,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8824,28 +8825,29 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122607273</v>
+        <v>122607077</v>
       </c>
       <c r="B74" t="n">
-        <v>8441</v>
+        <v>56594</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8858,30 +8860,29 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -8891,13 +8892,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>485932</v>
+        <v>485772</v>
       </c>
       <c r="R74" t="n">
-        <v>6790416</v>
+        <v>6790421</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8926,7 +8927,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8936,7 +8937,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8945,7 +8946,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8961,6 +8961,4720 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>122671610</v>
+      </c>
+      <c r="B75" t="n">
+        <v>78393</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>486013</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6790366</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>122671569</v>
+      </c>
+      <c r="B76" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>485951</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6790408</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>122671453</v>
+      </c>
+      <c r="B77" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>485835</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6790356</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>122671541</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>485879</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6790409</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>122671659</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>486020</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6790412</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>122671536</v>
+      </c>
+      <c r="B80" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>485910</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6790394</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>122671564</v>
+      </c>
+      <c r="B81" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>485933</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6790411</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>122671879</v>
+      </c>
+      <c r="B82" t="n">
+        <v>56594</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>486429</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6790399</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>på ett par platser intill granar</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>122671424</v>
+      </c>
+      <c r="B83" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>485783</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6790367</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>122671570</v>
+      </c>
+      <c r="B84" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>485953</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6790411</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>122671608</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79275</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>486013</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6790366</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>122671674</v>
+      </c>
+      <c r="B86" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>486266</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6790373</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>122671493</v>
+      </c>
+      <c r="B87" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>485859</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6790362</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>122671523</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57537</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>485893</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6790386</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>122671679</v>
+      </c>
+      <c r="B89" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>486342</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6790369</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>122671575</v>
+      </c>
+      <c r="B90" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>485989</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6790394</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>122671506</v>
+      </c>
+      <c r="B91" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>485861</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6790364</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>122671512</v>
+      </c>
+      <c r="B92" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>485876</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6790371</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>122671647</v>
+      </c>
+      <c r="B93" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>486035</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6790369</v>
+      </c>
+      <c r="S93" t="n">
+        <v>25</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>122671675</v>
+      </c>
+      <c r="B94" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>486331</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6790370</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>122671609</v>
+      </c>
+      <c r="B95" t="n">
+        <v>78394</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>486013</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6790366</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>122671587</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79275</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>485985</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6790379</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>122671508</v>
+      </c>
+      <c r="B97" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>485871</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6790368</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>122671579</v>
+      </c>
+      <c r="B98" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>485989</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6790378</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>122671384</v>
+      </c>
+      <c r="B99" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>485777</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6790392</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>122671668</v>
+      </c>
+      <c r="B100" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>486079</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6790394</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>122671422</v>
+      </c>
+      <c r="B101" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>485784</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6790390</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>122671378</v>
+      </c>
+      <c r="B102" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>485757</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6790379</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>122671521</v>
+      </c>
+      <c r="B103" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>485893</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6790386</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>122671888</v>
+      </c>
+      <c r="B104" t="n">
+        <v>56594</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>485897</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6790441</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>under betestall rikligt</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>122671555</v>
+      </c>
+      <c r="B105" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>485915</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6790407</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>122671595</v>
+      </c>
+      <c r="B106" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>485984</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6790370</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>122671658</v>
+      </c>
+      <c r="B107" t="n">
+        <v>57537</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>486037</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6790372</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>122671534</v>
+      </c>
+      <c r="B108" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>485901</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6790392</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>122671681</v>
+      </c>
+      <c r="B109" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>486342</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6790369</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>122671651</v>
+      </c>
+      <c r="B110" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>486048</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6790360</v>
+      </c>
+      <c r="S110" t="n">
+        <v>25</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>122671447</v>
+      </c>
+      <c r="B111" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>485830</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6790346</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>122671667</v>
+      </c>
+      <c r="B112" t="n">
+        <v>78691</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>185</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>486043</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6790416</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>122671519</v>
+      </c>
+      <c r="B113" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>485876</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6790381</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>122671440</v>
+      </c>
+      <c r="B114" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>485819</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6790340</v>
+      </c>
+      <c r="S114" t="n">
+        <v>5</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>122671592</v>
+      </c>
+      <c r="B115" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>485984</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6790371</v>
+      </c>
+      <c r="S115" t="n">
+        <v>5</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>122671434</v>
+      </c>
+      <c r="B116" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>485799</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6790349</v>
+      </c>
+      <c r="S116" t="n">
+        <v>5</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>122671559</v>
+      </c>
+      <c r="B117" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>485916</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6790407</v>
+      </c>
+      <c r="S117" t="n">
+        <v>5</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>122671537</v>
+      </c>
+      <c r="B118" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>485910</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6790394</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY118"/>
+  <dimension ref="A1:AY196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2711,10 +2711,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122607941</v>
+        <v>122607160</v>
       </c>
       <c r="B20" t="n">
-        <v>78393</v>
+        <v>78657</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2727,21 +2727,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2751,13 +2751,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>485504</v>
+        <v>485961</v>
       </c>
       <c r="R20" t="n">
-        <v>6790441</v>
+        <v>6790453</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2811,19 +2811,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122607160</v>
+        <v>122606145</v>
       </c>
       <c r="B21" t="n">
         <v>78657</v>
@@ -2863,13 +2863,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>485961</v>
+        <v>485616</v>
       </c>
       <c r="R21" t="n">
-        <v>6790453</v>
+        <v>6790356</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2923,19 +2923,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122606145</v>
+        <v>122606653</v>
       </c>
       <c r="B22" t="n">
         <v>78657</v>
@@ -2971,14 +2971,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>485616</v>
+        <v>485568</v>
       </c>
       <c r="R22" t="n">
-        <v>6790356</v>
+        <v>6790397</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,22 +3035,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122606653</v>
+        <v>122607941</v>
       </c>
       <c r="B23" t="n">
-        <v>78657</v>
+        <v>78393</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,34 +3063,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>485568</v>
+        <v>485504</v>
       </c>
       <c r="R23" t="n">
-        <v>6790397</v>
+        <v>6790441</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3147,12 +3147,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3617,10 +3617,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122607141</v>
+        <v>122607254</v>
       </c>
       <c r="B28" t="n">
-        <v>56594</v>
+        <v>78657</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3629,43 +3629,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>485906</v>
+        <v>486016</v>
       </c>
       <c r="R28" t="n">
-        <v>6790433</v>
+        <v>6790443</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3697,7 +3692,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3707,7 +3702,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3734,7 +3729,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122607254</v>
+        <v>122606408</v>
       </c>
       <c r="B29" t="n">
         <v>78657</v>
@@ -3774,13 +3769,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486016</v>
+        <v>485407</v>
       </c>
       <c r="R29" t="n">
-        <v>6790443</v>
+        <v>6790439</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3809,7 +3804,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3819,7 +3814,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3834,19 +3829,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122606408</v>
+        <v>122606339</v>
       </c>
       <c r="B30" t="n">
         <v>78657</v>
@@ -3886,13 +3881,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>485407</v>
+        <v>485528</v>
       </c>
       <c r="R30" t="n">
-        <v>6790439</v>
+        <v>6790365</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3921,7 +3916,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3926,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,19 +3941,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122606339</v>
+        <v>122606919</v>
       </c>
       <c r="B31" t="n">
         <v>78657</v>
@@ -3998,10 +3993,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>485528</v>
+        <v>485753</v>
       </c>
       <c r="R31" t="n">
-        <v>6790365</v>
+        <v>6790423</v>
       </c>
       <c r="S31" t="n">
         <v>9</v>
@@ -4033,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,10 +4065,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122606919</v>
+        <v>122607141</v>
       </c>
       <c r="B32" t="n">
-        <v>78657</v>
+        <v>56594</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4082,38 +4077,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>485753</v>
+        <v>485906</v>
       </c>
       <c r="R32" t="n">
-        <v>6790423</v>
+        <v>6790433</v>
       </c>
       <c r="S32" t="n">
         <v>9</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122607118</v>
+        <v>122608061</v>
       </c>
       <c r="B33" t="n">
-        <v>56594</v>
+        <v>78657</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4194,43 +4194,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>485884</v>
+        <v>486229</v>
       </c>
       <c r="R33" t="n">
-        <v>6790450</v>
+        <v>6790440</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -4262,7 +4257,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4272,7 +4267,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4299,10 +4299,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122608061</v>
+        <v>122607118</v>
       </c>
       <c r="B34" t="n">
-        <v>78657</v>
+        <v>56594</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4311,38 +4311,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486229</v>
+        <v>485884</v>
       </c>
       <c r="R34" t="n">
-        <v>6790440</v>
+        <v>6790450</v>
       </c>
       <c r="S34" t="n">
         <v>9</v>
@@ -4374,7 +4379,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4384,12 +4389,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5541,10 +5541,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122607596</v>
+        <v>122606677</v>
       </c>
       <c r="B45" t="n">
-        <v>56594</v>
+        <v>78657</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5553,43 +5553,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486109</v>
+        <v>485490</v>
       </c>
       <c r="R45" t="n">
-        <v>6790384</v>
+        <v>6790430</v>
       </c>
       <c r="S45" t="n">
         <v>9</v>
@@ -5621,7 +5616,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5631,7 +5626,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5658,7 +5653,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122606677</v>
+        <v>122606154</v>
       </c>
       <c r="B46" t="n">
         <v>78657</v>
@@ -5698,13 +5693,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>485490</v>
+        <v>485616</v>
       </c>
       <c r="R46" t="n">
-        <v>6790430</v>
+        <v>6790354</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5733,7 +5728,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5743,7 +5738,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5758,22 +5753,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122606154</v>
+        <v>122607596</v>
       </c>
       <c r="B47" t="n">
-        <v>78657</v>
+        <v>56594</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5782,41 +5777,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>485616</v>
+        <v>486109</v>
       </c>
       <c r="R47" t="n">
-        <v>6790354</v>
+        <v>6790384</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5870,12 +5870,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -7130,10 +7130,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122607719</v>
+        <v>122608903</v>
       </c>
       <c r="B59" t="n">
-        <v>78657</v>
+        <v>78394</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7146,37 +7146,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486157</v>
+        <v>486211</v>
       </c>
       <c r="R59" t="n">
-        <v>6790397</v>
+        <v>6790317</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7242,10 +7242,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122608903</v>
+        <v>122608928</v>
       </c>
       <c r="B60" t="n">
-        <v>78394</v>
+        <v>79275</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7258,21 +7258,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7282,13 +7282,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486211</v>
+        <v>486063</v>
       </c>
       <c r="R60" t="n">
-        <v>6790317</v>
+        <v>6790348</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7354,10 +7354,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122608928</v>
+        <v>122607719</v>
       </c>
       <c r="B61" t="n">
-        <v>79275</v>
+        <v>78657</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7370,37 +7370,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486063</v>
+        <v>486157</v>
       </c>
       <c r="R61" t="n">
-        <v>6790348</v>
+        <v>6790397</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -13676,6 +13676,8321 @@
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>122689596</v>
+      </c>
+      <c r="B119" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>485656</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6790462</v>
+      </c>
+      <c r="S119" t="n">
+        <v>5</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>122689899</v>
+      </c>
+      <c r="B120" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>485399</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6790454</v>
+      </c>
+      <c r="S120" t="n">
+        <v>5</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>122689904</v>
+      </c>
+      <c r="B121" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>485427</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6790445</v>
+      </c>
+      <c r="S121" t="n">
+        <v>5</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>122689611</v>
+      </c>
+      <c r="B122" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>485653</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6790460</v>
+      </c>
+      <c r="S122" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122689853</v>
+      </c>
+      <c r="B123" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>485439</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6790465</v>
+      </c>
+      <c r="S123" t="n">
+        <v>5</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>122689936</v>
+      </c>
+      <c r="B124" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>485535</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6790402</v>
+      </c>
+      <c r="S124" t="n">
+        <v>5</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>122689924</v>
+      </c>
+      <c r="B125" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>485489</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6790405</v>
+      </c>
+      <c r="S125" t="n">
+        <v>5</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>122689824</v>
+      </c>
+      <c r="B126" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>485497</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6790458</v>
+      </c>
+      <c r="S126" t="n">
+        <v>5</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>122689974</v>
+      </c>
+      <c r="B127" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>485719</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6790394</v>
+      </c>
+      <c r="S127" t="n">
+        <v>5</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>122689934</v>
+      </c>
+      <c r="B128" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>485527</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6790426</v>
+      </c>
+      <c r="S128" t="n">
+        <v>5</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>122689939</v>
+      </c>
+      <c r="B129" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>485533</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6790398</v>
+      </c>
+      <c r="S129" t="n">
+        <v>5</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>122689581</v>
+      </c>
+      <c r="B130" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>485671</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6790449</v>
+      </c>
+      <c r="S130" t="n">
+        <v>5</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>122689943</v>
+      </c>
+      <c r="B131" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>485590</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6790388</v>
+      </c>
+      <c r="S131" t="n">
+        <v>5</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>122689761</v>
+      </c>
+      <c r="B132" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>485563</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6790470</v>
+      </c>
+      <c r="S132" t="n">
+        <v>5</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>122689633</v>
+      </c>
+      <c r="B133" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>485624</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6790469</v>
+      </c>
+      <c r="S133" t="n">
+        <v>5</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>122689941</v>
+      </c>
+      <c r="B134" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>485558</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6790391</v>
+      </c>
+      <c r="S134" t="n">
+        <v>5</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>122689447</v>
+      </c>
+      <c r="B135" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>485729</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6790386</v>
+      </c>
+      <c r="S135" t="n">
+        <v>5</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF135" t="inlineStr"/>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>122689630</v>
+      </c>
+      <c r="B136" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>485638</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6790456</v>
+      </c>
+      <c r="S136" t="n">
+        <v>5</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>122689764</v>
+      </c>
+      <c r="B137" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>485560</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6790469</v>
+      </c>
+      <c r="S137" t="n">
+        <v>5</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>122689732</v>
+      </c>
+      <c r="B138" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>485601</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6790468</v>
+      </c>
+      <c r="S138" t="n">
+        <v>5</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>122689872</v>
+      </c>
+      <c r="B139" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>485412</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6790481</v>
+      </c>
+      <c r="S139" t="n">
+        <v>5</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>122689748</v>
+      </c>
+      <c r="B140" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>485586</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6790473</v>
+      </c>
+      <c r="S140" t="n">
+        <v>5</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>122689768</v>
+      </c>
+      <c r="B141" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>485537</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6790465</v>
+      </c>
+      <c r="S141" t="n">
+        <v>5</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>122689970</v>
+      </c>
+      <c r="B142" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>485704</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6790400</v>
+      </c>
+      <c r="S142" t="n">
+        <v>5</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>122689594</v>
+      </c>
+      <c r="B143" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>485662</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6790461</v>
+      </c>
+      <c r="S143" t="n">
+        <v>5</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>122689556</v>
+      </c>
+      <c r="B144" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>485678</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6790447</v>
+      </c>
+      <c r="S144" t="n">
+        <v>5</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>122689548</v>
+      </c>
+      <c r="B145" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>485686</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6790446</v>
+      </c>
+      <c r="S145" t="n">
+        <v>5</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>122689736</v>
+      </c>
+      <c r="B146" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>485597</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6790468</v>
+      </c>
+      <c r="S146" t="n">
+        <v>5</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>122689966</v>
+      </c>
+      <c r="B147" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>485678</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6790402</v>
+      </c>
+      <c r="S147" t="n">
+        <v>5</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>122689889</v>
+      </c>
+      <c r="B148" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>485406</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6790464</v>
+      </c>
+      <c r="S148" t="n">
+        <v>5</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>122689723</v>
+      </c>
+      <c r="B149" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>485609</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6790472</v>
+      </c>
+      <c r="S149" t="n">
+        <v>5</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>122689846</v>
+      </c>
+      <c r="B150" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>485443</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6790455</v>
+      </c>
+      <c r="S150" t="n">
+        <v>5</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>122689942</v>
+      </c>
+      <c r="B151" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>485554</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6790400</v>
+      </c>
+      <c r="S151" t="n">
+        <v>5</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>122689859</v>
+      </c>
+      <c r="B152" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>485425</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6790473</v>
+      </c>
+      <c r="S152" t="n">
+        <v>5</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>122689851</v>
+      </c>
+      <c r="B153" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>485442</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6790462</v>
+      </c>
+      <c r="S153" t="n">
+        <v>5</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>122689950</v>
+      </c>
+      <c r="B154" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>485623</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6790393</v>
+      </c>
+      <c r="S154" t="n">
+        <v>5</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>122689794</v>
+      </c>
+      <c r="B155" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>485529</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6790463</v>
+      </c>
+      <c r="S155" t="n">
+        <v>5</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>122689540</v>
+      </c>
+      <c r="B156" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>485689</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6790436</v>
+      </c>
+      <c r="S156" t="n">
+        <v>5</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>122689738</v>
+      </c>
+      <c r="B157" t="n">
+        <v>90857</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>485597</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6790468</v>
+      </c>
+      <c r="S157" t="n">
+        <v>5</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>122689928</v>
+      </c>
+      <c r="B158" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>485524</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6790423</v>
+      </c>
+      <c r="S158" t="n">
+        <v>5</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF158" t="inlineStr"/>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>122689963</v>
+      </c>
+      <c r="B159" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>485658</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6790402</v>
+      </c>
+      <c r="S159" t="n">
+        <v>5</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF159" t="inlineStr"/>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>122689911</v>
+      </c>
+      <c r="B160" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>485439</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6790444</v>
+      </c>
+      <c r="S160" t="n">
+        <v>5</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>122689619</v>
+      </c>
+      <c r="B161" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>485645</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6790451</v>
+      </c>
+      <c r="S161" t="n">
+        <v>5</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>122689842</v>
+      </c>
+      <c r="B162" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>485449</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6790454</v>
+      </c>
+      <c r="S162" t="n">
+        <v>5</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>122689865</v>
+      </c>
+      <c r="B163" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>485417</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6790479</v>
+      </c>
+      <c r="S163" t="n">
+        <v>5</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>122689349</v>
+      </c>
+      <c r="B164" t="n">
+        <v>56594</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>485774</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6790357</v>
+      </c>
+      <c r="S164" t="n">
+        <v>25</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>flög åt väster</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>122689879</v>
+      </c>
+      <c r="B165" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>485409</v>
+      </c>
+      <c r="R165" t="n">
+        <v>6790470</v>
+      </c>
+      <c r="S165" t="n">
+        <v>5</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF165" t="inlineStr"/>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>122689895</v>
+      </c>
+      <c r="B166" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>485405</v>
+      </c>
+      <c r="R166" t="n">
+        <v>6790460</v>
+      </c>
+      <c r="S166" t="n">
+        <v>5</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>122689593</v>
+      </c>
+      <c r="B167" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>485660</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6790454</v>
+      </c>
+      <c r="S167" t="n">
+        <v>5</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF167" t="inlineStr"/>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>122689714</v>
+      </c>
+      <c r="B168" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>485613</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6790471</v>
+      </c>
+      <c r="S168" t="n">
+        <v>5</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF168" t="inlineStr"/>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>122689753</v>
+      </c>
+      <c r="B169" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>485577</v>
+      </c>
+      <c r="R169" t="n">
+        <v>6790471</v>
+      </c>
+      <c r="S169" t="n">
+        <v>5</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF169" t="inlineStr"/>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>122689914</v>
+      </c>
+      <c r="B170" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>485447</v>
+      </c>
+      <c r="R170" t="n">
+        <v>6790434</v>
+      </c>
+      <c r="S170" t="n">
+        <v>5</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>122689811</v>
+      </c>
+      <c r="B171" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>485510</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6790462</v>
+      </c>
+      <c r="S171" t="n">
+        <v>5</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF171" t="inlineStr"/>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>122689892</v>
+      </c>
+      <c r="B172" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>485406</v>
+      </c>
+      <c r="R172" t="n">
+        <v>6790461</v>
+      </c>
+      <c r="S172" t="n">
+        <v>5</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF172" t="inlineStr"/>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>122689829</v>
+      </c>
+      <c r="B173" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>485469</v>
+      </c>
+      <c r="R173" t="n">
+        <v>6790456</v>
+      </c>
+      <c r="S173" t="n">
+        <v>5</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF173" t="inlineStr"/>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>122689718</v>
+      </c>
+      <c r="B174" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>485610</v>
+      </c>
+      <c r="R174" t="n">
+        <v>6790472</v>
+      </c>
+      <c r="S174" t="n">
+        <v>5</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF174" t="inlineStr"/>
+      <c r="AG174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>122689838</v>
+      </c>
+      <c r="B175" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>485452</v>
+      </c>
+      <c r="R175" t="n">
+        <v>6790453</v>
+      </c>
+      <c r="S175" t="n">
+        <v>5</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF175" t="inlineStr"/>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>122689833</v>
+      </c>
+      <c r="B176" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>485457</v>
+      </c>
+      <c r="R176" t="n">
+        <v>6790457</v>
+      </c>
+      <c r="S176" t="n">
+        <v>5</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF176" t="inlineStr"/>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>122689972</v>
+      </c>
+      <c r="B177" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>485718</v>
+      </c>
+      <c r="R177" t="n">
+        <v>6790397</v>
+      </c>
+      <c r="S177" t="n">
+        <v>5</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF177" t="inlineStr"/>
+      <c r="AG177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>122689725</v>
+      </c>
+      <c r="B178" t="n">
+        <v>57400</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>485609</v>
+      </c>
+      <c r="R178" t="n">
+        <v>6790472</v>
+      </c>
+      <c r="S178" t="n">
+        <v>5</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>122689806</v>
+      </c>
+      <c r="B179" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>485524</v>
+      </c>
+      <c r="R179" t="n">
+        <v>6790465</v>
+      </c>
+      <c r="S179" t="n">
+        <v>5</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF179" t="inlineStr"/>
+      <c r="AG179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>122689959</v>
+      </c>
+      <c r="B180" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>485627</v>
+      </c>
+      <c r="R180" t="n">
+        <v>6790392</v>
+      </c>
+      <c r="S180" t="n">
+        <v>5</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF180" t="inlineStr"/>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>122689819</v>
+      </c>
+      <c r="B181" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>485500</v>
+      </c>
+      <c r="R181" t="n">
+        <v>6790456</v>
+      </c>
+      <c r="S181" t="n">
+        <v>5</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF181" t="inlineStr"/>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>122689572</v>
+      </c>
+      <c r="B182" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>485672</v>
+      </c>
+      <c r="R182" t="n">
+        <v>6790447</v>
+      </c>
+      <c r="S182" t="n">
+        <v>5</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF182" t="inlineStr"/>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>122689677</v>
+      </c>
+      <c r="B183" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>485615</v>
+      </c>
+      <c r="R183" t="n">
+        <v>6790468</v>
+      </c>
+      <c r="S183" t="n">
+        <v>5</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF183" t="inlineStr"/>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>122689756</v>
+      </c>
+      <c r="B184" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>485576</v>
+      </c>
+      <c r="R184" t="n">
+        <v>6790471</v>
+      </c>
+      <c r="S184" t="n">
+        <v>5</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF184" t="inlineStr"/>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>122689566</v>
+      </c>
+      <c r="B185" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>485670</v>
+      </c>
+      <c r="R185" t="n">
+        <v>6790450</v>
+      </c>
+      <c r="S185" t="n">
+        <v>5</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF185" t="inlineStr"/>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>122689617</v>
+      </c>
+      <c r="B186" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>485646</v>
+      </c>
+      <c r="R186" t="n">
+        <v>6790453</v>
+      </c>
+      <c r="S186" t="n">
+        <v>5</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF186" t="inlineStr"/>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>122689918</v>
+      </c>
+      <c r="B187" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>485463</v>
+      </c>
+      <c r="R187" t="n">
+        <v>6790428</v>
+      </c>
+      <c r="S187" t="n">
+        <v>5</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF187" t="inlineStr"/>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>122689875</v>
+      </c>
+      <c r="B188" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>485410</v>
+      </c>
+      <c r="R188" t="n">
+        <v>6790478</v>
+      </c>
+      <c r="S188" t="n">
+        <v>5</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF188" t="inlineStr"/>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>122689519</v>
+      </c>
+      <c r="B189" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>485696</v>
+      </c>
+      <c r="R189" t="n">
+        <v>6790431</v>
+      </c>
+      <c r="S189" t="n">
+        <v>5</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF189" t="inlineStr"/>
+      <c r="AG189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>122689954</v>
+      </c>
+      <c r="B190" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>485626</v>
+      </c>
+      <c r="R190" t="n">
+        <v>6790391</v>
+      </c>
+      <c r="S190" t="n">
+        <v>5</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF190" t="inlineStr"/>
+      <c r="AG190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>122689855</v>
+      </c>
+      <c r="B191" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>485432</v>
+      </c>
+      <c r="R191" t="n">
+        <v>6790469</v>
+      </c>
+      <c r="S191" t="n">
+        <v>5</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF191" t="inlineStr"/>
+      <c r="AG191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>122689863</v>
+      </c>
+      <c r="B192" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>485420</v>
+      </c>
+      <c r="R192" t="n">
+        <v>6790476</v>
+      </c>
+      <c r="S192" t="n">
+        <v>5</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF192" t="inlineStr"/>
+      <c r="AG192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>122689626</v>
+      </c>
+      <c r="B193" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>485638</v>
+      </c>
+      <c r="R193" t="n">
+        <v>6790452</v>
+      </c>
+      <c r="S193" t="n">
+        <v>5</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF193" t="inlineStr"/>
+      <c r="AG193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>122689743</v>
+      </c>
+      <c r="B194" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>485588</v>
+      </c>
+      <c r="R194" t="n">
+        <v>6790473</v>
+      </c>
+      <c r="S194" t="n">
+        <v>5</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF194" t="inlineStr"/>
+      <c r="AG194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>122689882</v>
+      </c>
+      <c r="B195" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>485408</v>
+      </c>
+      <c r="R195" t="n">
+        <v>6790469</v>
+      </c>
+      <c r="S195" t="n">
+        <v>5</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF195" t="inlineStr"/>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>122689920</v>
+      </c>
+      <c r="B196" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>N Lindflot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>485472</v>
+      </c>
+      <c r="R196" t="n">
+        <v>6790425</v>
+      </c>
+      <c r="S196" t="n">
+        <v>5</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF196" t="inlineStr"/>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122606669</v>
+        <v>122606208</v>
       </c>
       <c r="B2" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485407</v>
+        <v>485592</v>
       </c>
       <c r="R2" t="n">
-        <v>6790437</v>
+        <v>6790353</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122606394</v>
+        <v>122608856</v>
       </c>
       <c r="B3" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485411</v>
+        <v>486343</v>
       </c>
       <c r="R3" t="n">
-        <v>6790441</v>
+        <v>6790373</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122607558</v>
+        <v>122608792</v>
       </c>
       <c r="B4" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122607224</v>
+        <v>122606708</v>
       </c>
       <c r="B5" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,46 +1023,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485981</v>
+        <v>485568</v>
       </c>
       <c r="R5" t="n">
-        <v>6790453</v>
+        <v>6790397</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122606651</v>
+        <v>122606145</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485432</v>
+        <v>485616</v>
       </c>
       <c r="R6" t="n">
-        <v>6790417</v>
+        <v>6790356</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,22 +1223,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122608705</v>
+        <v>122607014</v>
       </c>
       <c r="B7" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,17 +1271,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485504</v>
+        <v>485706</v>
       </c>
       <c r="R7" t="n">
-        <v>6790441</v>
+        <v>6790427</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,22 +1335,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122608832</v>
+        <v>122607400</v>
       </c>
       <c r="B8" t="n">
-        <v>78394</v>
+        <v>78660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1427,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122606955</v>
+        <v>122608158</v>
       </c>
       <c r="B9" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,14 +1495,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485759</v>
+        <v>486281</v>
       </c>
       <c r="R9" t="n">
-        <v>6790467</v>
+        <v>6790441</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1539,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1544,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122606286</v>
+        <v>122608694</v>
       </c>
       <c r="B10" t="n">
-        <v>78657</v>
+        <v>56594</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,41 +1588,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485541</v>
+        <v>486035</v>
       </c>
       <c r="R10" t="n">
-        <v>6790372</v>
+        <v>6790401</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,12 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På 3 tallar på stammen</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,22 +1676,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122608158</v>
+        <v>122607596</v>
       </c>
       <c r="B11" t="n">
-        <v>78657</v>
+        <v>56594</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,38 +1700,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486281</v>
+        <v>486109</v>
       </c>
       <c r="R11" t="n">
-        <v>6790441</v>
+        <v>6790384</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,12 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122607048</v>
+        <v>122609017</v>
       </c>
       <c r="B12" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,14 +1841,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485855</v>
+        <v>486064</v>
       </c>
       <c r="R12" t="n">
-        <v>6790443</v>
+        <v>6790364</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1885,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122606452</v>
+        <v>122608902</v>
       </c>
       <c r="B13" t="n">
-        <v>78657</v>
+        <v>78397</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,34 +1933,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485428</v>
+        <v>486280</v>
       </c>
       <c r="R13" t="n">
-        <v>6790393</v>
+        <v>6790345</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -1997,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606946</v>
+        <v>122606171</v>
       </c>
       <c r="B14" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2074,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485706</v>
+        <v>485662</v>
       </c>
       <c r="R14" t="n">
-        <v>6790427</v>
+        <v>6790357</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2109,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,7 +2141,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122607446</v>
+        <v>122607224</v>
       </c>
       <c r="B15" t="n">
         <v>56594</v>
@@ -2191,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486045</v>
+        <v>485981</v>
       </c>
       <c r="R15" t="n">
-        <v>6790383</v>
+        <v>6790453</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2226,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122607495</v>
+        <v>122608832</v>
       </c>
       <c r="B16" t="n">
-        <v>78657</v>
+        <v>78397</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,21 +2274,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2303,13 +2298,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486056</v>
+        <v>485504</v>
       </c>
       <c r="R16" t="n">
-        <v>6790394</v>
+        <v>6790441</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2338,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,22 +2358,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122606139</v>
+        <v>122606131</v>
       </c>
       <c r="B17" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2411,17 +2406,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485662</v>
+        <v>485629</v>
       </c>
       <c r="R17" t="n">
-        <v>6790357</v>
+        <v>6790369</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2450,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2455,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2475,22 +2470,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122608892</v>
+        <v>122606108</v>
       </c>
       <c r="B18" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2523,17 +2518,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486035</v>
+        <v>485649</v>
       </c>
       <c r="R18" t="n">
-        <v>6790401</v>
+        <v>6790375</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2562,7 +2557,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2567,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2587,22 +2582,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122607713</v>
+        <v>122606452</v>
       </c>
       <c r="B19" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,10 +2634,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486156</v>
+        <v>485428</v>
       </c>
       <c r="R19" t="n">
-        <v>6790429</v>
+        <v>6790393</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2674,7 +2669,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2679,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122607160</v>
+        <v>122607953</v>
       </c>
       <c r="B20" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2723,25 +2718,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2751,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>485961</v>
+        <v>486214</v>
       </c>
       <c r="R20" t="n">
-        <v>6790453</v>
+        <v>6790429</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2786,7 +2781,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2796,7 +2791,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,10 +2818,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122606145</v>
+        <v>122607915</v>
       </c>
       <c r="B21" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2863,13 +2858,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>485616</v>
+        <v>486193</v>
       </c>
       <c r="R21" t="n">
-        <v>6790356</v>
+        <v>6790410</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2898,7 +2893,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,7 +2903,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2923,22 +2918,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122606653</v>
+        <v>122606677</v>
       </c>
       <c r="B22" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2971,17 +2966,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>485568</v>
+        <v>485490</v>
       </c>
       <c r="R22" t="n">
-        <v>6790397</v>
+        <v>6790430</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3010,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,22 +3030,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122607941</v>
+        <v>122606807</v>
       </c>
       <c r="B23" t="n">
-        <v>78393</v>
+        <v>78660</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,21 +3058,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3087,13 +3082,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>485504</v>
+        <v>485749</v>
       </c>
       <c r="R23" t="n">
-        <v>6790441</v>
+        <v>6790424</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3122,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3147,22 +3142,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122606204</v>
+        <v>122608938</v>
       </c>
       <c r="B24" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3195,17 +3190,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>485615</v>
+        <v>486253</v>
       </c>
       <c r="R24" t="n">
-        <v>6790353</v>
+        <v>6790356</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3234,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3239,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,22 +3254,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122608844</v>
+        <v>122607107</v>
       </c>
       <c r="B25" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3307,14 +3302,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486338</v>
+        <v>485855</v>
       </c>
       <c r="R25" t="n">
-        <v>6790352</v>
+        <v>6790443</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3346,7 +3341,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3356,12 +3351,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,10 +3378,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122606977</v>
+        <v>122606230</v>
       </c>
       <c r="B26" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3428,10 +3418,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>485766</v>
+        <v>485561</v>
       </c>
       <c r="R26" t="n">
-        <v>6790457</v>
+        <v>6790367</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3463,7 +3453,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3473,12 +3463,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3505,10 +3490,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122607974</v>
+        <v>122606669</v>
       </c>
       <c r="B27" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3545,13 +3530,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486212</v>
+        <v>485407</v>
       </c>
       <c r="R27" t="n">
-        <v>6790432</v>
+        <v>6790437</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3580,7 +3565,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3590,7 +3575,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3605,22 +3590,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122607254</v>
+        <v>122607995</v>
       </c>
       <c r="B28" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3657,10 +3642,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486016</v>
+        <v>486213</v>
       </c>
       <c r="R28" t="n">
-        <v>6790443</v>
+        <v>6790435</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3692,7 +3677,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3702,7 +3687,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,10 +3714,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122606408</v>
+        <v>122608110</v>
       </c>
       <c r="B29" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3765,17 +3750,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>485407</v>
+        <v>486270</v>
       </c>
       <c r="R29" t="n">
-        <v>6790439</v>
+        <v>6790427</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3804,7 +3789,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3814,7 +3799,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3829,22 +3814,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122606339</v>
+        <v>122608828</v>
       </c>
       <c r="B30" t="n">
-        <v>78657</v>
+        <v>78396</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3857,21 +3842,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3881,13 +3866,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>485528</v>
+        <v>485504</v>
       </c>
       <c r="R30" t="n">
-        <v>6790365</v>
+        <v>6790441</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3916,7 +3901,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3926,7 +3911,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3941,22 +3926,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122606919</v>
+        <v>122606235</v>
       </c>
       <c r="B31" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3993,13 +3978,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>485753</v>
+        <v>485615</v>
       </c>
       <c r="R31" t="n">
-        <v>6790423</v>
+        <v>6790353</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4028,7 +4013,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4023,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4053,22 +4038,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122607141</v>
+        <v>122606651</v>
       </c>
       <c r="B32" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4077,43 +4062,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>485906</v>
+        <v>485432</v>
       </c>
       <c r="R32" t="n">
-        <v>6790433</v>
+        <v>6790417</v>
       </c>
       <c r="S32" t="n">
         <v>9</v>
@@ -4145,7 +4125,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4155,7 +4135,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122608061</v>
+        <v>122606919</v>
       </c>
       <c r="B33" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4222,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486229</v>
+        <v>485753</v>
       </c>
       <c r="R33" t="n">
-        <v>6790440</v>
+        <v>6790423</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -4257,7 +4237,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4267,12 +4247,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4299,10 +4274,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122607118</v>
+        <v>122607160</v>
       </c>
       <c r="B34" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4311,43 +4286,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485884</v>
+        <v>485961</v>
       </c>
       <c r="R34" t="n">
-        <v>6790450</v>
+        <v>6790453</v>
       </c>
       <c r="S34" t="n">
         <v>9</v>
@@ -4379,7 +4349,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4389,7 +4359,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4416,10 +4386,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122606176</v>
+        <v>122606286</v>
       </c>
       <c r="B35" t="n">
-        <v>78683</v>
+        <v>78660</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4428,25 +4398,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4456,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485613</v>
+        <v>485541</v>
       </c>
       <c r="R35" t="n">
-        <v>6790370</v>
+        <v>6790372</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
@@ -4491,7 +4461,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4501,7 +4471,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På 3 tallar på stammen</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4528,10 +4503,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122608110</v>
+        <v>122607518</v>
       </c>
       <c r="B36" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4564,14 +4539,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486270</v>
+        <v>486071</v>
       </c>
       <c r="R36" t="n">
-        <v>6790427</v>
+        <v>6790384</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -4603,7 +4578,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4613,7 +4588,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4640,10 +4615,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122606271</v>
+        <v>122607974</v>
       </c>
       <c r="B37" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4680,10 +4655,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>485553</v>
+        <v>486212</v>
       </c>
       <c r="R37" t="n">
-        <v>6790369</v>
+        <v>6790432</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -4715,7 +4690,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4725,7 +4700,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4752,10 +4727,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122606131</v>
+        <v>122606417</v>
       </c>
       <c r="B38" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4792,13 +4767,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>485629</v>
+        <v>485407</v>
       </c>
       <c r="R38" t="n">
-        <v>6790369</v>
+        <v>6790439</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4827,7 +4802,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4837,7 +4812,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4852,22 +4827,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122608902</v>
+        <v>122607446</v>
       </c>
       <c r="B39" t="n">
-        <v>78394</v>
+        <v>56594</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4876,38 +4851,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486280</v>
+        <v>486045</v>
       </c>
       <c r="R39" t="n">
-        <v>6790345</v>
+        <v>6790383</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
@@ -4939,7 +4919,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4949,7 +4929,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4976,10 +4956,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122606208</v>
+        <v>122606271</v>
       </c>
       <c r="B40" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4988,25 +4968,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5016,10 +4996,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>485592</v>
+        <v>485553</v>
       </c>
       <c r="R40" t="n">
-        <v>6790353</v>
+        <v>6790369</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -5051,7 +5031,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5061,7 +5041,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5088,10 +5068,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122608938</v>
+        <v>122608990</v>
       </c>
       <c r="B41" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5128,10 +5108,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486253</v>
+        <v>486070</v>
       </c>
       <c r="R41" t="n">
-        <v>6790356</v>
+        <v>6790363</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5163,7 +5143,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5173,7 +5153,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5200,10 +5180,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122608651</v>
+        <v>122607118</v>
       </c>
       <c r="B42" t="n">
-        <v>78657</v>
+        <v>56594</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5212,38 +5192,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486380</v>
+        <v>485884</v>
       </c>
       <c r="R42" t="n">
-        <v>6790321</v>
+        <v>6790450</v>
       </c>
       <c r="S42" t="n">
         <v>9</v>
@@ -5275,7 +5260,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5285,12 +5270,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5317,10 +5297,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122609017</v>
+        <v>122607254</v>
       </c>
       <c r="B43" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5353,14 +5333,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486064</v>
+        <v>486016</v>
       </c>
       <c r="R43" t="n">
-        <v>6790364</v>
+        <v>6790443</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5392,7 +5372,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5402,7 +5382,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5429,10 +5409,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122608926</v>
+        <v>122606977</v>
       </c>
       <c r="B44" t="n">
-        <v>78393</v>
+        <v>78660</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5445,34 +5425,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486252</v>
+        <v>485766</v>
       </c>
       <c r="R44" t="n">
-        <v>6790351</v>
+        <v>6790457</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -5504,7 +5484,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5514,7 +5494,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5541,10 +5526,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122606677</v>
+        <v>122607141</v>
       </c>
       <c r="B45" t="n">
-        <v>78657</v>
+        <v>56594</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5553,38 +5538,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>485490</v>
+        <v>485906</v>
       </c>
       <c r="R45" t="n">
-        <v>6790430</v>
+        <v>6790433</v>
       </c>
       <c r="S45" t="n">
         <v>9</v>
@@ -5616,7 +5606,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5626,7 +5616,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5653,10 +5643,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122606154</v>
+        <v>122607495</v>
       </c>
       <c r="B46" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5693,13 +5683,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>485616</v>
+        <v>486056</v>
       </c>
       <c r="R46" t="n">
-        <v>6790354</v>
+        <v>6790394</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5728,7 +5718,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5738,7 +5728,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5753,22 +5743,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122607596</v>
+        <v>122606176</v>
       </c>
       <c r="B47" t="n">
-        <v>56594</v>
+        <v>78686</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5781,39 +5771,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486109</v>
+        <v>485613</v>
       </c>
       <c r="R47" t="n">
-        <v>6790384</v>
+        <v>6790370</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5845,7 +5830,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5855,7 +5840,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5882,10 +5867,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122607915</v>
+        <v>122607713</v>
       </c>
       <c r="B48" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5922,10 +5907,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486193</v>
+        <v>486156</v>
       </c>
       <c r="R48" t="n">
-        <v>6790410</v>
+        <v>6790429</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5957,7 +5942,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5967,7 +5952,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5994,10 +5979,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122606807</v>
+        <v>122606955</v>
       </c>
       <c r="B49" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6034,10 +6019,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>485749</v>
+        <v>485759</v>
       </c>
       <c r="R49" t="n">
-        <v>6790424</v>
+        <v>6790467</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -6069,7 +6054,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6079,7 +6064,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6106,10 +6091,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122608856</v>
+        <v>122608844</v>
       </c>
       <c r="B50" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6118,25 +6103,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6146,10 +6131,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486343</v>
+        <v>486338</v>
       </c>
       <c r="R50" t="n">
-        <v>6790373</v>
+        <v>6790352</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -6181,7 +6166,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6191,7 +6176,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6218,10 +6208,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122608990</v>
+        <v>122606394</v>
       </c>
       <c r="B51" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6254,17 +6244,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486070</v>
+        <v>485411</v>
       </c>
       <c r="R51" t="n">
-        <v>6790363</v>
+        <v>6790441</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6293,7 +6283,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6303,7 +6293,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6318,22 +6308,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122607995</v>
+        <v>122606339</v>
       </c>
       <c r="B52" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6370,10 +6360,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486213</v>
+        <v>485528</v>
       </c>
       <c r="R52" t="n">
-        <v>6790435</v>
+        <v>6790365</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6405,7 +6395,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6415,7 +6405,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6442,10 +6432,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122606108</v>
+        <v>122608061</v>
       </c>
       <c r="B53" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6482,10 +6472,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>485649</v>
+        <v>486229</v>
       </c>
       <c r="R53" t="n">
-        <v>6790375</v>
+        <v>6790440</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6517,7 +6507,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6527,7 +6517,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6554,10 +6549,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122607518</v>
+        <v>122608651</v>
       </c>
       <c r="B54" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6590,14 +6585,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486071</v>
+        <v>486380</v>
       </c>
       <c r="R54" t="n">
-        <v>6790384</v>
+        <v>6790321</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6629,7 +6624,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6634,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6666,10 +6666,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122606230</v>
+        <v>122606154</v>
       </c>
       <c r="B55" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6706,13 +6706,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>485561</v>
+        <v>485616</v>
       </c>
       <c r="R55" t="n">
-        <v>6790367</v>
+        <v>6790354</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6766,22 +6766,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122607953</v>
+        <v>122608926</v>
       </c>
       <c r="B56" t="n">
-        <v>8441</v>
+        <v>78396</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6790,38 +6790,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486214</v>
+        <v>486252</v>
       </c>
       <c r="R56" t="n">
-        <v>6790429</v>
+        <v>6790351</v>
       </c>
       <c r="S56" t="n">
         <v>9</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6890,10 +6890,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122606760</v>
+        <v>122607273</v>
       </c>
       <c r="B57" t="n">
-        <v>57400</v>
+        <v>8441</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6902,33 +6902,34 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -6938,10 +6939,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>485504</v>
+        <v>485932</v>
       </c>
       <c r="R57" t="n">
-        <v>6790441</v>
+        <v>6790416</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6973,7 +6974,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6983,7 +6984,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6992,28 +6993,29 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122608713</v>
+        <v>122606247</v>
       </c>
       <c r="B58" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7022,49 +7024,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485504</v>
+        <v>485626</v>
       </c>
       <c r="R58" t="n">
-        <v>6790441</v>
+        <v>6790401</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7093,7 +7087,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7103,7 +7097,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7118,22 +7112,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122608903</v>
+        <v>122608724</v>
       </c>
       <c r="B59" t="n">
-        <v>78394</v>
+        <v>78660</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7146,21 +7140,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7205,7 +7199,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7215,7 +7209,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7242,10 +7236,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122608928</v>
+        <v>122607038</v>
       </c>
       <c r="B60" t="n">
-        <v>79275</v>
+        <v>78660</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7258,34 +7252,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486063</v>
+        <v>485772</v>
       </c>
       <c r="R60" t="n">
-        <v>6790348</v>
+        <v>6790421</v>
       </c>
       <c r="S60" t="n">
         <v>9</v>
@@ -7317,7 +7311,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7327,7 +7321,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7354,10 +7348,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122607719</v>
+        <v>122606760</v>
       </c>
       <c r="B61" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7370,37 +7364,45 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486157</v>
+        <v>485504</v>
       </c>
       <c r="R61" t="n">
-        <v>6790397</v>
+        <v>6790441</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7429,7 +7431,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7439,7 +7441,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7454,22 +7456,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122606247</v>
+        <v>122608142</v>
       </c>
       <c r="B62" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7502,14 +7504,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>485626</v>
+        <v>486240</v>
       </c>
       <c r="R62" t="n">
-        <v>6790401</v>
+        <v>6790382</v>
       </c>
       <c r="S62" t="n">
         <v>9</v>
@@ -7541,7 +7543,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7551,7 +7553,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7578,10 +7580,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122609008</v>
+        <v>122606642</v>
       </c>
       <c r="B63" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7614,17 +7616,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486063</v>
+        <v>485586</v>
       </c>
       <c r="R63" t="n">
-        <v>6790348</v>
+        <v>6790395</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7653,7 +7655,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7663,7 +7665,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7690,10 +7692,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122608724</v>
+        <v>122607688</v>
       </c>
       <c r="B64" t="n">
-        <v>78657</v>
+        <v>90857</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7706,37 +7708,41 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486211</v>
+        <v>486156</v>
       </c>
       <c r="R64" t="n">
-        <v>6790317</v>
+        <v>6790429</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7765,7 +7771,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7775,7 +7781,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7790,22 +7796,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122606143</v>
+        <v>122608643</v>
       </c>
       <c r="B65" t="n">
-        <v>78657</v>
+        <v>56594</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7814,41 +7820,49 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>485681</v>
+        <v>485504</v>
       </c>
       <c r="R65" t="n">
-        <v>6790440</v>
+        <v>6790441</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7877,7 +7891,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7887,7 +7901,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7902,22 +7916,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122606642</v>
+        <v>122609064</v>
       </c>
       <c r="B66" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7926,41 +7940,50 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>485586</v>
+        <v>486063</v>
       </c>
       <c r="R66" t="n">
-        <v>6790395</v>
+        <v>6790348</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7989,7 +8012,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7999,7 +8022,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8008,6 +8031,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8029,7 +8053,7 @@
         <v>122607445</v>
       </c>
       <c r="B67" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8138,10 +8162,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122609064</v>
+        <v>122608903</v>
       </c>
       <c r="B68" t="n">
-        <v>8441</v>
+        <v>78397</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8150,47 +8174,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486063</v>
+        <v>486211</v>
       </c>
       <c r="R68" t="n">
-        <v>6790348</v>
+        <v>6790317</v>
       </c>
       <c r="S68" t="n">
         <v>8</v>
@@ -8222,7 +8237,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8232,7 +8247,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8241,7 +8256,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8260,10 +8274,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122607038</v>
+        <v>122606143</v>
       </c>
       <c r="B69" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8300,10 +8314,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>485772</v>
+        <v>485681</v>
       </c>
       <c r="R69" t="n">
-        <v>6790421</v>
+        <v>6790440</v>
       </c>
       <c r="S69" t="n">
         <v>9</v>
@@ -8335,7 +8349,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8345,7 +8359,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8372,10 +8386,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122608142</v>
+        <v>122607216</v>
       </c>
       <c r="B70" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8384,41 +8398,50 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486240</v>
+        <v>485504</v>
       </c>
       <c r="R70" t="n">
-        <v>6790382</v>
+        <v>6790441</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8447,7 +8470,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8457,7 +8480,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8466,28 +8489,29 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122607273</v>
+        <v>122608928</v>
       </c>
       <c r="B71" t="n">
-        <v>8441</v>
+        <v>79278</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8496,50 +8520,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>485932</v>
+        <v>486063</v>
       </c>
       <c r="R71" t="n">
-        <v>6790416</v>
+        <v>6790348</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8568,7 +8583,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8578,7 +8593,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8587,7 +8602,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8606,10 +8620,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122607688</v>
+        <v>122609008</v>
       </c>
       <c r="B72" t="n">
-        <v>90854</v>
+        <v>78660</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8622,41 +8636,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486156</v>
+        <v>486063</v>
       </c>
       <c r="R72" t="n">
-        <v>6790429</v>
+        <v>6790348</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8685,7 +8695,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8695,7 +8705,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8710,22 +8720,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122606756</v>
+        <v>122607719</v>
       </c>
       <c r="B73" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8734,50 +8744,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>485504</v>
+        <v>486157</v>
       </c>
       <c r="R73" t="n">
-        <v>6790441</v>
+        <v>6790397</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8806,7 +8807,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8816,7 +8817,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8825,19 +8826,18 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122671610</v>
+        <v>122671608</v>
       </c>
       <c r="B75" t="n">
-        <v>78393</v>
+        <v>79278</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8980,21 +8980,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9070,10 +9070,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122671569</v>
+        <v>122671440</v>
       </c>
       <c r="B76" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9113,10 +9113,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>485951</v>
+        <v>485819</v>
       </c>
       <c r="R76" t="n">
-        <v>6790408</v>
+        <v>6790340</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9176,10 +9176,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122671453</v>
+        <v>122671681</v>
       </c>
       <c r="B77" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9188,30 +9188,36 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9219,13 +9225,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>485835</v>
+        <v>486342</v>
       </c>
       <c r="R77" t="n">
-        <v>6790356</v>
+        <v>6790369</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9282,10 +9288,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122671541</v>
+        <v>122671595</v>
       </c>
       <c r="B78" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9294,36 +9300,30 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9331,10 +9331,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>485879</v>
+        <v>485984</v>
       </c>
       <c r="R78" t="n">
-        <v>6790409</v>
+        <v>6790370</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9394,10 +9394,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122671659</v>
+        <v>122671534</v>
       </c>
       <c r="B79" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9406,36 +9406,30 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9443,10 +9437,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486020</v>
+        <v>485901</v>
       </c>
       <c r="R79" t="n">
-        <v>6790412</v>
+        <v>6790392</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9506,10 +9500,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122671536</v>
+        <v>122671519</v>
       </c>
       <c r="B80" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9549,10 +9543,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>485910</v>
+        <v>485876</v>
       </c>
       <c r="R80" t="n">
-        <v>6790394</v>
+        <v>6790381</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9612,10 +9606,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122671564</v>
+        <v>122671453</v>
       </c>
       <c r="B81" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9655,10 +9649,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>485933</v>
+        <v>485835</v>
       </c>
       <c r="R81" t="n">
-        <v>6790411</v>
+        <v>6790356</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9718,10 +9712,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122671879</v>
+        <v>122671651</v>
       </c>
       <c r="B82" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9730,35 +9724,30 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9766,13 +9755,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486429</v>
+        <v>486048</v>
       </c>
       <c r="R82" t="n">
-        <v>6790399</v>
+        <v>6790360</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9804,17 +9793,13 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>på ett par platser intill granar</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9833,10 +9818,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122671424</v>
+        <v>122671434</v>
       </c>
       <c r="B83" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9876,10 +9861,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>485783</v>
+        <v>485799</v>
       </c>
       <c r="R83" t="n">
-        <v>6790367</v>
+        <v>6790349</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9939,10 +9924,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122671570</v>
+        <v>122671378</v>
       </c>
       <c r="B84" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9982,10 +9967,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>485953</v>
+        <v>485757</v>
       </c>
       <c r="R84" t="n">
-        <v>6790411</v>
+        <v>6790379</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10045,10 +10030,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122671608</v>
+        <v>122671679</v>
       </c>
       <c r="B85" t="n">
-        <v>79275</v>
+        <v>78660</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10061,21 +10046,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10088,13 +10073,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486013</v>
+        <v>486342</v>
       </c>
       <c r="R85" t="n">
-        <v>6790366</v>
+        <v>6790369</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10151,10 +10136,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122671674</v>
+        <v>122671422</v>
       </c>
       <c r="B86" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10194,13 +10179,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486266</v>
+        <v>485784</v>
       </c>
       <c r="R86" t="n">
-        <v>6790373</v>
+        <v>6790390</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10257,10 +10242,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122671493</v>
+        <v>122671668</v>
       </c>
       <c r="B87" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10300,13 +10285,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>485859</v>
+        <v>486079</v>
       </c>
       <c r="R87" t="n">
-        <v>6790362</v>
+        <v>6790394</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10363,10 +10348,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122671523</v>
+        <v>122671667</v>
       </c>
       <c r="B88" t="n">
-        <v>57537</v>
+        <v>78694</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10379,31 +10364,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10411,13 +10391,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>485893</v>
+        <v>486043</v>
       </c>
       <c r="R88" t="n">
-        <v>6790386</v>
+        <v>6790416</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10455,6 +10435,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10473,10 +10454,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122671679</v>
+        <v>122671536</v>
       </c>
       <c r="B89" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10516,13 +10497,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486342</v>
+        <v>485910</v>
       </c>
       <c r="R89" t="n">
-        <v>6790369</v>
+        <v>6790394</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10579,10 +10560,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122671575</v>
+        <v>122671541</v>
       </c>
       <c r="B90" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10591,30 +10572,36 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10622,10 +10609,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>485989</v>
+        <v>485879</v>
       </c>
       <c r="R90" t="n">
-        <v>6790394</v>
+        <v>6790409</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10685,10 +10672,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122671506</v>
+        <v>122671888</v>
       </c>
       <c r="B91" t="n">
-        <v>78657</v>
+        <v>56594</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10697,30 +10684,35 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10728,10 +10720,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>485861</v>
+        <v>485897</v>
       </c>
       <c r="R91" t="n">
-        <v>6790364</v>
+        <v>6790441</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10766,13 +10758,17 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>under betestall rikligt</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10791,10 +10787,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122671512</v>
+        <v>122671609</v>
       </c>
       <c r="B92" t="n">
-        <v>78657</v>
+        <v>78397</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10807,21 +10803,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10834,10 +10830,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>485876</v>
+        <v>486013</v>
       </c>
       <c r="R92" t="n">
-        <v>6790371</v>
+        <v>6790366</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10897,10 +10893,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122671647</v>
+        <v>122671570</v>
       </c>
       <c r="B93" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10940,13 +10936,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>486035</v>
+        <v>485953</v>
       </c>
       <c r="R93" t="n">
-        <v>6790369</v>
+        <v>6790411</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11003,10 +10999,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122671675</v>
+        <v>122671674</v>
       </c>
       <c r="B94" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11046,10 +11042,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>486331</v>
+        <v>486266</v>
       </c>
       <c r="R94" t="n">
-        <v>6790370</v>
+        <v>6790373</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11109,10 +11105,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122671609</v>
+        <v>122671569</v>
       </c>
       <c r="B95" t="n">
-        <v>78394</v>
+        <v>78660</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11125,21 +11121,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11152,10 +11148,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>486013</v>
+        <v>485951</v>
       </c>
       <c r="R95" t="n">
-        <v>6790366</v>
+        <v>6790408</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11215,10 +11211,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122671587</v>
+        <v>122671879</v>
       </c>
       <c r="B96" t="n">
-        <v>79275</v>
+        <v>56594</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11227,30 +11223,35 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -11258,10 +11259,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>485985</v>
+        <v>486429</v>
       </c>
       <c r="R96" t="n">
-        <v>6790379</v>
+        <v>6790399</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11296,13 +11297,17 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>på ett par platser intill granar</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11321,10 +11326,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122671508</v>
+        <v>122671575</v>
       </c>
       <c r="B97" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11364,10 +11369,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>485871</v>
+        <v>485989</v>
       </c>
       <c r="R97" t="n">
-        <v>6790368</v>
+        <v>6790394</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11427,10 +11432,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122671579</v>
+        <v>122671647</v>
       </c>
       <c r="B98" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11470,13 +11475,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>485989</v>
+        <v>486035</v>
       </c>
       <c r="R98" t="n">
-        <v>6790378</v>
+        <v>6790369</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11533,10 +11538,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122671384</v>
+        <v>122671521</v>
       </c>
       <c r="B99" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11576,10 +11581,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>485777</v>
+        <v>485893</v>
       </c>
       <c r="R99" t="n">
-        <v>6790392</v>
+        <v>6790386</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11639,10 +11644,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122671668</v>
+        <v>122671592</v>
       </c>
       <c r="B100" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11682,13 +11687,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>486079</v>
+        <v>485984</v>
       </c>
       <c r="R100" t="n">
-        <v>6790394</v>
+        <v>6790371</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11745,10 +11750,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122671422</v>
+        <v>122671384</v>
       </c>
       <c r="B101" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11788,10 +11793,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>485784</v>
+        <v>485777</v>
       </c>
       <c r="R101" t="n">
-        <v>6790390</v>
+        <v>6790392</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11851,10 +11856,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122671378</v>
+        <v>122671512</v>
       </c>
       <c r="B102" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11894,10 +11899,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>485757</v>
+        <v>485876</v>
       </c>
       <c r="R102" t="n">
-        <v>6790379</v>
+        <v>6790371</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11957,10 +11962,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122671521</v>
+        <v>122671564</v>
       </c>
       <c r="B103" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12000,10 +12005,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>485893</v>
+        <v>485933</v>
       </c>
       <c r="R103" t="n">
-        <v>6790386</v>
+        <v>6790411</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12063,10 +12068,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122671888</v>
+        <v>122671508</v>
       </c>
       <c r="B104" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12075,35 +12080,30 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12111,10 +12111,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>485897</v>
+        <v>485871</v>
       </c>
       <c r="R104" t="n">
-        <v>6790441</v>
+        <v>6790368</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12149,17 +12149,13 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>under betestall rikligt</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -12178,10 +12174,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122671555</v>
+        <v>122671658</v>
       </c>
       <c r="B105" t="n">
-        <v>78657</v>
+        <v>57537</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12194,26 +12190,31 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -12221,10 +12222,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>485915</v>
+        <v>486037</v>
       </c>
       <c r="R105" t="n">
-        <v>6790407</v>
+        <v>6790372</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12265,7 +12266,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -12284,10 +12284,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122671595</v>
+        <v>122671659</v>
       </c>
       <c r="B106" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12296,30 +12296,36 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -12327,10 +12333,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>485984</v>
+        <v>486020</v>
       </c>
       <c r="R106" t="n">
-        <v>6790370</v>
+        <v>6790412</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12390,10 +12396,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122671658</v>
+        <v>122671587</v>
       </c>
       <c r="B107" t="n">
-        <v>57537</v>
+        <v>79278</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12406,31 +12412,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -12438,10 +12439,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>486037</v>
+        <v>485985</v>
       </c>
       <c r="R107" t="n">
-        <v>6790372</v>
+        <v>6790379</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12482,6 +12483,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -12500,10 +12502,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122671534</v>
+        <v>122671506</v>
       </c>
       <c r="B108" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12543,10 +12545,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>485901</v>
+        <v>485861</v>
       </c>
       <c r="R108" t="n">
-        <v>6790392</v>
+        <v>6790364</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12606,10 +12608,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122671681</v>
+        <v>122671610</v>
       </c>
       <c r="B109" t="n">
-        <v>8441</v>
+        <v>78396</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12618,36 +12620,30 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -12655,13 +12651,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>486342</v>
+        <v>486013</v>
       </c>
       <c r="R109" t="n">
-        <v>6790369</v>
+        <v>6790366</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12718,10 +12714,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122671651</v>
+        <v>122671447</v>
       </c>
       <c r="B110" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12761,13 +12757,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>486048</v>
+        <v>485830</v>
       </c>
       <c r="R110" t="n">
-        <v>6790360</v>
+        <v>6790346</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12824,10 +12820,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122671447</v>
+        <v>122671523</v>
       </c>
       <c r="B111" t="n">
-        <v>78657</v>
+        <v>57537</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12840,26 +12836,31 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12867,10 +12868,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>485830</v>
+        <v>485893</v>
       </c>
       <c r="R111" t="n">
-        <v>6790346</v>
+        <v>6790386</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12911,7 +12912,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12930,10 +12930,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122671667</v>
+        <v>122671579</v>
       </c>
       <c r="B112" t="n">
-        <v>78691</v>
+        <v>78660</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12946,21 +12946,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12973,13 +12973,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>486043</v>
+        <v>485989</v>
       </c>
       <c r="R112" t="n">
-        <v>6790416</v>
+        <v>6790378</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13036,10 +13036,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122671519</v>
+        <v>122671559</v>
       </c>
       <c r="B113" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13079,10 +13079,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>485876</v>
+        <v>485916</v>
       </c>
       <c r="R113" t="n">
-        <v>6790381</v>
+        <v>6790407</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13142,10 +13142,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122671440</v>
+        <v>122671555</v>
       </c>
       <c r="B114" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13185,10 +13185,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>485819</v>
+        <v>485915</v>
       </c>
       <c r="R114" t="n">
-        <v>6790340</v>
+        <v>6790407</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13248,10 +13248,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122671592</v>
+        <v>122671537</v>
       </c>
       <c r="B115" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13260,30 +13260,36 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -13291,10 +13297,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>485984</v>
+        <v>485910</v>
       </c>
       <c r="R115" t="n">
-        <v>6790371</v>
+        <v>6790394</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13354,10 +13360,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122671434</v>
+        <v>122671675</v>
       </c>
       <c r="B116" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13397,13 +13403,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>485799</v>
+        <v>486331</v>
       </c>
       <c r="R116" t="n">
-        <v>6790349</v>
+        <v>6790370</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13460,10 +13466,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122671559</v>
+        <v>122671424</v>
       </c>
       <c r="B117" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13503,10 +13509,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>485916</v>
+        <v>485783</v>
       </c>
       <c r="R117" t="n">
-        <v>6790407</v>
+        <v>6790367</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13566,10 +13572,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122671537</v>
+        <v>122671493</v>
       </c>
       <c r="B118" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13578,36 +13584,30 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -13615,10 +13615,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>485910</v>
+        <v>485859</v>
       </c>
       <c r="R118" t="n">
-        <v>6790394</v>
+        <v>6790362</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13678,7 +13678,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122689596</v>
+        <v>122689963</v>
       </c>
       <c r="B119" t="n">
         <v>78660</v>
@@ -13721,10 +13721,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>485656</v>
+        <v>485658</v>
       </c>
       <c r="R119" t="n">
-        <v>6790462</v>
+        <v>6790402</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13784,7 +13784,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122689899</v>
+        <v>122689736</v>
       </c>
       <c r="B120" t="n">
         <v>78660</v>
@@ -13827,10 +13827,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>485399</v>
+        <v>485597</v>
       </c>
       <c r="R120" t="n">
-        <v>6790454</v>
+        <v>6790468</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13890,7 +13890,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122689904</v>
+        <v>122689743</v>
       </c>
       <c r="B121" t="n">
         <v>78660</v>
@@ -13933,10 +13933,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>485427</v>
+        <v>485588</v>
       </c>
       <c r="R121" t="n">
-        <v>6790445</v>
+        <v>6790473</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13996,7 +13996,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122689611</v>
+        <v>122689732</v>
       </c>
       <c r="B122" t="n">
         <v>78660</v>
@@ -14039,10 +14039,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>485653</v>
+        <v>485601</v>
       </c>
       <c r="R122" t="n">
-        <v>6790460</v>
+        <v>6790468</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14102,7 +14102,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122689853</v>
+        <v>122689842</v>
       </c>
       <c r="B123" t="n">
         <v>78660</v>
@@ -14145,10 +14145,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>485439</v>
+        <v>485449</v>
       </c>
       <c r="R123" t="n">
-        <v>6790465</v>
+        <v>6790454</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14201,14 +14201,14 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122689936</v>
+        <v>122689838</v>
       </c>
       <c r="B124" t="n">
         <v>78660</v>
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>485535</v>
+        <v>485452</v>
       </c>
       <c r="R124" t="n">
-        <v>6790402</v>
+        <v>6790453</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14314,7 +14314,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122689924</v>
+        <v>122689918</v>
       </c>
       <c r="B125" t="n">
         <v>78660</v>
@@ -14357,10 +14357,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>485489</v>
+        <v>485463</v>
       </c>
       <c r="R125" t="n">
-        <v>6790405</v>
+        <v>6790428</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14420,7 +14420,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122689824</v>
+        <v>122689519</v>
       </c>
       <c r="B126" t="n">
         <v>78660</v>
@@ -14463,10 +14463,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>485497</v>
+        <v>485696</v>
       </c>
       <c r="R126" t="n">
-        <v>6790458</v>
+        <v>6790431</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14526,7 +14526,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122689974</v>
+        <v>122689447</v>
       </c>
       <c r="B127" t="n">
         <v>78660</v>
@@ -14569,10 +14569,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>485719</v>
+        <v>485729</v>
       </c>
       <c r="R127" t="n">
-        <v>6790394</v>
+        <v>6790386</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14632,7 +14632,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122689934</v>
+        <v>122689911</v>
       </c>
       <c r="B128" t="n">
         <v>78660</v>
@@ -14675,10 +14675,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>485527</v>
+        <v>485439</v>
       </c>
       <c r="R128" t="n">
-        <v>6790426</v>
+        <v>6790444</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14738,10 +14738,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122689939</v>
+        <v>122689972</v>
       </c>
       <c r="B129" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14750,36 +14750,30 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -14787,10 +14781,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>485533</v>
+        <v>485718</v>
       </c>
       <c r="R129" t="n">
-        <v>6790398</v>
+        <v>6790397</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14850,7 +14844,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122689581</v>
+        <v>122689768</v>
       </c>
       <c r="B130" t="n">
         <v>78660</v>
@@ -14893,10 +14887,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>485671</v>
+        <v>485537</v>
       </c>
       <c r="R130" t="n">
-        <v>6790449</v>
+        <v>6790465</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -14956,7 +14950,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122689943</v>
+        <v>122689933</v>
       </c>
       <c r="B131" t="n">
         <v>78660</v>
@@ -14999,10 +14993,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>485590</v>
+        <v>485524</v>
       </c>
       <c r="R131" t="n">
-        <v>6790388</v>
+        <v>6790423</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -15062,7 +15056,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122689761</v>
+        <v>122689714</v>
       </c>
       <c r="B132" t="n">
         <v>78660</v>
@@ -15105,10 +15099,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>485563</v>
+        <v>485613</v>
       </c>
       <c r="R132" t="n">
-        <v>6790470</v>
+        <v>6790471</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -15168,7 +15162,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122689633</v>
+        <v>122689581</v>
       </c>
       <c r="B133" t="n">
         <v>78660</v>
@@ -15211,10 +15205,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>485624</v>
+        <v>485671</v>
       </c>
       <c r="R133" t="n">
-        <v>6790469</v>
+        <v>6790449</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15274,7 +15268,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>122689941</v>
+        <v>122689540</v>
       </c>
       <c r="B134" t="n">
         <v>78660</v>
@@ -15317,10 +15311,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>485558</v>
+        <v>485689</v>
       </c>
       <c r="R134" t="n">
-        <v>6790391</v>
+        <v>6790436</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -15380,7 +15374,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>122689447</v>
+        <v>122689934</v>
       </c>
       <c r="B135" t="n">
         <v>78660</v>
@@ -15423,10 +15417,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>485729</v>
+        <v>485527</v>
       </c>
       <c r="R135" t="n">
-        <v>6790386</v>
+        <v>6790426</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -15486,7 +15480,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>122689630</v>
+        <v>122689753</v>
       </c>
       <c r="B136" t="n">
         <v>78660</v>
@@ -15529,10 +15523,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>485638</v>
+        <v>485577</v>
       </c>
       <c r="R136" t="n">
-        <v>6790456</v>
+        <v>6790471</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -15698,10 +15692,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>122689732</v>
+        <v>122689349</v>
       </c>
       <c r="B138" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15710,30 +15704,43 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
@@ -15741,13 +15748,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>485601</v>
+        <v>485774</v>
       </c>
       <c r="R138" t="n">
-        <v>6790468</v>
+        <v>6790357</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15779,13 +15786,17 @@
           <t>2025-02-20</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>flög åt väster</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -15804,7 +15815,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>122689872</v>
+        <v>122689941</v>
       </c>
       <c r="B139" t="n">
         <v>78660</v>
@@ -15847,10 +15858,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>485412</v>
+        <v>485558</v>
       </c>
       <c r="R139" t="n">
-        <v>6790481</v>
+        <v>6790391</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -15910,7 +15921,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>122689748</v>
+        <v>122689863</v>
       </c>
       <c r="B140" t="n">
         <v>78660</v>
@@ -15953,10 +15964,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>485586</v>
+        <v>485420</v>
       </c>
       <c r="R140" t="n">
-        <v>6790473</v>
+        <v>6790476</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -16016,7 +16027,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>122689768</v>
+        <v>122689566</v>
       </c>
       <c r="B141" t="n">
         <v>78660</v>
@@ -16059,10 +16070,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>485537</v>
+        <v>485670</v>
       </c>
       <c r="R141" t="n">
-        <v>6790465</v>
+        <v>6790450</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16122,7 +16133,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>122689970</v>
+        <v>122689756</v>
       </c>
       <c r="B142" t="n">
         <v>78660</v>
@@ -16165,10 +16176,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>485704</v>
+        <v>485576</v>
       </c>
       <c r="R142" t="n">
-        <v>6790400</v>
+        <v>6790471</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16228,7 +16239,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>122689594</v>
+        <v>122689556</v>
       </c>
       <c r="B143" t="n">
         <v>78660</v>
@@ -16271,10 +16282,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>485662</v>
+        <v>485678</v>
       </c>
       <c r="R143" t="n">
-        <v>6790461</v>
+        <v>6790447</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -16334,7 +16345,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>122689556</v>
+        <v>122689974</v>
       </c>
       <c r="B144" t="n">
         <v>78660</v>
@@ -16377,10 +16388,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>485678</v>
+        <v>485719</v>
       </c>
       <c r="R144" t="n">
-        <v>6790447</v>
+        <v>6790394</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -16440,7 +16451,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>122689548</v>
+        <v>122689630</v>
       </c>
       <c r="B145" t="n">
         <v>78660</v>
@@ -16483,10 +16494,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>485686</v>
+        <v>485638</v>
       </c>
       <c r="R145" t="n">
-        <v>6790446</v>
+        <v>6790456</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -16546,7 +16557,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>122689736</v>
+        <v>122689633</v>
       </c>
       <c r="B146" t="n">
         <v>78660</v>
@@ -16589,10 +16600,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>485597</v>
+        <v>485624</v>
       </c>
       <c r="R146" t="n">
-        <v>6790468</v>
+        <v>6790469</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -16652,7 +16663,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>122689966</v>
+        <v>122689761</v>
       </c>
       <c r="B147" t="n">
         <v>78660</v>
@@ -16695,10 +16706,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>485678</v>
+        <v>485563</v>
       </c>
       <c r="R147" t="n">
-        <v>6790402</v>
+        <v>6790470</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -16758,7 +16769,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>122689889</v>
+        <v>122689942</v>
       </c>
       <c r="B148" t="n">
         <v>78660</v>
@@ -16801,10 +16812,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>485406</v>
+        <v>485554</v>
       </c>
       <c r="R148" t="n">
-        <v>6790464</v>
+        <v>6790400</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -16864,10 +16875,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>122689723</v>
+        <v>122689619</v>
       </c>
       <c r="B149" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16876,36 +16887,30 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
@@ -16913,10 +16918,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>485609</v>
+        <v>485645</v>
       </c>
       <c r="R149" t="n">
-        <v>6790472</v>
+        <v>6790451</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -16976,7 +16981,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>122689846</v>
+        <v>122689677</v>
       </c>
       <c r="B150" t="n">
         <v>78660</v>
@@ -17019,10 +17024,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>485443</v>
+        <v>485615</v>
       </c>
       <c r="R150" t="n">
-        <v>6790455</v>
+        <v>6790468</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -17082,7 +17087,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>122689942</v>
+        <v>122689806</v>
       </c>
       <c r="B151" t="n">
         <v>78660</v>
@@ -17125,10 +17130,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>485554</v>
+        <v>485524</v>
       </c>
       <c r="R151" t="n">
-        <v>6790400</v>
+        <v>6790465</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -17188,7 +17193,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>122689859</v>
+        <v>122689572</v>
       </c>
       <c r="B152" t="n">
         <v>78660</v>
@@ -17231,10 +17236,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>485425</v>
+        <v>485672</v>
       </c>
       <c r="R152" t="n">
-        <v>6790473</v>
+        <v>6790447</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -17294,7 +17299,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>122689851</v>
+        <v>122689889</v>
       </c>
       <c r="B153" t="n">
         <v>78660</v>
@@ -17337,10 +17342,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>485442</v>
+        <v>485406</v>
       </c>
       <c r="R153" t="n">
-        <v>6790462</v>
+        <v>6790464</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -17400,7 +17405,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>122689950</v>
+        <v>122689875</v>
       </c>
       <c r="B154" t="n">
         <v>78660</v>
@@ -17443,10 +17448,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>485623</v>
+        <v>485410</v>
       </c>
       <c r="R154" t="n">
-        <v>6790393</v>
+        <v>6790478</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -17506,7 +17511,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122689794</v>
+        <v>122689594</v>
       </c>
       <c r="B155" t="n">
         <v>78660</v>
@@ -17549,10 +17554,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>485529</v>
+        <v>485662</v>
       </c>
       <c r="R155" t="n">
-        <v>6790463</v>
+        <v>6790461</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -17612,10 +17617,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122689540</v>
+        <v>122689725</v>
       </c>
       <c r="B156" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17628,26 +17633,31 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -17655,10 +17665,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>485689</v>
+        <v>485609</v>
       </c>
       <c r="R156" t="n">
-        <v>6790436</v>
+        <v>6790472</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -17699,7 +17709,6 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -17718,10 +17727,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>122689738</v>
+        <v>122689723</v>
       </c>
       <c r="B157" t="n">
-        <v>90857</v>
+        <v>8441</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17730,38 +17739,36 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -17769,10 +17776,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>485597</v>
+        <v>485609</v>
       </c>
       <c r="R157" t="n">
-        <v>6790468</v>
+        <v>6790472</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -17832,7 +17839,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122689928</v>
+        <v>122689819</v>
       </c>
       <c r="B158" t="n">
         <v>78660</v>
@@ -17875,10 +17882,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>485524</v>
+        <v>485500</v>
       </c>
       <c r="R158" t="n">
-        <v>6790423</v>
+        <v>6790456</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -17938,7 +17945,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>122689963</v>
+        <v>122689851</v>
       </c>
       <c r="B159" t="n">
         <v>78660</v>
@@ -17981,10 +17988,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>485658</v>
+        <v>485442</v>
       </c>
       <c r="R159" t="n">
-        <v>6790402</v>
+        <v>6790462</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -18037,14 +18044,14 @@
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>122689911</v>
+        <v>122689611</v>
       </c>
       <c r="B160" t="n">
         <v>78660</v>
@@ -18087,10 +18094,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>485439</v>
+        <v>485653</v>
       </c>
       <c r="R160" t="n">
-        <v>6790444</v>
+        <v>6790460</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -18150,7 +18157,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>122689619</v>
+        <v>122689748</v>
       </c>
       <c r="B161" t="n">
         <v>78660</v>
@@ -18193,10 +18200,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>485645</v>
+        <v>485586</v>
       </c>
       <c r="R161" t="n">
-        <v>6790451</v>
+        <v>6790473</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -18256,10 +18263,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>122689842</v>
+        <v>122689738</v>
       </c>
       <c r="B162" t="n">
-        <v>78660</v>
+        <v>90857</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18272,25 +18279,33 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
@@ -18299,10 +18314,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>485449</v>
+        <v>485597</v>
       </c>
       <c r="R162" t="n">
-        <v>6790454</v>
+        <v>6790468</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -18362,10 +18377,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122689865</v>
+        <v>122689718</v>
       </c>
       <c r="B163" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18374,36 +18389,30 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
@@ -18411,10 +18420,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>485417</v>
+        <v>485610</v>
       </c>
       <c r="R163" t="n">
-        <v>6790479</v>
+        <v>6790472</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -18474,10 +18483,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>122689349</v>
+        <v>122689824</v>
       </c>
       <c r="B164" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18486,43 +18495,30 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
@@ -18530,13 +18526,13 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>485774</v>
+        <v>485497</v>
       </c>
       <c r="R164" t="n">
-        <v>6790357</v>
+        <v>6790458</v>
       </c>
       <c r="S164" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18568,17 +18564,13 @@
           <t>2025-02-20</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>flög åt väster</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -18597,7 +18589,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122689879</v>
+        <v>122689626</v>
       </c>
       <c r="B165" t="n">
         <v>78660</v>
@@ -18640,10 +18632,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>485409</v>
+        <v>485638</v>
       </c>
       <c r="R165" t="n">
-        <v>6790470</v>
+        <v>6790452</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18703,7 +18695,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122689895</v>
+        <v>122689846</v>
       </c>
       <c r="B166" t="n">
         <v>78660</v>
@@ -18746,10 +18738,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>485405</v>
+        <v>485443</v>
       </c>
       <c r="R166" t="n">
-        <v>6790460</v>
+        <v>6790455</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -18802,14 +18794,14 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>122689593</v>
+        <v>122689829</v>
       </c>
       <c r="B167" t="n">
         <v>78660</v>
@@ -18852,10 +18844,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>485660</v>
+        <v>485469</v>
       </c>
       <c r="R167" t="n">
-        <v>6790454</v>
+        <v>6790456</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -18915,10 +18907,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>122689714</v>
+        <v>122689865</v>
       </c>
       <c r="B168" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18927,30 +18919,36 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
@@ -18958,10 +18956,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>485613</v>
+        <v>485417</v>
       </c>
       <c r="R168" t="n">
-        <v>6790471</v>
+        <v>6790479</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -19021,7 +19019,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>122689753</v>
+        <v>122689970</v>
       </c>
       <c r="B169" t="n">
         <v>78660</v>
@@ -19064,10 +19062,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>485577</v>
+        <v>485704</v>
       </c>
       <c r="R169" t="n">
-        <v>6790471</v>
+        <v>6790400</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -19127,10 +19125,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>122689914</v>
+        <v>122689939</v>
       </c>
       <c r="B170" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19139,30 +19137,36 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
@@ -19170,10 +19174,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>485447</v>
+        <v>485533</v>
       </c>
       <c r="R170" t="n">
-        <v>6790434</v>
+        <v>6790398</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -19233,7 +19237,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>122689811</v>
+        <v>122689593</v>
       </c>
       <c r="B171" t="n">
         <v>78660</v>
@@ -19276,10 +19280,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>485510</v>
+        <v>485660</v>
       </c>
       <c r="R171" t="n">
-        <v>6790462</v>
+        <v>6790454</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -19339,7 +19343,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>122689892</v>
+        <v>122689882</v>
       </c>
       <c r="B172" t="n">
         <v>78660</v>
@@ -19382,10 +19386,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>485406</v>
+        <v>485408</v>
       </c>
       <c r="R172" t="n">
-        <v>6790461</v>
+        <v>6790469</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -19445,7 +19449,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>122689829</v>
+        <v>122689914</v>
       </c>
       <c r="B173" t="n">
         <v>78660</v>
@@ -19488,10 +19492,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>485469</v>
+        <v>485447</v>
       </c>
       <c r="R173" t="n">
-        <v>6790456</v>
+        <v>6790434</v>
       </c>
       <c r="S173" t="n">
         <v>5</v>
@@ -19551,7 +19555,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>122689718</v>
+        <v>122689954</v>
       </c>
       <c r="B174" t="n">
         <v>78660</v>
@@ -19594,10 +19598,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>485610</v>
+        <v>485626</v>
       </c>
       <c r="R174" t="n">
-        <v>6790472</v>
+        <v>6790391</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -19657,7 +19661,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>122689838</v>
+        <v>122689617</v>
       </c>
       <c r="B175" t="n">
         <v>78660</v>
@@ -19700,7 +19704,7 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>485452</v>
+        <v>485646</v>
       </c>
       <c r="R175" t="n">
         <v>6790453</v>
@@ -19763,7 +19767,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122689833</v>
+        <v>122689855</v>
       </c>
       <c r="B176" t="n">
         <v>78660</v>
@@ -19806,10 +19810,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>485457</v>
+        <v>485432</v>
       </c>
       <c r="R176" t="n">
-        <v>6790457</v>
+        <v>6790469</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -19869,7 +19873,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122689972</v>
+        <v>122689920</v>
       </c>
       <c r="B177" t="n">
         <v>78660</v>
@@ -19912,10 +19916,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>485718</v>
+        <v>485472</v>
       </c>
       <c r="R177" t="n">
-        <v>6790397</v>
+        <v>6790425</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -19975,10 +19979,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122689725</v>
+        <v>122689924</v>
       </c>
       <c r="B178" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19991,31 +19995,26 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
@@ -20023,10 +20022,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>485609</v>
+        <v>485489</v>
       </c>
       <c r="R178" t="n">
-        <v>6790472</v>
+        <v>6790405</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -20067,6 +20066,7 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -20085,7 +20085,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122689806</v>
+        <v>122689959</v>
       </c>
       <c r="B179" t="n">
         <v>78660</v>
@@ -20128,10 +20128,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>485524</v>
+        <v>485627</v>
       </c>
       <c r="R179" t="n">
-        <v>6790465</v>
+        <v>6790392</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20191,7 +20191,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122689959</v>
+        <v>122689950</v>
       </c>
       <c r="B180" t="n">
         <v>78660</v>
@@ -20234,10 +20234,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>485627</v>
+        <v>485623</v>
       </c>
       <c r="R180" t="n">
-        <v>6790392</v>
+        <v>6790393</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -20297,7 +20297,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122689819</v>
+        <v>122689811</v>
       </c>
       <c r="B181" t="n">
         <v>78660</v>
@@ -20340,10 +20340,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>485500</v>
+        <v>485510</v>
       </c>
       <c r="R181" t="n">
-        <v>6790456</v>
+        <v>6790462</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -20403,7 +20403,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122689572</v>
+        <v>122689548</v>
       </c>
       <c r="B182" t="n">
         <v>78660</v>
@@ -20446,10 +20446,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>485672</v>
+        <v>485686</v>
       </c>
       <c r="R182" t="n">
-        <v>6790447</v>
+        <v>6790446</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -20509,7 +20509,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>122689677</v>
+        <v>122689879</v>
       </c>
       <c r="B183" t="n">
         <v>78660</v>
@@ -20552,10 +20552,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>485615</v>
+        <v>485409</v>
       </c>
       <c r="R183" t="n">
-        <v>6790468</v>
+        <v>6790470</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -20615,7 +20615,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122689756</v>
+        <v>122689936</v>
       </c>
       <c r="B184" t="n">
         <v>78660</v>
@@ -20658,10 +20658,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>485576</v>
+        <v>485535</v>
       </c>
       <c r="R184" t="n">
-        <v>6790471</v>
+        <v>6790402</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -20721,7 +20721,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>122689566</v>
+        <v>122689943</v>
       </c>
       <c r="B185" t="n">
         <v>78660</v>
@@ -20764,10 +20764,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>485670</v>
+        <v>485590</v>
       </c>
       <c r="R185" t="n">
-        <v>6790450</v>
+        <v>6790388</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -20827,7 +20827,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122689617</v>
+        <v>122689899</v>
       </c>
       <c r="B186" t="n">
         <v>78660</v>
@@ -20870,10 +20870,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>485646</v>
+        <v>485399</v>
       </c>
       <c r="R186" t="n">
-        <v>6790453</v>
+        <v>6790454</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -20933,7 +20933,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>122689918</v>
+        <v>122689895</v>
       </c>
       <c r="B187" t="n">
         <v>78660</v>
@@ -20976,10 +20976,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>485463</v>
+        <v>485405</v>
       </c>
       <c r="R187" t="n">
-        <v>6790428</v>
+        <v>6790460</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21039,7 +21039,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>122689875</v>
+        <v>122689833</v>
       </c>
       <c r="B188" t="n">
         <v>78660</v>
@@ -21082,10 +21082,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>485410</v>
+        <v>485457</v>
       </c>
       <c r="R188" t="n">
-        <v>6790478</v>
+        <v>6790457</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21145,7 +21145,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>122689519</v>
+        <v>122689872</v>
       </c>
       <c r="B189" t="n">
         <v>78660</v>
@@ -21188,10 +21188,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>485696</v>
+        <v>485412</v>
       </c>
       <c r="R189" t="n">
-        <v>6790431</v>
+        <v>6790481</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -21251,7 +21251,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122689954</v>
+        <v>122689794</v>
       </c>
       <c r="B190" t="n">
         <v>78660</v>
@@ -21294,10 +21294,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>485626</v>
+        <v>485529</v>
       </c>
       <c r="R190" t="n">
-        <v>6790391</v>
+        <v>6790463</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -21357,7 +21357,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122689855</v>
+        <v>122689892</v>
       </c>
       <c r="B191" t="n">
         <v>78660</v>
@@ -21400,10 +21400,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>485432</v>
+        <v>485406</v>
       </c>
       <c r="R191" t="n">
-        <v>6790469</v>
+        <v>6790461</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -21463,7 +21463,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122689863</v>
+        <v>122689966</v>
       </c>
       <c r="B192" t="n">
         <v>78660</v>
@@ -21506,10 +21506,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>485420</v>
+        <v>485678</v>
       </c>
       <c r="R192" t="n">
-        <v>6790476</v>
+        <v>6790402</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -21569,7 +21569,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122689626</v>
+        <v>122689596</v>
       </c>
       <c r="B193" t="n">
         <v>78660</v>
@@ -21612,10 +21612,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>485638</v>
+        <v>485656</v>
       </c>
       <c r="R193" t="n">
-        <v>6790452</v>
+        <v>6790462</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -21675,7 +21675,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122689743</v>
+        <v>122689904</v>
       </c>
       <c r="B194" t="n">
         <v>78660</v>
@@ -21718,10 +21718,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>485588</v>
+        <v>485427</v>
       </c>
       <c r="R194" t="n">
-        <v>6790473</v>
+        <v>6790445</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -21781,7 +21781,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122689882</v>
+        <v>122689853</v>
       </c>
       <c r="B195" t="n">
         <v>78660</v>
@@ -21824,10 +21824,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>485408</v>
+        <v>485439</v>
       </c>
       <c r="R195" t="n">
-        <v>6790469</v>
+        <v>6790465</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -21887,7 +21887,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122689920</v>
+        <v>122689859</v>
       </c>
       <c r="B196" t="n">
         <v>78660</v>
@@ -21930,10 +21930,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>485472</v>
+        <v>485425</v>
       </c>
       <c r="R196" t="n">
-        <v>6790425</v>
+        <v>6790473</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122606208</v>
+        <v>122607022</v>
       </c>
       <c r="B2" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485592</v>
+        <v>485706</v>
       </c>
       <c r="R2" t="n">
-        <v>6790353</v>
+        <v>6790427</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122608856</v>
+        <v>122606408</v>
       </c>
       <c r="B3" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486343</v>
+        <v>485407</v>
       </c>
       <c r="R3" t="n">
-        <v>6790373</v>
+        <v>6790439</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,19 +887,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122608792</v>
+        <v>122607435</v>
       </c>
       <c r="B4" t="n">
         <v>78660</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122606708</v>
+        <v>122606308</v>
       </c>
       <c r="B5" t="n">
         <v>78660</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122606145</v>
+        <v>122607224</v>
       </c>
       <c r="B6" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,41 +1135,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485616</v>
+        <v>485981</v>
       </c>
       <c r="R6" t="n">
-        <v>6790356</v>
+        <v>6790453</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122607014</v>
+        <v>122607118</v>
       </c>
       <c r="B7" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,41 +1252,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485706</v>
+        <v>485884</v>
       </c>
       <c r="R7" t="n">
-        <v>6790427</v>
+        <v>6790450</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,19 +1345,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122607400</v>
+        <v>122607108</v>
       </c>
       <c r="B8" t="n">
         <v>78660</v>
@@ -1422,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122608158</v>
+        <v>122608990</v>
       </c>
       <c r="B9" t="n">
         <v>78660</v>
@@ -1495,14 +1505,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486281</v>
+        <v>486070</v>
       </c>
       <c r="R9" t="n">
-        <v>6790441</v>
+        <v>6790363</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1534,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,12 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122608694</v>
+        <v>122606230</v>
       </c>
       <c r="B10" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,41 +1593,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486035</v>
+        <v>485561</v>
       </c>
       <c r="R10" t="n">
-        <v>6790401</v>
+        <v>6790367</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,22 +1681,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122607596</v>
+        <v>122606452</v>
       </c>
       <c r="B11" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,43 +1705,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486109</v>
+        <v>485428</v>
       </c>
       <c r="R11" t="n">
-        <v>6790384</v>
+        <v>6790393</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122609017</v>
+        <v>122606176</v>
       </c>
       <c r="B12" t="n">
-        <v>78660</v>
+        <v>78686</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,38 +1817,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486064</v>
+        <v>485613</v>
       </c>
       <c r="R12" t="n">
-        <v>6790364</v>
+        <v>6790370</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122608902</v>
+        <v>122607518</v>
       </c>
       <c r="B13" t="n">
-        <v>78397</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,34 +1933,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486280</v>
+        <v>486071</v>
       </c>
       <c r="R13" t="n">
-        <v>6790345</v>
+        <v>6790384</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,7 +2029,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606171</v>
+        <v>122606651</v>
       </c>
       <c r="B14" t="n">
         <v>78660</v>
@@ -2065,17 +2065,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485662</v>
+        <v>485432</v>
       </c>
       <c r="R14" t="n">
-        <v>6790357</v>
+        <v>6790417</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,19 +2129,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122607224</v>
+        <v>122607596</v>
       </c>
       <c r="B15" t="n">
         <v>56594</v>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485981</v>
+        <v>486109</v>
       </c>
       <c r="R15" t="n">
-        <v>6790453</v>
+        <v>6790384</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122608832</v>
+        <v>122607995</v>
       </c>
       <c r="B16" t="n">
-        <v>78397</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,21 +2274,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,13 +2298,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485504</v>
+        <v>486213</v>
       </c>
       <c r="R16" t="n">
-        <v>6790441</v>
+        <v>6790435</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,19 +2358,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122606131</v>
+        <v>122608844</v>
       </c>
       <c r="B17" t="n">
         <v>78660</v>
@@ -2406,14 +2406,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485629</v>
+        <v>486338</v>
       </c>
       <c r="R17" t="n">
-        <v>6790369</v>
+        <v>6790352</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,7 +2455,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,7 +2487,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122606108</v>
+        <v>122606193</v>
       </c>
       <c r="B18" t="n">
         <v>78660</v>
@@ -2518,17 +2523,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485649</v>
+        <v>485662</v>
       </c>
       <c r="R18" t="n">
-        <v>6790375</v>
+        <v>6790357</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2557,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2567,7 +2572,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2582,19 +2587,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122606452</v>
+        <v>122608651</v>
       </c>
       <c r="B19" t="n">
         <v>78660</v>
@@ -2630,14 +2635,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>485428</v>
+        <v>486380</v>
       </c>
       <c r="R19" t="n">
-        <v>6790393</v>
+        <v>6790321</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2669,7 +2674,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2679,7 +2684,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122607953</v>
+        <v>122609017</v>
       </c>
       <c r="B20" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2718,38 +2728,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486214</v>
+        <v>486064</v>
       </c>
       <c r="R20" t="n">
-        <v>6790429</v>
+        <v>6790364</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2781,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,7 +2828,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122607915</v>
+        <v>122607107</v>
       </c>
       <c r="B21" t="n">
         <v>78660</v>
@@ -2858,10 +2868,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486193</v>
+        <v>485855</v>
       </c>
       <c r="R21" t="n">
-        <v>6790410</v>
+        <v>6790443</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2893,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2903,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,7 +2940,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122606677</v>
+        <v>122606807</v>
       </c>
       <c r="B22" t="n">
         <v>78660</v>
@@ -2970,10 +2980,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>485490</v>
+        <v>485749</v>
       </c>
       <c r="R22" t="n">
-        <v>6790430</v>
+        <v>6790424</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -3005,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,10 +3052,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122606807</v>
+        <v>122607141</v>
       </c>
       <c r="B23" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3054,38 +3064,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>485749</v>
+        <v>485906</v>
       </c>
       <c r="R23" t="n">
-        <v>6790424</v>
+        <v>6790433</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3117,7 +3132,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3142,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3154,7 +3169,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122608938</v>
+        <v>122606286</v>
       </c>
       <c r="B24" t="n">
         <v>78660</v>
@@ -3190,14 +3205,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486253</v>
+        <v>485541</v>
       </c>
       <c r="R24" t="n">
-        <v>6790356</v>
+        <v>6790372</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3229,7 +3244,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,7 +3254,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På 3 tallar på stammen</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122607107</v>
+        <v>122607815</v>
       </c>
       <c r="B25" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3278,41 +3298,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>485855</v>
+        <v>486035</v>
       </c>
       <c r="R25" t="n">
-        <v>6790443</v>
+        <v>6790401</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3341,7 +3361,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3351,7 +3371,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3366,19 +3386,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122606230</v>
+        <v>122606271</v>
       </c>
       <c r="B26" t="n">
         <v>78660</v>
@@ -3418,10 +3438,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>485561</v>
+        <v>485553</v>
       </c>
       <c r="R26" t="n">
-        <v>6790367</v>
+        <v>6790369</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3453,7 +3473,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3463,7 +3483,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3490,7 +3510,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122606669</v>
+        <v>122606154</v>
       </c>
       <c r="B27" t="n">
         <v>78660</v>
@@ -3530,10 +3550,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>485407</v>
+        <v>485616</v>
       </c>
       <c r="R27" t="n">
-        <v>6790437</v>
+        <v>6790354</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3565,7 +3585,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3575,7 +3595,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3602,7 +3622,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122607995</v>
+        <v>122608938</v>
       </c>
       <c r="B28" t="n">
         <v>78660</v>
@@ -3638,14 +3658,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486213</v>
+        <v>486253</v>
       </c>
       <c r="R28" t="n">
-        <v>6790435</v>
+        <v>6790356</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3677,7 +3697,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3687,7 +3707,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,7 +3734,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122608110</v>
+        <v>122608158</v>
       </c>
       <c r="B29" t="n">
         <v>78660</v>
@@ -3754,10 +3774,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486270</v>
+        <v>486281</v>
       </c>
       <c r="R29" t="n">
-        <v>6790427</v>
+        <v>6790441</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3789,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3799,7 +3819,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3826,7 +3851,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122608828</v>
+        <v>122608926</v>
       </c>
       <c r="B30" t="n">
         <v>78396</v>
@@ -3862,17 +3887,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>485504</v>
+        <v>486252</v>
       </c>
       <c r="R30" t="n">
-        <v>6790441</v>
+        <v>6790351</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3901,7 +3926,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3911,7 +3936,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3926,19 +3951,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122606235</v>
+        <v>122606145</v>
       </c>
       <c r="B31" t="n">
         <v>78660</v>
@@ -3978,10 +4003,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>485615</v>
+        <v>485616</v>
       </c>
       <c r="R31" t="n">
-        <v>6790353</v>
+        <v>6790356</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4013,7 +4038,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4023,7 +4048,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4050,7 +4075,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122606651</v>
+        <v>122606669</v>
       </c>
       <c r="B32" t="n">
         <v>78660</v>
@@ -4090,13 +4115,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>485432</v>
+        <v>485407</v>
       </c>
       <c r="R32" t="n">
-        <v>6790417</v>
+        <v>6790437</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4125,7 +4150,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4135,7 +4160,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4150,12 +4175,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4386,10 +4411,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122606286</v>
+        <v>122607446</v>
       </c>
       <c r="B35" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4398,38 +4423,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485541</v>
+        <v>486045</v>
       </c>
       <c r="R35" t="n">
-        <v>6790372</v>
+        <v>6790383</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
@@ -4461,7 +4491,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4471,12 +4501,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På 3 tallar på stammen</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4503,7 +4528,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122607518</v>
+        <v>122607915</v>
       </c>
       <c r="B36" t="n">
         <v>78660</v>
@@ -4543,10 +4568,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486071</v>
+        <v>486193</v>
       </c>
       <c r="R36" t="n">
-        <v>6790384</v>
+        <v>6790410</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -4578,7 +4603,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4588,7 +4613,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4615,10 +4640,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122607974</v>
+        <v>122608856</v>
       </c>
       <c r="B37" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4627,38 +4652,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486212</v>
+        <v>486343</v>
       </c>
       <c r="R37" t="n">
-        <v>6790432</v>
+        <v>6790373</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -4690,7 +4715,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4700,7 +4725,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4727,10 +4752,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122606417</v>
+        <v>122607613</v>
       </c>
       <c r="B38" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4743,21 +4768,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4767,10 +4792,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>485407</v>
+        <v>485504</v>
       </c>
       <c r="R38" t="n">
-        <v>6790439</v>
+        <v>6790441</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4802,7 +4827,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4812,7 +4837,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4839,10 +4864,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122607446</v>
+        <v>122607948</v>
       </c>
       <c r="B39" t="n">
-        <v>56594</v>
+        <v>78397</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4851,46 +4876,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486045</v>
+        <v>485504</v>
       </c>
       <c r="R39" t="n">
-        <v>6790383</v>
+        <v>6790441</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4919,7 +4939,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4929,7 +4949,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4944,19 +4964,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122606271</v>
+        <v>122607254</v>
       </c>
       <c r="B40" t="n">
         <v>78660</v>
@@ -4996,10 +5016,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>485553</v>
+        <v>486016</v>
       </c>
       <c r="R40" t="n">
-        <v>6790369</v>
+        <v>6790443</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -5031,7 +5051,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5041,7 +5061,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5068,7 +5088,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122608990</v>
+        <v>122608061</v>
       </c>
       <c r="B41" t="n">
         <v>78660</v>
@@ -5104,14 +5124,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486070</v>
+        <v>486229</v>
       </c>
       <c r="R41" t="n">
-        <v>6790363</v>
+        <v>6790440</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5143,7 +5163,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +5173,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5180,10 +5205,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122607118</v>
+        <v>122606339</v>
       </c>
       <c r="B42" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5192,43 +5217,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>485884</v>
+        <v>485528</v>
       </c>
       <c r="R42" t="n">
-        <v>6790450</v>
+        <v>6790365</v>
       </c>
       <c r="S42" t="n">
         <v>9</v>
@@ -5260,7 +5280,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5270,7 +5290,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5297,7 +5317,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122607254</v>
+        <v>122607974</v>
       </c>
       <c r="B43" t="n">
         <v>78660</v>
@@ -5337,10 +5357,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486016</v>
+        <v>486212</v>
       </c>
       <c r="R43" t="n">
-        <v>6790443</v>
+        <v>6790432</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5372,7 +5392,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5382,7 +5402,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5409,7 +5429,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122606977</v>
+        <v>122606394</v>
       </c>
       <c r="B44" t="n">
         <v>78660</v>
@@ -5449,13 +5469,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>485766</v>
+        <v>485411</v>
       </c>
       <c r="R44" t="n">
-        <v>6790457</v>
+        <v>6790441</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5484,7 +5504,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5494,12 +5514,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5514,22 +5529,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122607141</v>
+        <v>122607713</v>
       </c>
       <c r="B45" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5538,43 +5553,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>485906</v>
+        <v>486156</v>
       </c>
       <c r="R45" t="n">
-        <v>6790433</v>
+        <v>6790429</v>
       </c>
       <c r="S45" t="n">
         <v>9</v>
@@ -5606,7 +5616,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5616,7 +5626,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5643,7 +5653,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122607495</v>
+        <v>122606977</v>
       </c>
       <c r="B46" t="n">
         <v>78660</v>
@@ -5683,10 +5693,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486056</v>
+        <v>485766</v>
       </c>
       <c r="R46" t="n">
-        <v>6790394</v>
+        <v>6790457</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5718,7 +5728,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5728,7 +5738,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5755,10 +5770,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122606176</v>
+        <v>122606677</v>
       </c>
       <c r="B47" t="n">
-        <v>78686</v>
+        <v>78660</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5767,25 +5782,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5795,10 +5810,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>485613</v>
+        <v>485490</v>
       </c>
       <c r="R47" t="n">
-        <v>6790370</v>
+        <v>6790430</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5830,7 +5845,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5840,7 +5855,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5867,7 +5882,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122607713</v>
+        <v>122608110</v>
       </c>
       <c r="B48" t="n">
         <v>78660</v>
@@ -5903,14 +5918,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486156</v>
+        <v>486270</v>
       </c>
       <c r="R48" t="n">
-        <v>6790429</v>
+        <v>6790427</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5942,7 +5957,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5952,7 +5967,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5979,10 +5994,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122606955</v>
+        <v>122607953</v>
       </c>
       <c r="B49" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5991,25 +6006,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6019,10 +6034,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>485759</v>
+        <v>486214</v>
       </c>
       <c r="R49" t="n">
-        <v>6790467</v>
+        <v>6790429</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -6054,7 +6069,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6064,7 +6079,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6091,7 +6106,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122608844</v>
+        <v>122606204</v>
       </c>
       <c r="B50" t="n">
         <v>78660</v>
@@ -6127,17 +6142,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486338</v>
+        <v>485615</v>
       </c>
       <c r="R50" t="n">
-        <v>6790352</v>
+        <v>6790353</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6166,7 +6181,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6176,12 +6191,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6196,19 +6206,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122606394</v>
+        <v>122606131</v>
       </c>
       <c r="B51" t="n">
         <v>78660</v>
@@ -6248,13 +6258,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>485411</v>
+        <v>485629</v>
       </c>
       <c r="R51" t="n">
-        <v>6790441</v>
+        <v>6790369</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6283,7 +6293,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6293,7 +6303,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6308,19 +6318,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122606339</v>
+        <v>122606108</v>
       </c>
       <c r="B52" t="n">
         <v>78660</v>
@@ -6360,10 +6370,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>485528</v>
+        <v>485649</v>
       </c>
       <c r="R52" t="n">
-        <v>6790365</v>
+        <v>6790375</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6395,7 +6405,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6405,7 +6415,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6432,10 +6442,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122608061</v>
+        <v>122606208</v>
       </c>
       <c r="B53" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6444,25 +6454,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6472,10 +6482,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486229</v>
+        <v>485592</v>
       </c>
       <c r="R53" t="n">
-        <v>6790440</v>
+        <v>6790353</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6507,7 +6517,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6517,12 +6527,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6549,7 +6554,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122608651</v>
+        <v>122606955</v>
       </c>
       <c r="B54" t="n">
         <v>78660</v>
@@ -6585,14 +6590,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486380</v>
+        <v>485759</v>
       </c>
       <c r="R54" t="n">
-        <v>6790321</v>
+        <v>6790467</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6624,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6634,12 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6666,7 +6666,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122606154</v>
+        <v>122607495</v>
       </c>
       <c r="B55" t="n">
         <v>78660</v>
@@ -6706,13 +6706,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>485616</v>
+        <v>486056</v>
       </c>
       <c r="R55" t="n">
-        <v>6790354</v>
+        <v>6790394</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6766,22 +6766,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122608926</v>
+        <v>122608902</v>
       </c>
       <c r="B56" t="n">
-        <v>78396</v>
+        <v>78397</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6794,21 +6794,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486252</v>
+        <v>486280</v>
       </c>
       <c r="R56" t="n">
-        <v>6790351</v>
+        <v>6790345</v>
       </c>
       <c r="S56" t="n">
         <v>9</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6890,10 +6890,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122607273</v>
+        <v>122606642</v>
       </c>
       <c r="B57" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6902,47 +6902,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>485932</v>
+        <v>485586</v>
       </c>
       <c r="R57" t="n">
-        <v>6790416</v>
+        <v>6790395</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6974,7 +6965,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6984,7 +6975,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6993,7 +6984,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7012,10 +7002,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122606247</v>
+        <v>122606760</v>
       </c>
       <c r="B58" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7028,37 +7018,45 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485626</v>
+        <v>485504</v>
       </c>
       <c r="R58" t="n">
-        <v>6790401</v>
+        <v>6790441</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7087,7 +7085,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7097,7 +7095,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7112,22 +7110,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122608724</v>
+        <v>122607227</v>
       </c>
       <c r="B59" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7136,41 +7134,49 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486211</v>
+        <v>485504</v>
       </c>
       <c r="R59" t="n">
-        <v>6790317</v>
+        <v>6790441</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7199,7 +7205,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7209,7 +7215,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7224,22 +7230,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122607038</v>
+        <v>122606756</v>
       </c>
       <c r="B60" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7248,41 +7254,50 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>485772</v>
+        <v>485504</v>
       </c>
       <c r="R60" t="n">
-        <v>6790421</v>
+        <v>6790441</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7311,7 +7326,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7321,7 +7336,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7330,28 +7345,29 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122606760</v>
+        <v>122608724</v>
       </c>
       <c r="B61" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7364,45 +7380,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>485504</v>
+        <v>486211</v>
       </c>
       <c r="R61" t="n">
-        <v>6790441</v>
+        <v>6790317</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7431,7 +7439,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7441,7 +7449,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7456,22 +7464,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122608142</v>
+        <v>122607688</v>
       </c>
       <c r="B62" t="n">
-        <v>78660</v>
+        <v>90857</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7484,34 +7492,38 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486240</v>
+        <v>486156</v>
       </c>
       <c r="R62" t="n">
-        <v>6790382</v>
+        <v>6790429</v>
       </c>
       <c r="S62" t="n">
         <v>9</v>
@@ -7543,7 +7555,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7553,7 +7565,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7568,22 +7580,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122606642</v>
+        <v>122608903</v>
       </c>
       <c r="B63" t="n">
-        <v>78660</v>
+        <v>78397</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7596,37 +7608,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>485586</v>
+        <v>486211</v>
       </c>
       <c r="R63" t="n">
-        <v>6790395</v>
+        <v>6790317</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7655,7 +7667,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7665,7 +7677,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7692,10 +7704,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122607688</v>
+        <v>122607445</v>
       </c>
       <c r="B64" t="n">
-        <v>90857</v>
+        <v>78660</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7708,41 +7720,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486156</v>
+        <v>486082</v>
       </c>
       <c r="R64" t="n">
-        <v>6790429</v>
+        <v>6790427</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7771,7 +7779,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7781,7 +7789,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7796,22 +7804,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122608643</v>
+        <v>122607273</v>
       </c>
       <c r="B65" t="n">
-        <v>56594</v>
+        <v>8441</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7824,29 +7832,30 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7856,10 +7865,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>485504</v>
+        <v>485932</v>
       </c>
       <c r="R65" t="n">
-        <v>6790441</v>
+        <v>6790416</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7891,7 +7900,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7901,7 +7910,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7910,18 +7919,19 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8050,7 +8060,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122607445</v>
+        <v>122609008</v>
       </c>
       <c r="B67" t="n">
         <v>78660</v>
@@ -8086,17 +8096,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486082</v>
+        <v>486063</v>
       </c>
       <c r="R67" t="n">
-        <v>6790427</v>
+        <v>6790348</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8125,7 +8135,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8135,7 +8145,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8162,10 +8172,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122608903</v>
+        <v>122606143</v>
       </c>
       <c r="B68" t="n">
-        <v>78397</v>
+        <v>78660</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8178,37 +8188,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486211</v>
+        <v>485681</v>
       </c>
       <c r="R68" t="n">
-        <v>6790317</v>
+        <v>6790440</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8237,7 +8247,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8247,7 +8257,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8274,7 +8284,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122606143</v>
+        <v>122607038</v>
       </c>
       <c r="B69" t="n">
         <v>78660</v>
@@ -8314,10 +8324,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>485681</v>
+        <v>485772</v>
       </c>
       <c r="R69" t="n">
-        <v>6790440</v>
+        <v>6790421</v>
       </c>
       <c r="S69" t="n">
         <v>9</v>
@@ -8349,7 +8359,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8359,7 +8369,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8386,10 +8396,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122607216</v>
+        <v>122606247</v>
       </c>
       <c r="B70" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8398,50 +8408,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>485504</v>
+        <v>485626</v>
       </c>
       <c r="R70" t="n">
-        <v>6790441</v>
+        <v>6790401</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8470,7 +8471,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8480,7 +8481,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8489,19 +8490,18 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8620,7 +8620,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122609008</v>
+        <v>122608142</v>
       </c>
       <c r="B72" t="n">
         <v>78660</v>
@@ -8660,13 +8660,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486063</v>
+        <v>486240</v>
       </c>
       <c r="R72" t="n">
-        <v>6790348</v>
+        <v>6790382</v>
       </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8732,10 +8732,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122607719</v>
+        <v>122607077</v>
       </c>
       <c r="B73" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8744,41 +8744,49 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486157</v>
+        <v>485772</v>
       </c>
       <c r="R73" t="n">
-        <v>6790397</v>
+        <v>6790421</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8807,7 +8815,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8817,7 +8825,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8844,10 +8852,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122607077</v>
+        <v>122607719</v>
       </c>
       <c r="B74" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8856,49 +8864,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>485772</v>
+        <v>486157</v>
       </c>
       <c r="R74" t="n">
-        <v>6790421</v>
+        <v>6790397</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8964,10 +8964,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122671608</v>
+        <v>122671508</v>
       </c>
       <c r="B75" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8980,21 +8980,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486013</v>
+        <v>485871</v>
       </c>
       <c r="R75" t="n">
-        <v>6790366</v>
+        <v>6790368</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9070,7 +9070,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122671440</v>
+        <v>122671534</v>
       </c>
       <c r="B76" t="n">
         <v>78660</v>
@@ -9113,10 +9113,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>485819</v>
+        <v>485901</v>
       </c>
       <c r="R76" t="n">
-        <v>6790340</v>
+        <v>6790392</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9176,10 +9176,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122671681</v>
+        <v>122671888</v>
       </c>
       <c r="B77" t="n">
-        <v>8441</v>
+        <v>56594</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9192,30 +9192,29 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -9225,13 +9224,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486342</v>
+        <v>485897</v>
       </c>
       <c r="R77" t="n">
-        <v>6790369</v>
+        <v>6790441</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9263,13 +9262,17 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>under betestall rikligt</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9288,10 +9291,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122671595</v>
+        <v>122671681</v>
       </c>
       <c r="B78" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9300,30 +9303,36 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9331,13 +9340,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>485984</v>
+        <v>486342</v>
       </c>
       <c r="R78" t="n">
-        <v>6790370</v>
+        <v>6790369</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9394,10 +9403,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122671534</v>
+        <v>122671608</v>
       </c>
       <c r="B79" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9410,21 +9419,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9437,10 +9446,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>485901</v>
+        <v>486013</v>
       </c>
       <c r="R79" t="n">
-        <v>6790392</v>
+        <v>6790366</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9606,10 +9615,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122671453</v>
+        <v>122671667</v>
       </c>
       <c r="B81" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9622,21 +9631,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9649,13 +9658,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>485835</v>
+        <v>486043</v>
       </c>
       <c r="R81" t="n">
-        <v>6790356</v>
+        <v>6790416</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9712,7 +9721,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122671651</v>
+        <v>122671564</v>
       </c>
       <c r="B82" t="n">
         <v>78660</v>
@@ -9755,13 +9764,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486048</v>
+        <v>485933</v>
       </c>
       <c r="R82" t="n">
-        <v>6790360</v>
+        <v>6790411</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9818,7 +9827,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122671434</v>
+        <v>122671555</v>
       </c>
       <c r="B83" t="n">
         <v>78660</v>
@@ -9861,10 +9870,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>485799</v>
+        <v>485915</v>
       </c>
       <c r="R83" t="n">
-        <v>6790349</v>
+        <v>6790407</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9924,7 +9933,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122671378</v>
+        <v>122671668</v>
       </c>
       <c r="B84" t="n">
         <v>78660</v>
@@ -9967,13 +9976,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>485757</v>
+        <v>486079</v>
       </c>
       <c r="R84" t="n">
-        <v>6790379</v>
+        <v>6790394</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10030,7 +10039,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122671679</v>
+        <v>122671675</v>
       </c>
       <c r="B85" t="n">
         <v>78660</v>
@@ -10073,10 +10082,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486342</v>
+        <v>486331</v>
       </c>
       <c r="R85" t="n">
-        <v>6790369</v>
+        <v>6790370</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10136,10 +10145,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122671422</v>
+        <v>122671610</v>
       </c>
       <c r="B86" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10152,21 +10161,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10179,10 +10188,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>485784</v>
+        <v>486013</v>
       </c>
       <c r="R86" t="n">
-        <v>6790390</v>
+        <v>6790366</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10242,7 +10251,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122671668</v>
+        <v>122671679</v>
       </c>
       <c r="B87" t="n">
         <v>78660</v>
@@ -10285,10 +10294,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486079</v>
+        <v>486342</v>
       </c>
       <c r="R87" t="n">
-        <v>6790394</v>
+        <v>6790369</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10348,10 +10357,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122671667</v>
+        <v>122671462</v>
       </c>
       <c r="B88" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10364,21 +10373,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10391,13 +10400,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486043</v>
+        <v>485835</v>
       </c>
       <c r="R88" t="n">
-        <v>6790416</v>
+        <v>6790356</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10560,10 +10569,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122671541</v>
+        <v>122671447</v>
       </c>
       <c r="B90" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10572,36 +10581,30 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10609,10 +10612,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>485879</v>
+        <v>485830</v>
       </c>
       <c r="R90" t="n">
-        <v>6790409</v>
+        <v>6790346</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10672,10 +10675,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122671888</v>
+        <v>122671592</v>
       </c>
       <c r="B91" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10684,35 +10687,30 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10720,10 +10718,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>485897</v>
+        <v>485984</v>
       </c>
       <c r="R91" t="n">
-        <v>6790441</v>
+        <v>6790371</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10758,17 +10756,13 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>under betestall rikligt</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10787,10 +10781,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122671609</v>
+        <v>122671384</v>
       </c>
       <c r="B92" t="n">
-        <v>78397</v>
+        <v>78660</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10803,21 +10797,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10830,10 +10824,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>486013</v>
+        <v>485777</v>
       </c>
       <c r="R92" t="n">
-        <v>6790366</v>
+        <v>6790392</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10893,7 +10887,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122671570</v>
+        <v>122671559</v>
       </c>
       <c r="B93" t="n">
         <v>78660</v>
@@ -10936,10 +10930,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>485953</v>
+        <v>485916</v>
       </c>
       <c r="R93" t="n">
-        <v>6790411</v>
+        <v>6790407</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10999,7 +10993,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122671674</v>
+        <v>122671434</v>
       </c>
       <c r="B94" t="n">
         <v>78660</v>
@@ -11042,13 +11036,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>486266</v>
+        <v>485799</v>
       </c>
       <c r="R94" t="n">
-        <v>6790373</v>
+        <v>6790349</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11105,7 +11099,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122671569</v>
+        <v>122671521</v>
       </c>
       <c r="B95" t="n">
         <v>78660</v>
@@ -11148,10 +11142,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>485951</v>
+        <v>485893</v>
       </c>
       <c r="R95" t="n">
-        <v>6790408</v>
+        <v>6790386</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11326,7 +11320,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122671575</v>
+        <v>122671570</v>
       </c>
       <c r="B97" t="n">
         <v>78660</v>
@@ -11369,10 +11363,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>485989</v>
+        <v>485953</v>
       </c>
       <c r="R97" t="n">
-        <v>6790394</v>
+        <v>6790411</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11432,7 +11426,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122671647</v>
+        <v>122671674</v>
       </c>
       <c r="B98" t="n">
         <v>78660</v>
@@ -11475,13 +11469,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>486035</v>
+        <v>486266</v>
       </c>
       <c r="R98" t="n">
-        <v>6790369</v>
+        <v>6790373</v>
       </c>
       <c r="S98" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11538,7 +11532,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122671521</v>
+        <v>122671575</v>
       </c>
       <c r="B99" t="n">
         <v>78660</v>
@@ -11581,10 +11575,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>485893</v>
+        <v>485989</v>
       </c>
       <c r="R99" t="n">
-        <v>6790386</v>
+        <v>6790394</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11644,7 +11638,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122671592</v>
+        <v>122671424</v>
       </c>
       <c r="B100" t="n">
         <v>78660</v>
@@ -11687,10 +11681,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>485984</v>
+        <v>485783</v>
       </c>
       <c r="R100" t="n">
-        <v>6790371</v>
+        <v>6790367</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11750,7 +11744,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122671384</v>
+        <v>122671440</v>
       </c>
       <c r="B101" t="n">
         <v>78660</v>
@@ -11793,10 +11787,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>485777</v>
+        <v>485819</v>
       </c>
       <c r="R101" t="n">
-        <v>6790392</v>
+        <v>6790340</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11856,7 +11850,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122671512</v>
+        <v>122671651</v>
       </c>
       <c r="B102" t="n">
         <v>78660</v>
@@ -11899,13 +11893,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>485876</v>
+        <v>486048</v>
       </c>
       <c r="R102" t="n">
-        <v>6790371</v>
+        <v>6790360</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11962,10 +11956,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122671564</v>
+        <v>122671523</v>
       </c>
       <c r="B103" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11978,26 +11972,31 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12005,10 +12004,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>485933</v>
+        <v>485893</v>
       </c>
       <c r="R103" t="n">
-        <v>6790411</v>
+        <v>6790386</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12049,7 +12048,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -12068,10 +12066,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122671508</v>
+        <v>122671541</v>
       </c>
       <c r="B104" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12080,30 +12078,36 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12111,10 +12115,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>485871</v>
+        <v>485879</v>
       </c>
       <c r="R104" t="n">
-        <v>6790368</v>
+        <v>6790409</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12284,7 +12288,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122671659</v>
+        <v>122671537</v>
       </c>
       <c r="B106" t="n">
         <v>8441</v>
@@ -12333,10 +12337,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>486020</v>
+        <v>485910</v>
       </c>
       <c r="R106" t="n">
-        <v>6790412</v>
+        <v>6790394</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12396,10 +12400,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122671587</v>
+        <v>122671595</v>
       </c>
       <c r="B107" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12412,21 +12416,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12439,10 +12443,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>485985</v>
+        <v>485984</v>
       </c>
       <c r="R107" t="n">
-        <v>6790379</v>
+        <v>6790370</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12502,7 +12506,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122671506</v>
+        <v>122671512</v>
       </c>
       <c r="B108" t="n">
         <v>78660</v>
@@ -12545,10 +12549,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>485861</v>
+        <v>485876</v>
       </c>
       <c r="R108" t="n">
-        <v>6790364</v>
+        <v>6790371</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12608,10 +12612,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122671610</v>
+        <v>122671569</v>
       </c>
       <c r="B109" t="n">
-        <v>78396</v>
+        <v>78660</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12624,21 +12628,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12651,10 +12655,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>486013</v>
+        <v>485951</v>
       </c>
       <c r="R109" t="n">
-        <v>6790366</v>
+        <v>6790408</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12714,10 +12718,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122671447</v>
+        <v>122671659</v>
       </c>
       <c r="B110" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12726,30 +12730,36 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12757,10 +12767,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>485830</v>
+        <v>486020</v>
       </c>
       <c r="R110" t="n">
-        <v>6790346</v>
+        <v>6790412</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12820,10 +12830,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122671523</v>
+        <v>122671647</v>
       </c>
       <c r="B111" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12836,31 +12846,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12868,13 +12873,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>485893</v>
+        <v>486035</v>
       </c>
       <c r="R111" t="n">
-        <v>6790386</v>
+        <v>6790369</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12912,6 +12917,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12930,10 +12936,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122671579</v>
+        <v>122671609</v>
       </c>
       <c r="B112" t="n">
-        <v>78660</v>
+        <v>78397</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12946,21 +12952,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12973,10 +12979,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>485989</v>
+        <v>486013</v>
       </c>
       <c r="R112" t="n">
-        <v>6790378</v>
+        <v>6790366</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13036,7 +13042,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122671559</v>
+        <v>122671506</v>
       </c>
       <c r="B113" t="n">
         <v>78660</v>
@@ -13079,10 +13085,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>485916</v>
+        <v>485861</v>
       </c>
       <c r="R113" t="n">
-        <v>6790407</v>
+        <v>6790364</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13142,7 +13148,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122671555</v>
+        <v>122671422</v>
       </c>
       <c r="B114" t="n">
         <v>78660</v>
@@ -13185,10 +13191,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>485915</v>
+        <v>485784</v>
       </c>
       <c r="R114" t="n">
-        <v>6790407</v>
+        <v>6790390</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13248,10 +13254,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122671537</v>
+        <v>122671587</v>
       </c>
       <c r="B115" t="n">
-        <v>8441</v>
+        <v>79278</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13260,36 +13266,30 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -13297,10 +13297,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>485910</v>
+        <v>485985</v>
       </c>
       <c r="R115" t="n">
-        <v>6790394</v>
+        <v>6790379</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13360,7 +13360,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122671675</v>
+        <v>122671579</v>
       </c>
       <c r="B116" t="n">
         <v>78660</v>
@@ -13403,13 +13403,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>486331</v>
+        <v>485989</v>
       </c>
       <c r="R116" t="n">
-        <v>6790370</v>
+        <v>6790378</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122671424</v>
+        <v>122671378</v>
       </c>
       <c r="B117" t="n">
         <v>78660</v>
@@ -13509,10 +13509,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>485783</v>
+        <v>485757</v>
       </c>
       <c r="R117" t="n">
-        <v>6790367</v>
+        <v>6790379</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13678,7 +13678,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122689963</v>
+        <v>122689743</v>
       </c>
       <c r="B119" t="n">
         <v>78660</v>
@@ -13721,10 +13721,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>485658</v>
+        <v>485588</v>
       </c>
       <c r="R119" t="n">
-        <v>6790402</v>
+        <v>6790473</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13784,7 +13784,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122689736</v>
+        <v>122689970</v>
       </c>
       <c r="B120" t="n">
         <v>78660</v>
@@ -13827,10 +13827,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>485597</v>
+        <v>485704</v>
       </c>
       <c r="R120" t="n">
-        <v>6790468</v>
+        <v>6790400</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13890,7 +13890,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122689743</v>
+        <v>122689718</v>
       </c>
       <c r="B121" t="n">
         <v>78660</v>
@@ -13933,10 +13933,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>485588</v>
+        <v>485610</v>
       </c>
       <c r="R121" t="n">
-        <v>6790473</v>
+        <v>6790472</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13996,10 +13996,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122689732</v>
+        <v>122689725</v>
       </c>
       <c r="B122" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14012,26 +14012,31 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -14039,10 +14044,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>485601</v>
+        <v>485609</v>
       </c>
       <c r="R122" t="n">
-        <v>6790468</v>
+        <v>6790472</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14083,7 +14088,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -14102,7 +14106,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122689842</v>
+        <v>122689875</v>
       </c>
       <c r="B123" t="n">
         <v>78660</v>
@@ -14145,10 +14149,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>485449</v>
+        <v>485410</v>
       </c>
       <c r="R123" t="n">
-        <v>6790454</v>
+        <v>6790478</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14201,14 +14205,14 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122689838</v>
+        <v>122689540</v>
       </c>
       <c r="B124" t="n">
         <v>78660</v>
@@ -14251,10 +14255,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>485452</v>
+        <v>485689</v>
       </c>
       <c r="R124" t="n">
-        <v>6790453</v>
+        <v>6790436</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14314,7 +14318,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122689918</v>
+        <v>122689833</v>
       </c>
       <c r="B125" t="n">
         <v>78660</v>
@@ -14357,10 +14361,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>485463</v>
+        <v>485457</v>
       </c>
       <c r="R125" t="n">
-        <v>6790428</v>
+        <v>6790457</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14420,7 +14424,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122689519</v>
+        <v>122689626</v>
       </c>
       <c r="B126" t="n">
         <v>78660</v>
@@ -14463,10 +14467,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>485696</v>
+        <v>485638</v>
       </c>
       <c r="R126" t="n">
-        <v>6790431</v>
+        <v>6790452</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14526,7 +14530,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122689447</v>
+        <v>122689838</v>
       </c>
       <c r="B127" t="n">
         <v>78660</v>
@@ -14569,10 +14573,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>485729</v>
+        <v>485452</v>
       </c>
       <c r="R127" t="n">
-        <v>6790386</v>
+        <v>6790453</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14632,7 +14636,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122689911</v>
+        <v>122689942</v>
       </c>
       <c r="B128" t="n">
         <v>78660</v>
@@ -14675,10 +14679,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>485439</v>
+        <v>485554</v>
       </c>
       <c r="R128" t="n">
-        <v>6790444</v>
+        <v>6790400</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14738,7 +14742,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122689972</v>
+        <v>122689794</v>
       </c>
       <c r="B129" t="n">
         <v>78660</v>
@@ -14781,10 +14785,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>485718</v>
+        <v>485529</v>
       </c>
       <c r="R129" t="n">
-        <v>6790397</v>
+        <v>6790463</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14844,7 +14848,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122689768</v>
+        <v>122689594</v>
       </c>
       <c r="B130" t="n">
         <v>78660</v>
@@ -14887,10 +14891,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>485537</v>
+        <v>485662</v>
       </c>
       <c r="R130" t="n">
-        <v>6790465</v>
+        <v>6790461</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -14950,7 +14954,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122689933</v>
+        <v>122689619</v>
       </c>
       <c r="B131" t="n">
         <v>78660</v>
@@ -14993,10 +14997,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>485524</v>
+        <v>485645</v>
       </c>
       <c r="R131" t="n">
-        <v>6790423</v>
+        <v>6790451</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -15056,7 +15060,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122689714</v>
+        <v>122689824</v>
       </c>
       <c r="B132" t="n">
         <v>78660</v>
@@ -15099,10 +15103,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>485613</v>
+        <v>485497</v>
       </c>
       <c r="R132" t="n">
-        <v>6790471</v>
+        <v>6790458</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -15162,7 +15166,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122689581</v>
+        <v>122689879</v>
       </c>
       <c r="B133" t="n">
         <v>78660</v>
@@ -15205,10 +15209,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>485671</v>
+        <v>485409</v>
       </c>
       <c r="R133" t="n">
-        <v>6790449</v>
+        <v>6790470</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15268,7 +15272,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>122689540</v>
+        <v>122689581</v>
       </c>
       <c r="B134" t="n">
         <v>78660</v>
@@ -15311,10 +15315,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>485689</v>
+        <v>485671</v>
       </c>
       <c r="R134" t="n">
-        <v>6790436</v>
+        <v>6790449</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -15374,7 +15378,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>122689934</v>
+        <v>122689920</v>
       </c>
       <c r="B135" t="n">
         <v>78660</v>
@@ -15417,10 +15421,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>485527</v>
+        <v>485472</v>
       </c>
       <c r="R135" t="n">
-        <v>6790426</v>
+        <v>6790425</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -15480,7 +15484,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>122689753</v>
+        <v>122689859</v>
       </c>
       <c r="B136" t="n">
         <v>78660</v>
@@ -15523,10 +15527,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>485577</v>
+        <v>485425</v>
       </c>
       <c r="R136" t="n">
-        <v>6790471</v>
+        <v>6790473</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -15586,7 +15590,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>122689764</v>
+        <v>122689556</v>
       </c>
       <c r="B137" t="n">
         <v>78660</v>
@@ -15629,10 +15633,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>485560</v>
+        <v>485678</v>
       </c>
       <c r="R137" t="n">
-        <v>6790469</v>
+        <v>6790447</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15692,10 +15696,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>122689349</v>
+        <v>122689954</v>
       </c>
       <c r="B138" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15704,43 +15708,30 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
@@ -15748,13 +15739,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>485774</v>
+        <v>485626</v>
       </c>
       <c r="R138" t="n">
-        <v>6790357</v>
+        <v>6790391</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15786,17 +15777,13 @@
           <t>2025-02-20</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>flög åt väster</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -15815,7 +15802,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>122689941</v>
+        <v>122689882</v>
       </c>
       <c r="B139" t="n">
         <v>78660</v>
@@ -15858,10 +15845,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>485558</v>
+        <v>485408</v>
       </c>
       <c r="R139" t="n">
-        <v>6790391</v>
+        <v>6790469</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -15921,7 +15908,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>122689863</v>
+        <v>122689918</v>
       </c>
       <c r="B140" t="n">
         <v>78660</v>
@@ -15964,10 +15951,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>485420</v>
+        <v>485463</v>
       </c>
       <c r="R140" t="n">
-        <v>6790476</v>
+        <v>6790428</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -16027,10 +16014,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>122689566</v>
+        <v>122689738</v>
       </c>
       <c r="B141" t="n">
-        <v>78660</v>
+        <v>90857</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16043,25 +16030,33 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -16070,10 +16065,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>485670</v>
+        <v>485597</v>
       </c>
       <c r="R141" t="n">
-        <v>6790450</v>
+        <v>6790468</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16133,7 +16128,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>122689756</v>
+        <v>122689963</v>
       </c>
       <c r="B142" t="n">
         <v>78660</v>
@@ -16176,10 +16171,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>485576</v>
+        <v>485658</v>
       </c>
       <c r="R142" t="n">
-        <v>6790471</v>
+        <v>6790402</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16239,7 +16234,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>122689556</v>
+        <v>122689819</v>
       </c>
       <c r="B143" t="n">
         <v>78660</v>
@@ -16282,10 +16277,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>485678</v>
+        <v>485500</v>
       </c>
       <c r="R143" t="n">
-        <v>6790447</v>
+        <v>6790456</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -16345,7 +16340,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>122689974</v>
+        <v>122689811</v>
       </c>
       <c r="B144" t="n">
         <v>78660</v>
@@ -16388,10 +16383,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>485719</v>
+        <v>485510</v>
       </c>
       <c r="R144" t="n">
-        <v>6790394</v>
+        <v>6790462</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -16451,7 +16446,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>122689630</v>
+        <v>122689941</v>
       </c>
       <c r="B145" t="n">
         <v>78660</v>
@@ -16494,10 +16489,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>485638</v>
+        <v>485558</v>
       </c>
       <c r="R145" t="n">
-        <v>6790456</v>
+        <v>6790391</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -16557,7 +16552,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>122689633</v>
+        <v>122689863</v>
       </c>
       <c r="B146" t="n">
         <v>78660</v>
@@ -16600,10 +16595,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>485624</v>
+        <v>485420</v>
       </c>
       <c r="R146" t="n">
-        <v>6790469</v>
+        <v>6790476</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -16663,7 +16658,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>122689761</v>
+        <v>122689768</v>
       </c>
       <c r="B147" t="n">
         <v>78660</v>
@@ -16706,10 +16701,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>485563</v>
+        <v>485537</v>
       </c>
       <c r="R147" t="n">
-        <v>6790470</v>
+        <v>6790465</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -16769,7 +16764,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>122689942</v>
+        <v>122689736</v>
       </c>
       <c r="B148" t="n">
         <v>78660</v>
@@ -16812,10 +16807,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>485554</v>
+        <v>485597</v>
       </c>
       <c r="R148" t="n">
-        <v>6790400</v>
+        <v>6790468</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -16875,7 +16870,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>122689619</v>
+        <v>122689806</v>
       </c>
       <c r="B149" t="n">
         <v>78660</v>
@@ -16918,10 +16913,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>485645</v>
+        <v>485524</v>
       </c>
       <c r="R149" t="n">
-        <v>6790451</v>
+        <v>6790465</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -16981,7 +16976,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>122689677</v>
+        <v>122689842</v>
       </c>
       <c r="B150" t="n">
         <v>78660</v>
@@ -17024,10 +17019,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>485615</v>
+        <v>485449</v>
       </c>
       <c r="R150" t="n">
-        <v>6790468</v>
+        <v>6790454</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -17087,7 +17082,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>122689806</v>
+        <v>122689846</v>
       </c>
       <c r="B151" t="n">
         <v>78660</v>
@@ -17130,10 +17125,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>485524</v>
+        <v>485443</v>
       </c>
       <c r="R151" t="n">
-        <v>6790465</v>
+        <v>6790455</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -17193,7 +17188,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>122689572</v>
+        <v>122689914</v>
       </c>
       <c r="B152" t="n">
         <v>78660</v>
@@ -17236,10 +17231,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>485672</v>
+        <v>485447</v>
       </c>
       <c r="R152" t="n">
-        <v>6790447</v>
+        <v>6790434</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -17299,7 +17294,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>122689889</v>
+        <v>122689972</v>
       </c>
       <c r="B153" t="n">
         <v>78660</v>
@@ -17342,10 +17337,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>485406</v>
+        <v>485718</v>
       </c>
       <c r="R153" t="n">
-        <v>6790464</v>
+        <v>6790397</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -17405,7 +17400,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>122689875</v>
+        <v>122689519</v>
       </c>
       <c r="B154" t="n">
         <v>78660</v>
@@ -17448,10 +17443,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>485410</v>
+        <v>485696</v>
       </c>
       <c r="R154" t="n">
-        <v>6790478</v>
+        <v>6790431</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -17511,7 +17506,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122689594</v>
+        <v>122689911</v>
       </c>
       <c r="B155" t="n">
         <v>78660</v>
@@ -17554,10 +17549,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>485662</v>
+        <v>485439</v>
       </c>
       <c r="R155" t="n">
-        <v>6790461</v>
+        <v>6790444</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -17617,10 +17612,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122689725</v>
+        <v>122689851</v>
       </c>
       <c r="B156" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17633,31 +17628,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -17665,10 +17655,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>485609</v>
+        <v>485442</v>
       </c>
       <c r="R156" t="n">
-        <v>6790472</v>
+        <v>6790462</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -17709,6 +17699,7 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -17727,10 +17718,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>122689723</v>
+        <v>122689748</v>
       </c>
       <c r="B157" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17739,36 +17730,30 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -17776,10 +17761,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>485609</v>
+        <v>485586</v>
       </c>
       <c r="R157" t="n">
-        <v>6790472</v>
+        <v>6790473</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -17839,7 +17824,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122689819</v>
+        <v>122689959</v>
       </c>
       <c r="B158" t="n">
         <v>78660</v>
@@ -17882,10 +17867,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>485500</v>
+        <v>485627</v>
       </c>
       <c r="R158" t="n">
-        <v>6790456</v>
+        <v>6790392</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -17945,7 +17930,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>122689851</v>
+        <v>122689950</v>
       </c>
       <c r="B159" t="n">
         <v>78660</v>
@@ -17988,10 +17973,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>485442</v>
+        <v>485623</v>
       </c>
       <c r="R159" t="n">
-        <v>6790462</v>
+        <v>6790393</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -18044,14 +18029,14 @@
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>122689611</v>
+        <v>122689966</v>
       </c>
       <c r="B160" t="n">
         <v>78660</v>
@@ -18094,10 +18079,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>485653</v>
+        <v>485678</v>
       </c>
       <c r="R160" t="n">
-        <v>6790460</v>
+        <v>6790402</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -18157,7 +18142,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>122689748</v>
+        <v>122689855</v>
       </c>
       <c r="B161" t="n">
         <v>78660</v>
@@ -18200,10 +18185,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>485586</v>
+        <v>485432</v>
       </c>
       <c r="R161" t="n">
-        <v>6790473</v>
+        <v>6790469</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -18263,10 +18248,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>122689738</v>
+        <v>122689732</v>
       </c>
       <c r="B162" t="n">
-        <v>90857</v>
+        <v>78660</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18279,33 +18264,25 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
@@ -18314,7 +18291,7 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>485597</v>
+        <v>485601</v>
       </c>
       <c r="R162" t="n">
         <v>6790468</v>
@@ -18377,10 +18354,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122689718</v>
+        <v>122689723</v>
       </c>
       <c r="B163" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18389,30 +18366,36 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
@@ -18420,7 +18403,7 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>485610</v>
+        <v>485609</v>
       </c>
       <c r="R163" t="n">
         <v>6790472</v>
@@ -18483,7 +18466,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>122689824</v>
+        <v>122689829</v>
       </c>
       <c r="B164" t="n">
         <v>78660</v>
@@ -18526,10 +18509,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>485497</v>
+        <v>485469</v>
       </c>
       <c r="R164" t="n">
-        <v>6790458</v>
+        <v>6790456</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18589,7 +18572,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122689626</v>
+        <v>122689933</v>
       </c>
       <c r="B165" t="n">
         <v>78660</v>
@@ -18632,10 +18615,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>485638</v>
+        <v>485524</v>
       </c>
       <c r="R165" t="n">
-        <v>6790452</v>
+        <v>6790423</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18695,7 +18678,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122689846</v>
+        <v>122689924</v>
       </c>
       <c r="B166" t="n">
         <v>78660</v>
@@ -18738,10 +18721,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>485443</v>
+        <v>485489</v>
       </c>
       <c r="R166" t="n">
-        <v>6790455</v>
+        <v>6790405</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -18794,14 +18777,14 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>122689829</v>
+        <v>122689630</v>
       </c>
       <c r="B167" t="n">
         <v>78660</v>
@@ -18844,7 +18827,7 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>485469</v>
+        <v>485638</v>
       </c>
       <c r="R167" t="n">
         <v>6790456</v>
@@ -18907,10 +18890,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>122689865</v>
+        <v>122689934</v>
       </c>
       <c r="B168" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18919,36 +18902,30 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
@@ -18956,10 +18933,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>485417</v>
+        <v>485527</v>
       </c>
       <c r="R168" t="n">
-        <v>6790479</v>
+        <v>6790426</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -19019,10 +18996,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>122689970</v>
+        <v>122689939</v>
       </c>
       <c r="B169" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19031,30 +19008,36 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
@@ -19062,10 +19045,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>485704</v>
+        <v>485533</v>
       </c>
       <c r="R169" t="n">
-        <v>6790400</v>
+        <v>6790398</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -19125,10 +19108,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>122689939</v>
+        <v>122689936</v>
       </c>
       <c r="B170" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19137,36 +19120,30 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
@@ -19174,10 +19151,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>485533</v>
+        <v>485535</v>
       </c>
       <c r="R170" t="n">
-        <v>6790398</v>
+        <v>6790402</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -19237,7 +19214,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>122689593</v>
+        <v>122689756</v>
       </c>
       <c r="B171" t="n">
         <v>78660</v>
@@ -19280,10 +19257,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>485660</v>
+        <v>485576</v>
       </c>
       <c r="R171" t="n">
-        <v>6790454</v>
+        <v>6790471</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -19343,7 +19320,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>122689882</v>
+        <v>122689899</v>
       </c>
       <c r="B172" t="n">
         <v>78660</v>
@@ -19386,10 +19363,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>485408</v>
+        <v>485399</v>
       </c>
       <c r="R172" t="n">
-        <v>6790469</v>
+        <v>6790454</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -19449,7 +19426,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>122689914</v>
+        <v>122689714</v>
       </c>
       <c r="B173" t="n">
         <v>78660</v>
@@ -19492,10 +19469,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>485447</v>
+        <v>485613</v>
       </c>
       <c r="R173" t="n">
-        <v>6790434</v>
+        <v>6790471</v>
       </c>
       <c r="S173" t="n">
         <v>5</v>
@@ -19555,7 +19532,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>122689954</v>
+        <v>122689764</v>
       </c>
       <c r="B174" t="n">
         <v>78660</v>
@@ -19598,10 +19575,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>485626</v>
+        <v>485560</v>
       </c>
       <c r="R174" t="n">
-        <v>6790391</v>
+        <v>6790469</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -19661,7 +19638,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>122689617</v>
+        <v>122689633</v>
       </c>
       <c r="B175" t="n">
         <v>78660</v>
@@ -19704,10 +19681,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>485646</v>
+        <v>485624</v>
       </c>
       <c r="R175" t="n">
-        <v>6790453</v>
+        <v>6790469</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -19767,7 +19744,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122689855</v>
+        <v>122689447</v>
       </c>
       <c r="B176" t="n">
         <v>78660</v>
@@ -19810,10 +19787,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>485432</v>
+        <v>485729</v>
       </c>
       <c r="R176" t="n">
-        <v>6790469</v>
+        <v>6790386</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -19873,10 +19850,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122689920</v>
+        <v>122689865</v>
       </c>
       <c r="B177" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -19885,30 +19862,36 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
@@ -19916,10 +19899,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>485472</v>
+        <v>485417</v>
       </c>
       <c r="R177" t="n">
-        <v>6790425</v>
+        <v>6790479</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -19979,7 +19962,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122689924</v>
+        <v>122689753</v>
       </c>
       <c r="B178" t="n">
         <v>78660</v>
@@ -20022,10 +20005,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>485489</v>
+        <v>485577</v>
       </c>
       <c r="R178" t="n">
-        <v>6790405</v>
+        <v>6790471</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -20085,7 +20068,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122689959</v>
+        <v>122689889</v>
       </c>
       <c r="B179" t="n">
         <v>78660</v>
@@ -20128,10 +20111,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>485627</v>
+        <v>485406</v>
       </c>
       <c r="R179" t="n">
-        <v>6790392</v>
+        <v>6790464</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20191,7 +20174,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122689950</v>
+        <v>122689892</v>
       </c>
       <c r="B180" t="n">
         <v>78660</v>
@@ -20234,10 +20217,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>485623</v>
+        <v>485406</v>
       </c>
       <c r="R180" t="n">
-        <v>6790393</v>
+        <v>6790461</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -20297,7 +20280,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122689811</v>
+        <v>122689974</v>
       </c>
       <c r="B181" t="n">
         <v>78660</v>
@@ -20340,10 +20323,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>485510</v>
+        <v>485719</v>
       </c>
       <c r="R181" t="n">
-        <v>6790462</v>
+        <v>6790394</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -20403,7 +20386,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122689548</v>
+        <v>122689611</v>
       </c>
       <c r="B182" t="n">
         <v>78660</v>
@@ -20446,10 +20429,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>485686</v>
+        <v>485653</v>
       </c>
       <c r="R182" t="n">
-        <v>6790446</v>
+        <v>6790460</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -20509,7 +20492,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>122689879</v>
+        <v>122689617</v>
       </c>
       <c r="B183" t="n">
         <v>78660</v>
@@ -20552,10 +20535,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>485409</v>
+        <v>485646</v>
       </c>
       <c r="R183" t="n">
-        <v>6790470</v>
+        <v>6790453</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -20615,7 +20598,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122689936</v>
+        <v>122689596</v>
       </c>
       <c r="B184" t="n">
         <v>78660</v>
@@ -20658,10 +20641,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>485535</v>
+        <v>485656</v>
       </c>
       <c r="R184" t="n">
-        <v>6790402</v>
+        <v>6790462</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -20721,7 +20704,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>122689943</v>
+        <v>122689761</v>
       </c>
       <c r="B185" t="n">
         <v>78660</v>
@@ -20764,10 +20747,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>485590</v>
+        <v>485563</v>
       </c>
       <c r="R185" t="n">
-        <v>6790388</v>
+        <v>6790470</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -20827,7 +20810,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122689899</v>
+        <v>122689872</v>
       </c>
       <c r="B186" t="n">
         <v>78660</v>
@@ -20870,10 +20853,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>485399</v>
+        <v>485412</v>
       </c>
       <c r="R186" t="n">
-        <v>6790454</v>
+        <v>6790481</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -21039,7 +21022,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>122689833</v>
+        <v>122689853</v>
       </c>
       <c r="B188" t="n">
         <v>78660</v>
@@ -21082,10 +21065,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>485457</v>
+        <v>485439</v>
       </c>
       <c r="R188" t="n">
-        <v>6790457</v>
+        <v>6790465</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21145,7 +21128,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>122689872</v>
+        <v>122689677</v>
       </c>
       <c r="B189" t="n">
         <v>78660</v>
@@ -21188,10 +21171,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>485412</v>
+        <v>485615</v>
       </c>
       <c r="R189" t="n">
-        <v>6790481</v>
+        <v>6790468</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -21251,7 +21234,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122689794</v>
+        <v>122689572</v>
       </c>
       <c r="B190" t="n">
         <v>78660</v>
@@ -21294,10 +21277,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>485529</v>
+        <v>485672</v>
       </c>
       <c r="R190" t="n">
-        <v>6790463</v>
+        <v>6790447</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -21357,7 +21340,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122689892</v>
+        <v>122689548</v>
       </c>
       <c r="B191" t="n">
         <v>78660</v>
@@ -21400,10 +21383,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>485406</v>
+        <v>485686</v>
       </c>
       <c r="R191" t="n">
-        <v>6790461</v>
+        <v>6790446</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -21463,7 +21446,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122689966</v>
+        <v>122689904</v>
       </c>
       <c r="B192" t="n">
         <v>78660</v>
@@ -21506,10 +21489,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>485678</v>
+        <v>485427</v>
       </c>
       <c r="R192" t="n">
-        <v>6790402</v>
+        <v>6790445</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -21569,7 +21552,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122689596</v>
+        <v>122689943</v>
       </c>
       <c r="B193" t="n">
         <v>78660</v>
@@ -21612,10 +21595,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>485656</v>
+        <v>485590</v>
       </c>
       <c r="R193" t="n">
-        <v>6790462</v>
+        <v>6790388</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -21675,7 +21658,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122689904</v>
+        <v>122689593</v>
       </c>
       <c r="B194" t="n">
         <v>78660</v>
@@ -21718,10 +21701,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>485427</v>
+        <v>485660</v>
       </c>
       <c r="R194" t="n">
-        <v>6790445</v>
+        <v>6790454</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -21781,10 +21764,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122689853</v>
+        <v>122689349</v>
       </c>
       <c r="B195" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21793,30 +21776,43 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
@@ -21824,13 +21820,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>485439</v>
+        <v>485774</v>
       </c>
       <c r="R195" t="n">
-        <v>6790465</v>
+        <v>6790357</v>
       </c>
       <c r="S195" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21862,13 +21858,17 @@
           <t>2025-02-20</t>
         </is>
       </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>flög åt väster</t>
+        </is>
+      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -21887,7 +21887,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122689859</v>
+        <v>122689566</v>
       </c>
       <c r="B196" t="n">
         <v>78660</v>
@@ -21930,10 +21930,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>485425</v>
+        <v>485670</v>
       </c>
       <c r="R196" t="n">
-        <v>6790473</v>
+        <v>6790450</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -1805,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122606176</v>
+        <v>122607596</v>
       </c>
       <c r="B12" t="n">
-        <v>78686</v>
+        <v>56594</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,34 +1821,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485613</v>
+        <v>486109</v>
       </c>
       <c r="R12" t="n">
-        <v>6790370</v>
+        <v>6790384</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1880,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122607518</v>
+        <v>122606176</v>
       </c>
       <c r="B13" t="n">
-        <v>78660</v>
+        <v>78686</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,25 +1934,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486071</v>
+        <v>485613</v>
       </c>
       <c r="R13" t="n">
-        <v>6790384</v>
+        <v>6790370</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -1992,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,7 +2034,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606651</v>
+        <v>122607518</v>
       </c>
       <c r="B14" t="n">
         <v>78660</v>
@@ -2069,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485432</v>
+        <v>486071</v>
       </c>
       <c r="R14" t="n">
-        <v>6790417</v>
+        <v>6790384</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2104,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122607596</v>
+        <v>122606651</v>
       </c>
       <c r="B15" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2153,43 +2158,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486109</v>
+        <v>485432</v>
       </c>
       <c r="R15" t="n">
-        <v>6790384</v>
+        <v>6790417</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3734,10 +3734,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122608158</v>
+        <v>122608926</v>
       </c>
       <c r="B29" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3750,34 +3750,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486281</v>
+        <v>486252</v>
       </c>
       <c r="R29" t="n">
-        <v>6790441</v>
+        <v>6790351</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3819,12 +3819,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3851,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122608926</v>
+        <v>122606145</v>
       </c>
       <c r="B30" t="n">
-        <v>78396</v>
+        <v>78660</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3867,37 +3862,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486252</v>
+        <v>485616</v>
       </c>
       <c r="R30" t="n">
-        <v>6790351</v>
+        <v>6790356</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3926,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3936,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3951,19 +3946,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122606145</v>
+        <v>122606669</v>
       </c>
       <c r="B31" t="n">
         <v>78660</v>
@@ -4003,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>485616</v>
+        <v>485407</v>
       </c>
       <c r="R31" t="n">
-        <v>6790356</v>
+        <v>6790437</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4038,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4048,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4075,7 +4070,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122606669</v>
+        <v>122608158</v>
       </c>
       <c r="B32" t="n">
         <v>78660</v>
@@ -4111,17 +4106,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>485407</v>
+        <v>486281</v>
       </c>
       <c r="R32" t="n">
-        <v>6790437</v>
+        <v>6790441</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4150,7 +4145,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4160,7 +4155,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4175,12 +4175,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -6554,7 +6554,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122606955</v>
+        <v>122607495</v>
       </c>
       <c r="B54" t="n">
         <v>78660</v>
@@ -6594,10 +6594,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>485759</v>
+        <v>486056</v>
       </c>
       <c r="R54" t="n">
-        <v>6790467</v>
+        <v>6790394</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6666,7 +6666,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122607495</v>
+        <v>122606955</v>
       </c>
       <c r="B55" t="n">
         <v>78660</v>
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486056</v>
+        <v>485759</v>
       </c>
       <c r="R55" t="n">
-        <v>6790394</v>
+        <v>6790467</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -10039,10 +10039,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122671675</v>
+        <v>122671610</v>
       </c>
       <c r="B85" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10055,21 +10055,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10082,13 +10082,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486331</v>
+        <v>486013</v>
       </c>
       <c r="R85" t="n">
-        <v>6790370</v>
+        <v>6790366</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10145,10 +10145,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122671610</v>
+        <v>122671675</v>
       </c>
       <c r="B86" t="n">
-        <v>78396</v>
+        <v>78660</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10161,21 +10161,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10188,13 +10188,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486013</v>
+        <v>486331</v>
       </c>
       <c r="R86" t="n">
-        <v>6790366</v>
+        <v>6790370</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -12718,10 +12718,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122671659</v>
+        <v>122671647</v>
       </c>
       <c r="B110" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12730,36 +12730,30 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12767,13 +12761,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>486020</v>
+        <v>486035</v>
       </c>
       <c r="R110" t="n">
-        <v>6790412</v>
+        <v>6790369</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12830,10 +12824,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122671647</v>
+        <v>122671659</v>
       </c>
       <c r="B111" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12842,30 +12836,36 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12873,13 +12873,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>486035</v>
+        <v>486020</v>
       </c>
       <c r="R111" t="n">
-        <v>6790369</v>
+        <v>6790412</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12936,10 +12936,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122671609</v>
+        <v>122671506</v>
       </c>
       <c r="B112" t="n">
-        <v>78397</v>
+        <v>78660</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12952,21 +12952,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>486013</v>
+        <v>485861</v>
       </c>
       <c r="R112" t="n">
-        <v>6790366</v>
+        <v>6790364</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13042,7 +13042,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122671506</v>
+        <v>122671422</v>
       </c>
       <c r="B113" t="n">
         <v>78660</v>
@@ -13085,10 +13085,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>485861</v>
+        <v>485784</v>
       </c>
       <c r="R113" t="n">
-        <v>6790364</v>
+        <v>6790390</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13148,10 +13148,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122671422</v>
+        <v>122671609</v>
       </c>
       <c r="B114" t="n">
-        <v>78660</v>
+        <v>78397</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13164,21 +13164,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13191,10 +13191,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>485784</v>
+        <v>486013</v>
       </c>
       <c r="R114" t="n">
-        <v>6790390</v>
+        <v>6790366</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -14212,7 +14212,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122689540</v>
+        <v>122689626</v>
       </c>
       <c r="B124" t="n">
         <v>78660</v>
@@ -14255,10 +14255,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>485689</v>
+        <v>485638</v>
       </c>
       <c r="R124" t="n">
-        <v>6790436</v>
+        <v>6790452</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14318,7 +14318,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122689833</v>
+        <v>122689838</v>
       </c>
       <c r="B125" t="n">
         <v>78660</v>
@@ -14361,10 +14361,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>485457</v>
+        <v>485452</v>
       </c>
       <c r="R125" t="n">
-        <v>6790457</v>
+        <v>6790453</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14424,7 +14424,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122689626</v>
+        <v>122689540</v>
       </c>
       <c r="B126" t="n">
         <v>78660</v>
@@ -14467,10 +14467,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>485638</v>
+        <v>485689</v>
       </c>
       <c r="R126" t="n">
-        <v>6790452</v>
+        <v>6790436</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14530,7 +14530,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122689838</v>
+        <v>122689833</v>
       </c>
       <c r="B127" t="n">
         <v>78660</v>
@@ -14573,10 +14573,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>485452</v>
+        <v>485457</v>
       </c>
       <c r="R127" t="n">
-        <v>6790453</v>
+        <v>6790457</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14636,7 +14636,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122689942</v>
+        <v>122689794</v>
       </c>
       <c r="B128" t="n">
         <v>78660</v>
@@ -14679,10 +14679,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>485554</v>
+        <v>485529</v>
       </c>
       <c r="R128" t="n">
-        <v>6790400</v>
+        <v>6790463</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14742,7 +14742,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122689794</v>
+        <v>122689594</v>
       </c>
       <c r="B129" t="n">
         <v>78660</v>
@@ -14785,10 +14785,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>485529</v>
+        <v>485662</v>
       </c>
       <c r="R129" t="n">
-        <v>6790463</v>
+        <v>6790461</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14848,7 +14848,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122689594</v>
+        <v>122689942</v>
       </c>
       <c r="B130" t="n">
         <v>78660</v>
@@ -14891,10 +14891,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>485662</v>
+        <v>485554</v>
       </c>
       <c r="R130" t="n">
-        <v>6790461</v>
+        <v>6790400</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -18890,7 +18890,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>122689934</v>
+        <v>122689936</v>
       </c>
       <c r="B168" t="n">
         <v>78660</v>
@@ -18933,10 +18933,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>485527</v>
+        <v>485535</v>
       </c>
       <c r="R168" t="n">
-        <v>6790426</v>
+        <v>6790402</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -18996,10 +18996,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>122689939</v>
+        <v>122689934</v>
       </c>
       <c r="B169" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19008,36 +19008,30 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
@@ -19045,10 +19039,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>485533</v>
+        <v>485527</v>
       </c>
       <c r="R169" t="n">
-        <v>6790398</v>
+        <v>6790426</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -19108,10 +19102,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>122689936</v>
+        <v>122689939</v>
       </c>
       <c r="B170" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19120,30 +19114,36 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
@@ -19151,10 +19151,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>485535</v>
+        <v>485533</v>
       </c>
       <c r="R170" t="n">
-        <v>6790402</v>
+        <v>6790398</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -19214,10 +19214,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>122689756</v>
+        <v>122689865</v>
       </c>
       <c r="B171" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19226,30 +19226,36 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
@@ -19257,10 +19263,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>485576</v>
+        <v>485417</v>
       </c>
       <c r="R171" t="n">
-        <v>6790471</v>
+        <v>6790479</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -19320,7 +19326,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>122689899</v>
+        <v>122689756</v>
       </c>
       <c r="B172" t="n">
         <v>78660</v>
@@ -19363,10 +19369,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>485399</v>
+        <v>485576</v>
       </c>
       <c r="R172" t="n">
-        <v>6790454</v>
+        <v>6790471</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -19426,7 +19432,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>122689714</v>
+        <v>122689899</v>
       </c>
       <c r="B173" t="n">
         <v>78660</v>
@@ -19469,10 +19475,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>485613</v>
+        <v>485399</v>
       </c>
       <c r="R173" t="n">
-        <v>6790471</v>
+        <v>6790454</v>
       </c>
       <c r="S173" t="n">
         <v>5</v>
@@ -19532,7 +19538,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>122689764</v>
+        <v>122689714</v>
       </c>
       <c r="B174" t="n">
         <v>78660</v>
@@ -19575,10 +19581,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>485560</v>
+        <v>485613</v>
       </c>
       <c r="R174" t="n">
-        <v>6790469</v>
+        <v>6790471</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -19638,7 +19644,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>122689633</v>
+        <v>122689764</v>
       </c>
       <c r="B175" t="n">
         <v>78660</v>
@@ -19681,7 +19687,7 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>485624</v>
+        <v>485560</v>
       </c>
       <c r="R175" t="n">
         <v>6790469</v>
@@ -19744,7 +19750,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122689447</v>
+        <v>122689633</v>
       </c>
       <c r="B176" t="n">
         <v>78660</v>
@@ -19787,10 +19793,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>485729</v>
+        <v>485624</v>
       </c>
       <c r="R176" t="n">
-        <v>6790386</v>
+        <v>6790469</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -19850,10 +19856,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122689865</v>
+        <v>122689447</v>
       </c>
       <c r="B177" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -19862,36 +19868,30 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
@@ -19899,10 +19899,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>485417</v>
+        <v>485729</v>
       </c>
       <c r="R177" t="n">
-        <v>6790479</v>
+        <v>6790386</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -20386,7 +20386,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122689611</v>
+        <v>122689596</v>
       </c>
       <c r="B182" t="n">
         <v>78660</v>
@@ -20429,10 +20429,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>485653</v>
+        <v>485656</v>
       </c>
       <c r="R182" t="n">
-        <v>6790460</v>
+        <v>6790462</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -20492,7 +20492,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>122689617</v>
+        <v>122689761</v>
       </c>
       <c r="B183" t="n">
         <v>78660</v>
@@ -20535,10 +20535,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>485646</v>
+        <v>485563</v>
       </c>
       <c r="R183" t="n">
-        <v>6790453</v>
+        <v>6790470</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -20598,7 +20598,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122689596</v>
+        <v>122689872</v>
       </c>
       <c r="B184" t="n">
         <v>78660</v>
@@ -20641,10 +20641,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>485656</v>
+        <v>485412</v>
       </c>
       <c r="R184" t="n">
-        <v>6790462</v>
+        <v>6790481</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -20704,7 +20704,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>122689761</v>
+        <v>122689611</v>
       </c>
       <c r="B185" t="n">
         <v>78660</v>
@@ -20747,10 +20747,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>485563</v>
+        <v>485653</v>
       </c>
       <c r="R185" t="n">
-        <v>6790470</v>
+        <v>6790460</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -20810,7 +20810,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122689872</v>
+        <v>122689617</v>
       </c>
       <c r="B186" t="n">
         <v>78660</v>
@@ -20853,10 +20853,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>485412</v>
+        <v>485646</v>
       </c>
       <c r="R186" t="n">
-        <v>6790481</v>
+        <v>6790453</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122607118</v>
+        <v>122607108</v>
       </c>
       <c r="B7" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,46 +1252,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485884</v>
+        <v>485504</v>
       </c>
       <c r="R7" t="n">
-        <v>6790450</v>
+        <v>6790441</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,19 +1340,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122607108</v>
+        <v>122608990</v>
       </c>
       <c r="B8" t="n">
         <v>78660</v>
@@ -1393,17 +1388,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485504</v>
+        <v>486070</v>
       </c>
       <c r="R8" t="n">
-        <v>6790441</v>
+        <v>6790363</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,19 +1452,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122608990</v>
+        <v>122606230</v>
       </c>
       <c r="B9" t="n">
         <v>78660</v>
@@ -1505,14 +1500,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486070</v>
+        <v>485561</v>
       </c>
       <c r="R9" t="n">
-        <v>6790363</v>
+        <v>6790367</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1544,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1576,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122606230</v>
+        <v>122606452</v>
       </c>
       <c r="B10" t="n">
         <v>78660</v>
@@ -1621,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485561</v>
+        <v>485428</v>
       </c>
       <c r="R10" t="n">
-        <v>6790367</v>
+        <v>6790393</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1656,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122606452</v>
+        <v>122607118</v>
       </c>
       <c r="B11" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,38 +1700,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485428</v>
+        <v>485884</v>
       </c>
       <c r="R11" t="n">
-        <v>6790393</v>
+        <v>6790450</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122607596</v>
+        <v>122606176</v>
       </c>
       <c r="B12" t="n">
-        <v>56594</v>
+        <v>78686</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,39 +1821,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486109</v>
+        <v>485613</v>
       </c>
       <c r="R12" t="n">
-        <v>6790384</v>
+        <v>6790370</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1885,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122606176</v>
+        <v>122607518</v>
       </c>
       <c r="B13" t="n">
-        <v>78686</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,25 +1929,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485613</v>
+        <v>486071</v>
       </c>
       <c r="R13" t="n">
-        <v>6790370</v>
+        <v>6790384</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -1997,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,7 +2029,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122607518</v>
+        <v>122606651</v>
       </c>
       <c r="B14" t="n">
         <v>78660</v>
@@ -2074,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486071</v>
+        <v>485432</v>
       </c>
       <c r="R14" t="n">
-        <v>6790384</v>
+        <v>6790417</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2109,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122606651</v>
+        <v>122607596</v>
       </c>
       <c r="B15" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,38 +2153,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485432</v>
+        <v>486109</v>
       </c>
       <c r="R15" t="n">
-        <v>6790417</v>
+        <v>6790384</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3169,7 +3169,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122606286</v>
+        <v>122606271</v>
       </c>
       <c r="B24" t="n">
         <v>78660</v>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>485541</v>
+        <v>485553</v>
       </c>
       <c r="R24" t="n">
-        <v>6790372</v>
+        <v>6790369</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3254,12 +3254,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På 3 tallar på stammen</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3286,10 +3281,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122607815</v>
+        <v>122606286</v>
       </c>
       <c r="B25" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3298,41 +3293,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486035</v>
+        <v>485541</v>
       </c>
       <c r="R25" t="n">
-        <v>6790401</v>
+        <v>6790372</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3361,7 +3356,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3371,7 +3366,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På 3 tallar på stammen</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3386,19 +3386,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122606271</v>
+        <v>122606154</v>
       </c>
       <c r="B26" t="n">
         <v>78660</v>
@@ -3438,13 +3438,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>485553</v>
+        <v>485616</v>
       </c>
       <c r="R26" t="n">
-        <v>6790369</v>
+        <v>6790354</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3498,22 +3498,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122606154</v>
+        <v>122607815</v>
       </c>
       <c r="B27" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3522,41 +3522,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>485616</v>
+        <v>486035</v>
       </c>
       <c r="R27" t="n">
-        <v>6790354</v>
+        <v>6790401</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3610,12 +3610,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122608926</v>
+        <v>122608158</v>
       </c>
       <c r="B29" t="n">
-        <v>78396</v>
+        <v>78660</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3750,34 +3750,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486252</v>
+        <v>486281</v>
       </c>
       <c r="R29" t="n">
-        <v>6790351</v>
+        <v>6790441</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3819,7 +3819,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3846,10 +3851,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122606145</v>
+        <v>122608926</v>
       </c>
       <c r="B30" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,37 +3867,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>485616</v>
+        <v>486252</v>
       </c>
       <c r="R30" t="n">
-        <v>6790356</v>
+        <v>6790351</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3921,7 +3926,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3936,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,19 +3951,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122606669</v>
+        <v>122606145</v>
       </c>
       <c r="B31" t="n">
         <v>78660</v>
@@ -3998,10 +4003,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>485407</v>
+        <v>485616</v>
       </c>
       <c r="R31" t="n">
-        <v>6790437</v>
+        <v>6790356</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4033,7 +4038,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4048,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,7 +4075,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122608158</v>
+        <v>122606669</v>
       </c>
       <c r="B32" t="n">
         <v>78660</v>
@@ -4106,17 +4111,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486281</v>
+        <v>485407</v>
       </c>
       <c r="R32" t="n">
-        <v>6790441</v>
+        <v>6790437</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4145,7 +4150,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4155,12 +4160,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4175,12 +4175,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -6554,7 +6554,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122607495</v>
+        <v>122606955</v>
       </c>
       <c r="B54" t="n">
         <v>78660</v>
@@ -6594,10 +6594,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486056</v>
+        <v>485759</v>
       </c>
       <c r="R54" t="n">
-        <v>6790394</v>
+        <v>6790467</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6666,7 +6666,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122606955</v>
+        <v>122607495</v>
       </c>
       <c r="B55" t="n">
         <v>78660</v>
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>485759</v>
+        <v>486056</v>
       </c>
       <c r="R55" t="n">
-        <v>6790467</v>
+        <v>6790394</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7816,10 +7816,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122607273</v>
+        <v>122609008</v>
       </c>
       <c r="B65" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7828,50 +7828,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>485932</v>
+        <v>486063</v>
       </c>
       <c r="R65" t="n">
-        <v>6790416</v>
+        <v>6790348</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7900,7 +7891,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7910,7 +7901,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7919,7 +7910,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7938,7 +7928,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122609064</v>
+        <v>122607273</v>
       </c>
       <c r="B66" t="n">
         <v>8441</v>
@@ -7983,17 +7973,17 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486063</v>
+        <v>485932</v>
       </c>
       <c r="R66" t="n">
-        <v>6790348</v>
+        <v>6790416</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8022,7 +8012,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8032,7 +8022,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8060,10 +8050,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122609008</v>
+        <v>122609064</v>
       </c>
       <c r="B67" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8072,28 +8062,37 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lindflot, Lindflot, Dlr</t>
@@ -8135,7 +8134,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8145,7 +8144,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8154,6 +8153,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -11532,7 +11532,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122671575</v>
+        <v>122671651</v>
       </c>
       <c r="B99" t="n">
         <v>78660</v>
@@ -11575,13 +11575,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>485989</v>
+        <v>486048</v>
       </c>
       <c r="R99" t="n">
-        <v>6790394</v>
+        <v>6790360</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11638,10 +11638,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122671424</v>
+        <v>122671523</v>
       </c>
       <c r="B100" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11654,26 +11654,31 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11681,10 +11686,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>485783</v>
+        <v>485893</v>
       </c>
       <c r="R100" t="n">
-        <v>6790367</v>
+        <v>6790386</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11725,7 +11730,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11744,10 +11748,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122671440</v>
+        <v>122671541</v>
       </c>
       <c r="B101" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11756,30 +11760,36 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11787,10 +11797,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>485819</v>
+        <v>485879</v>
       </c>
       <c r="R101" t="n">
-        <v>6790340</v>
+        <v>6790409</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11850,7 +11860,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122671651</v>
+        <v>122671575</v>
       </c>
       <c r="B102" t="n">
         <v>78660</v>
@@ -11893,13 +11903,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>486048</v>
+        <v>485989</v>
       </c>
       <c r="R102" t="n">
-        <v>6790360</v>
+        <v>6790394</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11956,10 +11966,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122671523</v>
+        <v>122671424</v>
       </c>
       <c r="B103" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11972,31 +11982,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12004,10 +12009,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>485893</v>
+        <v>485783</v>
       </c>
       <c r="R103" t="n">
-        <v>6790386</v>
+        <v>6790367</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12048,6 +12053,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -12066,10 +12072,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122671541</v>
+        <v>122671440</v>
       </c>
       <c r="B104" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12078,36 +12084,30 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>485879</v>
+        <v>485819</v>
       </c>
       <c r="R104" t="n">
-        <v>6790409</v>
+        <v>6790340</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12718,10 +12718,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122671647</v>
+        <v>122671659</v>
       </c>
       <c r="B110" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12730,30 +12730,36 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12761,13 +12767,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>486035</v>
+        <v>486020</v>
       </c>
       <c r="R110" t="n">
-        <v>6790369</v>
+        <v>6790412</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12824,10 +12830,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122671659</v>
+        <v>122671647</v>
       </c>
       <c r="B111" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12836,36 +12842,30 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12873,13 +12873,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>486020</v>
+        <v>486035</v>
       </c>
       <c r="R111" t="n">
-        <v>6790412</v>
+        <v>6790369</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122689794</v>
+        <v>122689942</v>
       </c>
       <c r="B128" t="n">
         <v>78660</v>
@@ -14679,10 +14679,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>485529</v>
+        <v>485554</v>
       </c>
       <c r="R128" t="n">
-        <v>6790463</v>
+        <v>6790400</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14742,7 +14742,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122689594</v>
+        <v>122689794</v>
       </c>
       <c r="B129" t="n">
         <v>78660</v>
@@ -14785,10 +14785,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>485662</v>
+        <v>485529</v>
       </c>
       <c r="R129" t="n">
-        <v>6790461</v>
+        <v>6790463</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14848,7 +14848,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122689942</v>
+        <v>122689594</v>
       </c>
       <c r="B130" t="n">
         <v>78660</v>
@@ -14891,10 +14891,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>485554</v>
+        <v>485662</v>
       </c>
       <c r="R130" t="n">
-        <v>6790400</v>
+        <v>6790461</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -17612,7 +17612,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122689851</v>
+        <v>122689959</v>
       </c>
       <c r="B156" t="n">
         <v>78660</v>
@@ -17655,10 +17655,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>485442</v>
+        <v>485627</v>
       </c>
       <c r="R156" t="n">
-        <v>6790462</v>
+        <v>6790392</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -17718,7 +17718,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>122689748</v>
+        <v>122689851</v>
       </c>
       <c r="B157" t="n">
         <v>78660</v>
@@ -17761,10 +17761,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>485586</v>
+        <v>485442</v>
       </c>
       <c r="R157" t="n">
-        <v>6790473</v>
+        <v>6790462</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -17824,7 +17824,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122689959</v>
+        <v>122689748</v>
       </c>
       <c r="B158" t="n">
         <v>78660</v>
@@ -17867,10 +17867,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>485627</v>
+        <v>485586</v>
       </c>
       <c r="R158" t="n">
-        <v>6790392</v>
+        <v>6790473</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -19214,10 +19214,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>122689865</v>
+        <v>122689756</v>
       </c>
       <c r="B171" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19226,36 +19226,30 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
@@ -19263,10 +19257,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>485417</v>
+        <v>485576</v>
       </c>
       <c r="R171" t="n">
-        <v>6790479</v>
+        <v>6790471</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -19326,7 +19320,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>122689756</v>
+        <v>122689899</v>
       </c>
       <c r="B172" t="n">
         <v>78660</v>
@@ -19369,10 +19363,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>485576</v>
+        <v>485399</v>
       </c>
       <c r="R172" t="n">
-        <v>6790471</v>
+        <v>6790454</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -19432,7 +19426,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>122689899</v>
+        <v>122689714</v>
       </c>
       <c r="B173" t="n">
         <v>78660</v>
@@ -19475,10 +19469,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>485399</v>
+        <v>485613</v>
       </c>
       <c r="R173" t="n">
-        <v>6790454</v>
+        <v>6790471</v>
       </c>
       <c r="S173" t="n">
         <v>5</v>
@@ -19538,7 +19532,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>122689714</v>
+        <v>122689764</v>
       </c>
       <c r="B174" t="n">
         <v>78660</v>
@@ -19581,10 +19575,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>485613</v>
+        <v>485560</v>
       </c>
       <c r="R174" t="n">
-        <v>6790471</v>
+        <v>6790469</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -19644,7 +19638,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>122689764</v>
+        <v>122689633</v>
       </c>
       <c r="B175" t="n">
         <v>78660</v>
@@ -19687,7 +19681,7 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>485560</v>
+        <v>485624</v>
       </c>
       <c r="R175" t="n">
         <v>6790469</v>
@@ -19750,7 +19744,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122689633</v>
+        <v>122689447</v>
       </c>
       <c r="B176" t="n">
         <v>78660</v>
@@ -19793,10 +19787,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>485624</v>
+        <v>485729</v>
       </c>
       <c r="R176" t="n">
-        <v>6790469</v>
+        <v>6790386</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -19856,10 +19850,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122689447</v>
+        <v>122689865</v>
       </c>
       <c r="B177" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -19868,30 +19862,36 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
@@ -19899,10 +19899,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>485729</v>
+        <v>485417</v>
       </c>
       <c r="R177" t="n">
-        <v>6790386</v>
+        <v>6790479</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -3734,10 +3734,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122608158</v>
+        <v>122608926</v>
       </c>
       <c r="B29" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3750,34 +3750,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486281</v>
+        <v>486252</v>
       </c>
       <c r="R29" t="n">
-        <v>6790441</v>
+        <v>6790351</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3819,12 +3819,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3851,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122608926</v>
+        <v>122606145</v>
       </c>
       <c r="B30" t="n">
-        <v>78396</v>
+        <v>78660</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3867,37 +3862,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486252</v>
+        <v>485616</v>
       </c>
       <c r="R30" t="n">
-        <v>6790351</v>
+        <v>6790356</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3926,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3936,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3951,19 +3946,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122606145</v>
+        <v>122606669</v>
       </c>
       <c r="B31" t="n">
         <v>78660</v>
@@ -4003,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>485616</v>
+        <v>485407</v>
       </c>
       <c r="R31" t="n">
-        <v>6790356</v>
+        <v>6790437</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4038,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4048,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4075,7 +4070,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122606669</v>
+        <v>122608158</v>
       </c>
       <c r="B32" t="n">
         <v>78660</v>
@@ -4111,17 +4106,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>485407</v>
+        <v>486281</v>
       </c>
       <c r="R32" t="n">
-        <v>6790437</v>
+        <v>6790441</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4150,7 +4145,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4160,7 +4155,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4175,12 +4175,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -6554,7 +6554,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122606955</v>
+        <v>122607495</v>
       </c>
       <c r="B54" t="n">
         <v>78660</v>
@@ -6594,10 +6594,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>485759</v>
+        <v>486056</v>
       </c>
       <c r="R54" t="n">
-        <v>6790467</v>
+        <v>6790394</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6666,7 +6666,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122607495</v>
+        <v>122606955</v>
       </c>
       <c r="B55" t="n">
         <v>78660</v>
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486056</v>
+        <v>485759</v>
       </c>
       <c r="R55" t="n">
-        <v>6790394</v>
+        <v>6790467</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7002,10 +7002,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122606760</v>
+        <v>122607227</v>
       </c>
       <c r="B58" t="n">
-        <v>57400</v>
+        <v>56594</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7014,25 +7014,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7040,7 +7040,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7122,10 +7122,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122607227</v>
+        <v>122606760</v>
       </c>
       <c r="B59" t="n">
-        <v>56594</v>
+        <v>57400</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7134,25 +7134,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7160,7 +7160,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -11532,7 +11532,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122671651</v>
+        <v>122671575</v>
       </c>
       <c r="B99" t="n">
         <v>78660</v>
@@ -11575,13 +11575,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>486048</v>
+        <v>485989</v>
       </c>
       <c r="R99" t="n">
-        <v>6790360</v>
+        <v>6790394</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11638,10 +11638,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122671523</v>
+        <v>122671424</v>
       </c>
       <c r="B100" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11654,31 +11654,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11686,10 +11681,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>485893</v>
+        <v>485783</v>
       </c>
       <c r="R100" t="n">
-        <v>6790386</v>
+        <v>6790367</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11730,6 +11725,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11748,10 +11744,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122671541</v>
+        <v>122671440</v>
       </c>
       <c r="B101" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11760,36 +11756,30 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11797,10 +11787,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>485879</v>
+        <v>485819</v>
       </c>
       <c r="R101" t="n">
-        <v>6790409</v>
+        <v>6790340</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11860,7 +11850,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122671575</v>
+        <v>122671651</v>
       </c>
       <c r="B102" t="n">
         <v>78660</v>
@@ -11903,13 +11893,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>485989</v>
+        <v>486048</v>
       </c>
       <c r="R102" t="n">
-        <v>6790394</v>
+        <v>6790360</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11966,10 +11956,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122671424</v>
+        <v>122671523</v>
       </c>
       <c r="B103" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11982,26 +11972,31 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12009,10 +12004,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>485783</v>
+        <v>485893</v>
       </c>
       <c r="R103" t="n">
-        <v>6790367</v>
+        <v>6790386</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12053,7 +12048,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -12072,10 +12066,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122671440</v>
+        <v>122671541</v>
       </c>
       <c r="B104" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12084,30 +12078,36 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>485819</v>
+        <v>485879</v>
       </c>
       <c r="R104" t="n">
-        <v>6790340</v>
+        <v>6790409</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12718,10 +12718,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122671659</v>
+        <v>122671647</v>
       </c>
       <c r="B110" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12730,36 +12730,30 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12767,13 +12761,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>486020</v>
+        <v>486035</v>
       </c>
       <c r="R110" t="n">
-        <v>6790412</v>
+        <v>6790369</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12830,10 +12824,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122671647</v>
+        <v>122671659</v>
       </c>
       <c r="B111" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12842,30 +12836,36 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12873,13 +12873,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>486035</v>
+        <v>486020</v>
       </c>
       <c r="R111" t="n">
-        <v>6790369</v>
+        <v>6790412</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122689626</v>
+        <v>122689540</v>
       </c>
       <c r="B124" t="n">
         <v>78660</v>
@@ -14255,10 +14255,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>485638</v>
+        <v>485689</v>
       </c>
       <c r="R124" t="n">
-        <v>6790452</v>
+        <v>6790436</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14318,7 +14318,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122689838</v>
+        <v>122689833</v>
       </c>
       <c r="B125" t="n">
         <v>78660</v>
@@ -14361,10 +14361,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>485452</v>
+        <v>485457</v>
       </c>
       <c r="R125" t="n">
-        <v>6790453</v>
+        <v>6790457</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14424,7 +14424,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122689540</v>
+        <v>122689838</v>
       </c>
       <c r="B126" t="n">
         <v>78660</v>
@@ -14467,10 +14467,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>485689</v>
+        <v>485452</v>
       </c>
       <c r="R126" t="n">
-        <v>6790436</v>
+        <v>6790453</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14530,7 +14530,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122689833</v>
+        <v>122689626</v>
       </c>
       <c r="B127" t="n">
         <v>78660</v>
@@ -14573,10 +14573,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>485457</v>
+        <v>485638</v>
       </c>
       <c r="R127" t="n">
-        <v>6790457</v>
+        <v>6790452</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -18354,10 +18354,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122689723</v>
+        <v>122689829</v>
       </c>
       <c r="B163" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18366,36 +18366,30 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
@@ -18403,10 +18397,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>485609</v>
+        <v>485469</v>
       </c>
       <c r="R163" t="n">
-        <v>6790472</v>
+        <v>6790456</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -18466,7 +18460,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>122689829</v>
+        <v>122689933</v>
       </c>
       <c r="B164" t="n">
         <v>78660</v>
@@ -18509,10 +18503,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>485469</v>
+        <v>485524</v>
       </c>
       <c r="R164" t="n">
-        <v>6790456</v>
+        <v>6790423</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18572,7 +18566,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122689933</v>
+        <v>122689924</v>
       </c>
       <c r="B165" t="n">
         <v>78660</v>
@@ -18615,10 +18609,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>485524</v>
+        <v>485489</v>
       </c>
       <c r="R165" t="n">
-        <v>6790423</v>
+        <v>6790405</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18678,7 +18672,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122689924</v>
+        <v>122689630</v>
       </c>
       <c r="B166" t="n">
         <v>78660</v>
@@ -18721,10 +18715,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>485489</v>
+        <v>485638</v>
       </c>
       <c r="R166" t="n">
-        <v>6790405</v>
+        <v>6790456</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -18784,10 +18778,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>122689630</v>
+        <v>122689723</v>
       </c>
       <c r="B167" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18796,30 +18790,36 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
@@ -18827,10 +18827,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>485638</v>
+        <v>485609</v>
       </c>
       <c r="R167" t="n">
-        <v>6790456</v>
+        <v>6790472</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122606308</v>
+        <v>122607224</v>
       </c>
       <c r="B5" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,41 +1023,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485568</v>
+        <v>485981</v>
       </c>
       <c r="R5" t="n">
-        <v>6790397</v>
+        <v>6790453</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122607224</v>
+        <v>122606308</v>
       </c>
       <c r="B6" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,46 +1140,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485981</v>
+        <v>485568</v>
       </c>
       <c r="R6" t="n">
-        <v>6790453</v>
+        <v>6790397</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,12 +1228,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122606176</v>
+        <v>122607596</v>
       </c>
       <c r="B12" t="n">
-        <v>78686</v>
+        <v>56594</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,34 +1821,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485613</v>
+        <v>486109</v>
       </c>
       <c r="R12" t="n">
-        <v>6790370</v>
+        <v>6790384</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1880,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122607518</v>
+        <v>122606176</v>
       </c>
       <c r="B13" t="n">
-        <v>78660</v>
+        <v>78686</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,25 +1934,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486071</v>
+        <v>485613</v>
       </c>
       <c r="R13" t="n">
-        <v>6790384</v>
+        <v>6790370</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -1992,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,7 +2034,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606651</v>
+        <v>122607518</v>
       </c>
       <c r="B14" t="n">
         <v>78660</v>
@@ -2069,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485432</v>
+        <v>486071</v>
       </c>
       <c r="R14" t="n">
-        <v>6790417</v>
+        <v>6790384</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2104,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122607596</v>
+        <v>122606651</v>
       </c>
       <c r="B15" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2153,43 +2158,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486109</v>
+        <v>485432</v>
       </c>
       <c r="R15" t="n">
-        <v>6790384</v>
+        <v>6790417</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3169,7 +3169,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122606271</v>
+        <v>122606286</v>
       </c>
       <c r="B24" t="n">
         <v>78660</v>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>485553</v>
+        <v>485541</v>
       </c>
       <c r="R24" t="n">
-        <v>6790369</v>
+        <v>6790372</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3254,7 +3254,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På 3 tallar på stammen</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3281,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122606286</v>
+        <v>122607815</v>
       </c>
       <c r="B25" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3293,41 +3298,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>485541</v>
+        <v>486035</v>
       </c>
       <c r="R25" t="n">
-        <v>6790372</v>
+        <v>6790401</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3356,7 +3361,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3366,12 +3371,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På 3 tallar på stammen</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3386,19 +3386,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122606154</v>
+        <v>122606271</v>
       </c>
       <c r="B26" t="n">
         <v>78660</v>
@@ -3438,13 +3438,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>485616</v>
+        <v>485553</v>
       </c>
       <c r="R26" t="n">
-        <v>6790354</v>
+        <v>6790369</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3498,22 +3498,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122607815</v>
+        <v>122606154</v>
       </c>
       <c r="B27" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3522,41 +3522,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486035</v>
+        <v>485616</v>
       </c>
       <c r="R27" t="n">
-        <v>6790401</v>
+        <v>6790354</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3610,12 +3610,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122608926</v>
+        <v>122608158</v>
       </c>
       <c r="B29" t="n">
-        <v>78396</v>
+        <v>78660</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3750,34 +3750,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486252</v>
+        <v>486281</v>
       </c>
       <c r="R29" t="n">
-        <v>6790351</v>
+        <v>6790441</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3819,7 +3819,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3846,10 +3851,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122606145</v>
+        <v>122608926</v>
       </c>
       <c r="B30" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,37 +3867,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>485616</v>
+        <v>486252</v>
       </c>
       <c r="R30" t="n">
-        <v>6790356</v>
+        <v>6790351</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3921,7 +3926,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3936,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,19 +3951,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122606669</v>
+        <v>122606145</v>
       </c>
       <c r="B31" t="n">
         <v>78660</v>
@@ -3998,10 +4003,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>485407</v>
+        <v>485616</v>
       </c>
       <c r="R31" t="n">
-        <v>6790437</v>
+        <v>6790356</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4033,7 +4038,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4048,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,7 +4075,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122608158</v>
+        <v>122606669</v>
       </c>
       <c r="B32" t="n">
         <v>78660</v>
@@ -4106,17 +4111,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486281</v>
+        <v>485407</v>
       </c>
       <c r="R32" t="n">
-        <v>6790441</v>
+        <v>6790437</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4145,7 +4150,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4155,12 +4160,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4175,12 +4175,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -5653,10 +5653,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122606977</v>
+        <v>122607953</v>
       </c>
       <c r="B46" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5665,25 +5665,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>485766</v>
+        <v>486214</v>
       </c>
       <c r="R46" t="n">
-        <v>6790457</v>
+        <v>6790429</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5738,12 +5738,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5770,7 +5765,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122606677</v>
+        <v>122606977</v>
       </c>
       <c r="B47" t="n">
         <v>78660</v>
@@ -5810,10 +5805,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>485490</v>
+        <v>485766</v>
       </c>
       <c r="R47" t="n">
-        <v>6790430</v>
+        <v>6790457</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5845,7 +5840,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5855,7 +5850,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5882,7 +5882,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122608110</v>
+        <v>122606677</v>
       </c>
       <c r="B48" t="n">
         <v>78660</v>
@@ -5918,14 +5918,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486270</v>
+        <v>485490</v>
       </c>
       <c r="R48" t="n">
-        <v>6790427</v>
+        <v>6790430</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5994,10 +5994,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122607953</v>
+        <v>122608110</v>
       </c>
       <c r="B49" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6006,38 +6006,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486214</v>
+        <v>486270</v>
       </c>
       <c r="R49" t="n">
-        <v>6790429</v>
+        <v>6790427</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6554,7 +6554,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122607495</v>
+        <v>122606955</v>
       </c>
       <c r="B54" t="n">
         <v>78660</v>
@@ -6594,10 +6594,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486056</v>
+        <v>485759</v>
       </c>
       <c r="R54" t="n">
-        <v>6790394</v>
+        <v>6790467</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6666,7 +6666,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122606955</v>
+        <v>122607495</v>
       </c>
       <c r="B55" t="n">
         <v>78660</v>
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>485759</v>
+        <v>486056</v>
       </c>
       <c r="R55" t="n">
-        <v>6790467</v>
+        <v>6790394</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7002,10 +7002,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122607227</v>
+        <v>122606760</v>
       </c>
       <c r="B58" t="n">
-        <v>56594</v>
+        <v>57400</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7014,25 +7014,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7040,7 +7040,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7122,10 +7122,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122606760</v>
+        <v>122607227</v>
       </c>
       <c r="B59" t="n">
-        <v>57400</v>
+        <v>56594</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7134,25 +7134,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7160,7 +7160,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -10039,10 +10039,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122671610</v>
+        <v>122671675</v>
       </c>
       <c r="B85" t="n">
-        <v>78396</v>
+        <v>78660</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10055,21 +10055,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10082,13 +10082,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486013</v>
+        <v>486331</v>
       </c>
       <c r="R85" t="n">
-        <v>6790366</v>
+        <v>6790370</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10145,10 +10145,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122671675</v>
+        <v>122671610</v>
       </c>
       <c r="B86" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10161,21 +10161,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10188,13 +10188,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486331</v>
+        <v>486013</v>
       </c>
       <c r="R86" t="n">
-        <v>6790370</v>
+        <v>6790366</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122671575</v>
+        <v>122671651</v>
       </c>
       <c r="B99" t="n">
         <v>78660</v>
@@ -11575,13 +11575,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>485989</v>
+        <v>486048</v>
       </c>
       <c r="R99" t="n">
-        <v>6790394</v>
+        <v>6790360</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11638,10 +11638,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122671424</v>
+        <v>122671523</v>
       </c>
       <c r="B100" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11654,26 +11654,31 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11681,10 +11686,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>485783</v>
+        <v>485893</v>
       </c>
       <c r="R100" t="n">
-        <v>6790367</v>
+        <v>6790386</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11725,7 +11730,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11744,10 +11748,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122671440</v>
+        <v>122671541</v>
       </c>
       <c r="B101" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11756,30 +11760,36 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11787,10 +11797,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>485819</v>
+        <v>485879</v>
       </c>
       <c r="R101" t="n">
-        <v>6790340</v>
+        <v>6790409</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11850,7 +11860,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122671651</v>
+        <v>122671575</v>
       </c>
       <c r="B102" t="n">
         <v>78660</v>
@@ -11893,13 +11903,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>486048</v>
+        <v>485989</v>
       </c>
       <c r="R102" t="n">
-        <v>6790360</v>
+        <v>6790394</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11956,10 +11966,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122671523</v>
+        <v>122671424</v>
       </c>
       <c r="B103" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11972,31 +11982,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12004,10 +12009,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>485893</v>
+        <v>485783</v>
       </c>
       <c r="R103" t="n">
-        <v>6790386</v>
+        <v>6790367</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12048,6 +12053,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -12066,10 +12072,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122671541</v>
+        <v>122671440</v>
       </c>
       <c r="B104" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12078,36 +12084,30 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>485879</v>
+        <v>485819</v>
       </c>
       <c r="R104" t="n">
-        <v>6790409</v>
+        <v>6790340</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -14636,7 +14636,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122689942</v>
+        <v>122689794</v>
       </c>
       <c r="B128" t="n">
         <v>78660</v>
@@ -14679,10 +14679,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>485554</v>
+        <v>485529</v>
       </c>
       <c r="R128" t="n">
-        <v>6790400</v>
+        <v>6790463</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14742,7 +14742,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122689794</v>
+        <v>122689594</v>
       </c>
       <c r="B129" t="n">
         <v>78660</v>
@@ -14785,10 +14785,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>485529</v>
+        <v>485662</v>
       </c>
       <c r="R129" t="n">
-        <v>6790463</v>
+        <v>6790461</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14848,7 +14848,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122689594</v>
+        <v>122689942</v>
       </c>
       <c r="B130" t="n">
         <v>78660</v>
@@ -14891,10 +14891,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>485662</v>
+        <v>485554</v>
       </c>
       <c r="R130" t="n">
-        <v>6790461</v>
+        <v>6790400</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -17612,7 +17612,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122689959</v>
+        <v>122689851</v>
       </c>
       <c r="B156" t="n">
         <v>78660</v>
@@ -17655,10 +17655,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>485627</v>
+        <v>485442</v>
       </c>
       <c r="R156" t="n">
-        <v>6790392</v>
+        <v>6790462</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -17718,7 +17718,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>122689851</v>
+        <v>122689748</v>
       </c>
       <c r="B157" t="n">
         <v>78660</v>
@@ -17761,10 +17761,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>485442</v>
+        <v>485586</v>
       </c>
       <c r="R157" t="n">
-        <v>6790462</v>
+        <v>6790473</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -17824,7 +17824,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122689748</v>
+        <v>122689959</v>
       </c>
       <c r="B158" t="n">
         <v>78660</v>
@@ -17867,10 +17867,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>485586</v>
+        <v>485627</v>
       </c>
       <c r="R158" t="n">
-        <v>6790473</v>
+        <v>6790392</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -18354,10 +18354,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122689829</v>
+        <v>122689723</v>
       </c>
       <c r="B163" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18366,30 +18366,36 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
@@ -18397,10 +18403,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>485469</v>
+        <v>485609</v>
       </c>
       <c r="R163" t="n">
-        <v>6790456</v>
+        <v>6790472</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -18460,7 +18466,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>122689933</v>
+        <v>122689829</v>
       </c>
       <c r="B164" t="n">
         <v>78660</v>
@@ -18503,10 +18509,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>485524</v>
+        <v>485469</v>
       </c>
       <c r="R164" t="n">
-        <v>6790423</v>
+        <v>6790456</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18566,7 +18572,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122689924</v>
+        <v>122689933</v>
       </c>
       <c r="B165" t="n">
         <v>78660</v>
@@ -18609,10 +18615,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>485489</v>
+        <v>485524</v>
       </c>
       <c r="R165" t="n">
-        <v>6790405</v>
+        <v>6790423</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18672,7 +18678,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122689630</v>
+        <v>122689924</v>
       </c>
       <c r="B166" t="n">
         <v>78660</v>
@@ -18715,10 +18721,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>485638</v>
+        <v>485489</v>
       </c>
       <c r="R166" t="n">
-        <v>6790456</v>
+        <v>6790405</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -18778,10 +18784,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>122689723</v>
+        <v>122689630</v>
       </c>
       <c r="B167" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18790,36 +18796,30 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
@@ -18827,10 +18827,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>485609</v>
+        <v>485638</v>
       </c>
       <c r="R167" t="n">
-        <v>6790472</v>
+        <v>6790456</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -20386,7 +20386,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122689596</v>
+        <v>122689611</v>
       </c>
       <c r="B182" t="n">
         <v>78660</v>
@@ -20429,10 +20429,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>485656</v>
+        <v>485653</v>
       </c>
       <c r="R182" t="n">
-        <v>6790462</v>
+        <v>6790460</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -20492,7 +20492,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>122689761</v>
+        <v>122689617</v>
       </c>
       <c r="B183" t="n">
         <v>78660</v>
@@ -20535,10 +20535,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>485563</v>
+        <v>485646</v>
       </c>
       <c r="R183" t="n">
-        <v>6790470</v>
+        <v>6790453</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -20598,7 +20598,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122689872</v>
+        <v>122689596</v>
       </c>
       <c r="B184" t="n">
         <v>78660</v>
@@ -20641,10 +20641,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>485412</v>
+        <v>485656</v>
       </c>
       <c r="R184" t="n">
-        <v>6790481</v>
+        <v>6790462</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -20704,7 +20704,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>122689611</v>
+        <v>122689761</v>
       </c>
       <c r="B185" t="n">
         <v>78660</v>
@@ -20747,10 +20747,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>485653</v>
+        <v>485563</v>
       </c>
       <c r="R185" t="n">
-        <v>6790460</v>
+        <v>6790470</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -20810,7 +20810,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122689617</v>
+        <v>122689872</v>
       </c>
       <c r="B186" t="n">
         <v>78660</v>
@@ -20853,10 +20853,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>485646</v>
+        <v>485412</v>
       </c>
       <c r="R186" t="n">
-        <v>6790453</v>
+        <v>6790481</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -1805,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122607596</v>
+        <v>122606176</v>
       </c>
       <c r="B12" t="n">
-        <v>56594</v>
+        <v>78686</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,39 +1821,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486109</v>
+        <v>485613</v>
       </c>
       <c r="R12" t="n">
-        <v>6790384</v>
+        <v>6790370</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1885,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122606176</v>
+        <v>122607518</v>
       </c>
       <c r="B13" t="n">
-        <v>78686</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,25 +1929,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485613</v>
+        <v>486071</v>
       </c>
       <c r="R13" t="n">
-        <v>6790370</v>
+        <v>6790384</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -1997,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,7 +2029,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122607518</v>
+        <v>122606651</v>
       </c>
       <c r="B14" t="n">
         <v>78660</v>
@@ -2074,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486071</v>
+        <v>485432</v>
       </c>
       <c r="R14" t="n">
-        <v>6790384</v>
+        <v>6790417</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2109,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122606651</v>
+        <v>122607596</v>
       </c>
       <c r="B15" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,38 +2153,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485432</v>
+        <v>486109</v>
       </c>
       <c r="R15" t="n">
-        <v>6790417</v>
+        <v>6790384</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3169,7 +3169,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122606286</v>
+        <v>122606271</v>
       </c>
       <c r="B24" t="n">
         <v>78660</v>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>485541</v>
+        <v>485553</v>
       </c>
       <c r="R24" t="n">
-        <v>6790372</v>
+        <v>6790369</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3254,12 +3254,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På 3 tallar på stammen</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3286,10 +3281,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122607815</v>
+        <v>122606286</v>
       </c>
       <c r="B25" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3298,41 +3293,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486035</v>
+        <v>485541</v>
       </c>
       <c r="R25" t="n">
-        <v>6790401</v>
+        <v>6790372</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3361,7 +3356,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3371,7 +3366,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På 3 tallar på stammen</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3386,19 +3386,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122606271</v>
+        <v>122606154</v>
       </c>
       <c r="B26" t="n">
         <v>78660</v>
@@ -3438,13 +3438,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>485553</v>
+        <v>485616</v>
       </c>
       <c r="R26" t="n">
-        <v>6790369</v>
+        <v>6790354</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3498,22 +3498,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122606154</v>
+        <v>122607815</v>
       </c>
       <c r="B27" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3522,41 +3522,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>485616</v>
+        <v>486035</v>
       </c>
       <c r="R27" t="n">
-        <v>6790354</v>
+        <v>6790401</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3610,12 +3610,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -10039,10 +10039,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122671675</v>
+        <v>122671610</v>
       </c>
       <c r="B85" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10055,21 +10055,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10082,13 +10082,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486331</v>
+        <v>486013</v>
       </c>
       <c r="R85" t="n">
-        <v>6790370</v>
+        <v>6790366</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10145,10 +10145,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122671610</v>
+        <v>122671675</v>
       </c>
       <c r="B86" t="n">
-        <v>78396</v>
+        <v>78660</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10161,21 +10161,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10188,13 +10188,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486013</v>
+        <v>486331</v>
       </c>
       <c r="R86" t="n">
-        <v>6790366</v>
+        <v>6790370</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122671651</v>
+        <v>122671575</v>
       </c>
       <c r="B99" t="n">
         <v>78660</v>
@@ -11575,13 +11575,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>486048</v>
+        <v>485989</v>
       </c>
       <c r="R99" t="n">
-        <v>6790360</v>
+        <v>6790394</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11638,10 +11638,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122671523</v>
+        <v>122671424</v>
       </c>
       <c r="B100" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11654,31 +11654,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11686,10 +11681,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>485893</v>
+        <v>485783</v>
       </c>
       <c r="R100" t="n">
-        <v>6790386</v>
+        <v>6790367</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11730,6 +11725,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11748,10 +11744,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122671541</v>
+        <v>122671440</v>
       </c>
       <c r="B101" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11760,36 +11756,30 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11797,10 +11787,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>485879</v>
+        <v>485819</v>
       </c>
       <c r="R101" t="n">
-        <v>6790409</v>
+        <v>6790340</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11860,7 +11850,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122671575</v>
+        <v>122671651</v>
       </c>
       <c r="B102" t="n">
         <v>78660</v>
@@ -11903,13 +11893,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>485989</v>
+        <v>486048</v>
       </c>
       <c r="R102" t="n">
-        <v>6790394</v>
+        <v>6790360</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11966,10 +11956,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122671424</v>
+        <v>122671523</v>
       </c>
       <c r="B103" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11982,26 +11972,31 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12009,10 +12004,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>485783</v>
+        <v>485893</v>
       </c>
       <c r="R103" t="n">
-        <v>6790367</v>
+        <v>6790386</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12053,7 +12048,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -12072,10 +12066,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122671440</v>
+        <v>122671541</v>
       </c>
       <c r="B104" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12084,30 +12078,36 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>485819</v>
+        <v>485879</v>
       </c>
       <c r="R104" t="n">
-        <v>6790340</v>
+        <v>6790409</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12718,10 +12718,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122671647</v>
+        <v>122671659</v>
       </c>
       <c r="B110" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12730,30 +12730,36 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12761,13 +12767,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>486035</v>
+        <v>486020</v>
       </c>
       <c r="R110" t="n">
-        <v>6790369</v>
+        <v>6790412</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12824,10 +12830,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122671659</v>
+        <v>122671647</v>
       </c>
       <c r="B111" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12836,36 +12842,30 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12873,13 +12873,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>486020</v>
+        <v>486035</v>
       </c>
       <c r="R111" t="n">
-        <v>6790412</v>
+        <v>6790369</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122689851</v>
+        <v>122689959</v>
       </c>
       <c r="B156" t="n">
         <v>78660</v>
@@ -17655,10 +17655,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>485442</v>
+        <v>485627</v>
       </c>
       <c r="R156" t="n">
-        <v>6790462</v>
+        <v>6790392</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -17718,7 +17718,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>122689748</v>
+        <v>122689851</v>
       </c>
       <c r="B157" t="n">
         <v>78660</v>
@@ -17761,10 +17761,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>485586</v>
+        <v>485442</v>
       </c>
       <c r="R157" t="n">
-        <v>6790473</v>
+        <v>6790462</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -17824,7 +17824,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122689959</v>
+        <v>122689748</v>
       </c>
       <c r="B158" t="n">
         <v>78660</v>
@@ -17867,10 +17867,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>485627</v>
+        <v>485586</v>
       </c>
       <c r="R158" t="n">
-        <v>6790392</v>
+        <v>6790473</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -19214,10 +19214,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>122689756</v>
+        <v>122689865</v>
       </c>
       <c r="B171" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19226,30 +19226,36 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
@@ -19257,10 +19263,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>485576</v>
+        <v>485417</v>
       </c>
       <c r="R171" t="n">
-        <v>6790471</v>
+        <v>6790479</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -19320,7 +19326,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>122689899</v>
+        <v>122689756</v>
       </c>
       <c r="B172" t="n">
         <v>78660</v>
@@ -19363,10 +19369,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>485399</v>
+        <v>485576</v>
       </c>
       <c r="R172" t="n">
-        <v>6790454</v>
+        <v>6790471</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -19426,7 +19432,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>122689714</v>
+        <v>122689899</v>
       </c>
       <c r="B173" t="n">
         <v>78660</v>
@@ -19469,10 +19475,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>485613</v>
+        <v>485399</v>
       </c>
       <c r="R173" t="n">
-        <v>6790471</v>
+        <v>6790454</v>
       </c>
       <c r="S173" t="n">
         <v>5</v>
@@ -19532,7 +19538,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>122689764</v>
+        <v>122689714</v>
       </c>
       <c r="B174" t="n">
         <v>78660</v>
@@ -19575,10 +19581,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>485560</v>
+        <v>485613</v>
       </c>
       <c r="R174" t="n">
-        <v>6790469</v>
+        <v>6790471</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -19638,7 +19644,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>122689633</v>
+        <v>122689764</v>
       </c>
       <c r="B175" t="n">
         <v>78660</v>
@@ -19681,7 +19687,7 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>485624</v>
+        <v>485560</v>
       </c>
       <c r="R175" t="n">
         <v>6790469</v>
@@ -19744,7 +19750,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122689447</v>
+        <v>122689633</v>
       </c>
       <c r="B176" t="n">
         <v>78660</v>
@@ -19787,10 +19793,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>485729</v>
+        <v>485624</v>
       </c>
       <c r="R176" t="n">
-        <v>6790386</v>
+        <v>6790469</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -19850,10 +19856,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122689865</v>
+        <v>122689447</v>
       </c>
       <c r="B177" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -19862,36 +19868,30 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
@@ -19899,10 +19899,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>485417</v>
+        <v>485729</v>
       </c>
       <c r="R177" t="n">
-        <v>6790479</v>
+        <v>6790386</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -1805,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122606176</v>
+        <v>122607596</v>
       </c>
       <c r="B12" t="n">
-        <v>78686</v>
+        <v>56594</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,34 +1821,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485613</v>
+        <v>486109</v>
       </c>
       <c r="R12" t="n">
-        <v>6790370</v>
+        <v>6790384</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1880,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122607518</v>
+        <v>122606176</v>
       </c>
       <c r="B13" t="n">
-        <v>78660</v>
+        <v>78686</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,25 +1934,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486071</v>
+        <v>485613</v>
       </c>
       <c r="R13" t="n">
-        <v>6790384</v>
+        <v>6790370</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -1992,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,7 +2034,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606651</v>
+        <v>122607518</v>
       </c>
       <c r="B14" t="n">
         <v>78660</v>
@@ -2069,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485432</v>
+        <v>486071</v>
       </c>
       <c r="R14" t="n">
-        <v>6790417</v>
+        <v>6790384</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2104,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122607596</v>
+        <v>122606651</v>
       </c>
       <c r="B15" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2153,43 +2158,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486109</v>
+        <v>485432</v>
       </c>
       <c r="R15" t="n">
-        <v>6790384</v>
+        <v>6790417</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3169,7 +3169,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122606271</v>
+        <v>122606286</v>
       </c>
       <c r="B24" t="n">
         <v>78660</v>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>485553</v>
+        <v>485541</v>
       </c>
       <c r="R24" t="n">
-        <v>6790369</v>
+        <v>6790372</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3254,7 +3254,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På 3 tallar på stammen</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3281,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122606286</v>
+        <v>122607815</v>
       </c>
       <c r="B25" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3293,41 +3298,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>485541</v>
+        <v>486035</v>
       </c>
       <c r="R25" t="n">
-        <v>6790372</v>
+        <v>6790401</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3356,7 +3361,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3366,12 +3371,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På 3 tallar på stammen</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3386,19 +3386,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122606154</v>
+        <v>122606271</v>
       </c>
       <c r="B26" t="n">
         <v>78660</v>
@@ -3438,13 +3438,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>485616</v>
+        <v>485553</v>
       </c>
       <c r="R26" t="n">
-        <v>6790354</v>
+        <v>6790369</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3498,22 +3498,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122607815</v>
+        <v>122606154</v>
       </c>
       <c r="B27" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3522,41 +3522,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486035</v>
+        <v>485616</v>
       </c>
       <c r="R27" t="n">
-        <v>6790401</v>
+        <v>6790354</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3610,12 +3610,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122608158</v>
+        <v>122608926</v>
       </c>
       <c r="B29" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3750,34 +3750,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486281</v>
+        <v>486252</v>
       </c>
       <c r="R29" t="n">
-        <v>6790441</v>
+        <v>6790351</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3819,12 +3819,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3851,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122608926</v>
+        <v>122606145</v>
       </c>
       <c r="B30" t="n">
-        <v>78396</v>
+        <v>78660</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3867,37 +3862,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486252</v>
+        <v>485616</v>
       </c>
       <c r="R30" t="n">
-        <v>6790351</v>
+        <v>6790356</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3926,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3936,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3951,19 +3946,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122606145</v>
+        <v>122606669</v>
       </c>
       <c r="B31" t="n">
         <v>78660</v>
@@ -4003,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>485616</v>
+        <v>485407</v>
       </c>
       <c r="R31" t="n">
-        <v>6790356</v>
+        <v>6790437</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4038,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4048,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4075,7 +4070,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122606669</v>
+        <v>122608158</v>
       </c>
       <c r="B32" t="n">
         <v>78660</v>
@@ -4111,17 +4106,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>485407</v>
+        <v>486281</v>
       </c>
       <c r="R32" t="n">
-        <v>6790437</v>
+        <v>6790441</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4150,7 +4145,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4160,7 +4155,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4175,12 +4175,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -7002,10 +7002,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122606760</v>
+        <v>122607227</v>
       </c>
       <c r="B58" t="n">
-        <v>57400</v>
+        <v>56594</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7014,25 +7014,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7040,7 +7040,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7122,10 +7122,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122607227</v>
+        <v>122606760</v>
       </c>
       <c r="B59" t="n">
-        <v>56594</v>
+        <v>57400</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7134,25 +7134,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7160,7 +7160,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7816,10 +7816,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122609008</v>
+        <v>122607273</v>
       </c>
       <c r="B65" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7828,41 +7828,50 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486063</v>
+        <v>485932</v>
       </c>
       <c r="R65" t="n">
-        <v>6790348</v>
+        <v>6790416</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7891,7 +7900,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7901,7 +7910,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7910,6 +7919,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7928,7 +7938,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122607273</v>
+        <v>122609064</v>
       </c>
       <c r="B66" t="n">
         <v>8441</v>
@@ -7973,17 +7983,17 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>485932</v>
+        <v>486063</v>
       </c>
       <c r="R66" t="n">
-        <v>6790416</v>
+        <v>6790348</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8012,7 +8022,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8022,7 +8032,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8050,10 +8060,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122609064</v>
+        <v>122609008</v>
       </c>
       <c r="B67" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8062,37 +8072,28 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lindflot, Lindflot, Dlr</t>
@@ -8134,7 +8135,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8144,7 +8145,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8153,7 +8154,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -11532,7 +11532,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122671575</v>
+        <v>122671651</v>
       </c>
       <c r="B99" t="n">
         <v>78660</v>
@@ -11575,13 +11575,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>485989</v>
+        <v>486048</v>
       </c>
       <c r="R99" t="n">
-        <v>6790394</v>
+        <v>6790360</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11638,10 +11638,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122671424</v>
+        <v>122671523</v>
       </c>
       <c r="B100" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11654,26 +11654,31 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11681,10 +11686,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>485783</v>
+        <v>485893</v>
       </c>
       <c r="R100" t="n">
-        <v>6790367</v>
+        <v>6790386</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11725,7 +11730,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11744,10 +11748,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122671440</v>
+        <v>122671541</v>
       </c>
       <c r="B101" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11756,30 +11760,36 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11787,10 +11797,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>485819</v>
+        <v>485879</v>
       </c>
       <c r="R101" t="n">
-        <v>6790340</v>
+        <v>6790409</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11850,7 +11860,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122671651</v>
+        <v>122671575</v>
       </c>
       <c r="B102" t="n">
         <v>78660</v>
@@ -11893,13 +11903,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>486048</v>
+        <v>485989</v>
       </c>
       <c r="R102" t="n">
-        <v>6790360</v>
+        <v>6790394</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11956,10 +11966,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122671523</v>
+        <v>122671424</v>
       </c>
       <c r="B103" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11972,31 +11982,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12004,10 +12009,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>485893</v>
+        <v>485783</v>
       </c>
       <c r="R103" t="n">
-        <v>6790386</v>
+        <v>6790367</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12048,6 +12053,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -12066,10 +12072,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122671541</v>
+        <v>122671440</v>
       </c>
       <c r="B104" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12078,36 +12084,30 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>485879</v>
+        <v>485819</v>
       </c>
       <c r="R104" t="n">
-        <v>6790409</v>
+        <v>6790340</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12718,10 +12718,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122671659</v>
+        <v>122671647</v>
       </c>
       <c r="B110" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12730,36 +12730,30 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12767,13 +12761,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>486020</v>
+        <v>486035</v>
       </c>
       <c r="R110" t="n">
-        <v>6790412</v>
+        <v>6790369</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12830,10 +12824,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122671647</v>
+        <v>122671659</v>
       </c>
       <c r="B111" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12842,30 +12836,36 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12873,13 +12873,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>486035</v>
+        <v>486020</v>
       </c>
       <c r="R111" t="n">
-        <v>6790369</v>
+        <v>6790412</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -1912,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122608856</v>
+        <v>122606452</v>
       </c>
       <c r="B13" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1924,38 +1924,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486343</v>
+        <v>485428</v>
       </c>
       <c r="R13" t="n">
-        <v>6790373</v>
+        <v>6790393</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606452</v>
+        <v>122608856</v>
       </c>
       <c r="B14" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,38 +2036,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485428</v>
+        <v>486343</v>
       </c>
       <c r="R14" t="n">
-        <v>6790393</v>
+        <v>6790373</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2360,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122607118</v>
+        <v>122606118</v>
       </c>
       <c r="B17" t="n">
-        <v>56688</v>
+        <v>78762</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2372,46 +2372,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485884</v>
+        <v>485662</v>
       </c>
       <c r="R17" t="n">
-        <v>6790450</v>
+        <v>6790357</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2440,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,19 +2460,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122606118</v>
+        <v>122606919</v>
       </c>
       <c r="B18" t="n">
         <v>78762</v>
@@ -2513,17 +2508,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485662</v>
+        <v>485753</v>
       </c>
       <c r="R18" t="n">
-        <v>6790357</v>
+        <v>6790423</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2552,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,19 +2572,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122606919</v>
+        <v>122607665</v>
       </c>
       <c r="B19" t="n">
         <v>78762</v>
@@ -2625,17 +2620,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>485753</v>
+        <v>486035</v>
       </c>
       <c r="R19" t="n">
-        <v>6790423</v>
+        <v>6790401</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2664,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2689,19 +2684,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122607665</v>
+        <v>122606286</v>
       </c>
       <c r="B20" t="n">
         <v>78762</v>
@@ -2737,17 +2732,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486035</v>
+        <v>485541</v>
       </c>
       <c r="R20" t="n">
-        <v>6790401</v>
+        <v>6790372</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2776,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2781,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På 3 tallar på stammen</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,19 +2801,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122606286</v>
+        <v>122609017</v>
       </c>
       <c r="B21" t="n">
         <v>78762</v>
@@ -2849,14 +2849,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>485541</v>
+        <v>486064</v>
       </c>
       <c r="R21" t="n">
-        <v>6790372</v>
+        <v>6790364</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,12 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På 3 tallar på stammen</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122609017</v>
+        <v>122607118</v>
       </c>
       <c r="B22" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2942,38 +2937,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486064</v>
+        <v>485884</v>
       </c>
       <c r="R22" t="n">
-        <v>6790364</v>
+        <v>6790450</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4167,10 +4167,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122607254</v>
+        <v>122606208</v>
       </c>
       <c r="B33" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4179,25 +4179,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486016</v>
+        <v>485592</v>
       </c>
       <c r="R33" t="n">
-        <v>6790443</v>
+        <v>6790353</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4279,7 +4279,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122608990</v>
+        <v>122607254</v>
       </c>
       <c r="B34" t="n">
         <v>78762</v>
@@ -4315,14 +4315,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486070</v>
+        <v>486016</v>
       </c>
       <c r="R34" t="n">
-        <v>6790363</v>
+        <v>6790443</v>
       </c>
       <c r="S34" t="n">
         <v>9</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4391,10 +4391,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122606208</v>
+        <v>122608990</v>
       </c>
       <c r="B35" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4403,38 +4403,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485592</v>
+        <v>486070</v>
       </c>
       <c r="R35" t="n">
-        <v>6790353</v>
+        <v>6790363</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4839,10 +4839,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122608938</v>
+        <v>122607596</v>
       </c>
       <c r="B39" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4851,38 +4851,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486253</v>
+        <v>486109</v>
       </c>
       <c r="R39" t="n">
-        <v>6790356</v>
+        <v>6790384</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
@@ -4914,7 +4919,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4924,7 +4929,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4951,10 +4956,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122607596</v>
+        <v>122608938</v>
       </c>
       <c r="B40" t="n">
-        <v>56688</v>
+        <v>78762</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4963,43 +4968,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486109</v>
+        <v>486253</v>
       </c>
       <c r="R40" t="n">
-        <v>6790384</v>
+        <v>6790356</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5638,10 +5638,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122607953</v>
+        <v>122608844</v>
       </c>
       <c r="B46" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5650,38 +5650,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486214</v>
+        <v>486338</v>
       </c>
       <c r="R46" t="n">
-        <v>6790429</v>
+        <v>6790352</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5723,7 +5723,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5750,7 +5755,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122608844</v>
+        <v>122606651</v>
       </c>
       <c r="B47" t="n">
         <v>78762</v>
@@ -5786,14 +5791,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486338</v>
+        <v>485432</v>
       </c>
       <c r="R47" t="n">
-        <v>6790352</v>
+        <v>6790417</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5825,7 +5830,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5835,12 +5840,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5867,10 +5867,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122606651</v>
+        <v>122607953</v>
       </c>
       <c r="B48" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5879,25 +5879,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5907,10 +5907,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>485432</v>
+        <v>486214</v>
       </c>
       <c r="R48" t="n">
-        <v>6790417</v>
+        <v>6790429</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -10248,10 +10248,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122671608</v>
+        <v>122671609</v>
       </c>
       <c r="B87" t="n">
-        <v>79380</v>
+        <v>78499</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10264,21 +10264,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10354,10 +10354,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122671536</v>
+        <v>122671608</v>
       </c>
       <c r="B88" t="n">
-        <v>78762</v>
+        <v>79380</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10370,21 +10370,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10397,10 +10397,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>485910</v>
+        <v>486013</v>
       </c>
       <c r="R88" t="n">
-        <v>6790394</v>
+        <v>6790366</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10460,7 +10460,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122671440</v>
+        <v>122671536</v>
       </c>
       <c r="B89" t="n">
         <v>78762</v>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>485819</v>
+        <v>485910</v>
       </c>
       <c r="R89" t="n">
-        <v>6790340</v>
+        <v>6790394</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10566,10 +10566,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122671609</v>
+        <v>122671440</v>
       </c>
       <c r="B90" t="n">
-        <v>78499</v>
+        <v>78762</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10582,21 +10582,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10609,10 +10609,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486013</v>
+        <v>485819</v>
       </c>
       <c r="R90" t="n">
-        <v>6790366</v>
+        <v>6790340</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10778,10 +10778,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122671559</v>
+        <v>122671879</v>
       </c>
       <c r="B92" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10790,30 +10790,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10821,10 +10826,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>485916</v>
+        <v>486429</v>
       </c>
       <c r="R92" t="n">
-        <v>6790407</v>
+        <v>6790399</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10859,13 +10864,17 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>på ett par platser intill granar</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10884,10 +10893,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122671879</v>
+        <v>122671559</v>
       </c>
       <c r="B93" t="n">
-        <v>56688</v>
+        <v>78762</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10896,35 +10905,30 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10932,10 +10936,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>486429</v>
+        <v>485916</v>
       </c>
       <c r="R93" t="n">
-        <v>6790399</v>
+        <v>6790407</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10970,17 +10974,13 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>på ett par platser intill granar</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -12498,10 +12498,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122671675</v>
+        <v>122671523</v>
       </c>
       <c r="B108" t="n">
-        <v>78762</v>
+        <v>57631</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12514,26 +12514,31 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -12541,13 +12546,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>486331</v>
+        <v>485893</v>
       </c>
       <c r="R108" t="n">
-        <v>6790370</v>
+        <v>6790386</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12585,7 +12590,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -12604,7 +12608,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122671424</v>
+        <v>122671675</v>
       </c>
       <c r="B109" t="n">
         <v>78762</v>
@@ -12647,13 +12651,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>485783</v>
+        <v>486331</v>
       </c>
       <c r="R109" t="n">
-        <v>6790367</v>
+        <v>6790370</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12710,10 +12714,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122671523</v>
+        <v>122671424</v>
       </c>
       <c r="B110" t="n">
-        <v>57631</v>
+        <v>78762</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12726,31 +12730,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12758,10 +12757,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>485893</v>
+        <v>485783</v>
       </c>
       <c r="R110" t="n">
-        <v>6790386</v>
+        <v>6790367</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12802,6 +12801,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -15723,7 +15723,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>122689855</v>
+        <v>122689838</v>
       </c>
       <c r="B138" t="n">
         <v>78762</v>
@@ -15766,10 +15766,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>485432</v>
+        <v>485452</v>
       </c>
       <c r="R138" t="n">
-        <v>6790469</v>
+        <v>6790453</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -15829,7 +15829,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>122689895</v>
+        <v>122689855</v>
       </c>
       <c r="B139" t="n">
         <v>78762</v>
@@ -15872,10 +15872,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>485405</v>
+        <v>485432</v>
       </c>
       <c r="R139" t="n">
-        <v>6790460</v>
+        <v>6790469</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -15935,7 +15935,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>122689920</v>
+        <v>122689895</v>
       </c>
       <c r="B140" t="n">
         <v>78762</v>
@@ -15978,10 +15978,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>485472</v>
+        <v>485405</v>
       </c>
       <c r="R140" t="n">
-        <v>6790425</v>
+        <v>6790460</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -16041,7 +16041,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>122689824</v>
+        <v>122689920</v>
       </c>
       <c r="B141" t="n">
         <v>78762</v>
@@ -16084,10 +16084,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>485497</v>
+        <v>485472</v>
       </c>
       <c r="R141" t="n">
-        <v>6790458</v>
+        <v>6790425</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16147,10 +16147,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>122689865</v>
+        <v>122689824</v>
       </c>
       <c r="B142" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16159,36 +16159,30 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -16196,10 +16190,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>485417</v>
+        <v>485497</v>
       </c>
       <c r="R142" t="n">
-        <v>6790479</v>
+        <v>6790458</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16471,10 +16465,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>122689838</v>
+        <v>122689865</v>
       </c>
       <c r="B145" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16483,30 +16477,36 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -16514,10 +16514,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>485452</v>
+        <v>485417</v>
       </c>
       <c r="R145" t="n">
-        <v>6790453</v>
+        <v>6790479</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -19333,7 +19333,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>122689882</v>
+        <v>122689572</v>
       </c>
       <c r="B172" t="n">
         <v>78762</v>
@@ -19376,10 +19376,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>485408</v>
+        <v>485672</v>
       </c>
       <c r="R172" t="n">
-        <v>6790469</v>
+        <v>6790447</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -19439,7 +19439,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>122689572</v>
+        <v>122689882</v>
       </c>
       <c r="B173" t="n">
         <v>78762</v>
@@ -19482,10 +19482,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>485672</v>
+        <v>485408</v>
       </c>
       <c r="R173" t="n">
-        <v>6790447</v>
+        <v>6790469</v>
       </c>
       <c r="S173" t="n">
         <v>5</v>
@@ -19863,7 +19863,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122689736</v>
+        <v>122689875</v>
       </c>
       <c r="B177" t="n">
         <v>78762</v>
@@ -19906,10 +19906,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>485597</v>
+        <v>485410</v>
       </c>
       <c r="R177" t="n">
-        <v>6790468</v>
+        <v>6790478</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -19969,7 +19969,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122689761</v>
+        <v>122689918</v>
       </c>
       <c r="B178" t="n">
         <v>78762</v>
@@ -20012,10 +20012,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>485563</v>
+        <v>485463</v>
       </c>
       <c r="R178" t="n">
-        <v>6790470</v>
+        <v>6790428</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -20075,7 +20075,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122689875</v>
+        <v>122689593</v>
       </c>
       <c r="B179" t="n">
         <v>78762</v>
@@ -20118,10 +20118,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>485410</v>
+        <v>485660</v>
       </c>
       <c r="R179" t="n">
-        <v>6790478</v>
+        <v>6790454</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20181,7 +20181,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122689918</v>
+        <v>122689736</v>
       </c>
       <c r="B180" t="n">
         <v>78762</v>
@@ -20224,10 +20224,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>485463</v>
+        <v>485597</v>
       </c>
       <c r="R180" t="n">
-        <v>6790428</v>
+        <v>6790468</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -20287,7 +20287,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122689593</v>
+        <v>122689761</v>
       </c>
       <c r="B181" t="n">
         <v>78762</v>
@@ -20330,10 +20330,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>485660</v>
+        <v>485563</v>
       </c>
       <c r="R181" t="n">
-        <v>6790454</v>
+        <v>6790470</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -4167,10 +4167,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122606208</v>
+        <v>122607254</v>
       </c>
       <c r="B33" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4179,25 +4179,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>485592</v>
+        <v>486016</v>
       </c>
       <c r="R33" t="n">
-        <v>6790353</v>
+        <v>6790443</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4279,7 +4279,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122607254</v>
+        <v>122608990</v>
       </c>
       <c r="B34" t="n">
         <v>78762</v>
@@ -4315,14 +4315,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486016</v>
+        <v>486070</v>
       </c>
       <c r="R34" t="n">
-        <v>6790443</v>
+        <v>6790363</v>
       </c>
       <c r="S34" t="n">
         <v>9</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4391,10 +4391,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122608990</v>
+        <v>122606208</v>
       </c>
       <c r="B35" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4403,38 +4403,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486070</v>
+        <v>485592</v>
       </c>
       <c r="R35" t="n">
-        <v>6790363</v>
+        <v>6790353</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5638,10 +5638,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122608844</v>
+        <v>122607953</v>
       </c>
       <c r="B46" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5650,38 +5650,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486338</v>
+        <v>486214</v>
       </c>
       <c r="R46" t="n">
-        <v>6790352</v>
+        <v>6790429</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5723,12 +5723,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5755,7 +5750,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122606651</v>
+        <v>122608844</v>
       </c>
       <c r="B47" t="n">
         <v>78762</v>
@@ -5791,14 +5786,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>485432</v>
+        <v>486338</v>
       </c>
       <c r="R47" t="n">
-        <v>6790417</v>
+        <v>6790352</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5830,7 +5825,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5840,7 +5835,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5867,10 +5867,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122607953</v>
+        <v>122606651</v>
       </c>
       <c r="B48" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5879,25 +5879,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5907,10 +5907,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486214</v>
+        <v>485432</v>
       </c>
       <c r="R48" t="n">
-        <v>6790429</v>
+        <v>6790417</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6315,7 +6315,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122608061</v>
+        <v>122608110</v>
       </c>
       <c r="B52" t="n">
         <v>78762</v>
@@ -6351,14 +6351,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486229</v>
+        <v>486270</v>
       </c>
       <c r="R52" t="n">
-        <v>6790440</v>
+        <v>6790427</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6400,12 +6400,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6432,7 +6427,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122608110</v>
+        <v>122608061</v>
       </c>
       <c r="B53" t="n">
         <v>78762</v>
@@ -6468,14 +6463,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486270</v>
+        <v>486229</v>
       </c>
       <c r="R53" t="n">
-        <v>6790427</v>
+        <v>6790440</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6507,7 +6502,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6517,7 +6512,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6890,10 +6890,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122608903</v>
+        <v>122606642</v>
       </c>
       <c r="B57" t="n">
-        <v>78499</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6906,37 +6906,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486211</v>
+        <v>485586</v>
       </c>
       <c r="R57" t="n">
-        <v>6790317</v>
+        <v>6790395</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7002,10 +7002,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122607038</v>
+        <v>122608713</v>
       </c>
       <c r="B58" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7014,41 +7014,49 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485772</v>
+        <v>485504</v>
       </c>
       <c r="R58" t="n">
-        <v>6790421</v>
+        <v>6790441</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7077,7 +7085,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7087,7 +7095,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7102,22 +7110,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122608713</v>
+        <v>122607273</v>
       </c>
       <c r="B59" t="n">
-        <v>56688</v>
+        <v>8441</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7130,29 +7138,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7162,10 +7171,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>485504</v>
+        <v>485932</v>
       </c>
       <c r="R59" t="n">
-        <v>6790441</v>
+        <v>6790416</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7197,7 +7206,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7207,7 +7216,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7216,28 +7225,29 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122608724</v>
+        <v>122608903</v>
       </c>
       <c r="B60" t="n">
-        <v>78762</v>
+        <v>78503</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7250,21 +7260,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7309,7 +7319,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7319,7 +7329,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7346,10 +7356,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122607445</v>
+        <v>122608928</v>
       </c>
       <c r="B61" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7362,37 +7372,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486082</v>
+        <v>486063</v>
       </c>
       <c r="R61" t="n">
-        <v>6790427</v>
+        <v>6790348</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7421,7 +7431,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7431,7 +7441,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7458,10 +7468,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122607719</v>
+        <v>122608724</v>
       </c>
       <c r="B62" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7494,17 +7504,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486157</v>
+        <v>486211</v>
       </c>
       <c r="R62" t="n">
-        <v>6790397</v>
+        <v>6790317</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7533,7 +7543,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7543,7 +7553,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7570,10 +7580,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122607077</v>
+        <v>122607038</v>
       </c>
       <c r="B63" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7582,36 +7592,28 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
@@ -7624,7 +7626,7 @@
         <v>6790421</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7653,7 +7655,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7663,7 +7665,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7690,10 +7692,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122606642</v>
+        <v>122607077</v>
       </c>
       <c r="B64" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7702,41 +7704,49 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>485586</v>
+        <v>485772</v>
       </c>
       <c r="R64" t="n">
-        <v>6790395</v>
+        <v>6790421</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7765,7 +7775,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7775,7 +7785,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7802,10 +7812,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122606143</v>
+        <v>122607688</v>
       </c>
       <c r="B65" t="n">
-        <v>78762</v>
+        <v>90964</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7818,34 +7828,38 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>485681</v>
+        <v>486156</v>
       </c>
       <c r="R65" t="n">
-        <v>6790440</v>
+        <v>6790429</v>
       </c>
       <c r="S65" t="n">
         <v>9</v>
@@ -7877,7 +7891,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7887,7 +7901,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7902,22 +7916,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122606247</v>
+        <v>122607445</v>
       </c>
       <c r="B66" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7954,13 +7968,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>485626</v>
+        <v>486082</v>
       </c>
       <c r="R66" t="n">
-        <v>6790401</v>
+        <v>6790427</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7989,7 +8003,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7999,7 +8013,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8026,7 +8040,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122607273</v>
+        <v>122607216</v>
       </c>
       <c r="B67" t="n">
         <v>8441</v>
@@ -8075,10 +8089,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>485932</v>
+        <v>485504</v>
       </c>
       <c r="R67" t="n">
-        <v>6790416</v>
+        <v>6790441</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8110,7 +8124,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8120,7 +8134,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8136,22 +8150,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122607688</v>
+        <v>122606760</v>
       </c>
       <c r="B68" t="n">
-        <v>90960</v>
+        <v>57494</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8164,41 +8178,45 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486156</v>
+        <v>485504</v>
       </c>
       <c r="R68" t="n">
-        <v>6790429</v>
+        <v>6790441</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8227,7 +8245,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8237,7 +8255,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8252,22 +8270,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122608142</v>
+        <v>122606247</v>
       </c>
       <c r="B69" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8300,14 +8318,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486240</v>
+        <v>485626</v>
       </c>
       <c r="R69" t="n">
-        <v>6790382</v>
+        <v>6790401</v>
       </c>
       <c r="S69" t="n">
         <v>9</v>
@@ -8339,7 +8357,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8349,7 +8367,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8376,10 +8394,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122606756</v>
+        <v>122608142</v>
       </c>
       <c r="B70" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8388,50 +8406,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>485504</v>
+        <v>486240</v>
       </c>
       <c r="R70" t="n">
-        <v>6790441</v>
+        <v>6790382</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8460,7 +8469,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8470,7 +8479,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8479,29 +8488,28 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122608928</v>
+        <v>122609008</v>
       </c>
       <c r="B71" t="n">
-        <v>79380</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8514,21 +8522,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8544,7 +8552,7 @@
         <v>6790348</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8573,7 +8581,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8583,7 +8591,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8610,10 +8618,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122609008</v>
+        <v>122609064</v>
       </c>
       <c r="B72" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8622,28 +8630,37 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Lindflot, Lindflot, Dlr</t>
@@ -8685,7 +8702,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8695,7 +8712,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8704,6 +8721,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8722,10 +8740,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122606760</v>
+        <v>122607719</v>
       </c>
       <c r="B73" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8738,45 +8756,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>485504</v>
+        <v>486157</v>
       </c>
       <c r="R73" t="n">
-        <v>6790441</v>
+        <v>6790397</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8805,7 +8815,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8815,7 +8825,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8830,22 +8840,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122609064</v>
+        <v>122606143</v>
       </c>
       <c r="B74" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8854,50 +8864,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486063</v>
+        <v>485681</v>
       </c>
       <c r="R74" t="n">
-        <v>6790348</v>
+        <v>6790440</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8926,7 +8927,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8936,7 +8937,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8945,7 +8946,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8964,10 +8964,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122671508</v>
+        <v>122671569</v>
       </c>
       <c r="B75" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>485871</v>
+        <v>485951</v>
       </c>
       <c r="R75" t="n">
-        <v>6790368</v>
+        <v>6790408</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9070,10 +9070,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122671674</v>
+        <v>122671575</v>
       </c>
       <c r="B76" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9113,13 +9113,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486266</v>
+        <v>485989</v>
       </c>
       <c r="R76" t="n">
-        <v>6790373</v>
+        <v>6790394</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9176,10 +9176,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122671575</v>
+        <v>122671570</v>
       </c>
       <c r="B77" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9219,10 +9219,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>485989</v>
+        <v>485953</v>
       </c>
       <c r="R77" t="n">
-        <v>6790394</v>
+        <v>6790411</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9282,10 +9282,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122671521</v>
+        <v>122671659</v>
       </c>
       <c r="B78" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9294,30 +9294,36 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9325,10 +9331,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>485893</v>
+        <v>486020</v>
       </c>
       <c r="R78" t="n">
-        <v>6790386</v>
+        <v>6790412</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9388,10 +9394,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122671679</v>
+        <v>122671667</v>
       </c>
       <c r="B79" t="n">
-        <v>78762</v>
+        <v>78800</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9404,21 +9410,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9431,10 +9437,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486342</v>
+        <v>486043</v>
       </c>
       <c r="R79" t="n">
-        <v>6790369</v>
+        <v>6790416</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9494,10 +9500,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122671537</v>
+        <v>122671506</v>
       </c>
       <c r="B80" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9506,36 +9512,30 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9543,10 +9543,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>485910</v>
+        <v>485861</v>
       </c>
       <c r="R80" t="n">
-        <v>6790394</v>
+        <v>6790364</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9606,10 +9606,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122671659</v>
+        <v>122671595</v>
       </c>
       <c r="B81" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9618,36 +9618,30 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -9655,10 +9649,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486020</v>
+        <v>485984</v>
       </c>
       <c r="R81" t="n">
-        <v>6790412</v>
+        <v>6790370</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9718,10 +9712,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122671587</v>
+        <v>122671508</v>
       </c>
       <c r="B82" t="n">
-        <v>79380</v>
+        <v>78766</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9734,21 +9728,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9761,10 +9755,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>485985</v>
+        <v>485871</v>
       </c>
       <c r="R82" t="n">
-        <v>6790379</v>
+        <v>6790368</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9824,10 +9818,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122671434</v>
+        <v>122671559</v>
       </c>
       <c r="B83" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9867,10 +9861,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>485799</v>
+        <v>485916</v>
       </c>
       <c r="R83" t="n">
-        <v>6790349</v>
+        <v>6790407</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9930,10 +9924,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122671519</v>
+        <v>122671888</v>
       </c>
       <c r="B84" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9942,30 +9936,35 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9973,10 +9972,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>485876</v>
+        <v>485897</v>
       </c>
       <c r="R84" t="n">
-        <v>6790381</v>
+        <v>6790441</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10011,13 +10010,17 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>under betestall rikligt</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -10036,10 +10039,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122671462</v>
+        <v>122671534</v>
       </c>
       <c r="B85" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10079,10 +10082,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>485835</v>
+        <v>485901</v>
       </c>
       <c r="R85" t="n">
-        <v>6790356</v>
+        <v>6790392</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10142,10 +10145,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122671564</v>
+        <v>122671587</v>
       </c>
       <c r="B86" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10158,21 +10161,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10185,10 +10188,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>485933</v>
+        <v>485985</v>
       </c>
       <c r="R86" t="n">
-        <v>6790411</v>
+        <v>6790379</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10248,10 +10251,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122671609</v>
+        <v>122671537</v>
       </c>
       <c r="B87" t="n">
-        <v>78499</v>
+        <v>8441</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10260,30 +10263,36 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10291,10 +10300,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486013</v>
+        <v>485910</v>
       </c>
       <c r="R87" t="n">
-        <v>6790366</v>
+        <v>6790394</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10354,10 +10363,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122671608</v>
+        <v>122671519</v>
       </c>
       <c r="B88" t="n">
-        <v>79380</v>
+        <v>78766</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10370,21 +10379,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10397,10 +10406,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486013</v>
+        <v>485876</v>
       </c>
       <c r="R88" t="n">
-        <v>6790366</v>
+        <v>6790381</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10460,10 +10469,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122671536</v>
+        <v>122671453</v>
       </c>
       <c r="B89" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10503,10 +10512,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>485910</v>
+        <v>485835</v>
       </c>
       <c r="R89" t="n">
-        <v>6790394</v>
+        <v>6790356</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10566,10 +10575,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122671440</v>
+        <v>122671610</v>
       </c>
       <c r="B90" t="n">
-        <v>78762</v>
+        <v>78502</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10582,21 +10591,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10609,10 +10618,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>485819</v>
+        <v>486013</v>
       </c>
       <c r="R90" t="n">
-        <v>6790340</v>
+        <v>6790366</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10672,10 +10681,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122671422</v>
+        <v>122671681</v>
       </c>
       <c r="B91" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10684,30 +10693,36 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10715,13 +10730,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>485784</v>
+        <v>486342</v>
       </c>
       <c r="R91" t="n">
-        <v>6790390</v>
+        <v>6790369</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10778,10 +10793,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122671879</v>
+        <v>122671592</v>
       </c>
       <c r="B92" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10790,35 +10805,30 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10826,10 +10836,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>486429</v>
+        <v>485984</v>
       </c>
       <c r="R92" t="n">
-        <v>6790399</v>
+        <v>6790371</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10864,17 +10874,13 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>på ett par platser intill granar</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10893,10 +10899,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122671559</v>
+        <v>122671440</v>
       </c>
       <c r="B93" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10936,10 +10942,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>485916</v>
+        <v>485819</v>
       </c>
       <c r="R93" t="n">
-        <v>6790407</v>
+        <v>6790340</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10999,10 +11005,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122671595</v>
+        <v>122671523</v>
       </c>
       <c r="B94" t="n">
-        <v>78762</v>
+        <v>57631</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11015,26 +11021,31 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11042,10 +11053,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>485984</v>
+        <v>485893</v>
       </c>
       <c r="R94" t="n">
-        <v>6790370</v>
+        <v>6790386</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11086,7 +11097,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11105,10 +11115,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122671570</v>
+        <v>122671424</v>
       </c>
       <c r="B95" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11148,10 +11158,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>485953</v>
+        <v>485783</v>
       </c>
       <c r="R95" t="n">
-        <v>6790411</v>
+        <v>6790367</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11211,10 +11221,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122671512</v>
+        <v>122671378</v>
       </c>
       <c r="B96" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11254,10 +11264,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>485876</v>
+        <v>485757</v>
       </c>
       <c r="R96" t="n">
-        <v>6790371</v>
+        <v>6790379</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11317,10 +11327,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122671569</v>
+        <v>122671879</v>
       </c>
       <c r="B97" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11329,30 +11339,35 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -11360,10 +11375,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>485951</v>
+        <v>486429</v>
       </c>
       <c r="R97" t="n">
-        <v>6790408</v>
+        <v>6790399</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11398,13 +11413,17 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>på ett par platser intill granar</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11423,10 +11442,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122671447</v>
+        <v>122671658</v>
       </c>
       <c r="B98" t="n">
-        <v>78762</v>
+        <v>57631</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11439,26 +11458,31 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -11466,10 +11490,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>485830</v>
+        <v>486037</v>
       </c>
       <c r="R98" t="n">
-        <v>6790346</v>
+        <v>6790372</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11510,7 +11534,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11529,10 +11552,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122671668</v>
+        <v>122671579</v>
       </c>
       <c r="B99" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11572,13 +11595,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>486079</v>
+        <v>485989</v>
       </c>
       <c r="R99" t="n">
-        <v>6790394</v>
+        <v>6790378</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11635,10 +11658,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122671506</v>
+        <v>122671541</v>
       </c>
       <c r="B100" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11647,30 +11670,36 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11678,10 +11707,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>485861</v>
+        <v>485879</v>
       </c>
       <c r="R100" t="n">
-        <v>6790364</v>
+        <v>6790409</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11741,10 +11770,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122671384</v>
+        <v>122671647</v>
       </c>
       <c r="B101" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11784,13 +11813,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>485777</v>
+        <v>486035</v>
       </c>
       <c r="R101" t="n">
-        <v>6790392</v>
+        <v>6790369</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11847,10 +11876,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122671493</v>
+        <v>122671521</v>
       </c>
       <c r="B102" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11890,10 +11919,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>485859</v>
+        <v>485893</v>
       </c>
       <c r="R102" t="n">
-        <v>6790362</v>
+        <v>6790386</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11953,10 +11982,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122671888</v>
+        <v>122671609</v>
       </c>
       <c r="B103" t="n">
-        <v>56688</v>
+        <v>78503</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11965,35 +11994,30 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12001,10 +12025,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>485897</v>
+        <v>486013</v>
       </c>
       <c r="R103" t="n">
-        <v>6790441</v>
+        <v>6790366</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12039,17 +12063,13 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>under betestall rikligt</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -12068,10 +12088,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122671534</v>
+        <v>122671434</v>
       </c>
       <c r="B104" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12111,10 +12131,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>485901</v>
+        <v>485799</v>
       </c>
       <c r="R104" t="n">
-        <v>6790392</v>
+        <v>6790349</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12174,10 +12194,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122671651</v>
+        <v>122671674</v>
       </c>
       <c r="B105" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12217,13 +12237,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>486048</v>
+        <v>486266</v>
       </c>
       <c r="R105" t="n">
-        <v>6790360</v>
+        <v>6790373</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12280,10 +12300,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122671378</v>
+        <v>122671493</v>
       </c>
       <c r="B106" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12323,10 +12343,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>485757</v>
+        <v>485859</v>
       </c>
       <c r="R106" t="n">
-        <v>6790379</v>
+        <v>6790362</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12386,10 +12406,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122671681</v>
+        <v>122671422</v>
       </c>
       <c r="B107" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12398,36 +12418,30 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -12435,13 +12449,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>486342</v>
+        <v>485784</v>
       </c>
       <c r="R107" t="n">
-        <v>6790369</v>
+        <v>6790390</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12498,10 +12512,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122671523</v>
+        <v>122671512</v>
       </c>
       <c r="B108" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12514,31 +12528,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -12546,10 +12555,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>485893</v>
+        <v>485876</v>
       </c>
       <c r="R108" t="n">
-        <v>6790386</v>
+        <v>6790371</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12590,6 +12599,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -12608,10 +12618,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122671675</v>
+        <v>122671536</v>
       </c>
       <c r="B109" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12651,13 +12661,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>486331</v>
+        <v>485910</v>
       </c>
       <c r="R109" t="n">
-        <v>6790370</v>
+        <v>6790394</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12714,10 +12724,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122671424</v>
+        <v>122671384</v>
       </c>
       <c r="B110" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12757,10 +12767,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>485783</v>
+        <v>485777</v>
       </c>
       <c r="R110" t="n">
-        <v>6790367</v>
+        <v>6790392</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12820,10 +12830,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122671658</v>
+        <v>122671668</v>
       </c>
       <c r="B111" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12836,31 +12846,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12868,13 +12873,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>486037</v>
+        <v>486079</v>
       </c>
       <c r="R111" t="n">
-        <v>6790372</v>
+        <v>6790394</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12912,6 +12917,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12930,10 +12936,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122671647</v>
+        <v>122671608</v>
       </c>
       <c r="B112" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12946,21 +12952,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12973,13 +12979,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>486035</v>
+        <v>486013</v>
       </c>
       <c r="R112" t="n">
-        <v>6790369</v>
+        <v>6790366</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13036,10 +13042,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122671579</v>
+        <v>122671555</v>
       </c>
       <c r="B113" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13079,10 +13085,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>485989</v>
+        <v>485915</v>
       </c>
       <c r="R113" t="n">
-        <v>6790378</v>
+        <v>6790407</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13142,10 +13148,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122671610</v>
+        <v>122671675</v>
       </c>
       <c r="B114" t="n">
-        <v>78498</v>
+        <v>78766</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13158,21 +13164,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13185,13 +13191,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>486013</v>
+        <v>486331</v>
       </c>
       <c r="R114" t="n">
-        <v>6790366</v>
+        <v>6790370</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13248,10 +13254,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122671667</v>
+        <v>122671447</v>
       </c>
       <c r="B115" t="n">
-        <v>78796</v>
+        <v>78766</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13264,21 +13270,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13291,13 +13297,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>486043</v>
+        <v>485830</v>
       </c>
       <c r="R115" t="n">
-        <v>6790416</v>
+        <v>6790346</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13354,10 +13360,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122671592</v>
+        <v>122671651</v>
       </c>
       <c r="B116" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13397,13 +13403,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>485984</v>
+        <v>486048</v>
       </c>
       <c r="R116" t="n">
-        <v>6790371</v>
+        <v>6790360</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13460,10 +13466,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122671555</v>
+        <v>122671679</v>
       </c>
       <c r="B117" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13503,13 +13509,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>485915</v>
+        <v>486342</v>
       </c>
       <c r="R117" t="n">
-        <v>6790407</v>
+        <v>6790369</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13566,10 +13572,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122671541</v>
+        <v>122671564</v>
       </c>
       <c r="B118" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13578,36 +13584,30 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -13615,10 +13615,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>485879</v>
+        <v>485933</v>
       </c>
       <c r="R118" t="n">
-        <v>6790409</v>
+        <v>6790411</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13678,10 +13678,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122689892</v>
+        <v>122689581</v>
       </c>
       <c r="B119" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13721,10 +13721,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>485406</v>
+        <v>485671</v>
       </c>
       <c r="R119" t="n">
-        <v>6790461</v>
+        <v>6790449</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13784,10 +13784,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122689349</v>
+        <v>122689933</v>
       </c>
       <c r="B120" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13796,43 +13796,30 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -13840,13 +13827,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>485774</v>
+        <v>485524</v>
       </c>
       <c r="R120" t="n">
-        <v>6790357</v>
+        <v>6790423</v>
       </c>
       <c r="S120" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13878,17 +13865,13 @@
           <t>2025-02-20</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>flög åt väster</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13907,10 +13890,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122689723</v>
+        <v>122689736</v>
       </c>
       <c r="B121" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13919,36 +13902,30 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13956,10 +13933,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>485609</v>
+        <v>485597</v>
       </c>
       <c r="R121" t="n">
-        <v>6790472</v>
+        <v>6790468</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14019,10 +13996,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122689966</v>
+        <v>122689748</v>
       </c>
       <c r="B122" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14062,10 +14039,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>485678</v>
+        <v>485586</v>
       </c>
       <c r="R122" t="n">
-        <v>6790402</v>
+        <v>6790473</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14125,10 +14102,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122689819</v>
+        <v>122689934</v>
       </c>
       <c r="B123" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14168,10 +14145,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>485500</v>
+        <v>485527</v>
       </c>
       <c r="R123" t="n">
-        <v>6790456</v>
+        <v>6790426</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14231,10 +14208,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122689879</v>
+        <v>122689794</v>
       </c>
       <c r="B124" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14274,10 +14251,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>485409</v>
+        <v>485529</v>
       </c>
       <c r="R124" t="n">
-        <v>6790470</v>
+        <v>6790463</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14337,10 +14314,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122689617</v>
+        <v>122689859</v>
       </c>
       <c r="B125" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14380,10 +14357,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>485646</v>
+        <v>485425</v>
       </c>
       <c r="R125" t="n">
-        <v>6790453</v>
+        <v>6790473</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14443,10 +14420,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122689899</v>
+        <v>122689865</v>
       </c>
       <c r="B126" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14455,30 +14432,36 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -14486,10 +14469,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>485399</v>
+        <v>485417</v>
       </c>
       <c r="R126" t="n">
-        <v>6790454</v>
+        <v>6790479</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14549,10 +14532,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122689842</v>
+        <v>122689851</v>
       </c>
       <c r="B127" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14592,10 +14575,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>485449</v>
+        <v>485442</v>
       </c>
       <c r="R127" t="n">
-        <v>6790454</v>
+        <v>6790462</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14655,10 +14638,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122689738</v>
+        <v>122689764</v>
       </c>
       <c r="B128" t="n">
-        <v>90960</v>
+        <v>78766</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14671,33 +14654,25 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
@@ -14706,10 +14681,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>485597</v>
+        <v>485560</v>
       </c>
       <c r="R128" t="n">
-        <v>6790468</v>
+        <v>6790469</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14769,10 +14744,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122689974</v>
+        <v>122689594</v>
       </c>
       <c r="B129" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14812,10 +14787,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>485719</v>
+        <v>485662</v>
       </c>
       <c r="R129" t="n">
-        <v>6790394</v>
+        <v>6790461</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14875,10 +14850,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122689872</v>
+        <v>122689842</v>
       </c>
       <c r="B130" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14918,10 +14893,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>485412</v>
+        <v>485449</v>
       </c>
       <c r="R130" t="n">
-        <v>6790481</v>
+        <v>6790454</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -14981,10 +14956,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122689556</v>
+        <v>122689596</v>
       </c>
       <c r="B131" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15024,10 +14999,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>485678</v>
+        <v>485656</v>
       </c>
       <c r="R131" t="n">
-        <v>6790447</v>
+        <v>6790462</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -15087,10 +15062,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122689936</v>
+        <v>122689954</v>
       </c>
       <c r="B132" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15130,10 +15105,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>485535</v>
+        <v>485626</v>
       </c>
       <c r="R132" t="n">
-        <v>6790402</v>
+        <v>6790391</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -15193,10 +15168,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122689851</v>
+        <v>122689806</v>
       </c>
       <c r="B133" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15236,10 +15211,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>485442</v>
+        <v>485524</v>
       </c>
       <c r="R133" t="n">
-        <v>6790462</v>
+        <v>6790465</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15299,10 +15274,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>122689519</v>
+        <v>122689617</v>
       </c>
       <c r="B134" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15342,10 +15317,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>485696</v>
+        <v>485646</v>
       </c>
       <c r="R134" t="n">
-        <v>6790431</v>
+        <v>6790453</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -15405,10 +15380,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>122689941</v>
+        <v>122689738</v>
       </c>
       <c r="B135" t="n">
-        <v>78762</v>
+        <v>90964</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15421,25 +15396,33 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
@@ -15448,10 +15431,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>485558</v>
+        <v>485597</v>
       </c>
       <c r="R135" t="n">
-        <v>6790391</v>
+        <v>6790468</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -15511,10 +15494,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>122689743</v>
+        <v>122689895</v>
       </c>
       <c r="B136" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15554,10 +15537,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>485588</v>
+        <v>485405</v>
       </c>
       <c r="R136" t="n">
-        <v>6790473</v>
+        <v>6790460</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -15617,10 +15600,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>122689677</v>
+        <v>122689942</v>
       </c>
       <c r="B137" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15660,10 +15643,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>485615</v>
+        <v>485554</v>
       </c>
       <c r="R137" t="n">
-        <v>6790468</v>
+        <v>6790400</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15723,10 +15706,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>122689838</v>
+        <v>122689540</v>
       </c>
       <c r="B138" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15766,10 +15749,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>485452</v>
+        <v>485689</v>
       </c>
       <c r="R138" t="n">
-        <v>6790453</v>
+        <v>6790436</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -15829,10 +15812,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>122689855</v>
+        <v>122689863</v>
       </c>
       <c r="B139" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15872,10 +15855,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>485432</v>
+        <v>485420</v>
       </c>
       <c r="R139" t="n">
-        <v>6790469</v>
+        <v>6790476</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -15935,10 +15918,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>122689895</v>
+        <v>122689829</v>
       </c>
       <c r="B140" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15978,10 +15961,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>485405</v>
+        <v>485469</v>
       </c>
       <c r="R140" t="n">
-        <v>6790460</v>
+        <v>6790456</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -16041,10 +16024,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>122689920</v>
+        <v>122689924</v>
       </c>
       <c r="B141" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16084,10 +16067,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>485472</v>
+        <v>485489</v>
       </c>
       <c r="R141" t="n">
-        <v>6790425</v>
+        <v>6790405</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16147,10 +16130,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>122689824</v>
+        <v>122689677</v>
       </c>
       <c r="B142" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16190,10 +16173,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>485497</v>
+        <v>485615</v>
       </c>
       <c r="R142" t="n">
-        <v>6790458</v>
+        <v>6790468</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16253,10 +16236,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>122689933</v>
+        <v>122689572</v>
       </c>
       <c r="B143" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16296,10 +16279,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>485524</v>
+        <v>485672</v>
       </c>
       <c r="R143" t="n">
-        <v>6790423</v>
+        <v>6790447</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -16359,10 +16342,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>122689794</v>
+        <v>122689761</v>
       </c>
       <c r="B144" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16402,10 +16385,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>485529</v>
+        <v>485563</v>
       </c>
       <c r="R144" t="n">
-        <v>6790463</v>
+        <v>6790470</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -16465,10 +16448,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>122689865</v>
+        <v>122689974</v>
       </c>
       <c r="B145" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16477,36 +16460,30 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -16514,10 +16491,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>485417</v>
+        <v>485719</v>
       </c>
       <c r="R145" t="n">
-        <v>6790479</v>
+        <v>6790394</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -16577,10 +16554,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>122689756</v>
+        <v>122689936</v>
       </c>
       <c r="B146" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16620,10 +16597,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>485576</v>
+        <v>485535</v>
       </c>
       <c r="R146" t="n">
-        <v>6790471</v>
+        <v>6790402</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -16683,10 +16660,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>122689943</v>
+        <v>122689756</v>
       </c>
       <c r="B147" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16726,10 +16703,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>485590</v>
+        <v>485576</v>
       </c>
       <c r="R147" t="n">
-        <v>6790388</v>
+        <v>6790471</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -16789,10 +16766,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>122689630</v>
+        <v>122689950</v>
       </c>
       <c r="B148" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16832,10 +16809,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>485638</v>
+        <v>485623</v>
       </c>
       <c r="R148" t="n">
-        <v>6790456</v>
+        <v>6790393</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -16895,10 +16872,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>122689959</v>
+        <v>122689941</v>
       </c>
       <c r="B149" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16938,10 +16915,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>485627</v>
+        <v>485558</v>
       </c>
       <c r="R149" t="n">
-        <v>6790392</v>
+        <v>6790391</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -17001,10 +16978,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>122689633</v>
+        <v>122689904</v>
       </c>
       <c r="B150" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17044,10 +17021,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>485624</v>
+        <v>485427</v>
       </c>
       <c r="R150" t="n">
-        <v>6790469</v>
+        <v>6790445</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -17107,10 +17084,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>122689846</v>
+        <v>122689819</v>
       </c>
       <c r="B151" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17150,10 +17127,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>485443</v>
+        <v>485500</v>
       </c>
       <c r="R151" t="n">
-        <v>6790455</v>
+        <v>6790456</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -17213,10 +17190,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>122689889</v>
+        <v>122689593</v>
       </c>
       <c r="B152" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17256,10 +17233,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>485406</v>
+        <v>485660</v>
       </c>
       <c r="R152" t="n">
-        <v>6790464</v>
+        <v>6790454</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -17319,10 +17296,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>122689811</v>
+        <v>122689892</v>
       </c>
       <c r="B153" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17362,10 +17339,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>485510</v>
+        <v>485406</v>
       </c>
       <c r="R153" t="n">
-        <v>6790462</v>
+        <v>6790461</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -17425,10 +17402,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>122689611</v>
+        <v>122689743</v>
       </c>
       <c r="B154" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17468,10 +17445,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>485653</v>
+        <v>485588</v>
       </c>
       <c r="R154" t="n">
-        <v>6790460</v>
+        <v>6790473</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -17531,10 +17508,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122689924</v>
+        <v>122689824</v>
       </c>
       <c r="B155" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17574,10 +17551,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>485489</v>
+        <v>485497</v>
       </c>
       <c r="R155" t="n">
-        <v>6790405</v>
+        <v>6790458</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -17637,10 +17614,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122689764</v>
+        <v>122689626</v>
       </c>
       <c r="B156" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17680,10 +17657,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>485560</v>
+        <v>485638</v>
       </c>
       <c r="R156" t="n">
-        <v>6790469</v>
+        <v>6790452</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -17743,10 +17720,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>122689566</v>
+        <v>122689725</v>
       </c>
       <c r="B157" t="n">
-        <v>78762</v>
+        <v>57494</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17759,26 +17736,31 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -17786,10 +17768,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>485670</v>
+        <v>485609</v>
       </c>
       <c r="R157" t="n">
-        <v>6790450</v>
+        <v>6790472</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -17830,7 +17812,6 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -17849,10 +17830,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122689829</v>
+        <v>122689349</v>
       </c>
       <c r="B158" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17861,30 +17842,43 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
@@ -17892,13 +17886,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>485469</v>
+        <v>485774</v>
       </c>
       <c r="R158" t="n">
-        <v>6790456</v>
+        <v>6790357</v>
       </c>
       <c r="S158" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17930,13 +17924,17 @@
           <t>2025-02-20</t>
         </is>
       </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>flög åt väster</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -17955,10 +17953,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>122689859</v>
+        <v>122689943</v>
       </c>
       <c r="B159" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17998,10 +17996,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>485425</v>
+        <v>485590</v>
       </c>
       <c r="R159" t="n">
-        <v>6790473</v>
+        <v>6790388</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -18061,10 +18059,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>122689963</v>
+        <v>122689914</v>
       </c>
       <c r="B160" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18104,10 +18102,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>485658</v>
+        <v>485447</v>
       </c>
       <c r="R160" t="n">
-        <v>6790402</v>
+        <v>6790434</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -18167,10 +18165,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>122689619</v>
+        <v>122689918</v>
       </c>
       <c r="B161" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18210,10 +18208,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>485645</v>
+        <v>485463</v>
       </c>
       <c r="R161" t="n">
-        <v>6790451</v>
+        <v>6790428</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -18273,10 +18271,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>122689581</v>
+        <v>122689619</v>
       </c>
       <c r="B162" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18316,10 +18314,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>485671</v>
+        <v>485645</v>
       </c>
       <c r="R162" t="n">
-        <v>6790449</v>
+        <v>6790451</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -18379,10 +18377,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122689447</v>
+        <v>122689566</v>
       </c>
       <c r="B163" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18422,10 +18420,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>485729</v>
+        <v>485670</v>
       </c>
       <c r="R163" t="n">
-        <v>6790386</v>
+        <v>6790450</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -18485,10 +18483,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>122689954</v>
+        <v>122689882</v>
       </c>
       <c r="B164" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18528,10 +18526,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>485626</v>
+        <v>485408</v>
       </c>
       <c r="R164" t="n">
-        <v>6790391</v>
+        <v>6790469</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18591,10 +18589,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122689904</v>
+        <v>122689899</v>
       </c>
       <c r="B165" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18634,10 +18632,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>485427</v>
+        <v>485399</v>
       </c>
       <c r="R165" t="n">
-        <v>6790445</v>
+        <v>6790454</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18697,10 +18695,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122689714</v>
+        <v>122689732</v>
       </c>
       <c r="B166" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18740,10 +18738,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>485613</v>
+        <v>485601</v>
       </c>
       <c r="R166" t="n">
-        <v>6790471</v>
+        <v>6790468</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -18803,10 +18801,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>122689853</v>
+        <v>122689972</v>
       </c>
       <c r="B167" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18846,10 +18844,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>485439</v>
+        <v>485718</v>
       </c>
       <c r="R167" t="n">
-        <v>6790465</v>
+        <v>6790397</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -18909,10 +18907,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>122689626</v>
+        <v>122689963</v>
       </c>
       <c r="B168" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18952,10 +18950,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>485638</v>
+        <v>485658</v>
       </c>
       <c r="R168" t="n">
-        <v>6790452</v>
+        <v>6790402</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -19015,10 +19013,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>122689942</v>
+        <v>122689811</v>
       </c>
       <c r="B169" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19058,10 +19056,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>485554</v>
+        <v>485510</v>
       </c>
       <c r="R169" t="n">
-        <v>6790400</v>
+        <v>6790462</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -19121,10 +19119,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>122689540</v>
+        <v>122689611</v>
       </c>
       <c r="B170" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19164,10 +19162,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>485689</v>
+        <v>485653</v>
       </c>
       <c r="R170" t="n">
-        <v>6790436</v>
+        <v>6790460</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -19227,10 +19225,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>122689863</v>
+        <v>122689959</v>
       </c>
       <c r="B171" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19270,10 +19268,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>485420</v>
+        <v>485627</v>
       </c>
       <c r="R171" t="n">
-        <v>6790476</v>
+        <v>6790392</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -19333,10 +19331,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>122689572</v>
+        <v>122689846</v>
       </c>
       <c r="B172" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19376,10 +19374,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>485672</v>
+        <v>485443</v>
       </c>
       <c r="R172" t="n">
-        <v>6790447</v>
+        <v>6790455</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -19439,10 +19437,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>122689882</v>
+        <v>122689966</v>
       </c>
       <c r="B173" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19482,10 +19480,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>485408</v>
+        <v>485678</v>
       </c>
       <c r="R173" t="n">
-        <v>6790469</v>
+        <v>6790402</v>
       </c>
       <c r="S173" t="n">
         <v>5</v>
@@ -19545,10 +19543,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>122689748</v>
+        <v>122689768</v>
       </c>
       <c r="B174" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19588,10 +19586,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>485586</v>
+        <v>485537</v>
       </c>
       <c r="R174" t="n">
-        <v>6790473</v>
+        <v>6790465</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -19651,10 +19649,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>122689934</v>
+        <v>122689855</v>
       </c>
       <c r="B175" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19694,10 +19692,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>485527</v>
+        <v>485432</v>
       </c>
       <c r="R175" t="n">
-        <v>6790426</v>
+        <v>6790469</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -19757,10 +19755,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122689911</v>
+        <v>122689633</v>
       </c>
       <c r="B176" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19800,10 +19798,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>485439</v>
+        <v>485624</v>
       </c>
       <c r="R176" t="n">
-        <v>6790444</v>
+        <v>6790469</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -19866,7 +19864,7 @@
         <v>122689875</v>
       </c>
       <c r="B177" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -19969,10 +19967,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122689918</v>
+        <v>122689838</v>
       </c>
       <c r="B178" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20012,10 +20010,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>485463</v>
+        <v>485452</v>
       </c>
       <c r="R178" t="n">
-        <v>6790428</v>
+        <v>6790453</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -20075,10 +20073,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122689593</v>
+        <v>122689853</v>
       </c>
       <c r="B179" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20118,10 +20116,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>485660</v>
+        <v>485439</v>
       </c>
       <c r="R179" t="n">
-        <v>6790454</v>
+        <v>6790465</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20181,10 +20179,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122689736</v>
+        <v>122689911</v>
       </c>
       <c r="B180" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20224,10 +20222,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>485597</v>
+        <v>485439</v>
       </c>
       <c r="R180" t="n">
-        <v>6790468</v>
+        <v>6790444</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -20287,10 +20285,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122689761</v>
+        <v>122689970</v>
       </c>
       <c r="B181" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20330,10 +20328,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>485563</v>
+        <v>485704</v>
       </c>
       <c r="R181" t="n">
-        <v>6790470</v>
+        <v>6790400</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -20393,10 +20391,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122689939</v>
+        <v>122689447</v>
       </c>
       <c r="B182" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20405,36 +20403,30 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
@@ -20442,10 +20434,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>485533</v>
+        <v>485729</v>
       </c>
       <c r="R182" t="n">
-        <v>6790398</v>
+        <v>6790386</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -20505,10 +20497,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>122689596</v>
+        <v>122689556</v>
       </c>
       <c r="B183" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20548,10 +20540,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>485656</v>
+        <v>485678</v>
       </c>
       <c r="R183" t="n">
-        <v>6790462</v>
+        <v>6790447</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -20611,10 +20603,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122689970</v>
+        <v>122689548</v>
       </c>
       <c r="B184" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20654,10 +20646,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>485704</v>
+        <v>485686</v>
       </c>
       <c r="R184" t="n">
-        <v>6790400</v>
+        <v>6790446</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -20717,10 +20709,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>122689914</v>
+        <v>122689630</v>
       </c>
       <c r="B185" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20760,10 +20752,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>485447</v>
+        <v>485638</v>
       </c>
       <c r="R185" t="n">
-        <v>6790434</v>
+        <v>6790456</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -20823,10 +20815,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122689950</v>
+        <v>122689519</v>
       </c>
       <c r="B186" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20866,10 +20858,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>485623</v>
+        <v>485696</v>
       </c>
       <c r="R186" t="n">
-        <v>6790393</v>
+        <v>6790431</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -20929,10 +20921,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>122689833</v>
+        <v>122689939</v>
       </c>
       <c r="B187" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20941,30 +20933,36 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
@@ -20972,10 +20970,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>485457</v>
+        <v>485533</v>
       </c>
       <c r="R187" t="n">
-        <v>6790457</v>
+        <v>6790398</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21035,10 +21033,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>122689806</v>
+        <v>122689889</v>
       </c>
       <c r="B188" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21078,10 +21076,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>485524</v>
+        <v>485406</v>
       </c>
       <c r="R188" t="n">
-        <v>6790465</v>
+        <v>6790464</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21141,10 +21139,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>122689725</v>
+        <v>122689920</v>
       </c>
       <c r="B189" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21157,31 +21155,26 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
@@ -21189,10 +21182,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>485609</v>
+        <v>485472</v>
       </c>
       <c r="R189" t="n">
-        <v>6790472</v>
+        <v>6790425</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -21233,6 +21226,7 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
+      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
@@ -21251,10 +21245,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122689594</v>
+        <v>122689718</v>
       </c>
       <c r="B190" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21294,10 +21288,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>485662</v>
+        <v>485610</v>
       </c>
       <c r="R190" t="n">
-        <v>6790461</v>
+        <v>6790472</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -21357,10 +21351,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122689732</v>
+        <v>122689833</v>
       </c>
       <c r="B191" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21400,10 +21394,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>485601</v>
+        <v>485457</v>
       </c>
       <c r="R191" t="n">
-        <v>6790468</v>
+        <v>6790457</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -21463,10 +21457,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122689768</v>
+        <v>122689714</v>
       </c>
       <c r="B192" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21506,10 +21500,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>485537</v>
+        <v>485613</v>
       </c>
       <c r="R192" t="n">
-        <v>6790465</v>
+        <v>6790471</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -21569,10 +21563,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122689548</v>
+        <v>122689872</v>
       </c>
       <c r="B193" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21612,10 +21606,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>485686</v>
+        <v>485412</v>
       </c>
       <c r="R193" t="n">
-        <v>6790446</v>
+        <v>6790481</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -21675,10 +21669,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122689753</v>
+        <v>122689723</v>
       </c>
       <c r="B194" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21687,30 +21681,36 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
@@ -21718,10 +21718,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>485577</v>
+        <v>485609</v>
       </c>
       <c r="R194" t="n">
-        <v>6790471</v>
+        <v>6790472</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -21781,10 +21781,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122689718</v>
+        <v>122689753</v>
       </c>
       <c r="B195" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21824,10 +21824,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>485610</v>
+        <v>485577</v>
       </c>
       <c r="R195" t="n">
-        <v>6790472</v>
+        <v>6790471</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -21887,10 +21887,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122689972</v>
+        <v>122689879</v>
       </c>
       <c r="B196" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -21930,10 +21930,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>485718</v>
+        <v>485409</v>
       </c>
       <c r="R196" t="n">
-        <v>6790397</v>
+        <v>6790470</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122608902</v>
+        <v>122607974</v>
       </c>
       <c r="B2" t="n">
-        <v>78499</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486280</v>
+        <v>486212</v>
       </c>
       <c r="R2" t="n">
-        <v>6790345</v>
+        <v>6790432</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122607047</v>
+        <v>122608792</v>
       </c>
       <c r="B3" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485706</v>
+        <v>486035</v>
       </c>
       <c r="R3" t="n">
-        <v>6790427</v>
+        <v>6790401</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122606308</v>
+        <v>122607160</v>
       </c>
       <c r="B4" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,17 +935,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485568</v>
+        <v>485961</v>
       </c>
       <c r="R4" t="n">
-        <v>6790397</v>
+        <v>6790453</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122606339</v>
+        <v>122607108</v>
       </c>
       <c r="B5" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485528</v>
+        <v>485504</v>
       </c>
       <c r="R5" t="n">
-        <v>6790365</v>
+        <v>6790441</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122607108</v>
+        <v>122607518</v>
       </c>
       <c r="B6" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485504</v>
+        <v>486071</v>
       </c>
       <c r="R6" t="n">
-        <v>6790441</v>
+        <v>6790384</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,22 +1223,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122608651</v>
+        <v>122608856</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486380</v>
+        <v>486343</v>
       </c>
       <c r="R7" t="n">
-        <v>6790321</v>
+        <v>6790373</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,12 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122606154</v>
+        <v>122607224</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,41 +1359,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485616</v>
+        <v>485981</v>
       </c>
       <c r="R8" t="n">
-        <v>6790354</v>
+        <v>6790453</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,19 +1452,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122607558</v>
+        <v>122607141</v>
       </c>
       <c r="B9" t="n">
         <v>56688</v>
@@ -1498,19 +1498,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486035</v>
+        <v>485906</v>
       </c>
       <c r="R9" t="n">
-        <v>6790401</v>
+        <v>6790433</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,22 +1569,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122608832</v>
+        <v>122606131</v>
       </c>
       <c r="B10" t="n">
-        <v>78499</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1597,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,13 +1621,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485504</v>
+        <v>485629</v>
       </c>
       <c r="R10" t="n">
-        <v>6790441</v>
+        <v>6790369</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,22 +1681,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122608926</v>
+        <v>122606271</v>
       </c>
       <c r="B11" t="n">
-        <v>78498</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,34 +1709,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486252</v>
+        <v>485553</v>
       </c>
       <c r="R11" t="n">
-        <v>6790351</v>
+        <v>6790369</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1763,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122607713</v>
+        <v>122608158</v>
       </c>
       <c r="B12" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,14 +1841,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486156</v>
+        <v>486281</v>
       </c>
       <c r="R12" t="n">
-        <v>6790429</v>
+        <v>6790441</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1875,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1890,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122606452</v>
+        <v>122609017</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,14 +1958,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485428</v>
+        <v>486064</v>
       </c>
       <c r="R13" t="n">
-        <v>6790393</v>
+        <v>6790364</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -1987,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122608856</v>
+        <v>122607948</v>
       </c>
       <c r="B14" t="n">
-        <v>8441</v>
+        <v>78503</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,41 +2046,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486343</v>
+        <v>485504</v>
       </c>
       <c r="R14" t="n">
-        <v>6790373</v>
+        <v>6790441</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2099,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,22 +2134,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122606955</v>
+        <v>122608926</v>
       </c>
       <c r="B15" t="n">
-        <v>78762</v>
+        <v>78502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,34 +2162,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485759</v>
+        <v>486252</v>
       </c>
       <c r="R15" t="n">
-        <v>6790467</v>
+        <v>6790351</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2211,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122606669</v>
+        <v>122606417</v>
       </c>
       <c r="B16" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,7 +2301,7 @@
         <v>485407</v>
       </c>
       <c r="R16" t="n">
-        <v>6790437</v>
+        <v>6790439</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2323,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122606118</v>
+        <v>122606209</v>
       </c>
       <c r="B17" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2435,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2455,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,10 +2482,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122606919</v>
+        <v>122607022</v>
       </c>
       <c r="B18" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2508,17 +2518,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485753</v>
+        <v>485706</v>
       </c>
       <c r="R18" t="n">
-        <v>6790423</v>
+        <v>6790427</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2547,7 +2557,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2567,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,22 +2582,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122607665</v>
+        <v>122606955</v>
       </c>
       <c r="B19" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,17 +2630,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486035</v>
+        <v>485759</v>
       </c>
       <c r="R19" t="n">
-        <v>6790401</v>
+        <v>6790467</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2659,7 +2669,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2679,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,22 +2694,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122606286</v>
+        <v>122607953</v>
       </c>
       <c r="B20" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2708,25 +2718,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2736,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>485541</v>
+        <v>486214</v>
       </c>
       <c r="R20" t="n">
-        <v>6790372</v>
+        <v>6790429</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2771,7 +2781,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,12 +2791,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På 3 tallar på stammen</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,10 +2818,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122609017</v>
+        <v>122608902</v>
       </c>
       <c r="B21" t="n">
-        <v>78762</v>
+        <v>78503</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2829,21 +2834,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2853,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486064</v>
+        <v>486280</v>
       </c>
       <c r="R21" t="n">
-        <v>6790364</v>
+        <v>6790345</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2888,7 +2893,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2903,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,10 +2930,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122607118</v>
+        <v>122607941</v>
       </c>
       <c r="B22" t="n">
-        <v>56688</v>
+        <v>78502</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2937,46 +2942,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>485884</v>
+        <v>485504</v>
       </c>
       <c r="R22" t="n">
-        <v>6790450</v>
+        <v>6790441</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,22 +3030,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122608828</v>
+        <v>122606807</v>
       </c>
       <c r="B23" t="n">
-        <v>78498</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3058,21 +3058,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>485504</v>
+        <v>485749</v>
       </c>
       <c r="R23" t="n">
-        <v>6790441</v>
+        <v>6790424</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3142,22 +3142,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122606235</v>
+        <v>122608061</v>
       </c>
       <c r="B24" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3194,13 +3194,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>485615</v>
+        <v>486229</v>
       </c>
       <c r="R24" t="n">
-        <v>6790353</v>
+        <v>6790440</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,7 +3239,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3254,22 +3259,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122606131</v>
+        <v>122606669</v>
       </c>
       <c r="B25" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3306,13 +3311,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>485629</v>
+        <v>485407</v>
       </c>
       <c r="R25" t="n">
-        <v>6790369</v>
+        <v>6790437</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3341,7 +3346,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3351,7 +3356,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3366,22 +3371,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122607141</v>
+        <v>122606154</v>
       </c>
       <c r="B26" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3390,46 +3395,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>485906</v>
+        <v>485616</v>
       </c>
       <c r="R26" t="n">
-        <v>6790433</v>
+        <v>6790354</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3483,22 +3483,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122607995</v>
+        <v>122608694</v>
       </c>
       <c r="B27" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3507,41 +3507,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486213</v>
+        <v>486035</v>
       </c>
       <c r="R27" t="n">
-        <v>6790435</v>
+        <v>6790401</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3595,22 +3595,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122606108</v>
+        <v>122608844</v>
       </c>
       <c r="B28" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3643,14 +3643,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>485649</v>
+        <v>486338</v>
       </c>
       <c r="R28" t="n">
-        <v>6790375</v>
+        <v>6790352</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3692,7 +3692,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3719,10 +3724,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122606394</v>
+        <v>122607915</v>
       </c>
       <c r="B29" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3759,13 +3764,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>485411</v>
+        <v>486193</v>
       </c>
       <c r="R29" t="n">
-        <v>6790441</v>
+        <v>6790410</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3794,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3804,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3819,12 +3824,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3834,7 +3839,7 @@
         <v>122606230</v>
       </c>
       <c r="B30" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3946,7 +3951,7 @@
         <v>122607048</v>
       </c>
       <c r="B31" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4055,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122606807</v>
+        <v>122606677</v>
       </c>
       <c r="B32" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4095,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>485749</v>
+        <v>485490</v>
       </c>
       <c r="R32" t="n">
-        <v>6790424</v>
+        <v>6790430</v>
       </c>
       <c r="S32" t="n">
         <v>9</v>
@@ -4130,7 +4135,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4140,7 +4145,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4167,10 +4172,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122607254</v>
+        <v>122606176</v>
       </c>
       <c r="B33" t="n">
-        <v>78762</v>
+        <v>78792</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4179,25 +4184,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4207,10 +4212,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486016</v>
+        <v>485613</v>
       </c>
       <c r="R33" t="n">
-        <v>6790443</v>
+        <v>6790370</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -4242,7 +4247,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4252,7 +4257,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4279,10 +4284,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122608990</v>
+        <v>122606208</v>
       </c>
       <c r="B34" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4291,38 +4296,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486070</v>
+        <v>485592</v>
       </c>
       <c r="R34" t="n">
-        <v>6790363</v>
+        <v>6790353</v>
       </c>
       <c r="S34" t="n">
         <v>9</v>
@@ -4354,7 +4359,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4364,7 +4369,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4391,10 +4396,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122606208</v>
+        <v>122606145</v>
       </c>
       <c r="B35" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4403,25 +4408,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4431,13 +4436,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485592</v>
+        <v>485616</v>
       </c>
       <c r="R35" t="n">
-        <v>6790353</v>
+        <v>6790356</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4466,7 +4471,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,7 +4481,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4491,22 +4496,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122606271</v>
+        <v>122608938</v>
       </c>
       <c r="B36" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4539,14 +4544,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485553</v>
+        <v>486253</v>
       </c>
       <c r="R36" t="n">
-        <v>6790369</v>
+        <v>6790356</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -4578,7 +4583,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4588,7 +4593,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4615,10 +4620,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122607495</v>
+        <v>122606651</v>
       </c>
       <c r="B37" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4655,10 +4660,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486056</v>
+        <v>485432</v>
       </c>
       <c r="R37" t="n">
-        <v>6790394</v>
+        <v>6790417</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -4690,7 +4695,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4700,7 +4705,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4727,10 +4732,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122607160</v>
+        <v>122607495</v>
       </c>
       <c r="B38" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4767,10 +4772,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>485961</v>
+        <v>486056</v>
       </c>
       <c r="R38" t="n">
-        <v>6790453</v>
+        <v>6790394</v>
       </c>
       <c r="S38" t="n">
         <v>9</v>
@@ -4802,7 +4807,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4812,7 +4817,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4839,7 +4844,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122607596</v>
+        <v>122607118</v>
       </c>
       <c r="B39" t="n">
         <v>56688</v>
@@ -4875,7 +4880,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4884,10 +4889,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486109</v>
+        <v>485884</v>
       </c>
       <c r="R39" t="n">
-        <v>6790384</v>
+        <v>6790450</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
@@ -4919,7 +4924,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4929,7 +4934,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4956,10 +4961,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122608938</v>
+        <v>122606919</v>
       </c>
       <c r="B40" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4992,14 +4997,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486253</v>
+        <v>485753</v>
       </c>
       <c r="R40" t="n">
-        <v>6790356</v>
+        <v>6790423</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -5031,7 +5036,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5041,7 +5046,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5068,10 +5073,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122606677</v>
+        <v>122607995</v>
       </c>
       <c r="B41" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5108,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>485490</v>
+        <v>486213</v>
       </c>
       <c r="R41" t="n">
-        <v>6790430</v>
+        <v>6790435</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5143,7 +5148,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +5158,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5180,10 +5185,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122606176</v>
+        <v>122606977</v>
       </c>
       <c r="B42" t="n">
-        <v>78788</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5192,25 +5197,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5220,10 +5225,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>485613</v>
+        <v>485766</v>
       </c>
       <c r="R42" t="n">
-        <v>6790370</v>
+        <v>6790457</v>
       </c>
       <c r="S42" t="n">
         <v>9</v>
@@ -5255,7 +5260,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5265,7 +5270,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5292,10 +5302,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122608158</v>
+        <v>122606204</v>
       </c>
       <c r="B43" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5328,17 +5338,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486281</v>
+        <v>485615</v>
       </c>
       <c r="R43" t="n">
-        <v>6790441</v>
+        <v>6790353</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5367,7 +5377,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5377,12 +5387,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5397,12 +5402,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5526,10 +5531,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122606145</v>
+        <v>122606286</v>
       </c>
       <c r="B45" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5566,13 +5571,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>485616</v>
+        <v>485541</v>
       </c>
       <c r="R45" t="n">
-        <v>6790356</v>
+        <v>6790372</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5601,7 +5606,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5611,7 +5616,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På 3 tallar på stammen</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5626,22 +5636,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122607953</v>
+        <v>122608651</v>
       </c>
       <c r="B46" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5650,38 +5660,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486214</v>
+        <v>486380</v>
       </c>
       <c r="R46" t="n">
-        <v>6790429</v>
+        <v>6790321</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5713,7 +5723,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5723,7 +5733,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5750,10 +5765,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122608844</v>
+        <v>122607596</v>
       </c>
       <c r="B47" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5762,38 +5777,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486338</v>
+        <v>486109</v>
       </c>
       <c r="R47" t="n">
-        <v>6790352</v>
+        <v>6790384</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5825,7 +5845,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5835,12 +5855,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5867,10 +5882,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122606651</v>
+        <v>122607713</v>
       </c>
       <c r="B48" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5907,10 +5922,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>485432</v>
+        <v>486156</v>
       </c>
       <c r="R48" t="n">
-        <v>6790417</v>
+        <v>6790429</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5942,7 +5957,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5952,7 +5967,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5979,10 +5994,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122607974</v>
+        <v>122606708</v>
       </c>
       <c r="B49" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6015,17 +6030,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486212</v>
+        <v>485568</v>
       </c>
       <c r="R49" t="n">
-        <v>6790432</v>
+        <v>6790397</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6054,7 +6069,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6064,7 +6079,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6079,22 +6094,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122607915</v>
+        <v>122608990</v>
       </c>
       <c r="B50" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6127,14 +6142,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486193</v>
+        <v>486070</v>
       </c>
       <c r="R50" t="n">
-        <v>6790410</v>
+        <v>6790363</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -6166,7 +6181,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6176,7 +6191,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6203,10 +6218,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122606408</v>
+        <v>122606339</v>
       </c>
       <c r="B51" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6243,13 +6258,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>485407</v>
+        <v>485528</v>
       </c>
       <c r="R51" t="n">
-        <v>6790439</v>
+        <v>6790365</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6278,7 +6293,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6288,7 +6303,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6303,12 +6318,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6318,7 +6333,7 @@
         <v>122608110</v>
       </c>
       <c r="B52" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6427,10 +6442,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122608061</v>
+        <v>122607254</v>
       </c>
       <c r="B53" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6467,10 +6482,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486229</v>
+        <v>486016</v>
       </c>
       <c r="R53" t="n">
-        <v>6790440</v>
+        <v>6790443</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6502,7 +6517,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6512,12 +6527,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6544,10 +6554,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122607224</v>
+        <v>122606394</v>
       </c>
       <c r="B54" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6556,46 +6566,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>485981</v>
+        <v>485411</v>
       </c>
       <c r="R54" t="n">
-        <v>6790453</v>
+        <v>6790441</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6624,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6634,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6649,22 +6654,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122606977</v>
+        <v>122606108</v>
       </c>
       <c r="B55" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6701,10 +6706,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>485766</v>
+        <v>485649</v>
       </c>
       <c r="R55" t="n">
-        <v>6790457</v>
+        <v>6790375</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6736,7 +6741,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6746,12 +6751,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6778,10 +6778,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122607518</v>
+        <v>122606452</v>
       </c>
       <c r="B56" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486071</v>
+        <v>485428</v>
       </c>
       <c r="R56" t="n">
-        <v>6790384</v>
+        <v>6790393</v>
       </c>
       <c r="S56" t="n">
         <v>9</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -9070,10 +9070,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122671575</v>
+        <v>122671659</v>
       </c>
       <c r="B76" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9082,30 +9082,36 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9113,10 +9119,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>485989</v>
+        <v>486020</v>
       </c>
       <c r="R76" t="n">
-        <v>6790394</v>
+        <v>6790412</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9176,7 +9182,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122671570</v>
+        <v>122671575</v>
       </c>
       <c r="B77" t="n">
         <v>78766</v>
@@ -9219,10 +9225,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>485953</v>
+        <v>485989</v>
       </c>
       <c r="R77" t="n">
-        <v>6790411</v>
+        <v>6790394</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9282,10 +9288,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122671659</v>
+        <v>122671570</v>
       </c>
       <c r="B78" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9294,36 +9300,30 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9331,10 +9331,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486020</v>
+        <v>485953</v>
       </c>
       <c r="R78" t="n">
-        <v>6790412</v>
+        <v>6790411</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -10039,10 +10039,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122671534</v>
+        <v>122671587</v>
       </c>
       <c r="B85" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10055,21 +10055,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10082,10 +10082,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>485901</v>
+        <v>485985</v>
       </c>
       <c r="R85" t="n">
-        <v>6790392</v>
+        <v>6790379</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10145,10 +10145,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122671587</v>
+        <v>122671534</v>
       </c>
       <c r="B86" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10161,21 +10161,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10188,10 +10188,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>485985</v>
+        <v>485901</v>
       </c>
       <c r="R86" t="n">
-        <v>6790379</v>
+        <v>6790392</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -11115,10 +11115,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122671424</v>
+        <v>122671879</v>
       </c>
       <c r="B95" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11127,30 +11127,35 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11158,10 +11163,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>485783</v>
+        <v>486429</v>
       </c>
       <c r="R95" t="n">
-        <v>6790367</v>
+        <v>6790399</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11196,13 +11201,17 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>på ett par platser intill granar</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11221,7 +11230,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122671378</v>
+        <v>122671424</v>
       </c>
       <c r="B96" t="n">
         <v>78766</v>
@@ -11264,10 +11273,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>485757</v>
+        <v>485783</v>
       </c>
       <c r="R96" t="n">
-        <v>6790379</v>
+        <v>6790367</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11327,10 +11336,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122671879</v>
+        <v>122671378</v>
       </c>
       <c r="B97" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11339,35 +11348,30 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -11375,10 +11379,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>486429</v>
+        <v>485757</v>
       </c>
       <c r="R97" t="n">
-        <v>6790399</v>
+        <v>6790379</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11413,17 +11417,13 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>på ett par platser intill granar</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -12088,7 +12088,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122671434</v>
+        <v>122671422</v>
       </c>
       <c r="B104" t="n">
         <v>78766</v>
@@ -12131,10 +12131,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>485799</v>
+        <v>485784</v>
       </c>
       <c r="R104" t="n">
-        <v>6790349</v>
+        <v>6790390</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12194,7 +12194,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122671674</v>
+        <v>122671512</v>
       </c>
       <c r="B105" t="n">
         <v>78766</v>
@@ -12237,13 +12237,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>486266</v>
+        <v>485876</v>
       </c>
       <c r="R105" t="n">
-        <v>6790373</v>
+        <v>6790371</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122671493</v>
+        <v>122671434</v>
       </c>
       <c r="B106" t="n">
         <v>78766</v>
@@ -12343,10 +12343,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>485859</v>
+        <v>485799</v>
       </c>
       <c r="R106" t="n">
-        <v>6790362</v>
+        <v>6790349</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12406,7 +12406,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122671422</v>
+        <v>122671674</v>
       </c>
       <c r="B107" t="n">
         <v>78766</v>
@@ -12449,13 +12449,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>485784</v>
+        <v>486266</v>
       </c>
       <c r="R107" t="n">
-        <v>6790390</v>
+        <v>6790373</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122671512</v>
+        <v>122671493</v>
       </c>
       <c r="B108" t="n">
         <v>78766</v>
@@ -12555,10 +12555,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>485876</v>
+        <v>485859</v>
       </c>
       <c r="R108" t="n">
-        <v>6790371</v>
+        <v>6790362</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -15380,10 +15380,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>122689738</v>
+        <v>122689942</v>
       </c>
       <c r="B135" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15396,33 +15396,25 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
@@ -15431,10 +15423,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>485597</v>
+        <v>485554</v>
       </c>
       <c r="R135" t="n">
-        <v>6790468</v>
+        <v>6790400</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -15494,7 +15486,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>122689895</v>
+        <v>122689540</v>
       </c>
       <c r="B136" t="n">
         <v>78766</v>
@@ -15537,10 +15529,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>485405</v>
+        <v>485689</v>
       </c>
       <c r="R136" t="n">
-        <v>6790460</v>
+        <v>6790436</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -15600,7 +15592,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>122689942</v>
+        <v>122689863</v>
       </c>
       <c r="B137" t="n">
         <v>78766</v>
@@ -15643,10 +15635,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>485554</v>
+        <v>485420</v>
       </c>
       <c r="R137" t="n">
-        <v>6790400</v>
+        <v>6790476</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15706,10 +15698,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>122689540</v>
+        <v>122689738</v>
       </c>
       <c r="B138" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15722,25 +15714,33 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
@@ -15749,10 +15749,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>485689</v>
+        <v>485597</v>
       </c>
       <c r="R138" t="n">
-        <v>6790436</v>
+        <v>6790468</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -15812,7 +15812,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>122689863</v>
+        <v>122689895</v>
       </c>
       <c r="B139" t="n">
         <v>78766</v>
@@ -15855,10 +15855,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>485420</v>
+        <v>485405</v>
       </c>
       <c r="R139" t="n">
-        <v>6790476</v>
+        <v>6790460</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -15918,7 +15918,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>122689829</v>
+        <v>122689924</v>
       </c>
       <c r="B140" t="n">
         <v>78766</v>
@@ -15961,10 +15961,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>485469</v>
+        <v>485489</v>
       </c>
       <c r="R140" t="n">
-        <v>6790456</v>
+        <v>6790405</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -16024,7 +16024,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>122689924</v>
+        <v>122689677</v>
       </c>
       <c r="B141" t="n">
         <v>78766</v>
@@ -16067,10 +16067,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>485489</v>
+        <v>485615</v>
       </c>
       <c r="R141" t="n">
-        <v>6790405</v>
+        <v>6790468</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16130,7 +16130,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>122689677</v>
+        <v>122689829</v>
       </c>
       <c r="B142" t="n">
         <v>78766</v>
@@ -16173,10 +16173,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>485615</v>
+        <v>485469</v>
       </c>
       <c r="R142" t="n">
-        <v>6790468</v>
+        <v>6790456</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -18165,7 +18165,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>122689918</v>
+        <v>122689619</v>
       </c>
       <c r="B161" t="n">
         <v>78766</v>
@@ -18208,10 +18208,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>485463</v>
+        <v>485645</v>
       </c>
       <c r="R161" t="n">
-        <v>6790428</v>
+        <v>6790451</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -18271,7 +18271,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>122689619</v>
+        <v>122689566</v>
       </c>
       <c r="B162" t="n">
         <v>78766</v>
@@ -18314,10 +18314,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>485645</v>
+        <v>485670</v>
       </c>
       <c r="R162" t="n">
-        <v>6790451</v>
+        <v>6790450</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -18377,7 +18377,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122689566</v>
+        <v>122689918</v>
       </c>
       <c r="B163" t="n">
         <v>78766</v>
@@ -18420,10 +18420,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>485670</v>
+        <v>485463</v>
       </c>
       <c r="R163" t="n">
-        <v>6790450</v>
+        <v>6790428</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -18907,7 +18907,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>122689963</v>
+        <v>122689959</v>
       </c>
       <c r="B168" t="n">
         <v>78766</v>
@@ -18950,10 +18950,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>485658</v>
+        <v>485627</v>
       </c>
       <c r="R168" t="n">
-        <v>6790402</v>
+        <v>6790392</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -19013,7 +19013,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>122689811</v>
+        <v>122689963</v>
       </c>
       <c r="B169" t="n">
         <v>78766</v>
@@ -19056,10 +19056,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>485510</v>
+        <v>485658</v>
       </c>
       <c r="R169" t="n">
-        <v>6790462</v>
+        <v>6790402</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -19119,7 +19119,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>122689611</v>
+        <v>122689811</v>
       </c>
       <c r="B170" t="n">
         <v>78766</v>
@@ -19162,10 +19162,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>485653</v>
+        <v>485510</v>
       </c>
       <c r="R170" t="n">
-        <v>6790460</v>
+        <v>6790462</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -19225,7 +19225,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>122689959</v>
+        <v>122689611</v>
       </c>
       <c r="B171" t="n">
         <v>78766</v>
@@ -19268,10 +19268,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>485627</v>
+        <v>485653</v>
       </c>
       <c r="R171" t="n">
-        <v>6790392</v>
+        <v>6790460</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122607974</v>
+        <v>122609017</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486212</v>
+        <v>486064</v>
       </c>
       <c r="R2" t="n">
-        <v>6790432</v>
+        <v>6790364</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122608792</v>
+        <v>122606171</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486035</v>
+        <v>485662</v>
       </c>
       <c r="R3" t="n">
-        <v>6790401</v>
+        <v>6790357</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122607160</v>
+        <v>122606924</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -935,17 +935,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485961</v>
+        <v>485706</v>
       </c>
       <c r="R4" t="n">
-        <v>6790453</v>
+        <v>6790427</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,19 +999,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122607108</v>
+        <v>122606919</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485504</v>
+        <v>485753</v>
       </c>
       <c r="R5" t="n">
-        <v>6790441</v>
+        <v>6790423</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,19 +1111,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122607518</v>
+        <v>122607254</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486071</v>
+        <v>486016</v>
       </c>
       <c r="R6" t="n">
-        <v>6790384</v>
+        <v>6790443</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122608856</v>
+        <v>122608964</v>
       </c>
       <c r="B7" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,41 +1247,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486343</v>
+        <v>486035</v>
       </c>
       <c r="R7" t="n">
-        <v>6790373</v>
+        <v>6790401</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,22 +1335,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122607224</v>
+        <v>122606751</v>
       </c>
       <c r="B8" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,46 +1359,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485981</v>
+        <v>485504</v>
       </c>
       <c r="R8" t="n">
-        <v>6790453</v>
+        <v>6790441</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,22 +1447,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122607141</v>
+        <v>122606452</v>
       </c>
       <c r="B9" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,43 +1471,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485906</v>
+        <v>485428</v>
       </c>
       <c r="R9" t="n">
-        <v>6790433</v>
+        <v>6790393</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1544,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122606131</v>
+        <v>122606708</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1617,17 +1607,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485629</v>
+        <v>485568</v>
       </c>
       <c r="R10" t="n">
-        <v>6790369</v>
+        <v>6790397</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1656,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,19 +1671,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122606271</v>
+        <v>122606408</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1733,13 +1723,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485553</v>
+        <v>485407</v>
       </c>
       <c r="R11" t="n">
-        <v>6790369</v>
+        <v>6790439</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,19 +1783,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122608158</v>
+        <v>122606235</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1841,17 +1831,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486281</v>
+        <v>485615</v>
       </c>
       <c r="R12" t="n">
-        <v>6790441</v>
+        <v>6790353</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1880,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,12 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,19 +1895,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122609017</v>
+        <v>122606145</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1958,17 +1943,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486064</v>
+        <v>485616</v>
       </c>
       <c r="R13" t="n">
-        <v>6790364</v>
+        <v>6790356</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1997,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,22 +2007,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122607948</v>
+        <v>122606176</v>
       </c>
       <c r="B14" t="n">
-        <v>78503</v>
+        <v>78792</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,25 +2031,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,13 +2059,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485504</v>
+        <v>485613</v>
       </c>
       <c r="R14" t="n">
-        <v>6790441</v>
+        <v>6790370</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2109,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,22 +2119,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122608926</v>
+        <v>122607713</v>
       </c>
       <c r="B15" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,34 +2147,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486252</v>
+        <v>486156</v>
       </c>
       <c r="R15" t="n">
-        <v>6790351</v>
+        <v>6790429</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2221,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,7 +2243,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122606417</v>
+        <v>122606651</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2298,13 +2283,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485407</v>
+        <v>485432</v>
       </c>
       <c r="R16" t="n">
-        <v>6790439</v>
+        <v>6790417</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2333,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,19 +2343,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122606209</v>
+        <v>122606108</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2406,17 +2391,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485662</v>
+        <v>485649</v>
       </c>
       <c r="R17" t="n">
-        <v>6790357</v>
+        <v>6790375</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2445,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,19 +2455,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122607022</v>
+        <v>122606154</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2518,17 +2503,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485706</v>
+        <v>485616</v>
       </c>
       <c r="R18" t="n">
-        <v>6790427</v>
+        <v>6790354</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2557,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2567,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2582,22 +2567,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122606955</v>
+        <v>122607118</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2606,38 +2591,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>485759</v>
+        <v>485884</v>
       </c>
       <c r="R19" t="n">
-        <v>6790467</v>
+        <v>6790450</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2669,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2679,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,7 +2696,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122607953</v>
+        <v>122606208</v>
       </c>
       <c r="B20" t="n">
         <v>8441</v>
@@ -2746,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486214</v>
+        <v>485592</v>
       </c>
       <c r="R20" t="n">
-        <v>6790429</v>
+        <v>6790353</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2781,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,7 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,7 +2808,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122608902</v>
+        <v>122607948</v>
       </c>
       <c r="B21" t="n">
         <v>78503</v>
@@ -2854,17 +2844,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486280</v>
+        <v>485504</v>
       </c>
       <c r="R21" t="n">
-        <v>6790345</v>
+        <v>6790441</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2893,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2903,7 +2893,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2918,22 +2908,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122607941</v>
+        <v>122606977</v>
       </c>
       <c r="B22" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2946,21 +2936,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2970,13 +2960,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>485504</v>
+        <v>485766</v>
       </c>
       <c r="R22" t="n">
-        <v>6790441</v>
+        <v>6790457</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3005,7 +2995,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3005,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,19 +3025,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122606807</v>
+        <v>122606230</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -3082,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>485749</v>
+        <v>485561</v>
       </c>
       <c r="R23" t="n">
-        <v>6790424</v>
+        <v>6790367</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3117,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3154,7 +3149,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122608061</v>
+        <v>122606286</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -3194,10 +3189,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486229</v>
+        <v>485541</v>
       </c>
       <c r="R24" t="n">
-        <v>6790440</v>
+        <v>6790372</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3229,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,12 +3234,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På 5 tallar</t>
+          <t>På 3 tallar på stammen</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3271,10 +3266,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122606669</v>
+        <v>122608828</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3287,21 +3282,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3311,10 +3306,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>485407</v>
+        <v>485504</v>
       </c>
       <c r="R25" t="n">
-        <v>6790437</v>
+        <v>6790441</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3346,7 +3341,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3356,7 +3351,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3383,7 +3378,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122606154</v>
+        <v>122608938</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3419,17 +3414,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>485616</v>
+        <v>486253</v>
       </c>
       <c r="R26" t="n">
-        <v>6790354</v>
+        <v>6790356</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3458,7 +3453,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3468,7 +3463,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3483,22 +3478,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122608694</v>
+        <v>122606271</v>
       </c>
       <c r="B27" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3507,41 +3502,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486035</v>
+        <v>485553</v>
       </c>
       <c r="R27" t="n">
-        <v>6790401</v>
+        <v>6790369</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3570,7 +3565,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3580,7 +3575,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3595,19 +3590,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122608844</v>
+        <v>122606807</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -3643,14 +3638,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486338</v>
+        <v>485749</v>
       </c>
       <c r="R28" t="n">
-        <v>6790352</v>
+        <v>6790424</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3682,7 +3677,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3692,12 +3687,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3724,7 +3714,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122607915</v>
+        <v>122608061</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3764,10 +3754,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486193</v>
+        <v>486229</v>
       </c>
       <c r="R29" t="n">
-        <v>6790410</v>
+        <v>6790440</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3799,7 +3789,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3799,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3836,7 +3831,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122606230</v>
+        <v>122608158</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3872,14 +3867,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>485561</v>
+        <v>486281</v>
       </c>
       <c r="R30" t="n">
-        <v>6790367</v>
+        <v>6790441</v>
       </c>
       <c r="S30" t="n">
         <v>9</v>
@@ -3911,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3921,7 +3916,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3948,10 +3948,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122607048</v>
+        <v>122608856</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3960,38 +3960,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>485855</v>
+        <v>486343</v>
       </c>
       <c r="R31" t="n">
-        <v>6790443</v>
+        <v>6790373</v>
       </c>
       <c r="S31" t="n">
         <v>9</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4060,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122606677</v>
+        <v>122607953</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4072,25 +4072,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>485490</v>
+        <v>486214</v>
       </c>
       <c r="R32" t="n">
-        <v>6790430</v>
+        <v>6790429</v>
       </c>
       <c r="S32" t="n">
         <v>9</v>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4172,10 +4172,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122606176</v>
+        <v>122606955</v>
       </c>
       <c r="B33" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4184,25 +4184,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4212,10 +4212,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>485613</v>
+        <v>485759</v>
       </c>
       <c r="R33" t="n">
-        <v>6790370</v>
+        <v>6790467</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4284,10 +4284,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122606208</v>
+        <v>122607558</v>
       </c>
       <c r="B34" t="n">
-        <v>8441</v>
+        <v>56688</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4300,37 +4300,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485592</v>
+        <v>486035</v>
       </c>
       <c r="R34" t="n">
-        <v>6790353</v>
+        <v>6790401</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4384,22 +4384,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122606145</v>
+        <v>122607141</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4408,41 +4408,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485616</v>
+        <v>485906</v>
       </c>
       <c r="R35" t="n">
-        <v>6790356</v>
+        <v>6790433</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4471,7 +4476,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4481,7 +4486,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4496,19 +4501,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122608938</v>
+        <v>122607107</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4544,14 +4549,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486253</v>
+        <v>485855</v>
       </c>
       <c r="R36" t="n">
-        <v>6790356</v>
+        <v>6790443</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -4583,7 +4588,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4593,7 +4598,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4620,7 +4625,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122606651</v>
+        <v>122606339</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4660,10 +4665,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>485432</v>
+        <v>485528</v>
       </c>
       <c r="R37" t="n">
-        <v>6790417</v>
+        <v>6790365</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -4695,7 +4700,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4705,7 +4710,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4732,7 +4737,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122607495</v>
+        <v>122607915</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -4772,10 +4777,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486056</v>
+        <v>486193</v>
       </c>
       <c r="R38" t="n">
-        <v>6790394</v>
+        <v>6790410</v>
       </c>
       <c r="S38" t="n">
         <v>9</v>
@@ -4807,7 +4812,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4817,7 +4822,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4844,10 +4849,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122607118</v>
+        <v>122607995</v>
       </c>
       <c r="B39" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4856,43 +4861,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>485884</v>
+        <v>486213</v>
       </c>
       <c r="R39" t="n">
-        <v>6790450</v>
+        <v>6790435</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4961,7 +4961,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122606919</v>
+        <v>122608990</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -4997,14 +4997,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>485753</v>
+        <v>486070</v>
       </c>
       <c r="R40" t="n">
-        <v>6790423</v>
+        <v>6790363</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5073,10 +5073,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122607995</v>
+        <v>122607446</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5085,38 +5085,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486213</v>
+        <v>486045</v>
       </c>
       <c r="R41" t="n">
-        <v>6790435</v>
+        <v>6790383</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5148,7 +5153,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5158,7 +5163,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5185,10 +5190,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122606977</v>
+        <v>122608902</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5201,34 +5206,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>485766</v>
+        <v>486280</v>
       </c>
       <c r="R42" t="n">
-        <v>6790457</v>
+        <v>6790345</v>
       </c>
       <c r="S42" t="n">
         <v>9</v>
@@ -5260,7 +5265,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5270,12 +5275,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5302,10 +5302,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122606204</v>
+        <v>122607596</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5314,41 +5314,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>485615</v>
+        <v>486109</v>
       </c>
       <c r="R43" t="n">
-        <v>6790353</v>
+        <v>6790384</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5377,7 +5382,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5387,7 +5392,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5402,22 +5407,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122607446</v>
+        <v>122608926</v>
       </c>
       <c r="B44" t="n">
-        <v>56688</v>
+        <v>78502</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5426,43 +5431,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486045</v>
+        <v>486252</v>
       </c>
       <c r="R44" t="n">
-        <v>6790383</v>
+        <v>6790351</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5531,7 +5531,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122606286</v>
+        <v>122607495</v>
       </c>
       <c r="B45" t="n">
         <v>78766</v>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>485541</v>
+        <v>486056</v>
       </c>
       <c r="R45" t="n">
-        <v>6790372</v>
+        <v>6790394</v>
       </c>
       <c r="S45" t="n">
         <v>9</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5616,12 +5616,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På 3 tallar på stammen</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5648,7 +5643,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122608651</v>
+        <v>122606677</v>
       </c>
       <c r="B46" t="n">
         <v>78766</v>
@@ -5684,14 +5679,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486380</v>
+        <v>485490</v>
       </c>
       <c r="R46" t="n">
-        <v>6790321</v>
+        <v>6790430</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5723,7 +5718,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5733,12 +5728,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5765,10 +5755,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122607596</v>
+        <v>122608651</v>
       </c>
       <c r="B47" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5777,43 +5767,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486109</v>
+        <v>486380</v>
       </c>
       <c r="R47" t="n">
-        <v>6790384</v>
+        <v>6790321</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5845,7 +5830,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5855,7 +5840,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5882,7 +5872,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122607713</v>
+        <v>122606442</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -5922,13 +5912,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486156</v>
+        <v>485407</v>
       </c>
       <c r="R48" t="n">
-        <v>6790429</v>
+        <v>6790437</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5957,7 +5947,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5967,7 +5957,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5982,19 +5972,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122606708</v>
+        <v>122607518</v>
       </c>
       <c r="B49" t="n">
         <v>78766</v>
@@ -6030,17 +6020,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>485568</v>
+        <v>486071</v>
       </c>
       <c r="R49" t="n">
-        <v>6790397</v>
+        <v>6790384</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6069,7 +6059,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6079,7 +6069,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6094,22 +6084,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122608990</v>
+        <v>122607224</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6118,38 +6108,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486070</v>
+        <v>485981</v>
       </c>
       <c r="R50" t="n">
-        <v>6790363</v>
+        <v>6790453</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -6181,7 +6176,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6191,7 +6186,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6218,7 +6213,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122606339</v>
+        <v>122607974</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -6258,10 +6253,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>485528</v>
+        <v>486212</v>
       </c>
       <c r="R51" t="n">
-        <v>6790365</v>
+        <v>6790432</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -6293,7 +6288,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6303,7 +6298,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6330,7 +6325,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122608110</v>
+        <v>122606394</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -6366,17 +6361,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486270</v>
+        <v>485411</v>
       </c>
       <c r="R52" t="n">
-        <v>6790427</v>
+        <v>6790441</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6405,7 +6400,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6415,7 +6410,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6430,19 +6425,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122607254</v>
+        <v>122607160</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -6482,10 +6477,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486016</v>
+        <v>485961</v>
       </c>
       <c r="R53" t="n">
-        <v>6790443</v>
+        <v>6790453</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6517,7 +6512,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6527,7 +6522,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6554,7 +6549,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122606394</v>
+        <v>122608844</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6590,17 +6585,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>485411</v>
+        <v>486338</v>
       </c>
       <c r="R54" t="n">
-        <v>6790441</v>
+        <v>6790352</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6629,7 +6624,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6634,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6654,19 +6654,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122606108</v>
+        <v>122606131</v>
       </c>
       <c r="B55" t="n">
         <v>78766</v>
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>485649</v>
+        <v>485629</v>
       </c>
       <c r="R55" t="n">
-        <v>6790375</v>
+        <v>6790369</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6778,7 +6778,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122606452</v>
+        <v>122608110</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -6814,14 +6814,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>485428</v>
+        <v>486270</v>
       </c>
       <c r="R56" t="n">
-        <v>6790393</v>
+        <v>6790427</v>
       </c>
       <c r="S56" t="n">
         <v>9</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6890,10 +6890,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122606642</v>
+        <v>122608713</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6902,38 +6902,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>485586</v>
+        <v>485504</v>
       </c>
       <c r="R57" t="n">
-        <v>6790395</v>
+        <v>6790441</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6965,7 +6973,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6975,7 +6983,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6990,22 +6998,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122608713</v>
+        <v>122607688</v>
       </c>
       <c r="B58" t="n">
-        <v>56688</v>
+        <v>90964</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7014,49 +7022,45 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485504</v>
+        <v>486156</v>
       </c>
       <c r="R58" t="n">
-        <v>6790441</v>
+        <v>6790429</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7085,7 +7089,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7095,7 +7099,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7110,22 +7114,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122607273</v>
+        <v>122608142</v>
       </c>
       <c r="B59" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7134,50 +7138,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>485932</v>
+        <v>486240</v>
       </c>
       <c r="R59" t="n">
-        <v>6790416</v>
+        <v>6790382</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7206,7 +7201,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7216,7 +7211,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7225,7 +7220,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7244,10 +7238,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122608903</v>
+        <v>122609008</v>
       </c>
       <c r="B60" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7260,21 +7254,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7284,10 +7278,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486211</v>
+        <v>486063</v>
       </c>
       <c r="R60" t="n">
-        <v>6790317</v>
+        <v>6790348</v>
       </c>
       <c r="S60" t="n">
         <v>8</v>
@@ -7319,7 +7313,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7329,7 +7323,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7356,10 +7350,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122608928</v>
+        <v>122606247</v>
       </c>
       <c r="B61" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7372,34 +7366,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486063</v>
+        <v>485626</v>
       </c>
       <c r="R61" t="n">
-        <v>6790348</v>
+        <v>6790401</v>
       </c>
       <c r="S61" t="n">
         <v>9</v>
@@ -7431,7 +7425,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7441,7 +7435,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7468,10 +7462,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122608724</v>
+        <v>122608928</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7484,21 +7478,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7508,13 +7502,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486211</v>
+        <v>486063</v>
       </c>
       <c r="R62" t="n">
-        <v>6790317</v>
+        <v>6790348</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7543,7 +7537,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7553,7 +7547,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7580,10 +7574,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122607038</v>
+        <v>122608903</v>
       </c>
       <c r="B63" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7596,37 +7590,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>485772</v>
+        <v>486211</v>
       </c>
       <c r="R63" t="n">
-        <v>6790421</v>
+        <v>6790317</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7655,7 +7649,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7665,7 +7659,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7692,10 +7686,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122607077</v>
+        <v>122607273</v>
       </c>
       <c r="B64" t="n">
-        <v>56688</v>
+        <v>8441</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7708,29 +7702,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7740,13 +7735,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>485772</v>
+        <v>485932</v>
       </c>
       <c r="R64" t="n">
-        <v>6790421</v>
+        <v>6790416</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7775,7 +7770,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7785,7 +7780,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7794,6 +7789,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7812,10 +7808,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122607688</v>
+        <v>122607719</v>
       </c>
       <c r="B65" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7828,41 +7824,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486156</v>
+        <v>486157</v>
       </c>
       <c r="R65" t="n">
-        <v>6790429</v>
+        <v>6790397</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7891,7 +7883,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7901,7 +7893,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7916,22 +7908,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122607445</v>
+        <v>122606756</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7940,38 +7932,47 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486082</v>
+        <v>485504</v>
       </c>
       <c r="R66" t="n">
-        <v>6790427</v>
+        <v>6790441</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8003,7 +8004,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8013,7 +8014,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8022,28 +8023,29 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122607216</v>
+        <v>122608724</v>
       </c>
       <c r="B67" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8052,50 +8054,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>485504</v>
+        <v>486211</v>
       </c>
       <c r="R67" t="n">
-        <v>6790441</v>
+        <v>6790317</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8124,7 +8117,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8134,7 +8127,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8143,29 +8136,28 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122606760</v>
+        <v>122607038</v>
       </c>
       <c r="B68" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8178,45 +8170,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>485504</v>
+        <v>485772</v>
       </c>
       <c r="R68" t="n">
-        <v>6790441</v>
+        <v>6790421</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8245,7 +8229,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8255,7 +8239,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8270,22 +8254,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122606247</v>
+        <v>122607077</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8294,41 +8278,49 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>485626</v>
+        <v>485772</v>
       </c>
       <c r="R69" t="n">
-        <v>6790401</v>
+        <v>6790421</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8357,7 +8349,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8367,7 +8359,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8394,10 +8386,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122608142</v>
+        <v>122609064</v>
       </c>
       <c r="B70" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8406,41 +8398,50 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486240</v>
+        <v>486063</v>
       </c>
       <c r="R70" t="n">
-        <v>6790382</v>
+        <v>6790348</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8469,7 +8470,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8479,7 +8480,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8488,6 +8489,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8506,7 +8508,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122609008</v>
+        <v>122606143</v>
       </c>
       <c r="B71" t="n">
         <v>78766</v>
@@ -8542,17 +8544,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486063</v>
+        <v>485681</v>
       </c>
       <c r="R71" t="n">
-        <v>6790348</v>
+        <v>6790440</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8581,7 +8583,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8591,7 +8593,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8618,10 +8620,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122609064</v>
+        <v>122607445</v>
       </c>
       <c r="B72" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8630,50 +8632,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486063</v>
+        <v>486082</v>
       </c>
       <c r="R72" t="n">
-        <v>6790348</v>
+        <v>6790427</v>
       </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8702,7 +8695,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8712,7 +8705,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8721,7 +8714,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8740,7 +8732,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122607719</v>
+        <v>122606642</v>
       </c>
       <c r="B73" t="n">
         <v>78766</v>
@@ -8780,13 +8772,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486157</v>
+        <v>485586</v>
       </c>
       <c r="R73" t="n">
-        <v>6790397</v>
+        <v>6790395</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8815,7 +8807,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8825,7 +8817,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8852,10 +8844,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122606143</v>
+        <v>122606760</v>
       </c>
       <c r="B74" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8868,37 +8860,45 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>485681</v>
+        <v>485504</v>
       </c>
       <c r="R74" t="n">
-        <v>6790440</v>
+        <v>6790441</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8952,19 +8952,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122671569</v>
+        <v>122671559</v>
       </c>
       <c r="B75" t="n">
         <v>78766</v>
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>485951</v>
+        <v>485916</v>
       </c>
       <c r="R75" t="n">
-        <v>6790408</v>
+        <v>6790407</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9070,10 +9070,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122671659</v>
+        <v>122671667</v>
       </c>
       <c r="B76" t="n">
-        <v>8441</v>
+        <v>78800</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9082,36 +9082,30 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9119,13 +9113,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486020</v>
+        <v>486043</v>
       </c>
       <c r="R76" t="n">
-        <v>6790412</v>
+        <v>6790416</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9182,10 +9176,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122671575</v>
+        <v>122671658</v>
       </c>
       <c r="B77" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9198,26 +9192,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9225,10 +9224,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>485989</v>
+        <v>486037</v>
       </c>
       <c r="R77" t="n">
-        <v>6790394</v>
+        <v>6790372</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9269,7 +9268,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9288,7 +9286,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122671570</v>
+        <v>122671521</v>
       </c>
       <c r="B78" t="n">
         <v>78766</v>
@@ -9331,10 +9329,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>485953</v>
+        <v>485893</v>
       </c>
       <c r="R78" t="n">
-        <v>6790411</v>
+        <v>6790386</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9394,10 +9392,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122671667</v>
+        <v>122671569</v>
       </c>
       <c r="B79" t="n">
-        <v>78800</v>
+        <v>78766</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9410,21 +9408,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9437,13 +9435,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486043</v>
+        <v>485951</v>
       </c>
       <c r="R79" t="n">
-        <v>6790416</v>
+        <v>6790408</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9500,7 +9498,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122671506</v>
+        <v>122671493</v>
       </c>
       <c r="B80" t="n">
         <v>78766</v>
@@ -9543,10 +9541,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>485861</v>
+        <v>485859</v>
       </c>
       <c r="R80" t="n">
-        <v>6790364</v>
+        <v>6790362</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9606,10 +9604,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122671595</v>
+        <v>122671879</v>
       </c>
       <c r="B81" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9618,30 +9616,35 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -9649,10 +9652,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>485984</v>
+        <v>486429</v>
       </c>
       <c r="R81" t="n">
-        <v>6790370</v>
+        <v>6790399</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9687,13 +9690,17 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>på ett par platser intill granar</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9712,7 +9719,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122671508</v>
+        <v>122671679</v>
       </c>
       <c r="B82" t="n">
         <v>78766</v>
@@ -9755,13 +9762,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>485871</v>
+        <v>486342</v>
       </c>
       <c r="R82" t="n">
-        <v>6790368</v>
+        <v>6790369</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9818,7 +9825,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122671559</v>
+        <v>122671447</v>
       </c>
       <c r="B83" t="n">
         <v>78766</v>
@@ -9861,10 +9868,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>485916</v>
+        <v>485830</v>
       </c>
       <c r="R83" t="n">
-        <v>6790407</v>
+        <v>6790346</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9924,10 +9931,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122671888</v>
+        <v>122671512</v>
       </c>
       <c r="B84" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9936,35 +9943,30 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9972,10 +9974,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>485897</v>
+        <v>485876</v>
       </c>
       <c r="R84" t="n">
-        <v>6790441</v>
+        <v>6790371</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10010,17 +10012,13 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>under betestall rikligt</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -10039,10 +10037,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122671587</v>
+        <v>122671555</v>
       </c>
       <c r="B85" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10055,21 +10053,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10082,10 +10080,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>485985</v>
+        <v>485915</v>
       </c>
       <c r="R85" t="n">
-        <v>6790379</v>
+        <v>6790407</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10145,10 +10143,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122671534</v>
+        <v>122671537</v>
       </c>
       <c r="B86" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10157,30 +10155,36 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10188,10 +10192,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>485901</v>
+        <v>485910</v>
       </c>
       <c r="R86" t="n">
-        <v>6790392</v>
+        <v>6790394</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10251,10 +10255,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122671537</v>
+        <v>122671675</v>
       </c>
       <c r="B87" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10263,36 +10267,30 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10300,13 +10298,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>485910</v>
+        <v>486331</v>
       </c>
       <c r="R87" t="n">
-        <v>6790394</v>
+        <v>6790370</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10363,10 +10361,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122671519</v>
+        <v>122671609</v>
       </c>
       <c r="B88" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10379,21 +10377,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10406,10 +10404,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>485876</v>
+        <v>486013</v>
       </c>
       <c r="R88" t="n">
-        <v>6790381</v>
+        <v>6790366</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10469,7 +10467,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122671453</v>
+        <v>122671508</v>
       </c>
       <c r="B89" t="n">
         <v>78766</v>
@@ -10512,10 +10510,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>485835</v>
+        <v>485871</v>
       </c>
       <c r="R89" t="n">
-        <v>6790356</v>
+        <v>6790368</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10575,10 +10573,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122671610</v>
+        <v>122671384</v>
       </c>
       <c r="B90" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10591,21 +10589,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10618,10 +10616,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486013</v>
+        <v>485777</v>
       </c>
       <c r="R90" t="n">
-        <v>6790366</v>
+        <v>6790392</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10681,10 +10679,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122671681</v>
+        <v>122671668</v>
       </c>
       <c r="B91" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10693,36 +10691,30 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10730,10 +10722,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>486342</v>
+        <v>486079</v>
       </c>
       <c r="R91" t="n">
-        <v>6790369</v>
+        <v>6790394</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10793,10 +10785,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122671592</v>
+        <v>122671608</v>
       </c>
       <c r="B92" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10809,21 +10801,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10836,10 +10828,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>485984</v>
+        <v>486013</v>
       </c>
       <c r="R92" t="n">
-        <v>6790371</v>
+        <v>6790366</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10899,10 +10891,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122671440</v>
+        <v>122671587</v>
       </c>
       <c r="B93" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10915,21 +10907,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10942,10 +10934,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>485819</v>
+        <v>485985</v>
       </c>
       <c r="R93" t="n">
-        <v>6790340</v>
+        <v>6790379</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11005,10 +10997,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122671523</v>
+        <v>122671579</v>
       </c>
       <c r="B94" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11021,31 +11013,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11053,10 +11040,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>485893</v>
+        <v>485989</v>
       </c>
       <c r="R94" t="n">
-        <v>6790386</v>
+        <v>6790378</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11097,6 +11084,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11115,10 +11103,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122671879</v>
+        <v>122671378</v>
       </c>
       <c r="B95" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11127,35 +11115,30 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11163,10 +11146,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>486429</v>
+        <v>485757</v>
       </c>
       <c r="R95" t="n">
-        <v>6790399</v>
+        <v>6790379</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11201,17 +11184,13 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>på ett par platser intill granar</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11230,7 +11209,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122671424</v>
+        <v>122671434</v>
       </c>
       <c r="B96" t="n">
         <v>78766</v>
@@ -11273,10 +11252,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>485783</v>
+        <v>485799</v>
       </c>
       <c r="R96" t="n">
-        <v>6790367</v>
+        <v>6790349</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11336,7 +11315,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122671378</v>
+        <v>122671674</v>
       </c>
       <c r="B97" t="n">
         <v>78766</v>
@@ -11379,13 +11358,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>485757</v>
+        <v>486266</v>
       </c>
       <c r="R97" t="n">
-        <v>6790379</v>
+        <v>6790373</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11442,10 +11421,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122671658</v>
+        <v>122671534</v>
       </c>
       <c r="B98" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11458,31 +11437,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -11490,10 +11464,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>486037</v>
+        <v>485901</v>
       </c>
       <c r="R98" t="n">
-        <v>6790372</v>
+        <v>6790392</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11534,6 +11508,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11552,10 +11527,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122671579</v>
+        <v>122671541</v>
       </c>
       <c r="B99" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11564,30 +11539,36 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -11595,10 +11576,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>485989</v>
+        <v>485879</v>
       </c>
       <c r="R99" t="n">
-        <v>6790378</v>
+        <v>6790409</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11658,7 +11639,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122671541</v>
+        <v>122671681</v>
       </c>
       <c r="B100" t="n">
         <v>8441</v>
@@ -11707,13 +11688,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>485879</v>
+        <v>486342</v>
       </c>
       <c r="R100" t="n">
-        <v>6790409</v>
+        <v>6790369</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11770,7 +11751,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122671647</v>
+        <v>122671519</v>
       </c>
       <c r="B101" t="n">
         <v>78766</v>
@@ -11813,13 +11794,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>486035</v>
+        <v>485876</v>
       </c>
       <c r="R101" t="n">
-        <v>6790369</v>
+        <v>6790381</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11876,10 +11857,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122671521</v>
+        <v>122671523</v>
       </c>
       <c r="B102" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11892,26 +11873,31 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -11963,7 +11949,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11982,10 +11967,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122671609</v>
+        <v>122671422</v>
       </c>
       <c r="B103" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11998,21 +11983,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12025,10 +12010,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>486013</v>
+        <v>485784</v>
       </c>
       <c r="R103" t="n">
-        <v>6790366</v>
+        <v>6790390</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12088,10 +12073,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122671422</v>
+        <v>122671888</v>
       </c>
       <c r="B104" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12100,30 +12085,35 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12131,10 +12121,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>485784</v>
+        <v>485897</v>
       </c>
       <c r="R104" t="n">
-        <v>6790390</v>
+        <v>6790441</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12169,13 +12159,17 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>under betestall rikligt</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -12194,7 +12188,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122671512</v>
+        <v>122671575</v>
       </c>
       <c r="B105" t="n">
         <v>78766</v>
@@ -12237,10 +12231,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>485876</v>
+        <v>485989</v>
       </c>
       <c r="R105" t="n">
-        <v>6790371</v>
+        <v>6790394</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12300,7 +12294,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122671434</v>
+        <v>122671462</v>
       </c>
       <c r="B106" t="n">
         <v>78766</v>
@@ -12343,10 +12337,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>485799</v>
+        <v>485835</v>
       </c>
       <c r="R106" t="n">
-        <v>6790349</v>
+        <v>6790356</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12406,7 +12400,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122671674</v>
+        <v>122671592</v>
       </c>
       <c r="B107" t="n">
         <v>78766</v>
@@ -12449,13 +12443,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>486266</v>
+        <v>485984</v>
       </c>
       <c r="R107" t="n">
-        <v>6790373</v>
+        <v>6790371</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12512,7 +12506,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122671493</v>
+        <v>122671424</v>
       </c>
       <c r="B108" t="n">
         <v>78766</v>
@@ -12555,10 +12549,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>485859</v>
+        <v>485783</v>
       </c>
       <c r="R108" t="n">
-        <v>6790362</v>
+        <v>6790367</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12618,7 +12612,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122671536</v>
+        <v>122671570</v>
       </c>
       <c r="B109" t="n">
         <v>78766</v>
@@ -12661,10 +12655,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>485910</v>
+        <v>485953</v>
       </c>
       <c r="R109" t="n">
-        <v>6790394</v>
+        <v>6790411</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12724,7 +12718,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122671384</v>
+        <v>122671564</v>
       </c>
       <c r="B110" t="n">
         <v>78766</v>
@@ -12767,10 +12761,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>485777</v>
+        <v>485933</v>
       </c>
       <c r="R110" t="n">
-        <v>6790392</v>
+        <v>6790411</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12830,7 +12824,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122671668</v>
+        <v>122671536</v>
       </c>
       <c r="B111" t="n">
         <v>78766</v>
@@ -12873,13 +12867,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>486079</v>
+        <v>485910</v>
       </c>
       <c r="R111" t="n">
         <v>6790394</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12936,10 +12930,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122671608</v>
+        <v>122671659</v>
       </c>
       <c r="B112" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12948,30 +12942,36 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>486013</v>
+        <v>486020</v>
       </c>
       <c r="R112" t="n">
-        <v>6790366</v>
+        <v>6790412</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13042,7 +13042,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122671555</v>
+        <v>122671595</v>
       </c>
       <c r="B113" t="n">
         <v>78766</v>
@@ -13085,10 +13085,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>485915</v>
+        <v>485984</v>
       </c>
       <c r="R113" t="n">
-        <v>6790407</v>
+        <v>6790370</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13148,10 +13148,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122671675</v>
+        <v>122671610</v>
       </c>
       <c r="B114" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13164,21 +13164,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13191,13 +13191,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>486331</v>
+        <v>486013</v>
       </c>
       <c r="R114" t="n">
-        <v>6790370</v>
+        <v>6790366</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122671447</v>
+        <v>122671647</v>
       </c>
       <c r="B115" t="n">
         <v>78766</v>
@@ -13297,13 +13297,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>485830</v>
+        <v>486035</v>
       </c>
       <c r="R115" t="n">
-        <v>6790346</v>
+        <v>6790369</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122671651</v>
+        <v>122671506</v>
       </c>
       <c r="B116" t="n">
         <v>78766</v>
@@ -13403,13 +13403,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>486048</v>
+        <v>485861</v>
       </c>
       <c r="R116" t="n">
-        <v>6790360</v>
+        <v>6790364</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122671679</v>
+        <v>122671651</v>
       </c>
       <c r="B117" t="n">
         <v>78766</v>
@@ -13509,13 +13509,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>486342</v>
+        <v>486048</v>
       </c>
       <c r="R117" t="n">
-        <v>6790369</v>
+        <v>6790360</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122671564</v>
+        <v>122671440</v>
       </c>
       <c r="B118" t="n">
         <v>78766</v>
@@ -13615,10 +13615,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>485933</v>
+        <v>485819</v>
       </c>
       <c r="R118" t="n">
-        <v>6790411</v>
+        <v>6790340</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13678,7 +13678,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122689581</v>
+        <v>122689855</v>
       </c>
       <c r="B119" t="n">
         <v>78766</v>
@@ -13721,10 +13721,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>485671</v>
+        <v>485432</v>
       </c>
       <c r="R119" t="n">
-        <v>6790449</v>
+        <v>6790469</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13784,7 +13784,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122689933</v>
+        <v>122689928</v>
       </c>
       <c r="B120" t="n">
         <v>78766</v>
@@ -13890,7 +13890,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122689736</v>
+        <v>122689853</v>
       </c>
       <c r="B121" t="n">
         <v>78766</v>
@@ -13933,10 +13933,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>485597</v>
+        <v>485439</v>
       </c>
       <c r="R121" t="n">
-        <v>6790468</v>
+        <v>6790465</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13996,7 +13996,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122689748</v>
+        <v>122689824</v>
       </c>
       <c r="B122" t="n">
         <v>78766</v>
@@ -14039,10 +14039,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>485586</v>
+        <v>485497</v>
       </c>
       <c r="R122" t="n">
-        <v>6790473</v>
+        <v>6790458</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14102,7 +14102,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122689934</v>
+        <v>122689447</v>
       </c>
       <c r="B123" t="n">
         <v>78766</v>
@@ -14145,10 +14145,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>485527</v>
+        <v>485729</v>
       </c>
       <c r="R123" t="n">
-        <v>6790426</v>
+        <v>6790386</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14208,7 +14208,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122689794</v>
+        <v>122689859</v>
       </c>
       <c r="B124" t="n">
         <v>78766</v>
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>485529</v>
+        <v>485425</v>
       </c>
       <c r="R124" t="n">
-        <v>6790463</v>
+        <v>6790473</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14314,7 +14314,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122689859</v>
+        <v>122689892</v>
       </c>
       <c r="B125" t="n">
         <v>78766</v>
@@ -14357,10 +14357,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>485425</v>
+        <v>485406</v>
       </c>
       <c r="R125" t="n">
-        <v>6790473</v>
+        <v>6790461</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14420,10 +14420,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122689865</v>
+        <v>122689540</v>
       </c>
       <c r="B126" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14432,36 +14432,30 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -14469,10 +14463,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>485417</v>
+        <v>485689</v>
       </c>
       <c r="R126" t="n">
-        <v>6790479</v>
+        <v>6790436</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14532,7 +14526,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122689851</v>
+        <v>122689942</v>
       </c>
       <c r="B127" t="n">
         <v>78766</v>
@@ -14575,10 +14569,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>485442</v>
+        <v>485554</v>
       </c>
       <c r="R127" t="n">
-        <v>6790462</v>
+        <v>6790400</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14638,7 +14632,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122689764</v>
+        <v>122689974</v>
       </c>
       <c r="B128" t="n">
         <v>78766</v>
@@ -14681,10 +14675,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>485560</v>
+        <v>485719</v>
       </c>
       <c r="R128" t="n">
-        <v>6790469</v>
+        <v>6790394</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14744,7 +14738,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122689594</v>
+        <v>122689950</v>
       </c>
       <c r="B129" t="n">
         <v>78766</v>
@@ -14787,10 +14781,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>485662</v>
+        <v>485623</v>
       </c>
       <c r="R129" t="n">
-        <v>6790461</v>
+        <v>6790393</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14850,7 +14844,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122689842</v>
+        <v>122689581</v>
       </c>
       <c r="B130" t="n">
         <v>78766</v>
@@ -14893,10 +14887,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>485449</v>
+        <v>485671</v>
       </c>
       <c r="R130" t="n">
-        <v>6790454</v>
+        <v>6790449</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -14956,7 +14950,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122689596</v>
+        <v>122689838</v>
       </c>
       <c r="B131" t="n">
         <v>78766</v>
@@ -14999,10 +14993,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>485656</v>
+        <v>485452</v>
       </c>
       <c r="R131" t="n">
-        <v>6790462</v>
+        <v>6790453</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -15062,7 +15056,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122689954</v>
+        <v>122689819</v>
       </c>
       <c r="B132" t="n">
         <v>78766</v>
@@ -15105,10 +15099,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>485626</v>
+        <v>485500</v>
       </c>
       <c r="R132" t="n">
-        <v>6790391</v>
+        <v>6790456</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -15168,7 +15162,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122689806</v>
+        <v>122689736</v>
       </c>
       <c r="B133" t="n">
         <v>78766</v>
@@ -15211,10 +15205,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>485524</v>
+        <v>485597</v>
       </c>
       <c r="R133" t="n">
-        <v>6790465</v>
+        <v>6790468</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15274,7 +15268,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>122689617</v>
+        <v>122689918</v>
       </c>
       <c r="B134" t="n">
         <v>78766</v>
@@ -15317,10 +15311,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>485646</v>
+        <v>485463</v>
       </c>
       <c r="R134" t="n">
-        <v>6790453</v>
+        <v>6790428</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -15380,7 +15374,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>122689942</v>
+        <v>122689548</v>
       </c>
       <c r="B135" t="n">
         <v>78766</v>
@@ -15423,10 +15417,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>485554</v>
+        <v>485686</v>
       </c>
       <c r="R135" t="n">
-        <v>6790400</v>
+        <v>6790446</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -15486,7 +15480,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>122689540</v>
+        <v>122689959</v>
       </c>
       <c r="B136" t="n">
         <v>78766</v>
@@ -15529,10 +15523,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>485689</v>
+        <v>485627</v>
       </c>
       <c r="R136" t="n">
-        <v>6790436</v>
+        <v>6790392</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -15592,7 +15586,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>122689863</v>
+        <v>122689941</v>
       </c>
       <c r="B137" t="n">
         <v>78766</v>
@@ -15635,10 +15629,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>485420</v>
+        <v>485558</v>
       </c>
       <c r="R137" t="n">
-        <v>6790476</v>
+        <v>6790391</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15698,10 +15692,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>122689738</v>
+        <v>122689972</v>
       </c>
       <c r="B138" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15714,33 +15708,25 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
@@ -15749,10 +15735,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>485597</v>
+        <v>485718</v>
       </c>
       <c r="R138" t="n">
-        <v>6790468</v>
+        <v>6790397</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -15812,7 +15798,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>122689895</v>
+        <v>122689920</v>
       </c>
       <c r="B139" t="n">
         <v>78766</v>
@@ -15855,10 +15841,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>485405</v>
+        <v>485472</v>
       </c>
       <c r="R139" t="n">
-        <v>6790460</v>
+        <v>6790425</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -15918,7 +15904,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>122689924</v>
+        <v>122689863</v>
       </c>
       <c r="B140" t="n">
         <v>78766</v>
@@ -15961,10 +15947,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>485489</v>
+        <v>485420</v>
       </c>
       <c r="R140" t="n">
-        <v>6790405</v>
+        <v>6790476</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -16024,7 +16010,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>122689677</v>
+        <v>122689829</v>
       </c>
       <c r="B141" t="n">
         <v>78766</v>
@@ -16067,10 +16053,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>485615</v>
+        <v>485469</v>
       </c>
       <c r="R141" t="n">
-        <v>6790468</v>
+        <v>6790456</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16130,7 +16116,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>122689829</v>
+        <v>122689756</v>
       </c>
       <c r="B142" t="n">
         <v>78766</v>
@@ -16173,10 +16159,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>485469</v>
+        <v>485576</v>
       </c>
       <c r="R142" t="n">
-        <v>6790456</v>
+        <v>6790471</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16236,7 +16222,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>122689572</v>
+        <v>122689811</v>
       </c>
       <c r="B143" t="n">
         <v>78766</v>
@@ -16279,10 +16265,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>485672</v>
+        <v>485510</v>
       </c>
       <c r="R143" t="n">
-        <v>6790447</v>
+        <v>6790462</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -16342,10 +16328,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>122689761</v>
+        <v>122689738</v>
       </c>
       <c r="B144" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16358,25 +16344,33 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
@@ -16385,10 +16379,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>485563</v>
+        <v>485597</v>
       </c>
       <c r="R144" t="n">
-        <v>6790470</v>
+        <v>6790468</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -16448,7 +16442,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>122689974</v>
+        <v>122689833</v>
       </c>
       <c r="B145" t="n">
         <v>78766</v>
@@ -16491,10 +16485,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>485719</v>
+        <v>485457</v>
       </c>
       <c r="R145" t="n">
-        <v>6790394</v>
+        <v>6790457</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -16554,7 +16548,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>122689936</v>
+        <v>122689630</v>
       </c>
       <c r="B146" t="n">
         <v>78766</v>
@@ -16597,10 +16591,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>485535</v>
+        <v>485638</v>
       </c>
       <c r="R146" t="n">
-        <v>6790402</v>
+        <v>6790456</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -16660,7 +16654,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>122689756</v>
+        <v>122689934</v>
       </c>
       <c r="B147" t="n">
         <v>78766</v>
@@ -16703,10 +16697,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>485576</v>
+        <v>485527</v>
       </c>
       <c r="R147" t="n">
-        <v>6790471</v>
+        <v>6790426</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -16766,7 +16760,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>122689950</v>
+        <v>122689794</v>
       </c>
       <c r="B148" t="n">
         <v>78766</v>
@@ -16809,10 +16803,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>485623</v>
+        <v>485529</v>
       </c>
       <c r="R148" t="n">
-        <v>6790393</v>
+        <v>6790463</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -16872,7 +16866,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>122689941</v>
+        <v>122689611</v>
       </c>
       <c r="B149" t="n">
         <v>78766</v>
@@ -16915,10 +16909,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>485558</v>
+        <v>485653</v>
       </c>
       <c r="R149" t="n">
-        <v>6790391</v>
+        <v>6790460</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -16978,7 +16972,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>122689904</v>
+        <v>122689626</v>
       </c>
       <c r="B150" t="n">
         <v>78766</v>
@@ -17021,10 +17015,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>485427</v>
+        <v>485638</v>
       </c>
       <c r="R150" t="n">
-        <v>6790445</v>
+        <v>6790452</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -17084,7 +17078,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>122689819</v>
+        <v>122689748</v>
       </c>
       <c r="B151" t="n">
         <v>78766</v>
@@ -17127,10 +17121,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>485500</v>
+        <v>485586</v>
       </c>
       <c r="R151" t="n">
-        <v>6790456</v>
+        <v>6790473</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -17190,7 +17184,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>122689593</v>
+        <v>122689904</v>
       </c>
       <c r="B152" t="n">
         <v>78766</v>
@@ -17233,10 +17227,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>485660</v>
+        <v>485427</v>
       </c>
       <c r="R152" t="n">
-        <v>6790454</v>
+        <v>6790445</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -17296,7 +17290,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>122689892</v>
+        <v>122689966</v>
       </c>
       <c r="B153" t="n">
         <v>78766</v>
@@ -17339,10 +17333,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>485406</v>
+        <v>485678</v>
       </c>
       <c r="R153" t="n">
-        <v>6790461</v>
+        <v>6790402</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -17402,7 +17396,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>122689743</v>
+        <v>122689963</v>
       </c>
       <c r="B154" t="n">
         <v>78766</v>
@@ -17445,10 +17439,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>485588</v>
+        <v>485658</v>
       </c>
       <c r="R154" t="n">
-        <v>6790473</v>
+        <v>6790402</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -17508,7 +17502,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122689824</v>
+        <v>122689899</v>
       </c>
       <c r="B155" t="n">
         <v>78766</v>
@@ -17551,10 +17545,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>485497</v>
+        <v>485399</v>
       </c>
       <c r="R155" t="n">
-        <v>6790458</v>
+        <v>6790454</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -17614,10 +17608,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122689626</v>
+        <v>122689349</v>
       </c>
       <c r="B156" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17626,30 +17620,43 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -17657,13 +17664,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>485638</v>
+        <v>485774</v>
       </c>
       <c r="R156" t="n">
-        <v>6790452</v>
+        <v>6790357</v>
       </c>
       <c r="S156" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17695,13 +17702,17 @@
           <t>2025-02-20</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>flög åt väster</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -17830,10 +17841,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122689349</v>
+        <v>122689889</v>
       </c>
       <c r="B158" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17842,43 +17853,30 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
@@ -17886,13 +17884,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>485774</v>
+        <v>485406</v>
       </c>
       <c r="R158" t="n">
-        <v>6790357</v>
+        <v>6790464</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17924,17 +17922,13 @@
           <t>2025-02-20</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>flög åt väster</t>
-        </is>
-      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -17953,7 +17947,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>122689943</v>
+        <v>122689882</v>
       </c>
       <c r="B159" t="n">
         <v>78766</v>
@@ -17996,10 +17990,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>485590</v>
+        <v>485408</v>
       </c>
       <c r="R159" t="n">
-        <v>6790388</v>
+        <v>6790469</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -18059,7 +18053,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>122689914</v>
+        <v>122689936</v>
       </c>
       <c r="B160" t="n">
         <v>78766</v>
@@ -18102,10 +18096,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>485447</v>
+        <v>485535</v>
       </c>
       <c r="R160" t="n">
-        <v>6790434</v>
+        <v>6790402</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -18165,7 +18159,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>122689619</v>
+        <v>122689556</v>
       </c>
       <c r="B161" t="n">
         <v>78766</v>
@@ -18208,10 +18202,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>485645</v>
+        <v>485678</v>
       </c>
       <c r="R161" t="n">
-        <v>6790451</v>
+        <v>6790447</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -18377,7 +18371,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122689918</v>
+        <v>122689851</v>
       </c>
       <c r="B163" t="n">
         <v>78766</v>
@@ -18420,10 +18414,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>485463</v>
+        <v>485442</v>
       </c>
       <c r="R163" t="n">
-        <v>6790428</v>
+        <v>6790462</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -18483,7 +18477,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>122689882</v>
+        <v>122689761</v>
       </c>
       <c r="B164" t="n">
         <v>78766</v>
@@ -18526,10 +18520,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>485408</v>
+        <v>485563</v>
       </c>
       <c r="R164" t="n">
-        <v>6790469</v>
+        <v>6790470</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -18589,7 +18583,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122689899</v>
+        <v>122689806</v>
       </c>
       <c r="B165" t="n">
         <v>78766</v>
@@ -18632,10 +18626,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>485399</v>
+        <v>485524</v>
       </c>
       <c r="R165" t="n">
-        <v>6790454</v>
+        <v>6790465</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18695,10 +18689,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122689732</v>
+        <v>122689723</v>
       </c>
       <c r="B166" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18707,30 +18701,36 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
@@ -18738,10 +18738,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>485601</v>
+        <v>485609</v>
       </c>
       <c r="R166" t="n">
-        <v>6790468</v>
+        <v>6790472</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -18801,7 +18801,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>122689972</v>
+        <v>122689846</v>
       </c>
       <c r="B167" t="n">
         <v>78766</v>
@@ -18844,10 +18844,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>485718</v>
+        <v>485443</v>
       </c>
       <c r="R167" t="n">
-        <v>6790397</v>
+        <v>6790455</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -18907,7 +18907,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>122689959</v>
+        <v>122689718</v>
       </c>
       <c r="B168" t="n">
         <v>78766</v>
@@ -18950,10 +18950,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>485627</v>
+        <v>485610</v>
       </c>
       <c r="R168" t="n">
-        <v>6790392</v>
+        <v>6790472</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -19013,7 +19013,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>122689963</v>
+        <v>122689943</v>
       </c>
       <c r="B169" t="n">
         <v>78766</v>
@@ -19056,10 +19056,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>485658</v>
+        <v>485590</v>
       </c>
       <c r="R169" t="n">
-        <v>6790402</v>
+        <v>6790388</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -19119,7 +19119,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>122689811</v>
+        <v>122689596</v>
       </c>
       <c r="B170" t="n">
         <v>78766</v>
@@ -19162,7 +19162,7 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>485510</v>
+        <v>485656</v>
       </c>
       <c r="R170" t="n">
         <v>6790462</v>
@@ -19225,7 +19225,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>122689611</v>
+        <v>122689914</v>
       </c>
       <c r="B171" t="n">
         <v>78766</v>
@@ -19268,10 +19268,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>485653</v>
+        <v>485447</v>
       </c>
       <c r="R171" t="n">
-        <v>6790460</v>
+        <v>6790434</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -19331,7 +19331,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>122689846</v>
+        <v>122689732</v>
       </c>
       <c r="B172" t="n">
         <v>78766</v>
@@ -19374,10 +19374,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>485443</v>
+        <v>485601</v>
       </c>
       <c r="R172" t="n">
-        <v>6790455</v>
+        <v>6790468</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -19437,7 +19437,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>122689966</v>
+        <v>122689924</v>
       </c>
       <c r="B173" t="n">
         <v>78766</v>
@@ -19480,10 +19480,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>485678</v>
+        <v>485489</v>
       </c>
       <c r="R173" t="n">
-        <v>6790402</v>
+        <v>6790405</v>
       </c>
       <c r="S173" t="n">
         <v>5</v>
@@ -19543,7 +19543,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>122689768</v>
+        <v>122689954</v>
       </c>
       <c r="B174" t="n">
         <v>78766</v>
@@ -19586,10 +19586,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>485537</v>
+        <v>485626</v>
       </c>
       <c r="R174" t="n">
-        <v>6790465</v>
+        <v>6790391</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -19649,7 +19649,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>122689855</v>
+        <v>122689714</v>
       </c>
       <c r="B175" t="n">
         <v>78766</v>
@@ -19692,10 +19692,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>485432</v>
+        <v>485613</v>
       </c>
       <c r="R175" t="n">
-        <v>6790469</v>
+        <v>6790471</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -19755,7 +19755,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122689633</v>
+        <v>122689593</v>
       </c>
       <c r="B176" t="n">
         <v>78766</v>
@@ -19798,10 +19798,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>485624</v>
+        <v>485660</v>
       </c>
       <c r="R176" t="n">
-        <v>6790469</v>
+        <v>6790454</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -19861,10 +19861,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122689875</v>
+        <v>122689939</v>
       </c>
       <c r="B177" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -19873,30 +19873,36 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
@@ -19904,10 +19910,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>485410</v>
+        <v>485533</v>
       </c>
       <c r="R177" t="n">
-        <v>6790478</v>
+        <v>6790398</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -19967,7 +19973,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122689838</v>
+        <v>122689572</v>
       </c>
       <c r="B178" t="n">
         <v>78766</v>
@@ -20010,10 +20016,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>485452</v>
+        <v>485672</v>
       </c>
       <c r="R178" t="n">
-        <v>6790453</v>
+        <v>6790447</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -20073,7 +20079,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122689853</v>
+        <v>122689768</v>
       </c>
       <c r="B179" t="n">
         <v>78766</v>
@@ -20116,7 +20122,7 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>485439</v>
+        <v>485537</v>
       </c>
       <c r="R179" t="n">
         <v>6790465</v>
@@ -20179,7 +20185,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122689911</v>
+        <v>122689753</v>
       </c>
       <c r="B180" t="n">
         <v>78766</v>
@@ -20222,10 +20228,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>485439</v>
+        <v>485577</v>
       </c>
       <c r="R180" t="n">
-        <v>6790444</v>
+        <v>6790471</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -20285,7 +20291,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122689970</v>
+        <v>122689619</v>
       </c>
       <c r="B181" t="n">
         <v>78766</v>
@@ -20328,10 +20334,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>485704</v>
+        <v>485645</v>
       </c>
       <c r="R181" t="n">
-        <v>6790400</v>
+        <v>6790451</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -20391,7 +20397,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122689447</v>
+        <v>122689743</v>
       </c>
       <c r="B182" t="n">
         <v>78766</v>
@@ -20434,10 +20440,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>485729</v>
+        <v>485588</v>
       </c>
       <c r="R182" t="n">
-        <v>6790386</v>
+        <v>6790473</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -20497,7 +20503,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>122689556</v>
+        <v>122689895</v>
       </c>
       <c r="B183" t="n">
         <v>78766</v>
@@ -20540,10 +20546,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>485678</v>
+        <v>485405</v>
       </c>
       <c r="R183" t="n">
-        <v>6790447</v>
+        <v>6790460</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -20603,7 +20609,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122689548</v>
+        <v>122689879</v>
       </c>
       <c r="B184" t="n">
         <v>78766</v>
@@ -20646,10 +20652,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>485686</v>
+        <v>485409</v>
       </c>
       <c r="R184" t="n">
-        <v>6790446</v>
+        <v>6790470</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -20709,7 +20715,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>122689630</v>
+        <v>122689842</v>
       </c>
       <c r="B185" t="n">
         <v>78766</v>
@@ -20752,10 +20758,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>485638</v>
+        <v>485449</v>
       </c>
       <c r="R185" t="n">
-        <v>6790456</v>
+        <v>6790454</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -20815,10 +20821,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122689519</v>
+        <v>122689865</v>
       </c>
       <c r="B186" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20827,30 +20833,36 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
@@ -20858,10 +20870,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>485696</v>
+        <v>485417</v>
       </c>
       <c r="R186" t="n">
-        <v>6790431</v>
+        <v>6790479</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -20921,10 +20933,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>122689939</v>
+        <v>122689519</v>
       </c>
       <c r="B187" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20933,36 +20945,30 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
@@ -20970,10 +20976,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>485533</v>
+        <v>485696</v>
       </c>
       <c r="R187" t="n">
-        <v>6790398</v>
+        <v>6790431</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21033,7 +21039,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>122689889</v>
+        <v>122689911</v>
       </c>
       <c r="B188" t="n">
         <v>78766</v>
@@ -21076,10 +21082,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>485406</v>
+        <v>485439</v>
       </c>
       <c r="R188" t="n">
-        <v>6790464</v>
+        <v>6790444</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21139,7 +21145,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>122689920</v>
+        <v>122689875</v>
       </c>
       <c r="B189" t="n">
         <v>78766</v>
@@ -21182,10 +21188,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>485472</v>
+        <v>485410</v>
       </c>
       <c r="R189" t="n">
-        <v>6790425</v>
+        <v>6790478</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -21245,7 +21251,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122689718</v>
+        <v>122689617</v>
       </c>
       <c r="B190" t="n">
         <v>78766</v>
@@ -21288,10 +21294,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>485610</v>
+        <v>485646</v>
       </c>
       <c r="R190" t="n">
-        <v>6790472</v>
+        <v>6790453</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -21351,7 +21357,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122689833</v>
+        <v>122689970</v>
       </c>
       <c r="B191" t="n">
         <v>78766</v>
@@ -21394,10 +21400,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>485457</v>
+        <v>485704</v>
       </c>
       <c r="R191" t="n">
-        <v>6790457</v>
+        <v>6790400</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -21457,7 +21463,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122689714</v>
+        <v>122689764</v>
       </c>
       <c r="B192" t="n">
         <v>78766</v>
@@ -21500,10 +21506,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>485613</v>
+        <v>485560</v>
       </c>
       <c r="R192" t="n">
-        <v>6790471</v>
+        <v>6790469</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -21563,7 +21569,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122689872</v>
+        <v>122689633</v>
       </c>
       <c r="B193" t="n">
         <v>78766</v>
@@ -21606,10 +21612,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>485412</v>
+        <v>485624</v>
       </c>
       <c r="R193" t="n">
-        <v>6790481</v>
+        <v>6790469</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -21669,10 +21675,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122689723</v>
+        <v>122689872</v>
       </c>
       <c r="B194" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21681,36 +21687,30 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
@@ -21718,10 +21718,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>485609</v>
+        <v>485412</v>
       </c>
       <c r="R194" t="n">
-        <v>6790472</v>
+        <v>6790481</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -21781,7 +21781,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122689753</v>
+        <v>122689677</v>
       </c>
       <c r="B195" t="n">
         <v>78766</v>
@@ -21824,10 +21824,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>485577</v>
+        <v>485615</v>
       </c>
       <c r="R195" t="n">
-        <v>6790471</v>
+        <v>6790468</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -21887,7 +21887,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122689879</v>
+        <v>122689594</v>
       </c>
       <c r="B196" t="n">
         <v>78766</v>
@@ -21930,10 +21930,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>485409</v>
+        <v>485662</v>
       </c>
       <c r="R196" t="n">
-        <v>6790470</v>
+        <v>6790461</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>

--- a/artfynd/A 2121-2025 artfynd.xlsx
+++ b/artfynd/A 2121-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609017</v>
+        <v>122608792</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486064</v>
+        <v>486035</v>
       </c>
       <c r="R2" t="n">
-        <v>6790364</v>
+        <v>6790401</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122606171</v>
+        <v>122606946</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485662</v>
+        <v>485706</v>
       </c>
       <c r="R3" t="n">
-        <v>6790357</v>
+        <v>6790427</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122606924</v>
+        <v>122606131</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -935,17 +935,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485706</v>
+        <v>485629</v>
       </c>
       <c r="R4" t="n">
-        <v>6790427</v>
+        <v>6790369</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,19 +999,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122606919</v>
+        <v>122606394</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485753</v>
+        <v>485411</v>
       </c>
       <c r="R5" t="n">
-        <v>6790423</v>
+        <v>6790441</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,19 +1111,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122607254</v>
+        <v>122608967</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486016</v>
+        <v>485504</v>
       </c>
       <c r="R6" t="n">
-        <v>6790443</v>
+        <v>6790441</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,19 +1223,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122608964</v>
+        <v>122608158</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1271,17 +1271,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486035</v>
+        <v>486281</v>
       </c>
       <c r="R7" t="n">
-        <v>6790401</v>
+        <v>6790441</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,19 +1340,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122606751</v>
+        <v>122607995</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1387,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485504</v>
+        <v>486213</v>
       </c>
       <c r="R8" t="n">
-        <v>6790441</v>
+        <v>6790435</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,19 +1452,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122606452</v>
+        <v>122606708</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1495,17 +1500,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485428</v>
+        <v>485568</v>
       </c>
       <c r="R9" t="n">
-        <v>6790393</v>
+        <v>6790397</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,19 +1564,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122606708</v>
+        <v>122608651</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1607,17 +1612,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485568</v>
+        <v>486380</v>
       </c>
       <c r="R10" t="n">
-        <v>6790397</v>
+        <v>6790321</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1661,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,22 +1681,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122606408</v>
+        <v>122607224</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,41 +1705,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485407</v>
+        <v>485981</v>
       </c>
       <c r="R11" t="n">
-        <v>6790439</v>
+        <v>6790453</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,22 +1798,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122606235</v>
+        <v>122607118</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,41 +1822,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485615</v>
+        <v>485884</v>
       </c>
       <c r="R12" t="n">
-        <v>6790353</v>
+        <v>6790450</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,22 +1915,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122606145</v>
+        <v>122607948</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1943,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485616</v>
+        <v>485504</v>
       </c>
       <c r="R13" t="n">
-        <v>6790356</v>
+        <v>6790441</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606176</v>
+        <v>122608828</v>
       </c>
       <c r="B14" t="n">
-        <v>78792</v>
+        <v>78502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,25 +2051,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,13 +2079,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485613</v>
+        <v>485504</v>
       </c>
       <c r="R14" t="n">
-        <v>6790370</v>
+        <v>6790441</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2094,7 +2114,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2124,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,19 +2139,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122607713</v>
+        <v>122606118</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2167,17 +2187,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486156</v>
+        <v>485662</v>
       </c>
       <c r="R15" t="n">
-        <v>6790429</v>
+        <v>6790357</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,19 +2251,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122606651</v>
+        <v>122608938</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2279,14 +2299,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485432</v>
+        <v>486253</v>
       </c>
       <c r="R16" t="n">
-        <v>6790417</v>
+        <v>6790356</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2318,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,7 +2375,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122606108</v>
+        <v>122608110</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2391,14 +2411,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Gräsmyren, Gräsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485649</v>
+        <v>486270</v>
       </c>
       <c r="R17" t="n">
-        <v>6790375</v>
+        <v>6790427</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2430,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,7 +2487,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122606154</v>
+        <v>122606286</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2507,13 +2527,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485616</v>
+        <v>485541</v>
       </c>
       <c r="R18" t="n">
-        <v>6790354</v>
+        <v>6790372</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2542,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2572,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På 3 tallar på stammen</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2567,22 +2592,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122607118</v>
+        <v>122606442</v>
       </c>
       <c r="B19" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,46 +2616,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>485884</v>
+        <v>485407</v>
       </c>
       <c r="R19" t="n">
-        <v>6790450</v>
+        <v>6790437</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2659,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,22 +2704,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122606208</v>
+        <v>122606145</v>
       </c>
       <c r="B20" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2708,25 +2728,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2736,13 +2756,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>485592</v>
+        <v>485616</v>
       </c>
       <c r="R20" t="n">
-        <v>6790353</v>
+        <v>6790356</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2771,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2796,22 +2816,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122607948</v>
+        <v>122607160</v>
       </c>
       <c r="B21" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2824,21 +2844,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2848,13 +2868,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>485504</v>
+        <v>485961</v>
       </c>
       <c r="R21" t="n">
-        <v>6790441</v>
+        <v>6790453</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2883,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2908,22 +2928,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122606977</v>
+        <v>122607141</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2932,38 +2952,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>485766</v>
+        <v>485906</v>
       </c>
       <c r="R22" t="n">
-        <v>6790457</v>
+        <v>6790433</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -2995,7 +3020,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3005,12 +3030,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,7 +3057,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122606230</v>
+        <v>122607254</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -3077,10 +3097,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>485561</v>
+        <v>486016</v>
       </c>
       <c r="R23" t="n">
-        <v>6790367</v>
+        <v>6790443</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3112,7 +3132,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3142,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,7 +3169,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122606286</v>
+        <v>122606955</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -3189,10 +3209,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>485541</v>
+        <v>485759</v>
       </c>
       <c r="R24" t="n">
-        <v>6790372</v>
+        <v>6790467</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3224,7 +3244,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,12 +3254,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På 3 tallar på stammen</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,10 +3281,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122608828</v>
+        <v>122607815</v>
       </c>
       <c r="B25" t="n">
-        <v>78502</v>
+        <v>56688</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3278,41 +3293,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>485504</v>
+        <v>486035</v>
       </c>
       <c r="R25" t="n">
-        <v>6790441</v>
+        <v>6790401</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3341,7 +3356,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3351,7 +3366,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3366,19 +3381,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122608938</v>
+        <v>122607915</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3414,14 +3429,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486253</v>
+        <v>486193</v>
       </c>
       <c r="R26" t="n">
-        <v>6790356</v>
+        <v>6790410</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3453,7 +3468,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3463,7 +3478,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3490,7 +3505,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122606271</v>
+        <v>122606408</v>
       </c>
       <c r="B27" t="n">
         <v>78766</v>
@@ -3530,13 +3545,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>485553</v>
+        <v>485407</v>
       </c>
       <c r="R27" t="n">
-        <v>6790369</v>
+        <v>6790439</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3565,7 +3580,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3575,7 +3590,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3590,19 +3605,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122606807</v>
+        <v>122608990</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -3638,14 +3653,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>485749</v>
+        <v>486070</v>
       </c>
       <c r="R28" t="n">
-        <v>6790424</v>
+        <v>6790363</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3677,7 +3692,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3687,7 +3702,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,7 +3729,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122608061</v>
+        <v>122607518</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3754,10 +3769,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486229</v>
+        <v>486071</v>
       </c>
       <c r="R29" t="n">
-        <v>6790440</v>
+        <v>6790384</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3789,7 +3804,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3799,12 +3814,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,7 +3841,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122608158</v>
+        <v>122609017</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3867,14 +3877,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486281</v>
+        <v>486064</v>
       </c>
       <c r="R30" t="n">
-        <v>6790441</v>
+        <v>6790364</v>
       </c>
       <c r="S30" t="n">
         <v>9</v>
@@ -3906,7 +3916,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,12 +3926,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3948,10 +3953,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122608856</v>
+        <v>122606230</v>
       </c>
       <c r="B31" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3960,38 +3965,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486343</v>
+        <v>485561</v>
       </c>
       <c r="R31" t="n">
-        <v>6790373</v>
+        <v>6790367</v>
       </c>
       <c r="S31" t="n">
         <v>9</v>
@@ -4023,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4033,7 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4060,7 +4065,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122607953</v>
+        <v>122608856</v>
       </c>
       <c r="B32" t="n">
         <v>8441</v>
@@ -4096,14 +4101,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486214</v>
+        <v>486343</v>
       </c>
       <c r="R32" t="n">
-        <v>6790429</v>
+        <v>6790373</v>
       </c>
       <c r="S32" t="n">
         <v>9</v>
@@ -4135,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4145,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4172,10 +4177,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122606955</v>
+        <v>122606176</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>78792</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4184,25 +4189,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4212,10 +4217,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>485759</v>
+        <v>485613</v>
       </c>
       <c r="R33" t="n">
-        <v>6790467</v>
+        <v>6790370</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -4247,7 +4252,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,7 +4262,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4284,10 +4289,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122607558</v>
+        <v>122607953</v>
       </c>
       <c r="B34" t="n">
-        <v>56688</v>
+        <v>8441</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4300,37 +4305,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Jäskänget, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486035</v>
+        <v>486214</v>
       </c>
       <c r="R34" t="n">
-        <v>6790401</v>
+        <v>6790429</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4359,7 +4364,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4369,7 +4374,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4384,22 +4389,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122607141</v>
+        <v>122607974</v>
       </c>
       <c r="B35" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4408,43 +4413,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485906</v>
+        <v>486212</v>
       </c>
       <c r="R35" t="n">
-        <v>6790433</v>
+        <v>6790432</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4513,7 +4513,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122607107</v>
+        <v>122606108</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4553,10 +4553,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485855</v>
+        <v>485649</v>
       </c>
       <c r="R36" t="n">
-        <v>6790443</v>
+        <v>6790375</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4625,7 +4625,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122606339</v>
+        <v>122606807</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>485528</v>
+        <v>485749</v>
       </c>
       <c r="R37" t="n">
-        <v>6790365</v>
+        <v>6790424</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4737,7 +4737,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122607915</v>
+        <v>122606154</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -4777,13 +4777,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486193</v>
+        <v>485616</v>
       </c>
       <c r="R38" t="n">
-        <v>6790410</v>
+        <v>6790354</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4837,19 +4837,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122607995</v>
+        <v>122607107</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486213</v>
+        <v>485855</v>
       </c>
       <c r="R39" t="n">
-        <v>6790435</v>
+        <v>6790443</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4961,10 +4961,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122608990</v>
+        <v>122607596</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4973,38 +4973,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486070</v>
+        <v>486109</v>
       </c>
       <c r="R40" t="n">
-        <v>6790363</v>
+        <v>6790384</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -5036,7 +5041,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5046,7 +5051,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5190,10 +5195,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122608902</v>
+        <v>122608844</v>
       </c>
       <c r="B42" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5206,21 +5211,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5230,10 +5235,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486280</v>
+        <v>486338</v>
       </c>
       <c r="R42" t="n">
-        <v>6790345</v>
+        <v>6790352</v>
       </c>
       <c r="S42" t="n">
         <v>9</v>
@@ -5265,7 +5270,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5275,7 +5280,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5302,10 +5312,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122607596</v>
+        <v>122606977</v>
       </c>
       <c r="B43" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5314,43 +5324,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486109</v>
+        <v>485766</v>
       </c>
       <c r="R43" t="n">
-        <v>6790384</v>
+        <v>6790457</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5382,7 +5387,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5392,7 +5397,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På 3 tallar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5419,10 +5429,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122608926</v>
+        <v>122606339</v>
       </c>
       <c r="B44" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5435,34 +5445,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486252</v>
+        <v>485528</v>
       </c>
       <c r="R44" t="n">
-        <v>6790351</v>
+        <v>6790365</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -5494,7 +5504,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5504,7 +5514,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5531,7 +5541,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122607495</v>
+        <v>122606204</v>
       </c>
       <c r="B45" t="n">
         <v>78766</v>
@@ -5571,13 +5581,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486056</v>
+        <v>485615</v>
       </c>
       <c r="R45" t="n">
-        <v>6790394</v>
+        <v>6790353</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5606,7 +5616,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5616,7 +5626,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5631,12 +5641,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5755,7 +5765,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122608651</v>
+        <v>122607713</v>
       </c>
       <c r="B47" t="n">
         <v>78766</v>
@@ -5791,14 +5801,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486380</v>
+        <v>486156</v>
       </c>
       <c r="R47" t="n">
-        <v>6790321</v>
+        <v>6790429</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5830,7 +5840,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5840,12 +5850,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På 3 tallar</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5872,10 +5877,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122606442</v>
+        <v>122608926</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5888,37 +5893,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>485407</v>
+        <v>486252</v>
       </c>
       <c r="R48" t="n">
-        <v>6790437</v>
+        <v>6790351</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5947,7 +5952,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5957,7 +5962,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5972,22 +5977,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122607518</v>
+        <v>122608902</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6000,34 +6005,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486071</v>
+        <v>486280</v>
       </c>
       <c r="R49" t="n">
-        <v>6790384</v>
+        <v>6790345</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -6059,7 +6064,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6069,7 +6074,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6096,10 +6101,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122607224</v>
+        <v>122608061</v>
       </c>
       <c r="B50" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6108,43 +6113,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>485981</v>
+        <v>486229</v>
       </c>
       <c r="R50" t="n">
-        <v>6790453</v>
+        <v>6790440</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6186,7 +6186,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På 5 tallar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6213,7 +6218,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122607974</v>
+        <v>122606452</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -6253,10 +6258,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486212</v>
+        <v>485428</v>
       </c>
       <c r="R51" t="n">
-        <v>6790432</v>
+        <v>6790393</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -6288,7 +6293,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6298,7 +6303,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6325,7 +6330,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122606394</v>
+        <v>122606919</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -6365,13 +6370,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>485411</v>
+        <v>485753</v>
       </c>
       <c r="R52" t="n">
-        <v>6790441</v>
+        <v>6790423</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6400,7 +6405,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6410,7 +6415,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6425,19 +6430,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122607160</v>
+        <v>122607495</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -6477,10 +6482,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>485961</v>
+        <v>486056</v>
       </c>
       <c r="R53" t="n">
-        <v>6790453</v>
+        <v>6790394</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6512,7 +6517,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6522,7 +6527,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6549,10 +6554,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122608844</v>
+        <v>122606208</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6561,38 +6566,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486338</v>
+        <v>485592</v>
       </c>
       <c r="R54" t="n">
-        <v>6790352</v>
+        <v>6790353</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6624,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6634,12 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På 5 tallar</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6666,7 +6666,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122606131</v>
+        <v>122606271</v>
       </c>
       <c r="B55" t="n">
         <v>78766</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>485629</v>
+        <v>485553</v>
       </c>
       <c r="R55" t="n">
         <v>6790369</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6778,7 +6778,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122608110</v>
+        <v>122606651</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -6814,14 +6814,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gräsmyren, Gräsmyren, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486270</v>
+        <v>485432</v>
       </c>
       <c r="R56" t="n">
-        <v>6790427</v>
+        <v>6790417</v>
       </c>
       <c r="S56" t="n">
         <v>9</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7010,10 +7010,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122607688</v>
+        <v>122607038</v>
       </c>
       <c r="B58" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7026,38 +7026,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486156</v>
+        <v>485772</v>
       </c>
       <c r="R58" t="n">
-        <v>6790429</v>
+        <v>6790421</v>
       </c>
       <c r="S58" t="n">
         <v>9</v>
@@ -7089,7 +7085,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7099,7 +7095,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7114,22 +7110,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122608142</v>
+        <v>122606760</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7142,37 +7138,45 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486240</v>
+        <v>485504</v>
       </c>
       <c r="R59" t="n">
-        <v>6790382</v>
+        <v>6790441</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7201,7 +7205,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7211,7 +7215,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7226,19 +7230,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122609008</v>
+        <v>122606247</v>
       </c>
       <c r="B60" t="n">
         <v>78766</v>
@@ -7274,17 +7278,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486063</v>
+        <v>485626</v>
       </c>
       <c r="R60" t="n">
-        <v>6790348</v>
+        <v>6790401</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7313,7 +7317,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7323,7 +7327,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7350,7 +7354,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122606247</v>
+        <v>122608724</v>
       </c>
       <c r="B61" t="n">
         <v>78766</v>
@@ -7386,17 +7390,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Jäskänget, Jäskänget, Dlr</t>
+          <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>485626</v>
+        <v>486211</v>
       </c>
       <c r="R61" t="n">
-        <v>6790401</v>
+        <v>6790317</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7425,7 +7429,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7435,7 +7439,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7462,10 +7466,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122608928</v>
+        <v>122607445</v>
       </c>
       <c r="B62" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7478,37 +7482,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486063</v>
+        <v>486082</v>
       </c>
       <c r="R62" t="n">
-        <v>6790348</v>
+        <v>6790427</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7537,7 +7541,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7547,7 +7551,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7574,10 +7578,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122608903</v>
+        <v>122609064</v>
       </c>
       <c r="B63" t="n">
-        <v>78503</v>
+        <v>8441</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7586,38 +7590,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lindflot, Lindflot, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486211</v>
+        <v>486063</v>
       </c>
       <c r="R63" t="n">
-        <v>6790317</v>
+        <v>6790348</v>
       </c>
       <c r="S63" t="n">
         <v>8</v>
@@ -7649,7 +7662,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7659,7 +7672,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7668,6 +7681,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7686,7 +7700,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122607273</v>
+        <v>122606756</v>
       </c>
       <c r="B64" t="n">
         <v>8441</v>
@@ -7735,10 +7749,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>485932</v>
+        <v>485504</v>
       </c>
       <c r="R64" t="n">
-        <v>6790416</v>
+        <v>6790441</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7770,7 +7784,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7780,7 +7794,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7796,19 +7810,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122607719</v>
+        <v>122606143</v>
       </c>
       <c r="B65" t="n">
         <v>78766</v>
@@ -7848,13 +7862,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486157</v>
+        <v>485681</v>
       </c>
       <c r="R65" t="n">
-        <v>6790397</v>
+        <v>6790440</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7883,7 +7897,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7893,7 +7907,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7920,10 +7934,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122606756</v>
+        <v>122607077</v>
       </c>
       <c r="B66" t="n">
-        <v>8441</v>
+        <v>56688</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7936,30 +7950,29 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7969,13 +7982,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>485504</v>
+        <v>485772</v>
       </c>
       <c r="R66" t="n">
-        <v>6790441</v>
+        <v>6790421</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8004,7 +8017,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8014,7 +8027,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8023,26 +8036,25 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122608724</v>
+        <v>122606642</v>
       </c>
       <c r="B67" t="n">
         <v>78766</v>
@@ -8078,17 +8090,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lindflot, Lindflot, Dlr</t>
+          <t>Jäskänget, Jäskänget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486211</v>
+        <v>485